--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46090.17289254726</v>
+        <v>46090.1728925463</v>
       </c>
       <c r="F2" t="n">
         <v>43</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46090.88122588059</v>
+        <v>46090.88122587963</v>
       </c>
       <c r="F3" t="n">
         <v>177</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46090.13122588059</v>
+        <v>46090.13122587963</v>
       </c>
       <c r="F4" t="n">
         <v>142</v>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46090.92289254726</v>
+        <v>46090.9228925463</v>
       </c>
       <c r="F5" t="n">
         <v>258</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46089.96455921392</v>
+        <v>46089.96455921296</v>
       </c>
       <c r="F6" t="n">
         <v>178</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46090.13122588059</v>
+        <v>46090.13122587963</v>
       </c>
       <c r="F7" t="n">
         <v>293</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46090.71455921392</v>
+        <v>46090.71455921296</v>
       </c>
       <c r="F8" t="n">
         <v>137</v>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46089.83955921392</v>
+        <v>46089.83955921296</v>
       </c>
       <c r="F9" t="n">
         <v>140</v>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46089.96455921392</v>
+        <v>46089.96455921296</v>
       </c>
       <c r="F10" t="n">
         <v>110</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46090.54789254726</v>
+        <v>46090.5478925463</v>
       </c>
       <c r="F11" t="n">
         <v>178</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46090.25622588059</v>
+        <v>46090.25622587963</v>
       </c>
       <c r="F12" t="n">
         <v>132</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46091.04789254726</v>
+        <v>46091.0478925463</v>
       </c>
       <c r="F13" t="n">
         <v>149</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46089.54789254726</v>
+        <v>46089.5478925463</v>
       </c>
       <c r="F14" t="n">
         <v>290</v>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46090.33955921392</v>
+        <v>46090.33955921296</v>
       </c>
       <c r="F15" t="n">
         <v>158</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46089.96455921392</v>
+        <v>46089.96455921296</v>
       </c>
       <c r="F16" t="n">
         <v>41</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46090.54789254726</v>
+        <v>46090.5478925463</v>
       </c>
       <c r="F17" t="n">
         <v>176</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46089.58955921392</v>
+        <v>46089.58955921296</v>
       </c>
       <c r="F18" t="n">
         <v>79</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46089.50622588059</v>
+        <v>46089.50622587963</v>
       </c>
       <c r="F19" t="n">
         <v>160</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46090.92289254726</v>
+        <v>46090.9228925463</v>
       </c>
       <c r="F20" t="n">
         <v>272</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46089.54789254726</v>
+        <v>46089.5478925463</v>
       </c>
       <c r="F21" t="n">
         <v>216</v>
@@ -1126,6 +1126,732 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>279d5e6a-1a50-4095-9a32-d0f269151edb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>c6d56985-5a6a-49e6-b8e8-860c6dc07e10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>46089.97717457186</v>
+      </c>
+      <c r="F22" t="n">
+        <v>67</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>29277be5-f937-40ad-97a4-30f03681c4f9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>162938ad-c468-4930-b7f5-9496fa97cb6d</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46091.1855079052</v>
+      </c>
+      <c r="F23" t="n">
+        <v>188</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>27242eb4-3702-4d45-b09f-93429a584055</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>9588dd77-b44f-4bf3-99f6-007d91bcf8be</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46091.1855079052</v>
+      </c>
+      <c r="F24" t="n">
+        <v>236</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a46b787e-f224-443c-a27d-cef547d94bcd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20af1d8a-3d5b-492a-a2ce-1c385c06bfef</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46089.60217457186</v>
+      </c>
+      <c r="F25" t="n">
+        <v>293</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1884e245-7bdc-4c9e-8039-3a6743f3cdd5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>100f9133-3187-40ff-95f7-3381c810ecbe</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46090.64384123853</v>
+      </c>
+      <c r="F26" t="n">
+        <v>207</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>f763a695-453e-44ad-808a-a5950c955207</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3b1ea915-a4cb-46f3-8469-42dee4357ff4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>46090.1855079052</v>
+      </c>
+      <c r="F27" t="n">
+        <v>219</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>c3074ddb-6363-46e8-a747-462e73590d4e</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>70e66201-db63-4fa9-ae20-29c7b57463de</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>46090.5605079052</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>f7d839a6-a244-492c-8d4b-81f842d46a39</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>71c0efec-c333-4ff7-a09b-e7e4545e8f93</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46090.89384123853</v>
+      </c>
+      <c r="F29" t="n">
+        <v>138</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3339df5a-94b5-46cc-8ac8-ee2a6bd79a77</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>a2b02321-c657-4cf4-a44c-696320598cbc</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>46090.72717457186</v>
+      </c>
+      <c r="F30" t="n">
+        <v>248</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>255d9ea0-a9db-445a-9bbf-7039185a5cb0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6c69de8b-13ff-49d1-b8e8-fb733d1441fd</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46091.10217457186</v>
+      </c>
+      <c r="F31" t="n">
+        <v>145</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>34b85d31-7986-450b-8726-66e021a3eb6e</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dd10f970-adb3-439b-a7c0-f782639e5b91</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>46090.35217457186</v>
+      </c>
+      <c r="F32" t="n">
+        <v>224</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0654e23c-3ae2-4f52-97dc-682a75d2588b</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>a8eb50ee-b5ff-4191-a0a6-cd163a09d918</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>46090.26884123853</v>
+      </c>
+      <c r="F33" t="n">
+        <v>288</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fb179b67-2296-41a8-8ef9-d62de459f60f</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>995349d6-0520-40f2-b77d-5734b81dcf25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>46089.85217457186</v>
+      </c>
+      <c r="F34" t="n">
+        <v>97</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>a0a0dc2a-9830-419a-af71-7cd8d67873b4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>98f4be1e-4f41-44ad-84f8-4993472c4f92</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>46091.1855079052</v>
+      </c>
+      <c r="F35" t="n">
+        <v>232</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>c42888f2-ea1f-4d6f-987a-56533c2a6976</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fd499e9e-741b-4826-848a-b0360d2d2cad</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>46091.1855079052</v>
+      </c>
+      <c r="F36" t="n">
+        <v>224</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3dcf51c3-9002-40a9-8c4b-5a4fdb655da4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8a7ebb39-c7f9-40fd-a82f-3b4057d25bda</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>46089.97717457186</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>214fb7e2-d2d8-4b75-b252-de2b196347d0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>baed2d45-70d0-467a-a088-f25779fdae91</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>46090.76884123853</v>
+      </c>
+      <c r="F38" t="n">
+        <v>165</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>01334564-331f-4e7d-ba30-27869f720feb</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1a6a020a-171d-4bfe-b6ab-348ae858d2ec</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>46090.01884123853</v>
+      </c>
+      <c r="F39" t="n">
+        <v>266</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7c96709d-a66d-4163-87ff-803c3f8fdf34</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>61a36c48-8a6b-44e8-9d99-91cb11828130</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>46090.51884123853</v>
+      </c>
+      <c r="F40" t="n">
+        <v>289</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4af8d204-bb18-4583-8d24-8b1546562af9</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ff77c13e-e11d-47b0-a19e-83a916c763ae</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>46090.22717457186</v>
+      </c>
+      <c r="F41" t="n">
+        <v>157</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8b01807b-4e47-4b4b-b462-87c71105f33f</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3df449ec-e9f5-4939-9471-b3ba82db3d19</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>46090.26884123853</v>
+      </c>
+      <c r="F42" t="n">
+        <v>170</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>a367bbae-ed10-4bb2-9421-5ffadd3b6217</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>a93c4311-1888-4651-827e-20c3b73c9cd4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>46089.5605079052</v>
+      </c>
+      <c r="F43" t="n">
+        <v>247</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
         </is>
       </c>
     </row>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,123 +465,157 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>location</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>impact_on_quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f54be6ab-5ffa-467b-8491-7296a84584d9</t>
+          <t>ef8ad327-c601-41d0-a482-6a27c84c7077</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>587898f6-6200-4138-be13-e3ab66f210c4</t>
+          <t>4be68844-cc57-4ba9-aa60-2cafb5850a1d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46090.1728925463</v>
+        <v>46087.6483843597</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>17.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>b6597ba6-be2e-4494-b5e4-4318ede9b77c</t>
+          <t>a1c19e1d-f39e-4feb-baca-a282c3dd07c7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77d2c691-0325-441d-bfc6-901783c5c7c8</t>
+          <t>6aa80042-bb21-47b7-9798-a07bf162bd43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>port_hold</t>
+          <t>delay</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46090.88122587963</v>
+        <v>46073.56505105895</v>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>11.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>97aa2779-88d0-497d-8ed0-c135c781ac18</t>
+          <t>88e95b9a-58d7-4b7f-b833-9b70a9f7b31c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>da8e516a-ddc6-448c-977f-79825faea957</t>
+          <t>41f746ae-f463-4924-8f5a-4feb5e761282</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>port_hold</t>
+          <t>delay</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46090.13122587963</v>
+        <v>46075.52338439552</v>
       </c>
       <c r="F4" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Dubai Port</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>12.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>72a2825d-1961-497d-ac1d-0d31aa097da2</t>
+          <t>c1202d8f-2327-4e7c-9a9b-d84640770543</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8ed657de-b20c-4dc6-a2aa-114d2b14e8a7</t>
+          <t>6511ec56-3b55-47e4-a940-073fcfc7704c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>humidity_drop</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,26 +624,34 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46090.9228925463</v>
+        <v>46068.52338439874</v>
       </c>
       <c r="F5" t="n">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>15.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcaf2871-daf0-4130-818c-66cc982fd2d7</t>
+          <t>9180bd25-ffed-4880-88f5-0d1a1dd025a6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>f20c6d33-86ae-4f1b-99c1-2c2d27f1ed48</t>
+          <t>27f0ce13-bc80-40dd-93d9-de7772b26aab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,63 +661,79 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46089.96455921296</v>
+        <v>46070.31505107182</v>
       </c>
       <c r="F6" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7ce55db6-23df-45da-8f55-c812b3b3de0c</t>
+          <t>2c9e9556-dd5f-4ea5-84ff-eba18a464f16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c6f4bf0c-d721-4399-9db0-fdc38f7dee6b</t>
+          <t>7495a54d-cde1-438b-970d-efd2afa339d4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>humidity_drop</t>
+          <t>handling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46090.13122587963</v>
+        <v>46068.27338443044</v>
       </c>
       <c r="F7" t="n">
-        <v>293</v>
+        <v>161</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.94</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b57f42d7-0eb4-47c1-804d-953364b94d2e</t>
+          <t>9eb0510f-631f-4ada-804e-396e2438220c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>385b6595-ca58-4c09-9ebc-8e6cba2a2fe5</t>
+          <t>300cc3cb-8731-4997-9a38-d4a42813126a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -689,26 +747,34 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46090.71455921296</v>
+        <v>46064.48171777</v>
       </c>
       <c r="F8" t="n">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b15047fa-6041-498b-9ce8-9d04b8609db7</t>
+          <t>b84604ae-467f-464e-9f24-4a58511bf5f1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>aa85741f-4d9b-4087-8cf2-b96a516055ea</t>
+          <t>2a08e59a-b052-43fa-aa73-aa1a2b1c9b26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -718,63 +784,79 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46089.83955921296</v>
+        <v>46085.14838444308</v>
       </c>
       <c r="F9" t="n">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7f584deb-8890-4743-8ddf-33dc428154e9</t>
+          <t>b5868afe-62a7-4480-a731-cdcb34edcf7f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9a715d47-fc82-42d0-abba-ef8e86253321</t>
+          <t>6e65b115-d395-48de-bd21-3f62b8b4a71e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>handling</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46089.96455921296</v>
+        <v>46063.23171777962</v>
       </c>
       <c r="F10" t="n">
-        <v>110</v>
+        <v>269</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5b5b305d-b16f-412c-b918-d59f084076c9</t>
+          <t>7e4a2819-df75-49f6-accc-57e1b0d27c67</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>74732bc0-19b7-4e99-86bc-f2da620d5f9b</t>
+          <t>cd68e5a5-91c0-483c-acfe-5efcf5e6586f</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -784,30 +866,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46090.5478925463</v>
+        <v>46064.35671779846</v>
       </c>
       <c r="F11" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>13.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2e6ec7ad-cffe-4d1d-abe6-03fb2efc5a27</t>
+          <t>bf5ae9e7-68be-4d83-b50e-b2043ddba679</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bf22230b-294c-47cd-a4d0-bf09c9d79641</t>
+          <t>c24409dc-91d4-4d82-ad88-7b6ed02a66cb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -817,30 +907,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46090.25622587963</v>
+        <v>46068.14838447125</v>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>d394315e-9533-4350-b664-e0505d4eaa76</t>
+          <t>90565d27-a2ed-4f2b-8748-1d1cec3029d1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>82223922-493e-4543-97fe-89d1734d81e3</t>
+          <t>b1cac26f-d19b-4604-a5d6-8f2ab6b40ac8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -850,35 +948,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46091.0478925463</v>
+        <v>46086.02338448114</v>
       </c>
       <c r="F13" t="n">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eb7f6518-676f-4b0c-a75c-49afb7cd0ff5</t>
+          <t>cfbdfae2-8f90-4104-b98e-aa9c5725c7ea</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>af67cc2a-d3ef-45af-8906-26cd45264209</t>
+          <t>77d07d9f-27c8-49be-86d6-a9979add2308</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>handling</t>
+          <t>humidity_drop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -887,163 +993,203 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46089.5478925463</v>
+        <v>46072.60671782083</v>
       </c>
       <c r="F14" t="n">
         <v>290</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>17.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e5bcda76-6054-4ce5-a714-f53c150cffc7</t>
+          <t>3fdb7982-892d-4816-99fa-17cc146bae08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1320a2b8-eb6f-4c49-9d7a-005ac5707ae0</t>
+          <t>39c3fbea-15e8-426a-84d0-c1669249c59b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46090.33955921296</v>
+        <v>46077.52338449075</v>
       </c>
       <c r="F15" t="n">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>13.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a7a1f389-76e5-4a81-ab37-a4d16fd1f049</t>
+          <t>ff16230c-8bbc-4910-a2ac-2500e6518adb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>00bf5e26-15ec-4628-b10a-3207ffab17df</t>
+          <t>0f8bd409-c429-45cc-8f94-9844aa0ee90c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>delay</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46089.96455921296</v>
+        <v>46070.23171782727</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>14.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19f63085-4704-4ae8-ae6a-d36630c358fd</t>
+          <t>c12e9032-585b-49eb-bfc5-aa81604b9ca5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>e7cba827-a545-4c5a-bf92-4f028f71d71c</t>
+          <t>707de5cd-fb6b-4a30-986c-b17cba594623</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>port_hold</t>
+          <t>handling</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46090.5478925463</v>
+        <v>46078.48171784603</v>
       </c>
       <c r="F17" t="n">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7a10261b-c2dc-46b0-8271-632ee7cd20ff</t>
+          <t>85562abd-cbda-4a9b-9586-1d5b0abba5a8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>b2a6f3a4-06cf-4812-b8b9-52bc035fc9c3</t>
+          <t>f735c0a2-39ab-4eb2-b957-0fc92229d6c3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>humidity_drop</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46089.58955921296</v>
+        <v>46088.44005118249</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>16.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3945f9e8-3fab-406c-9d91-06607c3a758b</t>
+          <t>461015b2-77ed-46bf-85b1-55a935957682</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4bdcb435-42d1-42f1-805b-c4075c554a23</t>
+          <t>7fb1c193-3c1d-4548-bc4b-f8a9deb8a2ec</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1052,97 +1198,121 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46089.50622587963</v>
+        <v>46082.35671785609</v>
       </c>
       <c r="F19" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f78e8162-0b66-463e-a1ab-d24a8b82914e</t>
+          <t>abe75aff-2258-465c-81dc-7d2346513807</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>882082d6-f850-4532-a0b5-020a3f6a47d3</t>
+          <t>f33414c7-8ca1-4bca-8308-89379874ecd9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46090.9228925463</v>
+        <v>46067.52338452591</v>
       </c>
       <c r="F20" t="n">
-        <v>272</v>
+        <v>99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>16.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a58921c1-24eb-48fd-82c9-3ec5f4dbefc3</t>
+          <t>53c7a494-1a0b-41fc-b9b7-7f1cff97903a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9f07920d-ff67-475d-a79c-c367d148d8aa</t>
+          <t>28b08183-13fd-48b2-b03b-79a07672b4ee</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>handling</t>
+          <t>delay</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46089.5478925463</v>
+        <v>46078.81505123975</v>
       </c>
       <c r="F21" t="n">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>8.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>279d5e6a-1a50-4095-9a32-d0f269151edb</t>
+          <t>ebb1dbdf-61d3-4c9a-9a69-f179e848130a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>c6d56985-5a6a-49e6-b8e8-860c6dc07e10</t>
+          <t>759535a4-3ff4-4e9e-b514-767ff1f47bc5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>port_hold</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1151,26 +1321,34 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46089.97717457186</v>
+        <v>46062.23171791186</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>29277be5-f937-40ad-97a4-30f03681c4f9</t>
+          <t>4badac91-57dd-4906-b8c0-94fc7f2cacc5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>162938ad-c468-4930-b7f5-9496fa97cb6d</t>
+          <t>8e3a42b6-7e3a-415b-8285-6f4a522262ae</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1180,101 +1358,125 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46091.1855079052</v>
+        <v>46085.77338458481</v>
       </c>
       <c r="F23" t="n">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>27242eb4-3702-4d45-b09f-93429a584055</t>
+          <t>3fe9ff15-de65-4595-9acc-21a8e2406e2d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9588dd77-b44f-4bf3-99f6-007d91bcf8be</t>
+          <t>64665776-b45f-4292-9306-f536eb53c880</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46091.1855079052</v>
+        <v>46063.94005126404</v>
       </c>
       <c r="F24" t="n">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>18.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a46b787e-f224-443c-a27d-cef547d94bcd</t>
+          <t>4db22837-4830-4cf1-9f8c-6eb496b879a8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20af1d8a-3d5b-492a-a2ce-1c385c06bfef</t>
+          <t>f6e82685-6546-4bbe-82fb-61fd8804dd19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46089.60217457186</v>
+        <v>46087.35671794019</v>
       </c>
       <c r="F25" t="n">
-        <v>293</v>
+        <v>76</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>India Packhouse</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1884e245-7bdc-4c9e-8039-3a6743f3cdd5</t>
+          <t>a49a15e9-a291-4d19-91c0-19ad0d01c8be</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100f9133-3187-40ff-95f7-3381c810ecbe</t>
+          <t>7a5a3398-f721-42fa-8903-b1e713c76414</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>handling</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1283,64 +1485,80 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46090.64384123853</v>
+        <v>46078.81505128603</v>
       </c>
       <c r="F26" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>7.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f763a695-453e-44ad-808a-a5950c955207</t>
+          <t>14b6471e-7ad9-498c-baf8-8827b274531d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3b1ea915-a4cb-46f3-8469-42dee4357ff4</t>
+          <t>c6788dce-b2f6-4e2e-834e-f7d9538e6cbb</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>humidity_drop</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46090.1855079052</v>
+        <v>46068.14838462568</v>
       </c>
       <c r="F27" t="n">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>c3074ddb-6363-46e8-a747-462e73590d4e</t>
+          <t>95bb3f16-a8c3-4bc5-937e-1c424f13f07f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>70e66201-db63-4fa9-ae20-29c7b57463de</t>
+          <t>1b1f9b35-fa32-4208-8b89-1039a0dc53fb</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>port_hold</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1349,97 +1567,121 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>46090.5605079052</v>
+        <v>46074.48171796523</v>
       </c>
       <c r="F28" t="n">
-        <v>234</v>
+        <v>89</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>14.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f7d839a6-a244-492c-8d4b-81f842d46a39</t>
+          <t>ad87a408-8105-4b4a-a3e9-a6f3f7a3a4bc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>71c0efec-c333-4ff7-a09b-e7e4545e8f93</t>
+          <t>29952a5f-fc95-409c-ac44-205dbcd73c99</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>handling</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46090.89384123853</v>
+        <v>46068.94005130191</v>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3339df5a-94b5-46cc-8ac8-ee2a6bd79a77</t>
+          <t>5e98f7ed-1715-4d77-8077-85aebf48d933</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>a2b02321-c657-4cf4-a44c-696320598cbc</t>
+          <t>3e257604-da1d-4f4a-aa6b-f79a41f4e7cc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>handling</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>46090.72717457186</v>
+        <v>46078.3567179717</v>
       </c>
       <c r="F30" t="n">
-        <v>248</v>
+        <v>121</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>19.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>255d9ea0-a9db-445a-9bbf-7039185a5cb0</t>
+          <t>dfbc30aa-7d61-4d94-a4e7-c15d5046fcdd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6c69de8b-13ff-49d1-b8e8-fb733d1441fd</t>
+          <t>92bc79bf-5604-4ad0-9f70-ed16ee2ced28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1448,64 +1690,80 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>46091.10217457186</v>
+        <v>46075.02338464774</v>
       </c>
       <c r="F31" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>India Packhouse</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>16.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>34b85d31-7986-450b-8726-66e021a3eb6e</t>
+          <t>c31378bc-e5cd-4550-83c3-a0b68f8595b5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dd10f970-adb3-439b-a7c0-f782639e5b91</t>
+          <t>5a6e87e8-b74e-4742-ab42-d8747620b586</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>humidity_drop</t>
+          <t>delay</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>46090.35217457186</v>
+        <v>46062.06505131771</v>
       </c>
       <c r="F32" t="n">
-        <v>224</v>
+        <v>35</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dubai Port</t>
-        </is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>14.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0654e23c-3ae2-4f52-97dc-682a75d2588b</t>
+          <t>88f6d0ca-ace8-4efe-b8b5-8c521e8173d2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>a8eb50ee-b5ff-4191-a0a6-cd163a09d918</t>
+          <t>c2d22903-5424-47be-961d-3ba8a8503041</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>humidity_drop</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1514,26 +1772,34 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46090.26884123853</v>
+        <v>46069.1900513239</v>
       </c>
       <c r="F33" t="n">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>14.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fb179b67-2296-41a8-8ef9-d62de459f60f</t>
+          <t>ff5bc9dd-bc78-45c0-8b15-49aaa9fda558</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>995349d6-0520-40f2-b77d-5734b81dcf25</t>
+          <t>2a4dfcf7-9475-4fe9-b513-4aeb10a4811a</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1543,30 +1809,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46089.85217457186</v>
+        <v>46064.23171799703</v>
       </c>
       <c r="F34" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>Rotterdam Port</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>13.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a0a0dc2a-9830-419a-af71-7cd8d67873b4</t>
+          <t>7988666e-44ba-4a6c-950a-b863066389eb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>98f4be1e-4f41-44ad-84f8-4993472c4f92</t>
+          <t>3e60ebd0-04f4-4ed4-9dbb-853557da718e</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1576,35 +1850,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>46091.1855079052</v>
+        <v>46083.56505133984</v>
       </c>
       <c r="F35" t="n">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>10.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>c42888f2-ea1f-4d6f-987a-56533c2a6976</t>
+          <t>b4f7f5ad-a109-4f24-bbb7-b18ac6c509b5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>fd499e9e-741b-4826-848a-b0360d2d2cad</t>
+          <t>8614d93f-99b5-4f0e-acb8-f464b7f74c42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>port_hold</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1613,31 +1895,39 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46091.1855079052</v>
+        <v>46068.23171801262</v>
       </c>
       <c r="F36" t="n">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>US Distribution</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>12.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3dcf51c3-9002-40a9-8c4b-5a4fdb655da4</t>
+          <t>a2e6f1d6-7bb1-4a15-be02-9eaa0aa227c9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8a7ebb39-c7f9-40fd-a82f-3b4057d25bda</t>
+          <t>04918d26-82fb-43af-aac0-43556880bd01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1646,26 +1936,34 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46089.97717457186</v>
+        <v>46073.19005134939</v>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>11.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>214fb7e2-d2d8-4b75-b252-de2b196347d0</t>
+          <t>c77ff008-bf75-4df9-a504-6770cc96e2e1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>baed2d45-70d0-467a-a088-f25779fdae91</t>
+          <t>f419913b-9a01-411e-8381-fdd32f3d2b2a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1675,184 +1973,6259 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>46090.76884123853</v>
+        <v>46087.85671801919</v>
       </c>
       <c r="F38" t="n">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rotterdam Port</t>
-        </is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>7.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01334564-331f-4e7d-ba30-27869f720feb</t>
+          <t>edf2798b-ad58-4f5e-a3ee-18f7ff6dff82</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1a6a020a-171d-4bfe-b6ab-348ae858d2ec</t>
+          <t>93ed1fb4-275a-4964-a59d-582621935dff</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>46090.01884123853</v>
+        <v>46064.85671802853</v>
       </c>
       <c r="F39" t="n">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>US Distribution</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>17.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7c96709d-a66d-4163-87ff-803c3f8fdf34</t>
+          <t>7326485b-cc74-41bc-a70f-db80ffa38423</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>61a36c48-8a6b-44e8-9d99-91cb11828130</t>
+          <t>46b037b6-6e17-4979-a63f-36814487a3af</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>temperature_spike</t>
+          <t>humidity_drop</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46090.51884123853</v>
+        <v>46069.94005136505</v>
       </c>
       <c r="F40" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>India Packhouse</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4af8d204-bb18-4583-8d24-8b1546562af9</t>
+          <t>270b925b-7326-415a-9b96-e4e74bff638e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ff77c13e-e11d-47b0-a19e-83a916c763ae</t>
+          <t>5de7fb17-6dc3-4b12-bd49-6f47c5b7b945</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>port_hold</t>
+          <t>temperature_spike</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46090.22717457186</v>
+        <v>46066.31505138066</v>
       </c>
       <c r="F41" t="n">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>12.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8b01807b-4e47-4b4b-b462-87c71105f33f</t>
+          <t>05e2dccb-cb13-48ad-8e0e-be4ff47ec347</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3df449ec-e9f5-4939-9471-b3ba82db3d19</t>
+          <t>7f665975-fba5-46f6-a44d-106f1bcb2ba1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>humidity_drop</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>46090.26884123853</v>
+        <v>46068.8983847297</v>
       </c>
       <c r="F42" t="n">
-        <v>170</v>
+        <v>294</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>India Packhouse</t>
-        </is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>15.82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a367bbae-ed10-4bb2-9421-5ffadd3b6217</t>
+          <t>93c67d7c-1632-4c16-a641-7c2bbec134cf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>a93c4311-1888-4651-827e-20c3b73c9cd4</t>
+          <t>05cec554-9ccc-400a-9da8-a12372e534ac</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>46078.89838474819</v>
+      </c>
+      <c r="F43" t="n">
+        <v>51</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9fc9f092-aa47-4d7d-b83d-a5a00d7c7848</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>dbe26894-f9ba-491f-8c39-44910a6c4da1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>46078.89838475458</v>
+      </c>
+      <c r="F44" t="n">
+        <v>33</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>c57347c9-538a-4f75-ba9d-cd784927dc6c</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>14e43e63-9c38-4a82-ab60-cdc821ed8bd1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>46081.14838476406</v>
+      </c>
+      <c r="F45" t="n">
+        <v>158</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>13.53</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>f9a30fa6-be51-403b-9462-a55a54fbdd21</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>72ee5eab-0a54-4afb-97dc-6d3da856e0c2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>46073.81505147116</v>
+      </c>
+      <c r="F46" t="n">
+        <v>193</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ee3fc927-d201-4cad-b2a0-490d858e44b1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>41e84070-273d-44d4-9e12-765e84212c3d</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>46063.52338481087</v>
+      </c>
+      <c r="F47" t="n">
+        <v>142</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>73a76d08-066b-4d71-81d7-d82064a06c43</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4f6ecc72-70ca-4e95-86a2-69f77df9989e</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>handling</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>46089.523384817</v>
+      </c>
+      <c r="F48" t="n">
+        <v>144</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>b97122e3-6f40-449b-91ea-61867bcfe7db</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6bbce639-fe81-478e-941a-218c7516f6fe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>46088.35671815382</v>
+      </c>
+      <c r="F49" t="n">
+        <v>283</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>56cd12e8-fa88-4771-b77d-8e4ada40b789</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>b72a6518-b1aa-446f-a25c-766a4c023dec</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>46089.5605079052</v>
-      </c>
-      <c r="F43" t="n">
-        <v>247</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="E50" s="2" t="n">
+        <v>46091.39838482362</v>
+      </c>
+      <c r="F50" t="n">
+        <v>65</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Dubai Port</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>13.51</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>60d0da8a-cca2-424d-98a5-f5353bf5458b</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2b9453d9-8969-4b61-a6c0-64054db56bfc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>46084.06505149352</v>
+      </c>
+      <c r="F51" t="n">
+        <v>218</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>e97a6f6e-0584-47d8-bd29-c36e02d49e89</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7b0d7bf2-71dc-4057-9f55-0851c391075b</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>46086.10671816648</v>
+      </c>
+      <c r="F52" t="n">
+        <v>193</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5130d646-1805-42c7-9fd7-de71fd5af8ed</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>23eda4fc-440b-4827-a058-3b8bb7661d0e</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>46079.31505150304</v>
+      </c>
+      <c r="F53" t="n">
+        <v>201</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1304a412-f18f-4415-bee1-60cd663f94b6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>214d249b-63f0-4540-be40-8ee1671ef147</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>46088.60671818924</v>
+      </c>
+      <c r="F54" t="n">
+        <v>42</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>e116de3f-2ecc-4be4-ab8c-f49d0d1589e7</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>c93477a0-f43c-40dd-8d35-54c6d743d422</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>46080.48171819547</v>
+      </c>
+      <c r="F55" t="n">
+        <v>231</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>e606909d-26bb-46b8-aeb3-714f345a5750</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7d23f205-a6c1-4fed-9749-4b95e1287a96</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>46089.27338486532</v>
+      </c>
+      <c r="F56" t="n">
+        <v>124</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>18.79</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2bb900e5-0390-4a46-821d-4557b21ebf34</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>f34c1e4b-0f7d-43f2-be44-f3be84603dcf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>46073.98171822666</v>
+      </c>
+      <c r="F57" t="n">
+        <v>72</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>19.42</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7a334336-48d8-4ab8-9942-85f0af09ca96</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4372146f-8475-4633-9ad0-eafdd0356825</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>46062.77338490276</v>
+      </c>
+      <c r="F58" t="n">
+        <v>250</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>eee03ece-332e-4782-b26f-fec8d0a7e54a</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4d863745-5e9b-420d-bcdd-e55a2056e304</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>46072.44005157263</v>
+      </c>
+      <c r="F59" t="n">
+        <v>241</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>13.44</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2b242fd9-91c0-4c4f-bebb-5fa4511aaf94</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>e3e897f7-6bcf-4071-aa0b-3e2068711081</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>46083.52338490923</v>
+      </c>
+      <c r="F60" t="n">
+        <v>174</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>17.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>79e3de97-e7ab-48c0-8684-f28c7969145f</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>d7c4cdb4-2aa9-4803-9f20-53beb60c520e</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>46075.19005157926</v>
+      </c>
+      <c r="F61" t="n">
+        <v>165</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>47068fbc-1def-43d7-96ff-30bd72207f93</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>29cffb60-f529-417a-bd10-6ea85e0e9fb1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>46087.27338491873</v>
+      </c>
+      <c r="F62" t="n">
+        <v>246</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>a5c57af8-9914-4459-a04a-f5fb1200d242</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>8df4648c-aa84-4c63-90e2-546ec5cc70ea</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>46082.64838493785</v>
+      </c>
+      <c r="F63" t="n">
+        <v>218</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>17.56</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>822fcf19-714c-42ac-9232-73be776f6260</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>51f8db0c-7e4b-4175-87dd-6ae135a716df</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>46069.31505160772</v>
+      </c>
+      <c r="F64" t="n">
+        <v>190</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>424c9ad2-9830-4daa-84a4-9ed7b7deae7c</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>c14564b6-45de-4543-96c0-aeffa7176e09</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>46082.27338494424</v>
+      </c>
+      <c r="F65" t="n">
+        <v>89</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>15.71</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>de54204f-e109-496a-b8cb-fee2e853639a</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>9acfa595-ec4e-40f5-9472-d317cc1133bd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>46081.19005161731</v>
+      </c>
+      <c r="F66" t="n">
+        <v>264</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>98a71bea-ecaa-4088-91f5-1c23b97817a3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>08919299-0aad-48f7-bdd6-864f45ddba0d</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>46064.44005162052</v>
+      </c>
+      <c r="F67" t="n">
+        <v>258</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>edbcabf0-3234-4e6c-9350-37f9c433fde7</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cb43174c-2106-426c-bf47-b2e1e6ad86f9</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>46067.60671829034</v>
+      </c>
+      <c r="F68" t="n">
+        <v>226</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>17.16</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>9f2ec848-2f94-4d2a-bab4-2aab05063cce</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>8a15e5aa-8af6-4b9d-afb3-059a5871b331</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>46086.27338496036</v>
+      </c>
+      <c r="F69" t="n">
+        <v>136</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>16.88</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>d7679c89-40dd-4833-a3ae-683b03a1aef5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>16c4b746-224b-4eed-aa56-a44d015f60ae</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>46072.14838496348</v>
+      </c>
+      <c r="F70" t="n">
+        <v>84</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>18.81</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>b3a192d7-9e9e-4a3a-aacb-2a35043907b1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7f45b7cc-e1ac-4f4a-a0ad-4624b4598431</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>46080.44005163966</v>
+      </c>
+      <c r="F71" t="n">
+        <v>153</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>15.78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0e700f8b-53f7-47b9-9635-22de3a970849</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7c594f95-6dd0-4617-96f7-aa328c8f3997</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>46089.64838497622</v>
+      </c>
+      <c r="F72" t="n">
+        <v>68</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>f973c3f3-819c-4e46-8e68-90b564caeb53</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>9e4d0f79-436e-45d1-a1df-902745cc497c</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46065.23171831271</v>
+      </c>
+      <c r="F73" t="n">
+        <v>203</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>57b3c1eb-8c1c-45f3-a2a3-e48b1b972d43</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7d369a1e-a7ac-440c-b287-55f2cdd1adc9</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>46084.89838498276</v>
+      </c>
+      <c r="F74" t="n">
+        <v>239</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3353b8e7-8b54-4110-a120-791da3b30f48</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>15912d57-9eac-4ac2-86e3-80f2f725653c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>46080.98171831928</v>
+      </c>
+      <c r="F75" t="n">
+        <v>229</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>15.42</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>bca1a128-0034-4106-b5f8-fd773dc51438</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>f8649314-cedb-4d2f-967a-a495e66ddd48</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>46079.27338498909</v>
+      </c>
+      <c r="F76" t="n">
+        <v>150</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>bc005a87-d4ba-457c-b1ea-96f38e7f3fc3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>320a7d02-7c2a-4fcc-9023-77f15ef8db10</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>46069.27338499543</v>
+      </c>
+      <c r="F77" t="n">
+        <v>268</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>13.22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>b8238f31-eee3-4e68-a1a2-17729f1ade1f</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>97805945-91f2-466f-9124-78626f0d993a</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>46082.60671833823</v>
+      </c>
+      <c r="F78" t="n">
+        <v>244</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>11.52</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>591f8337-1799-481a-8c47-e6dc10f8fc44</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>37c909d9-b32f-4d79-b02a-80f65499582a</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>46085.14838501107</v>
+      </c>
+      <c r="F79" t="n">
+        <v>152</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>8.380000000000001</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>731d289b-5e0a-4dca-860d-6ac174cf25ab</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>d8285903-c1cb-4f85-8f94-91548ce0c32b</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>46083.60671835078</v>
+      </c>
+      <c r="F80" t="n">
+        <v>70</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>a843b18b-2960-4768-8f3a-cecff981d874</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>208e9e24-d0aa-4e27-aed4-7c2c3caa8b32</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>46072.48171835397</v>
+      </c>
+      <c r="F81" t="n">
+        <v>289</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>54768930-d0c6-4e7b-b973-8212cd8b8a27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>49923c6f-9f1f-4f57-bda9-2fd98922bf63</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>46072.10671835713</v>
+      </c>
+      <c r="F82" t="n">
+        <v>133</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>05563224-8ad9-479d-9968-59ef535408c2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1e165846-56a2-4aa6-bf35-43997fd35b71</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>46084.14838502691</v>
+      </c>
+      <c r="F83" t="n">
+        <v>49</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9f56bdf2-741c-4939-bbfe-5bbbdb74f6ed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>39cb4246-a847-4866-872e-47a8e8c0f198</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>46060.56505170627</v>
+      </c>
+      <c r="F84" t="n">
+        <v>157</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>78f4e12f-317c-4a97-8a28-d7dab1b0e937</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1655584c-e38e-40eb-a892-b992a949b1f1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46069.98171838226</v>
+      </c>
+      <c r="F85" t="n">
+        <v>296</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>674cbd02-c1d6-4b7d-bceb-8e61425583ca</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>05d05785-879a-4342-a0e4-2f1a40d3fb1a</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>46077.27338506135</v>
+      </c>
+      <c r="F86" t="n">
+        <v>218</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6024f75e-9eff-48cb-a5ec-68d110f1d303</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>96ae0f38-2776-45a7-b015-e0273c068f7d</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>46077.10671839801</v>
+      </c>
+      <c r="F87" t="n">
+        <v>83</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ce62af52-d14c-46cb-9625-d3351f4f1f17</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2964562a-659e-45f6-8b8d-c9e6a9b2b50e</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>46079.81505173459</v>
+      </c>
+      <c r="F88" t="n">
+        <v>296</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>13.41</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>a217192c-a9a6-4fe4-bd1f-bda113153535</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7515ced8-e432-48f9-9ee8-537176f85793</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>46072.35671840439</v>
+      </c>
+      <c r="F89" t="n">
+        <v>152</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>15.07</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>839c5a98-712b-4cbb-bb71-4a0d49d0a323</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3893cd84-a6b8-47ee-a279-10d914089f80</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>46064.69005175013</v>
+      </c>
+      <c r="F90" t="n">
+        <v>263</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6eed0e4f-fa03-48f8-84e1-e1b3044c0d11</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>f4ec9a8b-649e-431f-a4d3-b4aa3035b904</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>46082.8983850868</v>
+      </c>
+      <c r="F91" t="n">
+        <v>42</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>a518ca6b-67fe-4207-b522-d83800e5f1f7</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>da886dbe-27e0-49be-93c2-a416662f876f</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>46074.56505175973</v>
+      </c>
+      <c r="F92" t="n">
+        <v>117</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>d1857fac-64d2-45eb-9730-946534d53af5</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>6a939b86-1e76-4932-8264-3b29b10defcc</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>46068.94005177523</v>
+      </c>
+      <c r="F93" t="n">
+        <v>131</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>98cb1b84-2392-4327-ace5-274d1d412c0e</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>a3c598c5-f429-43dd-a3e8-6e4f82a53285</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>46080.52338511192</v>
+      </c>
+      <c r="F94" t="n">
+        <v>150</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>16.16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>574d6ec2-d0b3-46e3-8a5c-4fdf2fbbee7f</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>39d68d8e-5353-4e9c-99bf-a432af8b3f91</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>46066.73171845142</v>
+      </c>
+      <c r="F95" t="n">
+        <v>39</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>18.24</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>b54c0643-c341-4f94-afb9-6498c881a61c</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>6f61ce8f-ec92-4102-aaf5-cc631baba004</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>46064.02338513682</v>
+      </c>
+      <c r="F96" t="n">
+        <v>212</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>022576eb-24d3-4225-a24e-05daf21aa329</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>8b87a921-79f6-4a7a-95d1-51c466a0f8ee</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>46078.5233851523</v>
+      </c>
+      <c r="F97" t="n">
+        <v>185</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>14.58</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>da18231c-49bf-40f8-a827-7cdea8147adb</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>94785af3-e0e9-4b45-8e58-31e79033b895</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>46072.48171850132</v>
+      </c>
+      <c r="F98" t="n">
+        <v>249</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>bf342944-9dce-42e2-b40c-b6bb6f0bf4b6</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>494ed28b-02b1-48b6-a670-6550bcc26b77</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>46072.35671850449</v>
+      </c>
+      <c r="F99" t="n">
+        <v>182</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>768f5fc2-7a72-4b5f-947a-4dbfb2b410cc</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2553eac1-5123-47ba-9394-9ad3a0d05d63</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>46066.73171850768</v>
+      </c>
+      <c r="F100" t="n">
+        <v>135</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>14.73</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>da66f76e-6585-4fd6-8c97-a706546c534a</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>443a49d8-c669-41e3-9561-446e36bce769</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>46066.31505184413</v>
+      </c>
+      <c r="F101" t="n">
+        <v>94</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>17.09</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>214395e1-dc56-430a-8060-440b31759327</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2800bec7-a406-45e9-a101-bb39e5912ebf</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>46067.73171851841</v>
+      </c>
+      <c r="F102" t="n">
+        <v>36</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>19.78</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>86b6795e-9141-4f07-8700-2ad481d554e9</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>33ad837c-5603-475b-996e-fcde05dcd194</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>46085.60671852549</v>
+      </c>
+      <c r="F103" t="n">
+        <v>145</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>c30b88f1-495a-45ea-98a9-1e6140cc714c</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>49046a9c-b694-49dc-ae9c-64890aac03fe</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>46068.89838520788</v>
+      </c>
+      <c r="F104" t="n">
+        <v>168</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>16.43</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>9c0d719c-7fd1-4a53-9313-bc4da5d1e6e4</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>88927383-0763-4860-a06c-16d881681b75</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>46070.02338521754</v>
+      </c>
+      <c r="F105" t="n">
+        <v>241</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>18.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>b02ca22c-1b14-4655-b2b8-766606758638</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>bab1db4f-fc7d-4939-8e2f-bce0df93e125</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>46075.10671855711</v>
+      </c>
+      <c r="F106" t="n">
+        <v>277</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>17.24</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>757eeefd-67ca-464d-af5e-54ac68848e18</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>389d21e1-e916-4e04-8676-f442e372a522</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>46084.06505189384</v>
+      </c>
+      <c r="F107" t="n">
+        <v>62</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>19.24</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>5129c108-9f0f-4941-bf37-7fcac6af0890</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>15742ef7-7e59-4d81-b9d3-6dbb1b658865</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>46085.10671856373</v>
+      </c>
+      <c r="F108" t="n">
+        <v>278</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>16.78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>e793b982-3f68-4ddb-a9db-067048c0a46e</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>e8e672b7-97a1-411c-9e8a-3756cfe05bf0</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>46062.06505190658</v>
+      </c>
+      <c r="F109" t="n">
+        <v>142</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>19.82</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>aa048e0d-0297-4ca6-8c77-19912a0ae352</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0ab12e32-0885-49cf-a603-415aa936ac70</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>46061.64838525849</v>
+      </c>
+      <c r="F110" t="n">
+        <v>50</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>96c82b32-72f5-426a-a09f-3a397bd11f21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2b503220-fbcf-481e-a790-7b6a09d80942</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>46069.1067186229</v>
+      </c>
+      <c r="F111" t="n">
+        <v>87</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>74c83c39-83bd-4a95-8d98-36c809a4ea7c</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>08ebbc2e-5d19-4919-bbcb-a3a28e306590</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>46083.27338529602</v>
+      </c>
+      <c r="F112" t="n">
+        <v>82</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>17.49</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>c8b65906-598e-4694-9b26-204e3fcdc36a</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>27137464-4279-4a4d-b86e-81b3f35188ad</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>46067.85671863264</v>
+      </c>
+      <c r="F113" t="n">
+        <v>132</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ad30887a-1720-4635-ba52-d1ba77a49fe5</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>dbe9ca03-04ae-4e94-9fae-5743b0f24b14</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>46078.52338530245</v>
+      </c>
+      <c r="F114" t="n">
+        <v>152</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>6f2dc1db-8ca7-4c39-9d34-318439edbee6</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>bcf3ebbe-56d0-4e87-aea6-3a00f95f7813</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>46074.27338530582</v>
+      </c>
+      <c r="F115" t="n">
+        <v>186</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>058f1f1f-02dc-402a-a4c8-35856c6ac16f</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>708e3629-f3f6-44cb-a997-d8ecacf95f7a</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46078.5650519757</v>
+      </c>
+      <c r="F116" t="n">
+        <v>150</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3825f889-9890-4c1b-9473-bbcef77e6c47</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>bc9abcc9-4d4a-420f-8372-5205e0cdf4b9</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>46082.69005198522</v>
+      </c>
+      <c r="F117" t="n">
+        <v>201</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>b9c2a7d9-829a-4e92-9caa-e49e84cb9fbe</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>98cbc012-6265-4837-98b2-4452eba206ff</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>46067.89838532171</v>
+      </c>
+      <c r="F118" t="n">
+        <v>288</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>15.76</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cd2345b0-b23c-4af1-a469-3e65d53eb0a1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>56eeb38f-695e-4eb7-a3b8-e47da0305ef5</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>46068.64838532791</v>
+      </c>
+      <c r="F119" t="n">
+        <v>298</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>4c902011-0209-437f-a6d1-ddaf1765df9e</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>904fb266-de36-466f-95aa-5bbb3afd3359</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>46072.73171866765</v>
+      </c>
+      <c r="F120" t="n">
+        <v>103</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>14.86</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>7ce3938d-2277-47ac-bc24-81216c56f67e</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>df6b3b33-e073-4710-9217-63861ced26fd</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>46060.69005201053</v>
+      </c>
+      <c r="F121" t="n">
+        <v>241</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>e4e85b13-8925-466d-9655-52071be787fd</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>15515fee-323f-49cc-8c14-45ac5aaaa2be</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>46086.60671868041</v>
+      </c>
+      <c r="F122" t="n">
+        <v>105</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>bb5b9e9d-4e0e-4768-8529-8cccca2a30bf</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>98f76804-035c-4039-bbb5-91e0e9928670</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>46069.23171868356</v>
+      </c>
+      <c r="F123" t="n">
+        <v>124</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>53d71dbb-8021-4d5e-b0eb-0d514f29699d</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1338985f-cdc5-4125-bbd5-91e2f03a34fa</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>46087.23171868692</v>
+      </c>
+      <c r="F124" t="n">
+        <v>223</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>19.85</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>5f6afd63-2047-468b-9f13-c642169addd3</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>019c9e65-8071-4fc7-afd7-392452601fb8</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>46066.64838537537</v>
+      </c>
+      <c r="F125" t="n">
+        <v>42</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>9e3b635e-f54d-4104-9744-578f883800f4</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>48114cc9-726b-4116-b3cd-15d9da1ee4e9</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>46079.73171871188</v>
+      </c>
+      <c r="F126" t="n">
+        <v>249</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>9af7c065-01d0-488d-9de0-228958aeaf8d</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>3729f14d-54b6-42e9-ae50-1e58d8e0997e</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>46087.1483853817</v>
+      </c>
+      <c r="F127" t="n">
+        <v>232</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cde7b3d2-6b43-455f-ae7b-6e4187a39c13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>d8d03cb3-319e-4e5e-aaab-e8f4c8beebc8</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>46080.35671872141</v>
+      </c>
+      <c r="F128" t="n">
+        <v>82</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>9acb4c41-ebcd-4f42-b960-fec11adc5d2e</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>286c42e0-4e5e-4e23-bdc3-90c2a7e0734f</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>46090.8983853973</v>
+      </c>
+      <c r="F129" t="n">
+        <v>61</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>17.14</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>8ab74e1c-6db0-4802-a32a-28a6d52ee19e</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>6cf97494-7e37-43c6-89d4-ee3c5352d261</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>46074.98171874005</v>
+      </c>
+      <c r="F130" t="n">
+        <v>139</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>90c7a998-d302-4b5f-a183-fdd72a1d2b99</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>6b1b6507-e619-47a4-9d95-a173ed5926f7</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>46078.64838541315</v>
+      </c>
+      <c r="F131" t="n">
+        <v>180</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>b167b49f-2598-4864-bff2-9bc1112a0f73</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>83cb99d7-aa37-4a74-b120-e5b4ca485631</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>46066.69005208611</v>
+      </c>
+      <c r="F132" t="n">
+        <v>94</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>603c4a8d-6ae0-427d-ad1a-2bfe53ff90c9</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5214a5a3-8095-41f8-83e5-0d8a1ae0c93e</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>46081.14838542897</v>
+      </c>
+      <c r="F133" t="n">
+        <v>104</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>326c2f9a-9cb1-44ed-99bf-5e36d97f4ad3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>e9551e93-fb79-4a26-9c64-d325662230d7</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>46069.64838543216</v>
+      </c>
+      <c r="F134" t="n">
+        <v>289</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>60735988-bbdb-4d5b-b202-ef128b7d07f8</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ac26ba37-9c14-4c52-b209-710d7d1d3dd7</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>46071.94005210822</v>
+      </c>
+      <c r="F135" t="n">
+        <v>171</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>079a6872-2118-4697-b798-2ebd2d1aabeb</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>46edf1ff-a3d2-40e2-b7b6-5a6068e54b74</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>46061.10671878435</v>
+      </c>
+      <c r="F136" t="n">
+        <v>81</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>16.22</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>97321a19-f6f8-4075-8766-c4e80ab8156a</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>01081850-9bc3-439b-80b9-d647ba70a597</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>46076.06505212568</v>
+      </c>
+      <c r="F137" t="n">
+        <v>128</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>16.32</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>3b51f174-69fc-4057-801f-32b26f21887b</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>c4142406-c911-44f4-9055-529eb58dc8db</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>46064.10671879861</v>
+      </c>
+      <c r="F138" t="n">
+        <v>141</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>10.51</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>a6ae4d7c-057b-4fad-b5d9-40646ba3e542</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>46b954dd-a41b-4d2c-9721-135d5339a336</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>46078.35671880809</v>
+      </c>
+      <c r="F139" t="n">
+        <v>237</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>d7397476-cee1-46b5-8cf8-ec4d088a8230</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>7f5f7814-c4ee-47ae-84b5-2f9adee5703f</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>46072.85671881452</v>
+      </c>
+      <c r="F140" t="n">
+        <v>77</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>8f518a75-7cb8-4f8a-b652-b16046aba02e</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5546c57d-dfb9-4437-b58e-cae64e99201c</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>46079.39838548433</v>
+      </c>
+      <c r="F141" t="n">
+        <v>207</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>13.07</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>b2098d16-e19c-41de-8011-c275deca09b3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7c8cc332-8d14-43e6-8389-db8838264e46</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>46063.5650521542</v>
+      </c>
+      <c r="F142" t="n">
+        <v>289</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>e6b96736-5ce9-466f-866a-6de5c857d7c7</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>abe498f8-2caf-41c6-8b63-63c38b203a2a</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>46078.27338550008</v>
+      </c>
+      <c r="F143" t="n">
+        <v>187</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>16.49</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>df581f56-5291-4fec-9aa6-dfbe7e2244ee</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>6af6436f-696a-4182-8281-ddd10146ee56</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>46081.31505217918</v>
+      </c>
+      <c r="F144" t="n">
+        <v>58</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>db49e561-0d47-4a3f-ba3d-65bf98fe52e1</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>f7a572e0-37df-4c2d-8eed-ecd68ef5621c</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>46091.23171887387</v>
+      </c>
+      <c r="F145" t="n">
+        <v>232</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>6239a688-14ec-45d2-ac9c-7d778455a717</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>e63c3126-d5f7-43b6-80d6-2b759b82edf2</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>46078.6067188801</v>
+      </c>
+      <c r="F146" t="n">
+        <v>289</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>6b2bdfc3-4791-4ff7-a80d-2e9136b87034</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>cb1ceef3-6ec1-4fac-a69a-750e56189c43</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>46067.56505222286</v>
+      </c>
+      <c r="F147" t="n">
+        <v>203</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>a981aafc-a07e-4140-9de1-3ded5e1d3c2b</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3bef3c9a-647f-432e-943b-e87ad64f59f7</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>46068.35671889274</v>
+      </c>
+      <c r="F148" t="n">
+        <v>224</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>15.59</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>f68a4c9f-f5fa-437a-956c-8e7f26e1f591</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>8f1286bc-7b6f-4c19-9839-cc0e860e95cb</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>46077.19005224487</v>
+      </c>
+      <c r="F149" t="n">
+        <v>284</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>9fae82d6-20cb-432c-9042-1bb76b169ea9</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>c8eda967-4006-41e5-8489-6db62d32a93c</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>46075.06505226042</v>
+      </c>
+      <c r="F150" t="n">
+        <v>224</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>d9be5d01-46dd-4c27-810a-981f0262cb62</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>4f3362eb-9d90-4377-bf6d-4c5135fcf325</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>46063.52338560009</v>
+      </c>
+      <c r="F151" t="n">
+        <v>195</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>80e88e99-b2f2-4258-bc01-86061867121d</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>e8f12068-7a2b-4ea2-b603-1092dde7d0f4</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>46064.60671894284</v>
+      </c>
+      <c r="F152" t="n">
+        <v>90</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>81fd1e79-e860-4a0d-817e-8573ddebf3cd</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>408b6c1c-b343-4315-a4a6-c0af35d02716</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>46086.690052301</v>
+      </c>
+      <c r="F153" t="n">
+        <v>249</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2b039bdc-7335-42b1-a4e8-9c79c2a65a59</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>e72225f9-8a7a-4042-b081-3dee07da10d9</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>46061.7317189708</v>
+      </c>
+      <c r="F154" t="n">
+        <v>47</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>aae20d06-c26c-4ce6-b9cc-38a1c74e39f6</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0e930db9-3eab-4c3a-a051-82b74a2695ab</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>46086.23171897721</v>
+      </c>
+      <c r="F155" t="n">
+        <v>200</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>654e482c-07a6-4165-af77-a14da79c4ccb</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1f1089d4-8fbf-4559-b2c0-e22b83b16281</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>46080.60671899274</v>
+      </c>
+      <c r="F156" t="n">
+        <v>90</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>15.41</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>7c9feca1-0c2e-4878-ad12-ee72b2eb4dcf</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>64928630-6436-4f5e-9a7e-75f3528f16a1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>46064.06505233551</v>
+      </c>
+      <c r="F157" t="n">
+        <v>151</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>7847b9ba-9c93-4c5c-8043-b5476194fba9</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>269f4497-a43e-490c-a0b4-dbc8dac1dfb6</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>46089.94005233864</v>
+      </c>
+      <c r="F158" t="n">
+        <v>153</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>12.18</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>39d5fcd1-b51a-4f76-9518-5adcc6366949</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1b4fe61e-1248-4046-9526-574d99b7485b</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>46064.56505234868</v>
+      </c>
+      <c r="F159" t="n">
+        <v>249</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>18.16</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>efd790e8-bade-4260-b114-244f75df7caf</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>b530526c-1cb8-41bb-b01f-8ff48f5b7917</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>46069.44005235183</v>
+      </c>
+      <c r="F160" t="n">
+        <v>118</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>b665ee2e-b675-4dd4-80e8-36f5d9ee038e</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0dd66d1f-0027-435e-889e-819acdba53a2</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>46077.56505235528</v>
+      </c>
+      <c r="F161" t="n">
+        <v>242</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1a908dd0-ff60-4268-a188-9f8092e5d11d</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6b0589ea-32c5-4125-8fc5-24d63cbeb3b4</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>46081.0650523615</v>
+      </c>
+      <c r="F162" t="n">
+        <v>123</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>24da822a-1006-48df-af52-4a44555be848</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>81bed0b4-2b1f-41a9-b2b1-09484644b5b3</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>46082.64838570207</v>
+      </c>
+      <c r="F163" t="n">
+        <v>166</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4b713cb5-4c05-4d31-a533-f48b85ec647f</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>f351ad99-b309-4099-83bb-7f2a32ef4c8b</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>46088.77338571779</v>
+      </c>
+      <c r="F164" t="n">
+        <v>50</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>b7dbbcc7-0d51-4733-82b6-280f8612d5dd</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>96970421-476f-4f6c-ab8f-02c9513b74f9</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>46076.85671905747</v>
+      </c>
+      <c r="F165" t="n">
+        <v>95</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>8d1d7e4b-6eaf-47f1-ba9f-9d632b880e6b</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>39aab8f1-af33-494f-b46f-1ce7e0244e92</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>46080.35671906667</v>
+      </c>
+      <c r="F166" t="n">
+        <v>98</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>22d4feb8-9d8d-4f11-befb-1ab5a8819fa7</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>07c59212-97d0-4ae1-bb6c-18ba3c239f03</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>46071.69005240937</v>
+      </c>
+      <c r="F167" t="n">
+        <v>66</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>d5ee5561-fb1f-41f9-bc37-903910ded905</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>6d23d593-8f1a-47a3-b357-aa2d5af3dcad</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>46063.73171907934</v>
+      </c>
+      <c r="F168" t="n">
+        <v>267</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7c42b60a-dec0-49b6-a054-d23331b742f9</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>78b7b2e5-3250-4ca2-9049-3e96cea74a57</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>46088.81505241595</v>
+      </c>
+      <c r="F169" t="n">
+        <v>66</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>e3ee46d5-94e1-43ba-8a12-bd2e03adc72d</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>65515a28-cfcb-4d50-939d-8bffecf3f08b</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>46074.52338575873</v>
+      </c>
+      <c r="F170" t="n">
+        <v>84</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ab8991fa-d854-4b91-a253-14bf1d38aefa</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>95e35a1d-f59e-4a09-9520-994f07fac447</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>46075.64838576193</v>
+      </c>
+      <c r="F171" t="n">
+        <v>40</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>11.22</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>7c47f404-e7cb-46fc-8c57-ba782eb2e2af</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>9e06385a-f656-4542-b297-5749accc7c5b</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>46090.06505243176</v>
+      </c>
+      <c r="F172" t="n">
+        <v>46</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>7260c26e-cdbe-460d-9725-cd01a8617917</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>a8f1040b-bd71-4232-a82a-a910e6f46fb1</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>46074.35671910786</v>
+      </c>
+      <c r="F173" t="n">
+        <v>240</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>87fb7728-b960-4908-9341-5ed5f6e40918</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>b44fd318-ecea-4db1-bcaf-c7074c05f8b2</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>46084.23171911103</v>
+      </c>
+      <c r="F174" t="n">
+        <v>221</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>bd08d848-b018-4ced-b198-ddd63b6dcda1</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>36ddfe12-97af-433e-bb20-b2fe3c5885be</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>46066.39838579338</v>
+      </c>
+      <c r="F175" t="n">
+        <v>47</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>14.85</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>c987e7c0-0072-4fdd-b491-dd2cefe70db9</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>27304dc4-dc4e-4539-ad43-13ee96709f8b</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>46077.35671913916</v>
+      </c>
+      <c r="F176" t="n">
+        <v>189</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>8.42</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>749b79a3-9f54-42b8-b31f-c8d4e451cac0</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>87518ee2-b37f-48f3-bab0-2420c04b6b36</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>46084.39838581526</v>
+      </c>
+      <c r="F177" t="n">
+        <v>152</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>13.22</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>41d02348-53dd-4d7d-8335-2528cf12bcac</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>f45c9888-04fb-4a5d-89d3-070ce7ebcecc</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>46072.77338581848</v>
+      </c>
+      <c r="F178" t="n">
+        <v>35</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>f46d5c81-97e2-4691-8a0e-737672ee790c</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>c498f12b-9a2b-492c-8296-29b615421b18</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>46080.14838582161</v>
+      </c>
+      <c r="F179" t="n">
+        <v>102</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>bf0259d7-1bf3-417d-8d0f-ff61e9d48e6c</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7821e200-9344-4098-af41-c456c462f265</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>46077.10671915815</v>
+      </c>
+      <c r="F180" t="n">
+        <v>113</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>9d4dc752-9850-4ae6-8bf0-49d7feb6df63</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2d46177d-ac4c-4930-901e-fc698dfcf385</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>46080.35671916145</v>
+      </c>
+      <c r="F181" t="n">
+        <v>110</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>d3a6b84d-1ebe-4f7c-a992-8323abcb7652</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>b74ca62a-d30c-46b9-a88f-4a58427a9e6c</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>46065.19005250104</v>
+      </c>
+      <c r="F182" t="n">
+        <v>66</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>18.02</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>7778793b-f054-490a-be7f-cf5dc2cbdc28</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>a9d01b06-4fc2-4da1-b755-68cdc43cbfc2</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>46067.60671918935</v>
+      </c>
+      <c r="F183" t="n">
+        <v>214</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>13.97</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>e04f44ea-f70a-4828-a421-5c8b1bd0d828</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>b6acad2a-5b72-4b38-bd94-95218720fde8</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>46080.1483858592</v>
+      </c>
+      <c r="F184" t="n">
+        <v>208</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>8f1b185a-2cd8-4dde-8399-fee1e8617f59</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>77454a4c-3366-4b65-8114-cf6871f21ec9</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>46066.6483858655</v>
+      </c>
+      <c r="F185" t="n">
+        <v>210</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>9016d6a2-5cef-4e3a-a66c-708e74ec96a6</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>bd8d4e2a-f6c2-4187-8285-d2c71638245e</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>46082.19005253832</v>
+      </c>
+      <c r="F186" t="n">
+        <v>130</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>75af3630-87b6-4121-93f9-78474e8e6e76</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>009b5c08-5e9f-43a7-ac6c-b4b2d31a8dee</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>46068.77338587499</v>
+      </c>
+      <c r="F187" t="n">
+        <v>251</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10fa5469-3b8a-48d9-ba6b-8b3fcb737458</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>e0a98efa-a510-463f-8647-0430e0b60eb8</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>46076.60671922395</v>
+      </c>
+      <c r="F188" t="n">
+        <v>78</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>af022f39-a3af-47b5-99cd-a18e24c0f0ef</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>17e6e957-e771-4d82-8df9-9cd752d90ece</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>46085.44005257269</v>
+      </c>
+      <c r="F189" t="n">
+        <v>168</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>f107d9ff-3f34-44c4-8bd3-40ffc029e98e</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>b36cf1b7-72e1-446f-84b0-fc956068adc7</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>46080.89838591542</v>
+      </c>
+      <c r="F190" t="n">
+        <v>241</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>15.75</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46087.6483843597</v>
+        <v>46087.64838436343</v>
       </c>
       <c r="F2" t="n">
         <v>292</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46073.56505105895</v>
+        <v>46073.56505105324</v>
       </c>
       <c r="F3" t="n">
         <v>145</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46075.52338439552</v>
+        <v>46075.52338439815</v>
       </c>
       <c r="F4" t="n">
         <v>112</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46068.52338439874</v>
+        <v>46068.52338439815</v>
       </c>
       <c r="F5" t="n">
         <v>132</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46070.31505107182</v>
+        <v>46070.31505107639</v>
       </c>
       <c r="F6" t="n">
         <v>181</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46068.27338443044</v>
+        <v>46068.27338443287</v>
       </c>
       <c r="F7" t="n">
         <v>161</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46064.48171777</v>
+        <v>46064.4817177662</v>
       </c>
       <c r="F8" t="n">
         <v>198</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46085.14838444308</v>
+        <v>46085.14838444444</v>
       </c>
       <c r="F9" t="n">
         <v>244</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46063.23171777962</v>
+        <v>46063.23171777778</v>
       </c>
       <c r="F10" t="n">
         <v>269</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46064.35671779846</v>
+        <v>46064.35671780093</v>
       </c>
       <c r="F11" t="n">
         <v>186</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46068.14838447125</v>
+        <v>46068.14838446759</v>
       </c>
       <c r="F12" t="n">
         <v>92</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46086.02338448114</v>
+        <v>46086.02338447917</v>
       </c>
       <c r="F13" t="n">
         <v>213</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46072.60671782083</v>
+        <v>46072.60671782408</v>
       </c>
       <c r="F14" t="n">
         <v>290</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46077.52338449075</v>
+        <v>46077.52338449074</v>
       </c>
       <c r="F15" t="n">
         <v>71</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46070.23171782727</v>
+        <v>46070.23171782408</v>
       </c>
       <c r="F16" t="n">
         <v>33</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46078.48171784603</v>
+        <v>46078.48171784722</v>
       </c>
       <c r="F17" t="n">
         <v>234</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46088.44005118249</v>
+        <v>46088.44005118056</v>
       </c>
       <c r="F18" t="n">
         <v>61</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46082.35671785609</v>
+        <v>46082.3567178588</v>
       </c>
       <c r="F19" t="n">
         <v>172</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46067.52338452591</v>
+        <v>46067.52338452546</v>
       </c>
       <c r="F20" t="n">
         <v>99</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46078.81505123975</v>
+        <v>46078.81505123842</v>
       </c>
       <c r="F21" t="n">
         <v>269</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46062.23171791186</v>
+        <v>46062.23171791666</v>
       </c>
       <c r="F22" t="n">
         <v>48</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46085.77338458481</v>
+        <v>46085.77338458334</v>
       </c>
       <c r="F23" t="n">
         <v>159</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46063.94005126404</v>
+        <v>46063.94005126158</v>
       </c>
       <c r="F24" t="n">
         <v>126</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46087.35671794019</v>
+        <v>46087.35671793982</v>
       </c>
       <c r="F25" t="n">
         <v>76</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46078.81505128603</v>
+        <v>46078.81505128472</v>
       </c>
       <c r="F26" t="n">
         <v>215</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46068.14838462568</v>
+        <v>46068.14838462963</v>
       </c>
       <c r="F27" t="n">
         <v>244</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>46074.48171796523</v>
+        <v>46074.48171796296</v>
       </c>
       <c r="F28" t="n">
         <v>89</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46068.94005130191</v>
+        <v>46068.9400512963</v>
       </c>
       <c r="F29" t="n">
         <v>228</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>46078.3567179717</v>
+        <v>46078.35671797454</v>
       </c>
       <c r="F30" t="n">
         <v>121</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>46075.02338464774</v>
+        <v>46075.02338465278</v>
       </c>
       <c r="F31" t="n">
         <v>250</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>46062.06505131771</v>
+        <v>46062.06505131944</v>
       </c>
       <c r="F32" t="n">
         <v>35</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46069.1900513239</v>
+        <v>46069.19005131944</v>
       </c>
       <c r="F33" t="n">
         <v>140</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46064.23171799703</v>
+        <v>46064.23171799768</v>
       </c>
       <c r="F34" t="n">
         <v>79</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>46083.56505133984</v>
+        <v>46083.56505134259</v>
       </c>
       <c r="F35" t="n">
         <v>115</v>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46068.23171801262</v>
+        <v>46068.23171800926</v>
       </c>
       <c r="F36" t="n">
         <v>208</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46073.19005134939</v>
+        <v>46073.19005135417</v>
       </c>
       <c r="F37" t="n">
         <v>54</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>46087.85671801919</v>
+        <v>46087.85671802083</v>
       </c>
       <c r="F38" t="n">
         <v>66</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>46064.85671802853</v>
+        <v>46064.85671803241</v>
       </c>
       <c r="F39" t="n">
         <v>112</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46069.94005136505</v>
+        <v>46069.94005136574</v>
       </c>
       <c r="F40" t="n">
         <v>296</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46066.31505138066</v>
+        <v>46066.31505137731</v>
       </c>
       <c r="F41" t="n">
         <v>207</v>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>46068.8983847297</v>
+        <v>46068.89838473379</v>
       </c>
       <c r="F42" t="n">
         <v>294</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>46078.89838474819</v>
+        <v>46078.89838474537</v>
       </c>
       <c r="F43" t="n">
         <v>51</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46078.89838475458</v>
+        <v>46078.89838475695</v>
       </c>
       <c r="F44" t="n">
         <v>33</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>46081.14838476406</v>
+        <v>46081.14838476852</v>
       </c>
       <c r="F45" t="n">
         <v>158</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>46073.81505147116</v>
+        <v>46073.81505146991</v>
       </c>
       <c r="F46" t="n">
         <v>193</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>46063.52338481087</v>
+        <v>46063.52338481481</v>
       </c>
       <c r="F47" t="n">
         <v>142</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>46089.523384817</v>
+        <v>46089.52338481481</v>
       </c>
       <c r="F48" t="n">
         <v>144</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>46088.35671815382</v>
+        <v>46088.35671814815</v>
       </c>
       <c r="F49" t="n">
         <v>283</v>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46091.39838482362</v>
+        <v>46091.39838482639</v>
       </c>
       <c r="F50" t="n">
         <v>65</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>46084.06505149352</v>
+        <v>46084.06505149305</v>
       </c>
       <c r="F51" t="n">
         <v>218</v>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>46086.10671816648</v>
+        <v>46086.10671817129</v>
       </c>
       <c r="F52" t="n">
         <v>193</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>46079.31505150304</v>
+        <v>46079.31505150463</v>
       </c>
       <c r="F53" t="n">
         <v>201</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46088.60671818924</v>
+        <v>46088.60671819445</v>
       </c>
       <c r="F54" t="n">
         <v>42</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46080.48171819547</v>
+        <v>46080.48171819445</v>
       </c>
       <c r="F55" t="n">
         <v>231</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>46089.27338486532</v>
+        <v>46089.27338486111</v>
       </c>
       <c r="F56" t="n">
         <v>124</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46073.98171822666</v>
+        <v>46073.98171822917</v>
       </c>
       <c r="F57" t="n">
         <v>72</v>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>46062.77338490276</v>
+        <v>46062.77338490741</v>
       </c>
       <c r="F58" t="n">
         <v>250</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46072.44005157263</v>
+        <v>46072.44005157407</v>
       </c>
       <c r="F59" t="n">
         <v>241</v>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46083.52338490923</v>
+        <v>46083.52338490741</v>
       </c>
       <c r="F60" t="n">
         <v>174</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46075.19005157926</v>
+        <v>46075.19005157407</v>
       </c>
       <c r="F61" t="n">
         <v>165</v>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46087.27338491873</v>
+        <v>46087.27338491898</v>
       </c>
       <c r="F62" t="n">
         <v>246</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46082.64838493785</v>
+        <v>46082.64838494213</v>
       </c>
       <c r="F63" t="n">
         <v>218</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>46069.31505160772</v>
+        <v>46069.3150516088</v>
       </c>
       <c r="F64" t="n">
         <v>190</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46082.27338494424</v>
+        <v>46082.27338494213</v>
       </c>
       <c r="F65" t="n">
         <v>89</v>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>46081.19005161731</v>
+        <v>46081.19005162037</v>
       </c>
       <c r="F66" t="n">
         <v>264</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>46064.44005162052</v>
+        <v>46064.44005162037</v>
       </c>
       <c r="F67" t="n">
         <v>258</v>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>46067.60671829034</v>
+        <v>46067.60671828704</v>
       </c>
       <c r="F68" t="n">
         <v>226</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46086.27338496036</v>
+        <v>46086.27338496528</v>
       </c>
       <c r="F69" t="n">
         <v>136</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>46072.14838496348</v>
+        <v>46072.14838496528</v>
       </c>
       <c r="F70" t="n">
         <v>84</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46080.44005163966</v>
+        <v>46080.44005164352</v>
       </c>
       <c r="F71" t="n">
         <v>153</v>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46089.64838497622</v>
+        <v>46089.64838497685</v>
       </c>
       <c r="F72" t="n">
         <v>68</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>46065.23171831271</v>
+        <v>46065.23171831018</v>
       </c>
       <c r="F73" t="n">
         <v>203</v>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>46084.89838498276</v>
+        <v>46084.89838498842</v>
       </c>
       <c r="F74" t="n">
         <v>239</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>46080.98171831928</v>
+        <v>46080.98171832176</v>
       </c>
       <c r="F75" t="n">
         <v>229</v>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>46079.27338498909</v>
+        <v>46079.27338498842</v>
       </c>
       <c r="F76" t="n">
         <v>150</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46069.27338499543</v>
+        <v>46069.273385</v>
       </c>
       <c r="F77" t="n">
         <v>268</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46082.60671833823</v>
+        <v>46082.60671833334</v>
       </c>
       <c r="F78" t="n">
         <v>244</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>46085.14838501107</v>
+        <v>46085.14838501158</v>
       </c>
       <c r="F79" t="n">
         <v>152</v>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>46083.60671835078</v>
+        <v>46083.60671835648</v>
       </c>
       <c r="F80" t="n">
         <v>70</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>46072.48171835397</v>
+        <v>46072.48171835648</v>
       </c>
       <c r="F81" t="n">
         <v>289</v>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>46072.10671835713</v>
+        <v>46072.10671835648</v>
       </c>
       <c r="F82" t="n">
         <v>133</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>46084.14838502691</v>
+        <v>46084.14838502315</v>
       </c>
       <c r="F83" t="n">
         <v>49</v>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>46060.56505170627</v>
+        <v>46060.56505170139</v>
       </c>
       <c r="F84" t="n">
         <v>157</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>46069.98171838226</v>
+        <v>46069.98171837963</v>
       </c>
       <c r="F85" t="n">
         <v>296</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>46077.27338506135</v>
+        <v>46077.27338505787</v>
       </c>
       <c r="F86" t="n">
         <v>218</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46077.10671839801</v>
+        <v>46077.10671840278</v>
       </c>
       <c r="F87" t="n">
         <v>83</v>
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>46079.81505173459</v>
+        <v>46079.81505173611</v>
       </c>
       <c r="F88" t="n">
         <v>296</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>46072.35671840439</v>
+        <v>46072.35671840278</v>
       </c>
       <c r="F89" t="n">
         <v>152</v>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>46064.69005175013</v>
+        <v>46064.69005174768</v>
       </c>
       <c r="F90" t="n">
         <v>263</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>46082.8983850868</v>
+        <v>46082.89838508102</v>
       </c>
       <c r="F91" t="n">
         <v>42</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>46074.56505175973</v>
+        <v>46074.56505175926</v>
       </c>
       <c r="F92" t="n">
         <v>117</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>46068.94005177523</v>
+        <v>46068.94005177083</v>
       </c>
       <c r="F93" t="n">
         <v>131</v>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>46080.52338511192</v>
+        <v>46080.52338511574</v>
       </c>
       <c r="F94" t="n">
         <v>150</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>46066.73171845142</v>
+        <v>46066.73171844907</v>
       </c>
       <c r="F95" t="n">
         <v>39</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>46064.02338513682</v>
+        <v>46064.02338513889</v>
       </c>
       <c r="F96" t="n">
         <v>212</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>46078.5233851523</v>
+        <v>46078.52338515046</v>
       </c>
       <c r="F97" t="n">
         <v>185</v>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>46072.48171850132</v>
+        <v>46072.48171850695</v>
       </c>
       <c r="F98" t="n">
         <v>249</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>46072.35671850449</v>
+        <v>46072.35671850695</v>
       </c>
       <c r="F99" t="n">
         <v>182</v>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>46066.73171850768</v>
+        <v>46066.73171850695</v>
       </c>
       <c r="F100" t="n">
         <v>135</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46066.31505184413</v>
+        <v>46066.31505184028</v>
       </c>
       <c r="F101" t="n">
         <v>94</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>46067.73171851841</v>
+        <v>46067.73171851852</v>
       </c>
       <c r="F102" t="n">
         <v>36</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>46085.60671852549</v>
+        <v>46085.60671853009</v>
       </c>
       <c r="F103" t="n">
         <v>145</v>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>46068.89838520788</v>
+        <v>46068.89838520833</v>
       </c>
       <c r="F104" t="n">
         <v>168</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>46070.02338521754</v>
+        <v>46070.02338521991</v>
       </c>
       <c r="F105" t="n">
         <v>241</v>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46075.10671855711</v>
+        <v>46075.10671855324</v>
       </c>
       <c r="F106" t="n">
         <v>277</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>46084.06505189384</v>
+        <v>46084.06505189815</v>
       </c>
       <c r="F107" t="n">
         <v>62</v>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>46085.10671856373</v>
+        <v>46085.10671856481</v>
       </c>
       <c r="F108" t="n">
         <v>278</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46062.06505190658</v>
+        <v>46062.06505190973</v>
       </c>
       <c r="F109" t="n">
         <v>142</v>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>46061.64838525849</v>
+        <v>46061.64838525463</v>
       </c>
       <c r="F110" t="n">
         <v>50</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>46069.1067186229</v>
+        <v>46069.10671862269</v>
       </c>
       <c r="F111" t="n">
         <v>87</v>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>46083.27338529602</v>
+        <v>46083.27338530093</v>
       </c>
       <c r="F112" t="n">
         <v>82</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>46067.85671863264</v>
+        <v>46067.85671863426</v>
       </c>
       <c r="F113" t="n">
         <v>132</v>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>46078.52338530245</v>
+        <v>46078.52338530093</v>
       </c>
       <c r="F114" t="n">
         <v>152</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>46074.27338530582</v>
+        <v>46074.27338530093</v>
       </c>
       <c r="F115" t="n">
         <v>186</v>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>46078.5650519757</v>
+        <v>46078.56505197917</v>
       </c>
       <c r="F116" t="n">
         <v>150</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>46082.69005198522</v>
+        <v>46082.69005199074</v>
       </c>
       <c r="F117" t="n">
         <v>201</v>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>46067.89838532171</v>
+        <v>46067.89838532407</v>
       </c>
       <c r="F118" t="n">
         <v>288</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>46068.64838532791</v>
+        <v>46068.64838532407</v>
       </c>
       <c r="F119" t="n">
         <v>298</v>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>46072.73171866765</v>
+        <v>46072.73171866898</v>
       </c>
       <c r="F120" t="n">
         <v>103</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>46060.69005201053</v>
+        <v>46060.69005201389</v>
       </c>
       <c r="F121" t="n">
         <v>241</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>46086.60671868041</v>
+        <v>46086.60671868055</v>
       </c>
       <c r="F122" t="n">
         <v>105</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>46069.23171868356</v>
+        <v>46069.23171868055</v>
       </c>
       <c r="F123" t="n">
         <v>124</v>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>46087.23171868692</v>
+        <v>46087.23171869213</v>
       </c>
       <c r="F124" t="n">
         <v>223</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>46066.64838537537</v>
+        <v>46066.64838537037</v>
       </c>
       <c r="F125" t="n">
         <v>42</v>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>46079.73171871188</v>
+        <v>46079.73171871528</v>
       </c>
       <c r="F126" t="n">
         <v>249</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>46087.1483853817</v>
+        <v>46087.14838538194</v>
       </c>
       <c r="F127" t="n">
         <v>232</v>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>46080.35671872141</v>
+        <v>46080.35671872685</v>
       </c>
       <c r="F128" t="n">
         <v>82</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>46090.8983853973</v>
+        <v>46090.89838539352</v>
       </c>
       <c r="F129" t="n">
         <v>61</v>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>46074.98171874005</v>
+        <v>46074.98171873843</v>
       </c>
       <c r="F130" t="n">
         <v>139</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>46078.64838541315</v>
+        <v>46078.64838541667</v>
       </c>
       <c r="F131" t="n">
         <v>180</v>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>46066.69005208611</v>
+        <v>46066.69005208334</v>
       </c>
       <c r="F132" t="n">
         <v>94</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>46081.14838542897</v>
+        <v>46081.14838542824</v>
       </c>
       <c r="F133" t="n">
         <v>104</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>46069.64838543216</v>
+        <v>46069.64838542824</v>
       </c>
       <c r="F134" t="n">
         <v>289</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>46071.94005210822</v>
+        <v>46071.94005210648</v>
       </c>
       <c r="F135" t="n">
         <v>171</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>46061.10671878435</v>
+        <v>46061.10671878472</v>
       </c>
       <c r="F136" t="n">
         <v>81</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>46076.06505212568</v>
+        <v>46076.06505212963</v>
       </c>
       <c r="F137" t="n">
         <v>128</v>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>46064.10671879861</v>
+        <v>46064.1067187963</v>
       </c>
       <c r="F138" t="n">
         <v>141</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>46078.35671880809</v>
+        <v>46078.35671880787</v>
       </c>
       <c r="F139" t="n">
         <v>237</v>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>46072.85671881452</v>
+        <v>46072.85671881944</v>
       </c>
       <c r="F140" t="n">
         <v>77</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>46079.39838548433</v>
+        <v>46079.39838548611</v>
       </c>
       <c r="F141" t="n">
         <v>207</v>
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>46063.5650521542</v>
+        <v>46063.56505215278</v>
       </c>
       <c r="F142" t="n">
         <v>289</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>46078.27338550008</v>
+        <v>46078.27338549768</v>
       </c>
       <c r="F143" t="n">
         <v>187</v>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>46081.31505217918</v>
+        <v>46081.31505217592</v>
       </c>
       <c r="F144" t="n">
         <v>58</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>46091.23171887387</v>
+        <v>46091.23171887732</v>
       </c>
       <c r="F145" t="n">
         <v>232</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>46078.6067188801</v>
+        <v>46078.60671887732</v>
       </c>
       <c r="F146" t="n">
         <v>289</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>46067.56505222286</v>
+        <v>46067.56505222222</v>
       </c>
       <c r="F147" t="n">
         <v>203</v>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>46068.35671889274</v>
+        <v>46068.35671888889</v>
       </c>
       <c r="F148" t="n">
         <v>224</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>46077.19005224487</v>
+        <v>46077.19005224537</v>
       </c>
       <c r="F149" t="n">
         <v>284</v>
@@ -6569,7 +6569,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>46075.06505226042</v>
+        <v>46075.06505225694</v>
       </c>
       <c r="F150" t="n">
         <v>224</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>46063.52338560009</v>
+        <v>46063.52338560185</v>
       </c>
       <c r="F151" t="n">
         <v>195</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>46064.60671894284</v>
+        <v>46064.60671894676</v>
       </c>
       <c r="F152" t="n">
         <v>90</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>46086.690052301</v>
+        <v>46086.69005230324</v>
       </c>
       <c r="F153" t="n">
         <v>249</v>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>46061.7317189708</v>
+        <v>46061.73171896991</v>
       </c>
       <c r="F154" t="n">
         <v>47</v>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>46086.23171897721</v>
+        <v>46086.23171898148</v>
       </c>
       <c r="F155" t="n">
         <v>200</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>46080.60671899274</v>
+        <v>46080.60671899305</v>
       </c>
       <c r="F156" t="n">
         <v>90</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>46064.06505233551</v>
+        <v>46064.06505233797</v>
       </c>
       <c r="F157" t="n">
         <v>151</v>
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>46089.94005233864</v>
+        <v>46089.94005233797</v>
       </c>
       <c r="F158" t="n">
         <v>153</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>46064.56505234868</v>
+        <v>46064.56505234954</v>
       </c>
       <c r="F159" t="n">
         <v>249</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>46069.44005235183</v>
+        <v>46069.44005234954</v>
       </c>
       <c r="F160" t="n">
         <v>118</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>46077.56505235528</v>
+        <v>46077.56505234954</v>
       </c>
       <c r="F161" t="n">
         <v>242</v>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>46081.0650523615</v>
+        <v>46081.06505236111</v>
       </c>
       <c r="F162" t="n">
         <v>123</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>46082.64838570207</v>
+        <v>46082.64838570602</v>
       </c>
       <c r="F163" t="n">
         <v>166</v>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>46088.77338571779</v>
+        <v>46088.77338571759</v>
       </c>
       <c r="F164" t="n">
         <v>50</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>46076.85671905747</v>
+        <v>46076.8567190625</v>
       </c>
       <c r="F165" t="n">
         <v>95</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>46080.35671906667</v>
+        <v>46080.3567190625</v>
       </c>
       <c r="F166" t="n">
         <v>98</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>46071.69005240937</v>
+        <v>46071.69005240741</v>
       </c>
       <c r="F167" t="n">
         <v>66</v>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>46063.73171907934</v>
+        <v>46063.73171907407</v>
       </c>
       <c r="F168" t="n">
         <v>267</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>46088.81505241595</v>
+        <v>46088.81505241898</v>
       </c>
       <c r="F169" t="n">
         <v>66</v>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>46074.52338575873</v>
+        <v>46074.52338576389</v>
       </c>
       <c r="F170" t="n">
         <v>84</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>46075.64838576193</v>
+        <v>46075.64838576389</v>
       </c>
       <c r="F171" t="n">
         <v>40</v>
@@ -7471,7 +7471,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>46090.06505243176</v>
+        <v>46090.06505243055</v>
       </c>
       <c r="F172" t="n">
         <v>46</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>46074.35671910786</v>
+        <v>46074.35671910879</v>
       </c>
       <c r="F173" t="n">
         <v>240</v>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>46084.23171911103</v>
+        <v>46084.23171910879</v>
       </c>
       <c r="F174" t="n">
         <v>221</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>46066.39838579338</v>
+        <v>46066.39838579861</v>
       </c>
       <c r="F175" t="n">
         <v>47</v>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>46077.35671913916</v>
+        <v>46077.35671914352</v>
       </c>
       <c r="F176" t="n">
         <v>189</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>46084.39838581526</v>
+        <v>46084.39838581019</v>
       </c>
       <c r="F177" t="n">
         <v>152</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>46072.77338581848</v>
+        <v>46072.77338582176</v>
       </c>
       <c r="F178" t="n">
         <v>35</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>46080.14838582161</v>
+        <v>46080.14838582176</v>
       </c>
       <c r="F179" t="n">
         <v>102</v>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>46077.10671915815</v>
+        <v>46077.10671915509</v>
       </c>
       <c r="F180" t="n">
         <v>113</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>46080.35671916145</v>
+        <v>46080.35671916667</v>
       </c>
       <c r="F181" t="n">
         <v>110</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>46065.19005250104</v>
+        <v>46065.1900525</v>
       </c>
       <c r="F182" t="n">
         <v>66</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>46067.60671918935</v>
+        <v>46067.60671918982</v>
       </c>
       <c r="F183" t="n">
         <v>214</v>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>46080.1483858592</v>
+        <v>46080.14838585648</v>
       </c>
       <c r="F184" t="n">
         <v>208</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>46066.6483858655</v>
+        <v>46066.64838586806</v>
       </c>
       <c r="F185" t="n">
         <v>210</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>46082.19005253832</v>
+        <v>46082.19005253472</v>
       </c>
       <c r="F186" t="n">
         <v>130</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>46068.77338587499</v>
+        <v>46068.77338587963</v>
       </c>
       <c r="F187" t="n">
         <v>251</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>46076.60671922395</v>
+        <v>46076.60671922454</v>
       </c>
       <c r="F188" t="n">
         <v>78</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>46085.44005257269</v>
+        <v>46085.44005256944</v>
       </c>
       <c r="F189" t="n">
         <v>168</v>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>46080.89838591542</v>
+        <v>46080.89838591436</v>
       </c>
       <c r="F190" t="n">
         <v>241</v>
@@ -8226,6 +8226,744 @@
       </c>
       <c r="I190" t="n">
         <v>15.75</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>9dc25528-624f-4361-9a92-e3cbc79d2a2d</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>536c7b76-0b35-47fe-8090-e94300839e5d</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>46065.70604380868</v>
+      </c>
+      <c r="F191" t="n">
+        <v>60</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>11.77</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>d45bc1fd-a164-4532-a898-3ba31163ff63</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>47faa697-70a8-413d-abe3-16d329f90f21</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46061.83104381838</v>
+      </c>
+      <c r="F192" t="n">
+        <v>133</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>d0a4e160-6b71-47d6-b046-755301c2f8f4</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>61cf9ef7-621e-42d9-8fd9-dcfdf569ac33</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>46061.66437715817</v>
+      </c>
+      <c r="F193" t="n">
+        <v>101</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>17.41</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>f7f15424-11a3-4a4a-9362-16917b6739a0</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>aebbfc87-2e57-4bd8-8b84-8d979a122de3</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>46088.53937716169</v>
+      </c>
+      <c r="F194" t="n">
+        <v>54</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>386b3346-92e6-4128-a923-96688425e158</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>e342557d-a276-4f10-955b-ec102abce62b</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>46086.58104383809</v>
+      </c>
+      <c r="F195" t="n">
+        <v>192</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>13.55</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>e71f5670-8a0d-428b-b1ac-86a393526540</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>45edb267-a2bd-4af4-998f-c10c8084c51d</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>46068.58104384135</v>
+      </c>
+      <c r="F196" t="n">
+        <v>99</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>3a6d9f5f-8601-42a4-954c-661b0069c33c</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2bd70b43-a67f-4fb4-9462-f7266685bf22</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>46089.49771051119</v>
+      </c>
+      <c r="F197" t="n">
+        <v>216</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>27ea7c50-b2a9-46fc-9dfe-91614cefa114</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>f98000d5-f06a-4f64-b173-0a4e45a69242</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>46073.24771053942</v>
+      </c>
+      <c r="F198" t="n">
+        <v>129</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>8d1a3941-879b-4210-a645-8c853466d791</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>526c8661-27be-4a19-9b0d-f1806a1b4929</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>46090.45604387895</v>
+      </c>
+      <c r="F199" t="n">
+        <v>294</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>16.46</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>e8226ad4-da99-454e-b7b2-7b01e9b8fbcd</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>7bb684f9-d4e1-4d65-8b5b-fd5a72597f68</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>46086.03937721553</v>
+      </c>
+      <c r="F200" t="n">
+        <v>198</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>bc9d2985-bae0-4fb9-8747-336a4dcc5bc7</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>53748711-6386-4b79-a899-33fb7f1790d6</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>46085.74771055547</v>
+      </c>
+      <c r="F201" t="n">
+        <v>74</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>5409ad2a-1d75-48a9-be14-550194cdfdae</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>c8bfd8e2-fc2d-4a1d-88dd-6385d1e56223</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>46063.33104389194</v>
+      </c>
+      <c r="F202" t="n">
+        <v>239</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>13.71</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>a5d471b4-7d03-415e-bf80-4d4e777d24e8</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>9774cb84-086c-40db-865b-c976b64475a2</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>46072.03937724121</v>
+      </c>
+      <c r="F203" t="n">
+        <v>39</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>64239140-5e0e-4740-995e-209e05beaf5b</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>908ff0e0-f310-40fe-8b84-bcb2d57ad229</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>46070.58104391713</v>
+      </c>
+      <c r="F204" t="n">
+        <v>278</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ab49222d-6274-4af8-b6f5-bc939eb13247</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>135ff89b-d2fc-4935-9b2e-93553ce79319</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>46061.49771058725</v>
+      </c>
+      <c r="F205" t="n">
+        <v>129</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>14.57</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>947b0298-d244-4d5d-98a6-1c36836a4189</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>8a90a5d8-615a-414d-b948-ef092bb3d01f</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>46073.03937726333</v>
+      </c>
+      <c r="F206" t="n">
+        <v>141</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>89986222-cbf4-4c51-a234-7b3517aa41be</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>01e09385-4abb-4812-b1ea-404f354439d1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>46073.58104394564</v>
+      </c>
+      <c r="F207" t="n">
+        <v>38</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>15.79</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>5ac7af37-a39e-4457-ac90-50c775129ccb</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>e79ed416-2b36-485d-b7a8-c2747f1b5ebb</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>46062.28937729153</v>
+      </c>
+      <c r="F208" t="n">
+        <v>90</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I208"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>46065.70604380868</v>
+        <v>46065.70604380787</v>
       </c>
       <c r="F191" t="n">
         <v>60</v>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>46061.83104381838</v>
+        <v>46061.83104381945</v>
       </c>
       <c r="F192" t="n">
         <v>133</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>46061.66437715817</v>
+        <v>46061.66437715277</v>
       </c>
       <c r="F193" t="n">
         <v>101</v>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>46088.53937716169</v>
+        <v>46088.53937716435</v>
       </c>
       <c r="F194" t="n">
         <v>54</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>46086.58104383809</v>
+        <v>46086.58104384259</v>
       </c>
       <c r="F195" t="n">
         <v>192</v>
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>46068.58104384135</v>
+        <v>46068.58104384259</v>
       </c>
       <c r="F196" t="n">
         <v>99</v>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>46089.49771051119</v>
+        <v>46089.49771050926</v>
       </c>
       <c r="F197" t="n">
         <v>216</v>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>46073.24771053942</v>
+        <v>46073.24771054398</v>
       </c>
       <c r="F198" t="n">
         <v>129</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>46090.45604387895</v>
+        <v>46090.45604387731</v>
       </c>
       <c r="F199" t="n">
         <v>294</v>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>46086.03937721553</v>
+        <v>46086.03937721065</v>
       </c>
       <c r="F200" t="n">
         <v>198</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>46085.74771055547</v>
+        <v>46085.74771055556</v>
       </c>
       <c r="F201" t="n">
         <v>74</v>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>46063.33104389194</v>
+        <v>46063.33104388889</v>
       </c>
       <c r="F202" t="n">
         <v>239</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>46072.03937724121</v>
+        <v>46072.03937724537</v>
       </c>
       <c r="F203" t="n">
         <v>39</v>
@@ -8783,7 +8783,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>46070.58104391713</v>
+        <v>46070.58104391204</v>
       </c>
       <c r="F204" t="n">
         <v>278</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>46061.49771058725</v>
+        <v>46061.49771059028</v>
       </c>
       <c r="F205" t="n">
         <v>129</v>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>46073.03937726333</v>
+        <v>46073.03937726852</v>
       </c>
       <c r="F206" t="n">
         <v>141</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>46073.58104394564</v>
+        <v>46073.58104394676</v>
       </c>
       <c r="F207" t="n">
         <v>38</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>46062.28937729153</v>
+        <v>46062.28937729167</v>
       </c>
       <c r="F208" t="n">
         <v>90</v>
@@ -8964,6 +8964,785 @@
       </c>
       <c r="I208" t="n">
         <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>f83b6a37-539a-4c80-b14f-839c4df166b9</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>857d0806-0f10-4330-b2ed-de37b27b20a9</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>46060.79629734754</v>
+      </c>
+      <c r="F209" t="n">
+        <v>54</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>c5227ade-6075-4dd4-96da-62f52af21b9e</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>6c633a38-fa58-48b4-84a9-cde12968c4af</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>46069.58796402211</v>
+      </c>
+      <c r="F210" t="n">
+        <v>111</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>e7593a55-b3d2-4509-8d9a-f60de52441e7</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>d7f36b98-11ed-4cbb-bb59-667f7df12f6a</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>46071.04629735871</v>
+      </c>
+      <c r="F211" t="n">
+        <v>158</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>8.109999999999999</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>a2e26e14-a534-47de-b602-138fcc903540</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>61360ffd-a88c-4ad0-a464-3a300c2c0aab</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>46071.5046307118</v>
+      </c>
+      <c r="F212" t="n">
+        <v>261</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>b15946df-6dcb-4693-b21f-e3b1dd04737a</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>fa40a6ee-08f8-417d-a633-a760fad3092b</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46089.08796406156</v>
+      </c>
+      <c r="F213" t="n">
+        <v>67</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>19.33</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>385e8ba2-c5e0-4f1b-8511-61df94a9876e</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>050659a0-ca13-4690-bd39-f6d0fe86ccbc</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46061.50463074515</v>
+      </c>
+      <c r="F214" t="n">
+        <v>193</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>3f1b3a5e-bc0b-4602-bdb5-9bc4a6980ff7</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>3decbe6f-feb8-4242-9aac-1efb05f7a6ed</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46073.79629741496</v>
+      </c>
+      <c r="F215" t="n">
+        <v>79</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ab391f76-65b5-4e29-b0a1-f704552b813d</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>cf99d64b-36dd-4621-9f62-d18c7be066c1</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46084.08796408811</v>
+      </c>
+      <c r="F216" t="n">
+        <v>277</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>91d5e785-e5e0-42f9-a730-f91d66db0d95</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>0be1c8d4-3702-47dd-a82d-9014c688e352</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46071.37963076109</v>
+      </c>
+      <c r="F217" t="n">
+        <v>231</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>b7b97caf-0169-4734-80ad-3a30e08a7ebd</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>352bc9c0-e473-4f44-9c4e-34e92f74c107</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46080.67129743101</v>
+      </c>
+      <c r="F218" t="n">
+        <v>66</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>9.220000000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ca615932-7f76-4471-913e-f79a00ce619a</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>c1353d4a-e856-4a88-98f9-f735cab6e869</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46073.83796410132</v>
+      </c>
+      <c r="F219" t="n">
+        <v>297</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>15.61</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>3b3ada51-64e5-4d4b-9f78-7eba5c08b772</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>7a3042fb-ac42-468c-ae74-471addfd3050</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46067.83796411066</v>
+      </c>
+      <c r="F220" t="n">
+        <v>253</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>eb4f8209-ef53-4517-89b4-5e27b8ca378f</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>642f472d-2963-4870-a708-3e6cfe013157</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46078.04629745054</v>
+      </c>
+      <c r="F221" t="n">
+        <v>220</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>10.35</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>3f0d3181-e0f9-4f42-8d2d-05d01b6a30a4</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>3c4bda8b-4d61-470f-81bc-ac3410ffb05a</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46075.50463079038</v>
+      </c>
+      <c r="F222" t="n">
+        <v>150</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>974dd51a-a040-4140-9586-7342ebba60a7</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>4c0c5e7f-1307-49b9-a3fc-37bafcd1ec64</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46072.21296413307</v>
+      </c>
+      <c r="F223" t="n">
+        <v>178</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>314a67fb-22d1-4ea7-943e-d9104e61e40f</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>0d34b840-4a4b-42cc-8f1a-25de96dc0458</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46075.75463080929</v>
+      </c>
+      <c r="F224" t="n">
+        <v>67</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ef970be0-4e5d-40eb-8c2f-21c60e96b8fd</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>669b8b1a-0341-428d-97a3-b4e7169f7cd0</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46081.67129749214</v>
+      </c>
+      <c r="F225" t="n">
+        <v>127</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>bafe496e-c04e-4224-a10a-4357dfca4762</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>7e358781-1a40-4444-a375-286af92691c0</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46090.37963083173</v>
+      </c>
+      <c r="F226" t="n">
+        <v>176</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2dd5f850-b131-4487-b228-67d58fa75ad5</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>0e3b467c-d658-4c4d-ab9b-f395d55ef1f8</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46064.7962975016</v>
+      </c>
+      <c r="F227" t="n">
+        <v>169</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>5.67</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I227"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>46060.79629734754</v>
+        <v>46060.79629734954</v>
       </c>
       <c r="F209" t="n">
         <v>54</v>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>46069.58796402211</v>
+        <v>46069.58796402778</v>
       </c>
       <c r="F210" t="n">
         <v>111</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>46071.04629735871</v>
+        <v>46071.04629736111</v>
       </c>
       <c r="F211" t="n">
         <v>158</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>46071.5046307118</v>
+        <v>46071.50463070602</v>
       </c>
       <c r="F212" t="n">
         <v>261</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>46089.08796406156</v>
+        <v>46089.0879640625</v>
       </c>
       <c r="F213" t="n">
         <v>67</v>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>46061.50463074515</v>
+        <v>46061.50463074074</v>
       </c>
       <c r="F214" t="n">
         <v>193</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>46073.79629741496</v>
+        <v>46073.79629741898</v>
       </c>
       <c r="F215" t="n">
         <v>79</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>46084.08796408811</v>
+        <v>46084.08796408565</v>
       </c>
       <c r="F216" t="n">
         <v>277</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>46071.37963076109</v>
+        <v>46071.37963076389</v>
       </c>
       <c r="F217" t="n">
         <v>231</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>46080.67129743101</v>
+        <v>46080.67129743056</v>
       </c>
       <c r="F218" t="n">
         <v>66</v>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>46073.83796410132</v>
+        <v>46073.83796409722</v>
       </c>
       <c r="F219" t="n">
         <v>297</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>46067.83796411066</v>
+        <v>46067.8379641088</v>
       </c>
       <c r="F220" t="n">
         <v>253</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>46078.04629745054</v>
+        <v>46078.0462974537</v>
       </c>
       <c r="F221" t="n">
         <v>220</v>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>46075.50463079038</v>
+        <v>46075.50463078704</v>
       </c>
       <c r="F222" t="n">
         <v>150</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>46072.21296413307</v>
+        <v>46072.21296413195</v>
       </c>
       <c r="F223" t="n">
         <v>178</v>
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>46075.75463080929</v>
+        <v>46075.75463081019</v>
       </c>
       <c r="F224" t="n">
         <v>67</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>46081.67129749214</v>
+        <v>46081.67129748843</v>
       </c>
       <c r="F225" t="n">
         <v>127</v>
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>46090.37963083173</v>
+        <v>46090.37963083333</v>
       </c>
       <c r="F226" t="n">
         <v>176</v>
@@ -9726,7 +9726,7 @@
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>46064.7962975016</v>
+        <v>46064.7962975</v>
       </c>
       <c r="F227" t="n">
         <v>169</v>
@@ -9743,6 +9743,785 @@
       </c>
       <c r="I227" t="n">
         <v>5.67</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>3a0f3281-e7d2-4a20-b745-0fe3f2974069</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>4c59bf3e-035d-4908-9763-6d5ec796f45c</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>46081.17942066523</v>
+      </c>
+      <c r="F228" t="n">
+        <v>177</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>c0b1ef12-613b-4dff-91cc-7a9682a0b6cc</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>41107f68-3a74-4c9c-823c-daeeca3f891a</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46086.72108734177</v>
+      </c>
+      <c r="F229" t="n">
+        <v>69</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>f43d4b07-28bc-4ae9-8aef-22e5ed55b9a3</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>dcd2491e-29ba-4405-981d-8df9b2ecb71b</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46082.97108735154</v>
+      </c>
+      <c r="F230" t="n">
+        <v>151</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>16.81</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>c887ee80-dcda-4815-ad95-79d2273e1a91</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>9d88e637-9ff3-4fd6-874c-0aba4f9b3275</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>46088.34608736123</v>
+      </c>
+      <c r="F231" t="n">
+        <v>47</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>9.57</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>c08580f9-244a-483d-858d-87d2aead0018</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>4ba1722b-390e-4c3d-9142-1b8f5755a988</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>46071.09608736759</v>
+      </c>
+      <c r="F232" t="n">
+        <v>295</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>22c2df81-694e-42a0-9cdb-b9f69a49c1ce</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ac0483b3-194a-4dfc-8079-85023b436f98</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>46063.01275403745</v>
+      </c>
+      <c r="F233" t="n">
+        <v>150</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>9.039999999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>dd4e971e-60a0-4b8a-ba7a-45f7948fbf0f</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>26af686a-b539-47c3-abb2-f355aecd3e82</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46074.92942073876</v>
+      </c>
+      <c r="F234" t="n">
+        <v>177</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>5f57313d-7c45-4d8e-9730-c0243c2f133f</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>81f276ed-7123-4305-97f9-69112175e560</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46081.92942074213</v>
+      </c>
+      <c r="F235" t="n">
+        <v>289</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>b45938f1-9bd1-4a31-a0ac-1fd4e208bc93</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>97ec28a1-4680-48f2-9f72-04d3b3d0b9fe</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46064.38775408841</v>
+      </c>
+      <c r="F236" t="n">
+        <v>168</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>bb02412f-e50b-4a20-829f-ab3d7518c303</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>523cf0a8-0e7c-4952-afa2-d2314c99fa35</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46077.63775410113</v>
+      </c>
+      <c r="F237" t="n">
+        <v>91</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>18.19</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>98c0ede2-bec2-44b1-8645-3fcccec7fc2d</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>fa700996-3763-4bdc-b464-bee1e3fff5b4</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46083.84608744081</v>
+      </c>
+      <c r="F238" t="n">
+        <v>119</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>04870e31-4c39-43d4-9328-8081b3040ba4</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>22212b79-aa1e-49f8-bac3-84feebe30114</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>46081.34608744404</v>
+      </c>
+      <c r="F239" t="n">
+        <v>169</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>8f65a35e-423f-4e9b-ade4-e0fa02217a2f</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>a648b3b3-ea19-48ff-824d-8c137a79086d</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>46075.13775411386</v>
+      </c>
+      <c r="F240" t="n">
+        <v>283</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>9b9408fe-17f2-4192-8bec-2c04c7cc429b</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>c92240f0-3e68-424c-8f73-01df622bbb1e</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>46088.30442078369</v>
+      </c>
+      <c r="F241" t="n">
+        <v>267</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>9.529999999999999</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>aa5ae033-2cab-4d86-b3f0-5fe0d4db20b9</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>6909372d-c959-4d73-a0aa-7c4129adc2a7</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>46062.97108745373</v>
+      </c>
+      <c r="F242" t="n">
+        <v>42</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>d9d346e6-6943-4f1f-a13d-be96cc9b66d2</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>5fe61a1f-f21e-4469-9717-1f6f45471fb5</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>46060.76275412666</v>
+      </c>
+      <c r="F243" t="n">
+        <v>179</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>16.81</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ede92aaf-327b-472c-9776-bb51ecb262b8</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>bdf75d57-ba5d-4d13-914a-bc8398b6de57</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>46086.38775414233</v>
+      </c>
+      <c r="F244" t="n">
+        <v>269</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>971724a0-09d1-4cbc-aa35-6e7f3dffa521</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>e306753e-620e-4d67-a040-73c65dca1210</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>46075.76275414553</v>
+      </c>
+      <c r="F245" t="n">
+        <v>222</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>e4ff022e-d910-4767-9067-e4e47f9c4a0d</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>0a5e8503-5cd4-4982-86ef-ecd8f50fcd98</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>46078.63775414875</v>
+      </c>
+      <c r="F246" t="n">
+        <v>184</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>3.46</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>46081.17942066523</v>
+        <v>46081.17942065972</v>
       </c>
       <c r="F228" t="n">
         <v>177</v>
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>46086.72108734177</v>
+        <v>46086.72108733797</v>
       </c>
       <c r="F229" t="n">
         <v>69</v>
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>46082.97108735154</v>
+        <v>46082.97108734954</v>
       </c>
       <c r="F230" t="n">
         <v>151</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>46088.34608736123</v>
+        <v>46088.34608736111</v>
       </c>
       <c r="F231" t="n">
         <v>47</v>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>46071.09608736759</v>
+        <v>46071.09608737269</v>
       </c>
       <c r="F232" t="n">
         <v>295</v>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>46063.01275403745</v>
+        <v>46063.01275403935</v>
       </c>
       <c r="F233" t="n">
         <v>150</v>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>46074.92942073876</v>
+        <v>46074.92942074074</v>
       </c>
       <c r="F234" t="n">
         <v>177</v>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>46081.92942074213</v>
+        <v>46081.92942074074</v>
       </c>
       <c r="F235" t="n">
         <v>289</v>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>46064.38775408841</v>
+        <v>46064.38775408565</v>
       </c>
       <c r="F236" t="n">
         <v>168</v>
@@ -10136,7 +10136,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>46077.63775410113</v>
+        <v>46077.63775409722</v>
       </c>
       <c r="F237" t="n">
         <v>91</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>46083.84608744081</v>
+        <v>46083.84608744213</v>
       </c>
       <c r="F238" t="n">
         <v>119</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>46081.34608744404</v>
+        <v>46081.34608744213</v>
       </c>
       <c r="F239" t="n">
         <v>169</v>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>46075.13775411386</v>
+        <v>46075.13775410879</v>
       </c>
       <c r="F240" t="n">
         <v>283</v>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>46088.30442078369</v>
+        <v>46088.30442078703</v>
       </c>
       <c r="F241" t="n">
         <v>267</v>
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>46062.97108745373</v>
+        <v>46062.9710874537</v>
       </c>
       <c r="F242" t="n">
         <v>42</v>
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="E243" s="2" t="n">
-        <v>46060.76275412666</v>
+        <v>46060.76275413195</v>
       </c>
       <c r="F243" t="n">
         <v>179</v>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>46086.38775414233</v>
+        <v>46086.38775414352</v>
       </c>
       <c r="F244" t="n">
         <v>269</v>
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="E245" s="2" t="n">
-        <v>46075.76275414553</v>
+        <v>46075.76275414352</v>
       </c>
       <c r="F245" t="n">
         <v>222</v>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="E246" s="2" t="n">
-        <v>46078.63775414875</v>
+        <v>46078.63775414352</v>
       </c>
       <c r="F246" t="n">
         <v>184</v>
@@ -10522,6 +10522,662 @@
       </c>
       <c r="I246" t="n">
         <v>3.46</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>c1016c68-287d-4f29-bab8-9b76702396c8</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>58eaca07-7f6e-469e-82ee-ef26f1d55147</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>46070.11179397273</v>
+      </c>
+      <c r="F247" t="n">
+        <v>231</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>a4d6c7a1-4702-4a13-b72b-94d0ea7462b4</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>53658452-c234-44ab-96c8-521fb8f20a1f</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>46068.44512732185</v>
+      </c>
+      <c r="F248" t="n">
+        <v>260</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>5beba931-16a4-478d-a646-412538b0417d</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>89f8d0ff-245a-4035-ac17-001d9714ef1f</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>46061.69512733862</v>
+      </c>
+      <c r="F249" t="n">
+        <v>281</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>16.42</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>265d4c54-5aa2-4c01-871c-29e324a2de03</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>6f81e737-1bd6-4d70-95e2-2e2f7a796e33</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>46061.98679401483</v>
+      </c>
+      <c r="F250" t="n">
+        <v>84</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>18.36</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>87718e31-1c34-461e-a337-67116debcd3e</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>31f9bf89-f3bb-468e-b22c-d99c6352888f</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>46089.52846069095</v>
+      </c>
+      <c r="F251" t="n">
+        <v>153</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>9f39e3e5-b8d3-4a80-9091-6da4042bd86c</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ab35d860-c8ba-42ff-b36e-8c5b4712c812</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>46070.19512738294</v>
+      </c>
+      <c r="F252" t="n">
+        <v>53</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>15.01</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>bcfb5f4a-7202-4584-90bb-547e79eb35f4</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>24c1f530-8b3a-4895-a21f-f1baacf639d1</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>46083.90346071951</v>
+      </c>
+      <c r="F253" t="n">
+        <v>181</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>14.44</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>67d70de3-a59c-40df-9532-96edad771a7a</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>722acc51-a7ad-4e31-a890-834bf2b52348</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>46086.65346072913</v>
+      </c>
+      <c r="F254" t="n">
+        <v>106</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I254" t="n">
+        <v>17.62</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ce15928f-2ff3-4814-80d6-aeb3bbef63ed</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>50a27a7b-9ff6-4da6-8ade-41375578fa90</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>46082.19512740537</v>
+      </c>
+      <c r="F255" t="n">
+        <v>158</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2bf890fe-1220-4e41-96db-9d700e30dead</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>4f058fa4-0986-4766-a63e-5854c724ce2e</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>46078.36179407528</v>
+      </c>
+      <c r="F256" t="n">
+        <v>106</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1afe9a98-82e6-4e85-94c3-a0bb4a276f25</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>095b74d7-13d1-432f-ae1f-1210cc566b7d</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>46090.65346074829</v>
+      </c>
+      <c r="F257" t="n">
+        <v>92</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>43ed2aa2-453b-4124-a8b1-4750e8710a8f</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>c2811e74-9dd6-4c43-8775-2445557a6d14</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>46063.27846075143</v>
+      </c>
+      <c r="F258" t="n">
+        <v>264</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>918e676c-79fa-4624-89f3-02165c79f107</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>c90d96ca-e9ab-40ff-b2af-ed3144a590a5</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>46083.5701274408</v>
+      </c>
+      <c r="F259" t="n">
+        <v>141</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>32d33383-7745-4cee-9b5b-4f92d204032c</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>da65f702-8f71-46a3-9eb8-c03e65c831ee</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>46075.94512744399</v>
+      </c>
+      <c r="F260" t="n">
+        <v>34</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>19.29</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>f6e19e27-a831-403a-af6e-600935d746b2</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>e3bf582c-17ef-4b04-8385-194b5152b866</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>46073.07012745036</v>
+      </c>
+      <c r="F261" t="n">
+        <v>116</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>df0a1fff-b508-4b43-8968-8a969fdde98b</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>0e84fbd8-daa6-46f4-b937-24dc76d64f61</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>46079.40346078697</v>
+      </c>
+      <c r="F262" t="n">
+        <v>201</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>15.24</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:I276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10546,7 +10546,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>46070.11179397273</v>
+        <v>46070.11179396991</v>
       </c>
       <c r="F247" t="n">
         <v>231</v>
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>46068.44512732185</v>
+        <v>46068.44512732639</v>
       </c>
       <c r="F248" t="n">
         <v>260</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E249" s="2" t="n">
-        <v>46061.69512733862</v>
+        <v>46061.69512733796</v>
       </c>
       <c r="F249" t="n">
         <v>281</v>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="E250" s="2" t="n">
-        <v>46061.98679401483</v>
+        <v>46061.9867940162</v>
       </c>
       <c r="F250" t="n">
         <v>84</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>46089.52846069095</v>
+        <v>46089.52846069445</v>
       </c>
       <c r="F251" t="n">
         <v>153</v>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="E252" s="2" t="n">
-        <v>46070.19512738294</v>
+        <v>46070.19512738426</v>
       </c>
       <c r="F252" t="n">
         <v>53</v>
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="E253" s="2" t="n">
-        <v>46083.90346071951</v>
+        <v>46083.90346071759</v>
       </c>
       <c r="F253" t="n">
         <v>181</v>
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>46086.65346072913</v>
+        <v>46086.65346072917</v>
       </c>
       <c r="F254" t="n">
         <v>106</v>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="E255" s="2" t="n">
-        <v>46082.19512740537</v>
+        <v>46082.19512740741</v>
       </c>
       <c r="F255" t="n">
         <v>158</v>
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="E256" s="2" t="n">
-        <v>46078.36179407528</v>
+        <v>46078.36179407407</v>
       </c>
       <c r="F256" t="n">
         <v>106</v>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>46090.65346074829</v>
+        <v>46090.65346075231</v>
       </c>
       <c r="F257" t="n">
         <v>92</v>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>46063.27846075143</v>
+        <v>46063.27846075231</v>
       </c>
       <c r="F258" t="n">
         <v>264</v>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>46083.5701274408</v>
+        <v>46083.57012744213</v>
       </c>
       <c r="F259" t="n">
         <v>141</v>
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>46075.94512744399</v>
+        <v>46075.94512744213</v>
       </c>
       <c r="F260" t="n">
         <v>34</v>
@@ -11120,7 +11120,7 @@
         </is>
       </c>
       <c r="E261" s="2" t="n">
-        <v>46073.07012745036</v>
+        <v>46073.07012745371</v>
       </c>
       <c r="F261" t="n">
         <v>116</v>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="E262" s="2" t="n">
-        <v>46079.40346078697</v>
+        <v>46079.40346078703</v>
       </c>
       <c r="F262" t="n">
         <v>201</v>
@@ -11178,6 +11178,580 @@
       </c>
       <c r="I262" t="n">
         <v>15.24</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>37c404f6-b67e-4597-90f5-e43f9ab56ffd</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>35aa2688-4610-4dac-8329-49519fb81a39</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>46078.92818133988</v>
+      </c>
+      <c r="F263" t="n">
+        <v>192</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>29f3c0c0-f172-4719-b8cd-5013abbb031d</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>5b89f551-babc-4982-8875-556751dc288e</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>46086.01151467743</v>
+      </c>
+      <c r="F264" t="n">
+        <v>123</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>12e0784e-9bfa-48aa-9f35-88a75c441a98</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>b35949de-3dfb-4ba6-821e-ea840ebe883a</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46087.92818135347</v>
+      </c>
+      <c r="F265" t="n">
+        <v>46</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>de358935-8fc5-4b13-b6ff-a00ae93c8499</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>f79ad350-2ad4-495a-9723-309aa26a9a56</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46084.59484802608</v>
+      </c>
+      <c r="F266" t="n">
+        <v>153</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>be29f184-428f-45ad-93db-287079b8bdac</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>6cfc439b-196e-4a2d-a26f-27d348483dd3</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>46064.8865146957</v>
+      </c>
+      <c r="F267" t="n">
+        <v>281</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2e1f7947-9364-4bef-86ab-efb795611067</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2a1bc2c5-77cd-4203-9045-38933e5efd81</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>46060.96984804112</v>
+      </c>
+      <c r="F268" t="n">
+        <v>293</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>16.01</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>60fc4950-7f9b-46dd-9b34-753879c4ce57</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>a5baf645-5c6a-47dd-be45-4b96104ee25b</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>46069.46984805253</v>
+      </c>
+      <c r="F269" t="n">
+        <v>283</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>f220d4a7-d5c0-4124-bbcf-3c90cd7b0bba</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>d9ba2d5c-e81d-4dda-959f-8da6cf67c3e2</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>46089.13651472214</v>
+      </c>
+      <c r="F270" t="n">
+        <v>165</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>9e02f23e-3d55-42aa-aeef-78dc25ca119d</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ad575945-0ffb-4bcc-8d2b-98ee38a0753e</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>46064.38651472513</v>
+      </c>
+      <c r="F271" t="n">
+        <v>87</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>5f991d5a-b76a-47e9-9534-915c0b0ccac4</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>c75a6c59-e493-4467-b660-dad12e3401ac</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>46083.09484807288</v>
+      </c>
+      <c r="F272" t="n">
+        <v>54</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ffa0d3ae-0088-4fb6-bfd3-9226ab54fb04</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>e940d1e4-0acf-4d9e-b5e1-d8b10596b24a</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>46083.76151474248</v>
+      </c>
+      <c r="F273" t="n">
+        <v>269</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>363e0e28-141f-432b-841c-c01a05597718</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>5d7787cb-7f5f-45f1-942d-a99b6564d550</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>46083.34484811343</v>
+      </c>
+      <c r="F274" t="n">
+        <v>161</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>34ede41c-d785-405d-b87e-dbfda84d31fa</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>0a09acdd-3439-413f-9023-581788539b59</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>46074.21984812769</v>
+      </c>
+      <c r="F275" t="n">
+        <v>135</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>a1ad9489-955b-4f87-aa7b-fee828f0959f</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>e1ad3d75-e7fa-4904-823d-a69a086b704e</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>46065.09484813941</v>
+      </c>
+      <c r="F276" t="n">
+        <v>46</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>18.96</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I276"/>
+  <dimension ref="A1:I297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11202,7 +11202,7 @@
         </is>
       </c>
       <c r="E263" s="2" t="n">
-        <v>46078.92818133988</v>
+        <v>46078.92818134259</v>
       </c>
       <c r="F263" t="n">
         <v>192</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>46086.01151467743</v>
+        <v>46086.01151467593</v>
       </c>
       <c r="F264" t="n">
         <v>123</v>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>46087.92818135347</v>
+        <v>46087.92818135417</v>
       </c>
       <c r="F265" t="n">
         <v>46</v>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>46084.59484802608</v>
+        <v>46084.59484802083</v>
       </c>
       <c r="F266" t="n">
         <v>153</v>
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>46064.8865146957</v>
+        <v>46064.88651469907</v>
       </c>
       <c r="F267" t="n">
         <v>281</v>
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>46060.96984804112</v>
+        <v>46060.96984804398</v>
       </c>
       <c r="F268" t="n">
         <v>293</v>
@@ -11448,7 +11448,7 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>46069.46984805253</v>
+        <v>46069.46984805555</v>
       </c>
       <c r="F269" t="n">
         <v>283</v>
@@ -11489,7 +11489,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>46089.13651472214</v>
+        <v>46089.13651472222</v>
       </c>
       <c r="F270" t="n">
         <v>165</v>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>46064.38651472513</v>
+        <v>46064.38651472222</v>
       </c>
       <c r="F271" t="n">
         <v>87</v>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>46083.09484807288</v>
+        <v>46083.09484806713</v>
       </c>
       <c r="F272" t="n">
         <v>54</v>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="E273" s="2" t="n">
-        <v>46083.76151474248</v>
+        <v>46083.76151474537</v>
       </c>
       <c r="F273" t="n">
         <v>269</v>
@@ -11694,7 +11694,7 @@
         </is>
       </c>
       <c r="E275" s="2" t="n">
-        <v>46074.21984812769</v>
+        <v>46074.219848125</v>
       </c>
       <c r="F275" t="n">
         <v>135</v>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>46065.09484813941</v>
+        <v>46065.09484813658</v>
       </c>
       <c r="F276" t="n">
         <v>46</v>
@@ -11752,6 +11752,867 @@
       </c>
       <c r="I276" t="n">
         <v>18.96</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>47089f14-4468-4a8f-9851-2dbbc1dc58f0</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>c92629df-3759-41d5-9132-d27d52263f12</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>46086.80481567408</v>
+      </c>
+      <c r="F277" t="n">
+        <v>179</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>9741a13b-9146-4886-93c1-09485cad70f5</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>061a9842-e334-492e-9e57-10f6a9533380</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>46063.72148234754</v>
+      </c>
+      <c r="F278" t="n">
+        <v>199</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>3675a684-1d66-43a0-bab8-2e1e205fb08a</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>17229131-e051-4a61-b82a-9f83bc45863e</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>46069.17981568717</v>
+      </c>
+      <c r="F279" t="n">
+        <v>190</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>10.67</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>f6ccf2f0-d16a-4134-9458-169135b85660</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>4ae48d55-eb7f-4c10-a390-9dd89386963c</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>46063.26314903648</v>
+      </c>
+      <c r="F280" t="n">
+        <v>208</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>c30c9b65-dc08-48b9-9847-4c583a3c875a</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>53ff8292-39e0-42be-b2cd-674b6c8237c0</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>46075.42981571238</v>
+      </c>
+      <c r="F281" t="n">
+        <v>269</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I281" t="n">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>517e96f2-0a41-4f7c-be19-0456e2d41e4f</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>ee5bd2f6-4903-4311-bb1d-bfc80a97cc86</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>46088.17981571573</v>
+      </c>
+      <c r="F282" t="n">
+        <v>281</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I282" t="n">
+        <v>18.07</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>08808ec1-b25a-40e0-9ade-bcc4a4b02eef</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>a5121bc6-b739-4ca2-8f6f-35d6f2615db4</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>46065.80481572814</v>
+      </c>
+      <c r="F283" t="n">
+        <v>201</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>292380c7-7ddb-4c5c-9de4-6b515ae5d5bc</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>eb1f00ff-1fe1-4943-9f2f-d5743c621a19</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>46068.80481573135</v>
+      </c>
+      <c r="F284" t="n">
+        <v>140</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I284" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>e32f245a-e61e-4c33-a2db-307db70ffb55</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>d8006394-103b-4106-9a7c-fce11b677073</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>46081.05481574679</v>
+      </c>
+      <c r="F285" t="n">
+        <v>148</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>15.95</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>a822264f-2c80-4a9f-aca8-34cd97c95ca9</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>88f6f350-56b4-4456-b412-2b48c8714cf3</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>46069.84648241686</v>
+      </c>
+      <c r="F286" t="n">
+        <v>69</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>aaf1066e-84bd-469e-9d8c-8e80041da0aa</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>429319d8-196b-4125-af5c-a90afd03818d</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>46076.88814908981</v>
+      </c>
+      <c r="F287" t="n">
+        <v>171</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>16.53</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>e50b999f-5e08-43b7-bc92-3d598ebb3d79</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>aeaef3db-23e4-4af5-9d22-85653f916edb</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>46063.30481575961</v>
+      </c>
+      <c r="F288" t="n">
+        <v>101</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I288" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>38159d34-cf2d-41fe-b0a1-b085f925ba19</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>67483aeb-f661-433a-8026-dc1a19d04a40</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>46084.88814909627</v>
+      </c>
+      <c r="F289" t="n">
+        <v>95</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>245e8ef1-d710-4c36-a2e6-dc5a229c3686</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>95d456b7-4823-4913-970a-8967073748d1</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>46085.8048157663</v>
+      </c>
+      <c r="F290" t="n">
+        <v>208</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>dd943898-f8e2-44b3-8958-bffc488833e7</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>0418ae8f-6703-4a6c-b83e-b0fe9fd037e4</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>46070.01314910276</v>
+      </c>
+      <c r="F291" t="n">
+        <v>49</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>19.45</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>54ed97e5-ad6d-4540-b101-dadb89dca717</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>784d086b-aa3b-4aa0-8ad9-4d8f0e1c4d5a</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>46064.13814911218</v>
+      </c>
+      <c r="F292" t="n">
+        <v>111</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>4dcce541-c11c-497e-95f6-1f4e65cc983f</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>9d772244-7f72-4a63-93d9-b46f6536dfbd</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>46077.30481578207</v>
+      </c>
+      <c r="F293" t="n">
+        <v>286</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>3829d2e8-6255-4648-9c62-c376cd3992aa</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>dc2dcf9c-646c-4875-800f-75faf2c477af</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>46086.8881491374</v>
+      </c>
+      <c r="F294" t="n">
+        <v>64</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>59cd20e7-9e04-4da9-87c2-b8b70fd75581</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>21b19f56-3bea-46b9-af6a-58e810292df8</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>46063.05481581039</v>
+      </c>
+      <c r="F295" t="n">
+        <v>158</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>43de9ce6-cf05-4eff-a008-f048d8263888</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>98621bb2-d51c-4362-83d6-8fb319ee80da</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>46088.92981581359</v>
+      </c>
+      <c r="F296" t="n">
+        <v>196</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>3f67edfe-8538-4d02-b214-73cf5a00c8e7</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>559699cf-6ee3-4045-a124-0f566ce5a841</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>46066.05481582</v>
+      </c>
+      <c r="F297" t="n">
+        <v>265</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I297" t="n">
+        <v>19.38</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I297"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>46086.80481567408</v>
+        <v>46086.8048156713</v>
       </c>
       <c r="F277" t="n">
         <v>179</v>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>46063.72148234754</v>
+        <v>46063.72148234954</v>
       </c>
       <c r="F278" t="n">
         <v>199</v>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>46069.17981568717</v>
+        <v>46069.17981568287</v>
       </c>
       <c r="F279" t="n">
         <v>190</v>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>46063.26314903648</v>
+        <v>46063.26314903935</v>
       </c>
       <c r="F280" t="n">
         <v>208</v>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>46075.42981571238</v>
+        <v>46075.42981571759</v>
       </c>
       <c r="F281" t="n">
         <v>269</v>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>46088.17981571573</v>
+        <v>46088.17981571759</v>
       </c>
       <c r="F282" t="n">
         <v>281</v>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>46065.80481572814</v>
+        <v>46065.80481572916</v>
       </c>
       <c r="F283" t="n">
         <v>201</v>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>46068.80481573135</v>
+        <v>46068.80481572916</v>
       </c>
       <c r="F284" t="n">
         <v>140</v>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="E285" s="2" t="n">
-        <v>46081.05481574679</v>
+        <v>46081.05481575232</v>
       </c>
       <c r="F285" t="n">
         <v>148</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>46069.84648241686</v>
+        <v>46069.84648241898</v>
       </c>
       <c r="F286" t="n">
         <v>69</v>
@@ -12186,7 +12186,7 @@
         </is>
       </c>
       <c r="E287" s="2" t="n">
-        <v>46076.88814908981</v>
+        <v>46076.88814908565</v>
       </c>
       <c r="F287" t="n">
         <v>171</v>
@@ -12227,7 +12227,7 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>46063.30481575961</v>
+        <v>46063.30481576389</v>
       </c>
       <c r="F288" t="n">
         <v>101</v>
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>46084.88814909627</v>
+        <v>46084.88814909722</v>
       </c>
       <c r="F289" t="n">
         <v>95</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>46085.8048157663</v>
+        <v>46085.80481576389</v>
       </c>
       <c r="F290" t="n">
         <v>208</v>
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>46070.01314910276</v>
+        <v>46070.01314909722</v>
       </c>
       <c r="F291" t="n">
         <v>49</v>
@@ -12391,7 +12391,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>46064.13814911218</v>
+        <v>46064.1381491088</v>
       </c>
       <c r="F292" t="n">
         <v>111</v>
@@ -12432,7 +12432,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>46077.30481578207</v>
+        <v>46077.30481578704</v>
       </c>
       <c r="F293" t="n">
         <v>286</v>
@@ -12473,7 +12473,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>46086.8881491374</v>
+        <v>46086.88814913195</v>
       </c>
       <c r="F294" t="n">
         <v>64</v>
@@ -12514,7 +12514,7 @@
         </is>
       </c>
       <c r="E295" s="2" t="n">
-        <v>46063.05481581039</v>
+        <v>46063.05481581019</v>
       </c>
       <c r="F295" t="n">
         <v>158</v>
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>46088.92981581359</v>
+        <v>46088.92981581019</v>
       </c>
       <c r="F296" t="n">
         <v>196</v>
@@ -12596,7 +12596,7 @@
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>46066.05481582</v>
+        <v>46066.05481582176</v>
       </c>
       <c r="F297" t="n">
         <v>265</v>
@@ -12613,6 +12613,662 @@
       </c>
       <c r="I297" t="n">
         <v>19.38</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>53448870-bc70-4dcb-8cf7-95de943830e1</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>c6a4dbc1-f752-41da-8749-21a410731bfa</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>46081.09517557322</v>
+      </c>
+      <c r="F298" t="n">
+        <v>45</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I298" t="n">
+        <v>11.41</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>d48d2b3b-abe4-4278-bdaa-449cafe6e858</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>7934b399-37d5-45b6-a6b9-88ab62284696</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>46085.22017558294</v>
+      </c>
+      <c r="F299" t="n">
+        <v>294</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>83af8e5f-b0eb-4d2c-a921-9bff7beb3676</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>09a00b98-2a99-482d-bf63-db20b449c231</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>46073.26184225954</v>
+      </c>
+      <c r="F300" t="n">
+        <v>73</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>6cd4ba28-38a0-4a13-8e30-20cfb0b7e62f</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>db0bb19c-1b2b-466e-a2e7-fb1fcbdfa089</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>46063.01184226352</v>
+      </c>
+      <c r="F301" t="n">
+        <v>119</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>e4586031-45d0-4b83-b0c3-d72d4538c78e</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>bece8b1d-7d8e-4589-a5e7-66a1213fa737</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>46068.26184227015</v>
+      </c>
+      <c r="F302" t="n">
+        <v>295</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1cf53d53-a7b2-4429-affd-2e30b342b201</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>c5ea309c-4537-438f-8cd8-cdbc21cd9ddd</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>46088.76184228919</v>
+      </c>
+      <c r="F303" t="n">
+        <v>266</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>e28ac769-4c0f-494e-89e8-ef64b81db3e2</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>b49bcc59-b5e9-4a3e-ba45-2e6e8c077cc0</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>46072.97017562882</v>
+      </c>
+      <c r="F304" t="n">
+        <v>202</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I304" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>892fbd06-cc88-47c4-aba5-0e01abe082cd</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>aa0d1ca4-0bdd-40e3-916d-4c8ccd6263da</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>46084.76184231482</v>
+      </c>
+      <c r="F305" t="n">
+        <v>139</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
+        <v>8.51</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>c270e889-205e-4e7d-ad3f-5edd4562367b</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>60f472af-3772-4903-a82f-dbd7aa94ff17</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>46078.38684233049</v>
+      </c>
+      <c r="F306" t="n">
+        <v>265</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>d5433a58-3f05-43fa-b81c-e3aa4295b588</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>a67911c6-8945-43ce-90b8-254bb38e13d8</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>46087.76184233694</v>
+      </c>
+      <c r="F307" t="n">
+        <v>147</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I307" t="n">
+        <v>14.12</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>e552803b-d051-4d7a-8204-048aa0977e4c</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>d93f8dd0-5fd0-4035-b2ec-18e9a72a6db4</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>46082.97017567351</v>
+      </c>
+      <c r="F308" t="n">
+        <v>121</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I308" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>760dad20-e2d6-4951-9db7-a9763b0685d5</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>3dfb7c84-20de-41bd-a508-c1ec5f108d6a</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>46067.9701756896</v>
+      </c>
+      <c r="F309" t="n">
+        <v>130</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I309" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>a77d35f3-969e-4743-bcc7-6630ae03866b</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>50409910-90a5-40ef-8968-8132feff19ac</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>46069.51184236252</v>
+      </c>
+      <c r="F310" t="n">
+        <v>240</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I310" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>6f0e9eb5-5e3d-4b10-a634-be6469763e62</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>59c74d3e-af1c-4cc5-be6a-be9b340d2fc5</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>46083.88684237839</v>
+      </c>
+      <c r="F311" t="n">
+        <v>267</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ec510061-4e12-42ad-9bf7-0e7fd7758d44</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>c3d88499-ee91-486f-8905-9ab7d20ac1aa</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>46083.88684238369</v>
+      </c>
+      <c r="F312" t="n">
+        <v>235</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>65381f9e-57e0-493e-9099-35f3d047f292</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>85601bfa-b688-4964-8b0b-a7f8115652ef</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>46071.76184238751</v>
+      </c>
+      <c r="F313" t="n">
+        <v>109</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>12.52</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I313"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>46081.09517557322</v>
+        <v>46081.0951755787</v>
       </c>
       <c r="F298" t="n">
         <v>45</v>
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>46085.22017558294</v>
+        <v>46085.2201755787</v>
       </c>
       <c r="F299" t="n">
         <v>294</v>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>46073.26184225954</v>
+        <v>46073.26184225694</v>
       </c>
       <c r="F300" t="n">
         <v>73</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>46063.01184226352</v>
+        <v>46063.01184226852</v>
       </c>
       <c r="F301" t="n">
         <v>119</v>
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>46068.26184227015</v>
+        <v>46068.26184226852</v>
       </c>
       <c r="F302" t="n">
         <v>295</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>46088.76184228919</v>
+        <v>46088.76184229166</v>
       </c>
       <c r="F303" t="n">
         <v>266</v>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>46072.97017562882</v>
+        <v>46072.970175625</v>
       </c>
       <c r="F304" t="n">
         <v>202</v>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>46078.38684233049</v>
+        <v>46078.38684232639</v>
       </c>
       <c r="F306" t="n">
         <v>265</v>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="E307" s="2" t="n">
-        <v>46087.76184233694</v>
+        <v>46087.76184233796</v>
       </c>
       <c r="F307" t="n">
         <v>147</v>
@@ -13047,7 +13047,7 @@
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>46082.97017567351</v>
+        <v>46082.9701756713</v>
       </c>
       <c r="F308" t="n">
         <v>121</v>
@@ -13088,7 +13088,7 @@
         </is>
       </c>
       <c r="E309" s="2" t="n">
-        <v>46067.9701756896</v>
+        <v>46067.97017569444</v>
       </c>
       <c r="F309" t="n">
         <v>130</v>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>46069.51184236252</v>
+        <v>46069.51184236111</v>
       </c>
       <c r="F310" t="n">
         <v>240</v>
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>46083.88684237839</v>
+        <v>46083.88684237268</v>
       </c>
       <c r="F311" t="n">
         <v>267</v>
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>46083.88684238369</v>
+        <v>46083.88684238426</v>
       </c>
       <c r="F312" t="n">
         <v>235</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>46071.76184238751</v>
+        <v>46071.76184238426</v>
       </c>
       <c r="F313" t="n">
         <v>109</v>
@@ -13269,6 +13269,826 @@
       </c>
       <c r="I313" t="n">
         <v>12.52</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>5f1bcd75-0fcf-421a-89fe-c226661cf6a2</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>8c51aa49-b13d-4c72-8707-9d7877b32082</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>46077.55738434723</v>
+      </c>
+      <c r="F314" t="n">
+        <v>153</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>a0197189-d1bf-4bae-9f1c-e0492b830f5e</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>70e4f9f8-888d-4677-a074-e4ec5cbd24de</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>46084.59905102677</v>
+      </c>
+      <c r="F315" t="n">
+        <v>62</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I315" t="n">
+        <v>19.12</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>8d7db4f7-1413-45b7-b888-7e5c5a5833bc</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2f9f8ba5-ea34-44f1-bf03-9f9610a4a3a3</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>46065.51571769665</v>
+      </c>
+      <c r="F316" t="n">
+        <v>60</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I316" t="n">
+        <v>19.52</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1fe0ed38-85d5-4d00-9c87-466a53212beb</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>adf072be-aa9c-4b75-b361-a2deb1c68e3a</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>46077.34905103344</v>
+      </c>
+      <c r="F317" t="n">
+        <v>293</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I317" t="n">
+        <v>19.17</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>cebec4b3-3458-411c-83dc-ce6f7872f986</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>8d5c1327-c2bf-448f-9715-c6af231009a9</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>46083.72405103986</v>
+      </c>
+      <c r="F318" t="n">
+        <v>177</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I318" t="n">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>b63dcb99-3f7d-4a26-96ea-b997783672fb</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>c8d8740b-92fd-4cc8-bf7c-fbc94e8b1aed</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>46073.26571771603</v>
+      </c>
+      <c r="F319" t="n">
+        <v>76</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I319" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>e64150d5-84c1-48f3-848f-da583a5ea96e</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>d15ab7b6-a885-42ef-b999-58cf8bcd720f</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>46077.01571772561</v>
+      </c>
+      <c r="F320" t="n">
+        <v>60</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I320" t="n">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>87712306-df09-4123-ac63-6fb2bd83caf5</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>859bccbb-3738-499d-a559-c907174e29f2</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>46072.93238439545</v>
+      </c>
+      <c r="F321" t="n">
+        <v>229</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I321" t="n">
+        <v>9.210000000000001</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>5777d89b-20a7-40e8-8fcd-25eea0935588</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>fa383ea1-aa85-4241-8259-e6c5ec39316f</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>46090.26571773209</v>
+      </c>
+      <c r="F322" t="n">
+        <v>138</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I322" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>6c6e8376-1bd2-4fec-8550-4ed613b8b9fc</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>7d01bdb8-2b6f-4993-acd1-d2fe9c427d29</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>46075.8907177385</v>
+      </c>
+      <c r="F323" t="n">
+        <v>131</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I323" t="n">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>6277f91b-7427-426b-ac67-e85551c54410</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>9c640618-38e5-4498-a62b-476e6cc2baf4</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>46077.64071774475</v>
+      </c>
+      <c r="F324" t="n">
+        <v>186</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I324" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>6966c75d-40d6-4000-a670-9156d3d644f2</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>8bfd4ec0-fa09-4d9f-bfc4-f1d35a9b754c</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>46086.26571775427</v>
+      </c>
+      <c r="F325" t="n">
+        <v>257</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I325" t="n">
+        <v>17.79</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>c29239e2-609e-473e-9dcd-261b4c504633</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>191fe4b7-5573-4747-b498-4e2581d7e30c</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>46077.14071777018</v>
+      </c>
+      <c r="F326" t="n">
+        <v>269</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I326" t="n">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>85f06a07-6f1d-4928-9c7b-fe36cf60923d</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2fdfeff1-05b7-4bbb-8824-96d8e84187a7</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>46065.05738444002</v>
+      </c>
+      <c r="F327" t="n">
+        <v>159</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I327" t="n">
+        <v>8.42</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>721e6608-f654-471d-a209-59bf252e5bec</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>c7cd60f3-2608-4c7a-bf34-0245032684a9</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>46089.09905113206</v>
+      </c>
+      <c r="F328" t="n">
+        <v>33</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I328" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>628fd5bd-0f39-4cca-bc7d-ac27c1b17727</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>c01171f0-ce05-4ae4-88db-2392f58aecac</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>46065.55738446852</v>
+      </c>
+      <c r="F329" t="n">
+        <v>263</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I329" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>7b52273c-8f1f-4593-bf20-cbc41b9410a8</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>80dcd774-783e-4909-b51f-571d70f7b635</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="n">
+        <v>46079.26571780822</v>
+      </c>
+      <c r="F330" t="n">
+        <v>221</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I330" t="n">
+        <v>17.37</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>38fbef38-e445-49eb-8fb4-dbc4a573dde2</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>5e355f22-61bc-4fca-a051-894897e522fd</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>46076.84905114794</v>
+      </c>
+      <c r="F331" t="n">
+        <v>213</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I331" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>3abbc33e-68cb-4804-b2f4-6ac399cc539f</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>40b123b9-bfba-47d6-a6b0-cf70b4c9e259</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>46081.93238449386</v>
+      </c>
+      <c r="F332" t="n">
+        <v>272</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I332" t="n">
+        <v>19.58</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>7d22e8c4-e781-4361-965f-ff7a146ecfcd</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ad841e60-97c5-40a6-8bc3-d950b61f54f6</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>46088.30738449706</v>
+      </c>
+      <c r="F333" t="n">
+        <v>173</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I333" t="n">
+        <v>11.02</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13293,7 +13293,7 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>46077.55738434723</v>
+        <v>46077.55738435185</v>
       </c>
       <c r="F314" t="n">
         <v>153</v>
@@ -13334,7 +13334,7 @@
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>46084.59905102677</v>
+        <v>46084.59905103009</v>
       </c>
       <c r="F315" t="n">
         <v>62</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>46065.51571769665</v>
+        <v>46065.51571769676</v>
       </c>
       <c r="F316" t="n">
         <v>60</v>
@@ -13416,7 +13416,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>46077.34905103344</v>
+        <v>46077.34905103009</v>
       </c>
       <c r="F317" t="n">
         <v>293</v>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>46083.72405103986</v>
+        <v>46083.72405104167</v>
       </c>
       <c r="F318" t="n">
         <v>177</v>
@@ -13498,7 +13498,7 @@
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>46073.26571771603</v>
+        <v>46073.26571771991</v>
       </c>
       <c r="F319" t="n">
         <v>76</v>
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>46077.01571772561</v>
+        <v>46077.01571771991</v>
       </c>
       <c r="F320" t="n">
         <v>60</v>
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>46072.93238439545</v>
+        <v>46072.93238439815</v>
       </c>
       <c r="F321" t="n">
         <v>229</v>
@@ -13621,7 +13621,7 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>46090.26571773209</v>
+        <v>46090.26571773148</v>
       </c>
       <c r="F322" t="n">
         <v>138</v>
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>46075.8907177385</v>
+        <v>46075.89071774305</v>
       </c>
       <c r="F323" t="n">
         <v>131</v>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>46077.64071774475</v>
+        <v>46077.64071774305</v>
       </c>
       <c r="F324" t="n">
         <v>186</v>
@@ -13744,7 +13744,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>46086.26571775427</v>
+        <v>46086.26571775463</v>
       </c>
       <c r="F325" t="n">
         <v>257</v>
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>46077.14071777018</v>
+        <v>46077.1407177662</v>
       </c>
       <c r="F326" t="n">
         <v>269</v>
@@ -13826,7 +13826,7 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>46065.05738444002</v>
+        <v>46065.05738444444</v>
       </c>
       <c r="F327" t="n">
         <v>159</v>
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>46089.09905113206</v>
+        <v>46089.09905113426</v>
       </c>
       <c r="F328" t="n">
         <v>33</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="E329" s="2" t="n">
-        <v>46065.55738446852</v>
+        <v>46065.55738446759</v>
       </c>
       <c r="F329" t="n">
         <v>263</v>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>46079.26571780822</v>
+        <v>46079.2657178125</v>
       </c>
       <c r="F330" t="n">
         <v>221</v>
@@ -13990,7 +13990,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>46076.84905114794</v>
+        <v>46076.84905114584</v>
       </c>
       <c r="F331" t="n">
         <v>213</v>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>46081.93238449386</v>
+        <v>46081.93238449074</v>
       </c>
       <c r="F332" t="n">
         <v>272</v>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>46088.30738449706</v>
+        <v>46088.30738450232</v>
       </c>
       <c r="F333" t="n">
         <v>173</v>
@@ -14089,6 +14089,990 @@
       </c>
       <c r="I333" t="n">
         <v>11.02</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>682db199-07a1-47bd-96eb-17f025b8e922</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>66a1fa9b-36e4-4c86-9863-e5ee6997ca94</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>46075.84607303462</v>
+      </c>
+      <c r="F334" t="n">
+        <v>163</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I334" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>64447ad6-e93f-4cff-a751-e8eac1f0f07a</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>b8c15e58-e7ec-49af-a166-4cea197fd8b6</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>46065.97107304156</v>
+      </c>
+      <c r="F335" t="n">
+        <v>217</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I335" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>af1c8a2f-b4d4-43e1-abb8-7c71c03b4cc3</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>7652c18e-722d-4640-8301-6948d24fb23d</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>46084.51273971156</v>
+      </c>
+      <c r="F336" t="n">
+        <v>78</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I336" t="n">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>5f8fe659-3ffb-4d84-9e51-8ca5db823935</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>a53df51c-a547-4ebe-9807-1555247cc5f1</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>46090.26273972156</v>
+      </c>
+      <c r="F337" t="n">
+        <v>288</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I337" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>b28fa7eb-66d0-4cc7-8357-30b0caf3cf78</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>3c8fb256-6a9d-49ea-8646-32ce0d81e579</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>46078.72107305824</v>
+      </c>
+      <c r="F338" t="n">
+        <v>56</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I338" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>dc144443-a43b-4fa3-b139-c1c85e51c97a</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>22df145d-4831-4d54-88a5-e8b583c14286</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>46085.30440639487</v>
+      </c>
+      <c r="F339" t="n">
+        <v>207</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I339" t="n">
+        <v>18.54</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>f4284434-a9ba-4c4e-9782-e02570712426</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>902bcfe6-d7f2-4e96-9655-4cc9010bcb4f</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>46088.30440639866</v>
+      </c>
+      <c r="F340" t="n">
+        <v>45</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I340" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>481b05eb-1f9f-4cc4-ac87-077ce575dd62</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>8c871962-2965-4819-9753-2ba6ff553a98</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>46070.26273973526</v>
+      </c>
+      <c r="F341" t="n">
+        <v>37</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I341" t="n">
+        <v>9.390000000000001</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>a6de379d-bd83-4f1d-aa54-ec707e5a748e</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>c9da8397-2620-4d0b-b0b1-74e91520491c</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>46063.97107307841</v>
+      </c>
+      <c r="F342" t="n">
+        <v>166</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I342" t="n">
+        <v>11.84</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1b26e545-bc19-4ef2-ad7d-9da3920ccac8</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>327fe8d7-1088-40e5-8cdb-c3d45b511ec7</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>46089.05440641504</v>
+      </c>
+      <c r="F343" t="n">
+        <v>77</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I343" t="n">
+        <v>15.93</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>fc47a4cc-a27f-4522-af83-fed2faba589f</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>205343d9-57cb-43b7-b9d3-bb5bba7f02d3</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>46076.42940642474</v>
+      </c>
+      <c r="F344" t="n">
+        <v>262</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I344" t="n">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>be14f5a6-2c1b-4b01-b10d-519ef0e9da14</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>278420f9-a71d-4ff9-bf8e-36c42d011f66</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="n">
+        <v>46071.38773976441</v>
+      </c>
+      <c r="F345" t="n">
+        <v>112</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I345" t="n">
+        <v>8.82</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>030e751d-e82c-42b5-a816-672ce4a77453</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>79ae80d8-a741-408a-b426-1045dd5f901f</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="n">
+        <v>46068.30440643826</v>
+      </c>
+      <c r="F346" t="n">
+        <v>53</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I346" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>73b1da3f-0c2e-453b-bde0-af7215e44937</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>cc6cb5f9-497e-4ae2-8243-025efb78c913</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="n">
+        <v>46062.47107310814</v>
+      </c>
+      <c r="F347" t="n">
+        <v>227</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I347" t="n">
+        <v>16.03</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>a004167d-2d7d-48d0-8c95-ab18d98e0462</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>4b5dcbfe-17f1-4847-bcf4-683026e1371d</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="n">
+        <v>46082.09607312428</v>
+      </c>
+      <c r="F348" t="n">
+        <v>68</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I348" t="n">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>30c85cad-fccc-4581-ab6c-c859846799c5</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>9272b8f7-149d-47b4-b746-9551e91eca22</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="n">
+        <v>46088.09607312745</v>
+      </c>
+      <c r="F349" t="n">
+        <v>244</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I349" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2343862a-c782-4541-b32d-a66b1d45ab78</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>fee0bceb-82a6-4201-94e4-42d1aa3dc818</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="n">
+        <v>46091.63773980387</v>
+      </c>
+      <c r="F350" t="n">
+        <v>54</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I350" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>8f9b8cb7-8c3d-4ce8-b618-e3ea67aa17dc</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>26083769-e9c1-45a4-9c19-a02cec237d0a</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="n">
+        <v>46063.01273981721</v>
+      </c>
+      <c r="F351" t="n">
+        <v>97</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I351" t="n">
+        <v>19.58</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>246cccf1-650e-40e1-81c0-72365d16044e</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>98e8ecd1-d581-41c6-b608-802dab97fc82</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="n">
+        <v>46077.72107315713</v>
+      </c>
+      <c r="F352" t="n">
+        <v>97</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I352" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2b039e31-2d68-4430-8213-f2cdec86502a</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>391956ce-a1c5-4e36-844e-9a756b23c3d7</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>46063.42940649675</v>
+      </c>
+      <c r="F353" t="n">
+        <v>191</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I353" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>293b8ef7-03c3-492e-86b5-1ccb70f7073d</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>d837b880-4ea0-42da-97b5-0c3a078fdd43</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="n">
+        <v>46085.17940650639</v>
+      </c>
+      <c r="F354" t="n">
+        <v>229</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I354" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>3a9179a0-3417-4c67-b132-cf590448a691</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>760239e4-e7af-4e92-86c9-53c238f76eef</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="n">
+        <v>46083.76273984633</v>
+      </c>
+      <c r="F355" t="n">
+        <v>73</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I355" t="n">
+        <v>12.51</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>6e152074-1e4e-42a6-bbc0-de4b022e8204</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2eca3f95-9c63-498f-8b10-3506a12aa77b</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="n">
+        <v>46085.76273984958</v>
+      </c>
+      <c r="F356" t="n">
+        <v>108</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I356" t="n">
+        <v>15.63</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>8af4a33b-c1e0-45f2-ac05-5eea63b86d57</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>b08d9958-573f-49f6-85f9-807f938ba9ca</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="n">
+        <v>46077.05440652255</v>
+      </c>
+      <c r="F357" t="n">
+        <v>211</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I357" t="n">
+        <v>3.59</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I357"/>
+  <dimension ref="A1:I376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>46075.84607303462</v>
+        <v>46075.84607303241</v>
       </c>
       <c r="F334" t="n">
         <v>163</v>
@@ -14154,7 +14154,7 @@
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>46065.97107304156</v>
+        <v>46065.97107304398</v>
       </c>
       <c r="F335" t="n">
         <v>217</v>
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>46084.51273971156</v>
+        <v>46084.51273971065</v>
       </c>
       <c r="F336" t="n">
         <v>78</v>
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>46090.26273972156</v>
+        <v>46090.26273972222</v>
       </c>
       <c r="F337" t="n">
         <v>288</v>
@@ -14277,7 +14277,7 @@
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>46078.72107305824</v>
+        <v>46078.72107305555</v>
       </c>
       <c r="F338" t="n">
         <v>56</v>
@@ -14318,7 +14318,7 @@
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>46085.30440639487</v>
+        <v>46085.30440640046</v>
       </c>
       <c r="F339" t="n">
         <v>207</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>46088.30440639866</v>
+        <v>46088.30440640046</v>
       </c>
       <c r="F340" t="n">
         <v>45</v>
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>46070.26273973526</v>
+        <v>46070.26273973379</v>
       </c>
       <c r="F341" t="n">
         <v>37</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>46063.97107307841</v>
+        <v>46063.9710730787</v>
       </c>
       <c r="F342" t="n">
         <v>166</v>
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="E343" s="2" t="n">
-        <v>46089.05440641504</v>
+        <v>46089.05440641204</v>
       </c>
       <c r="F343" t="n">
         <v>77</v>
@@ -14523,7 +14523,7 @@
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>46076.42940642474</v>
+        <v>46076.42940642361</v>
       </c>
       <c r="F344" t="n">
         <v>262</v>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>46071.38773976441</v>
+        <v>46071.38773976852</v>
       </c>
       <c r="F345" t="n">
         <v>112</v>
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>46068.30440643826</v>
+        <v>46068.30440643519</v>
       </c>
       <c r="F346" t="n">
         <v>53</v>
@@ -14646,7 +14646,7 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>46062.47107310814</v>
+        <v>46062.47107311343</v>
       </c>
       <c r="F347" t="n">
         <v>227</v>
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="E348" s="2" t="n">
-        <v>46082.09607312428</v>
+        <v>46082.096073125</v>
       </c>
       <c r="F348" t="n">
         <v>68</v>
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E349" s="2" t="n">
-        <v>46088.09607312745</v>
+        <v>46088.096073125</v>
       </c>
       <c r="F349" t="n">
         <v>244</v>
@@ -14769,7 +14769,7 @@
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>46091.63773980387</v>
+        <v>46091.63773980324</v>
       </c>
       <c r="F350" t="n">
         <v>54</v>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>46063.01273981721</v>
+        <v>46063.01273981482</v>
       </c>
       <c r="F351" t="n">
         <v>97</v>
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>46077.72107315713</v>
+        <v>46077.72107315972</v>
       </c>
       <c r="F352" t="n">
         <v>97</v>
@@ -14892,7 +14892,7 @@
         </is>
       </c>
       <c r="E353" s="2" t="n">
-        <v>46063.42940649675</v>
+        <v>46063.42940649306</v>
       </c>
       <c r="F353" t="n">
         <v>191</v>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="E354" s="2" t="n">
-        <v>46085.17940650639</v>
+        <v>46085.17940650463</v>
       </c>
       <c r="F354" t="n">
         <v>229</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="E355" s="2" t="n">
-        <v>46083.76273984633</v>
+        <v>46083.76273984954</v>
       </c>
       <c r="F355" t="n">
         <v>73</v>
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="E356" s="2" t="n">
-        <v>46085.76273984958</v>
+        <v>46085.76273984954</v>
       </c>
       <c r="F356" t="n">
         <v>108</v>
@@ -15056,7 +15056,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>46077.05440652255</v>
+        <v>46077.05440652778</v>
       </c>
       <c r="F357" t="n">
         <v>211</v>
@@ -15073,6 +15073,785 @@
       </c>
       <c r="I357" t="n">
         <v>3.59</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>35b777de-583a-4474-84cb-ba845d94a695</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>a02685a3-06d6-44f7-8ea3-dc4588f6c547</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="n">
+        <v>46065.38659728926</v>
+      </c>
+      <c r="F358" t="n">
+        <v>190</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I358" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>80258592-35d8-45a8-9057-0c1e2654cf74</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>304cf696-fdda-4cff-b693-bd08f6a45d2d</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="n">
+        <v>46089.88659729367</v>
+      </c>
+      <c r="F359" t="n">
+        <v>135</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I359" t="n">
+        <v>18.87</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>781801b9-11db-45ac-98b4-2571fa8c8c61</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>965ec4c0-6e8d-48c7-a87c-f39796e78c12</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="n">
+        <v>46077.05326397062</v>
+      </c>
+      <c r="F360" t="n">
+        <v>200</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I360" t="n">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>253f1afd-0227-4560-bbac-293232174525</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>b5295492-2520-4373-bb3e-a3fb01f98a8f</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="n">
+        <v>46061.6782639739</v>
+      </c>
+      <c r="F361" t="n">
+        <v>41</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I361" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>a720d273-5d3a-4354-af17-6eedeb61c2de</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>a8e216dc-a773-4d4d-b0c8-c4c52e979300</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="n">
+        <v>46090.13659731088</v>
+      </c>
+      <c r="F362" t="n">
+        <v>75</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I362" t="n">
+        <v>12.86</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>6973de3b-82b0-426b-a615-5eff1b65e527</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1b2493fe-1e16-4136-a930-639e79debe08</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>46069.26159731727</v>
+      </c>
+      <c r="F363" t="n">
+        <v>61</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I363" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>e87eea82-78bc-430c-94a2-27f6ec35eb2d</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>11a96b3b-ba33-4765-8c3d-2c27efc88d75</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>46065.51159732063</v>
+      </c>
+      <c r="F364" t="n">
+        <v>127</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I364" t="n">
+        <v>15.21</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>9ecda771-117e-4e15-9310-815d61910632</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>f0d987e5-7cf8-4d53-acc8-8586c7471d51</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>46075.76159732725</v>
+      </c>
+      <c r="F365" t="n">
+        <v>117</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I365" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>96b73ca2-51cd-49f1-b87b-43750caa5853</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>f33e0e7b-3c18-4892-95d1-1b9df8c2e7a7</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>46079.88659733043</v>
+      </c>
+      <c r="F366" t="n">
+        <v>55</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I366" t="n">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>cfebc85a-acb3-48b8-9e03-df0b3c394bc2</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>a99acec5-6416-4490-a246-eb2ec8d719d7</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="n">
+        <v>46074.59493069621</v>
+      </c>
+      <c r="F367" t="n">
+        <v>251</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I367" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>a61be83c-99d7-4cb1-af7a-2fbcbe1de3e4</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>5efd4503-96f5-4fb2-824f-e667ac52c10b</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>46085.13659736934</v>
+      </c>
+      <c r="F368" t="n">
+        <v>112</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I368" t="n">
+        <v>10.03</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>816df245-cf90-4acc-b369-6b0130e2365d</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>8319d142-4654-4038-ae44-51c3cb160448</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="n">
+        <v>46083.09493070896</v>
+      </c>
+      <c r="F369" t="n">
+        <v>220</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I369" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>b362292f-f58a-4b5c-acee-88dbfcc429a5</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>5f288a9f-0801-4d04-bc47-937e6ebfa0a3</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="n">
+        <v>46065.59493071572</v>
+      </c>
+      <c r="F370" t="n">
+        <v>226</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I370" t="n">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>abe28b42-5d25-4662-9057-01ca86fcbe02</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>af9ee15b-eb37-401b-a7df-624a933df8f8</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="n">
+        <v>46072.84493073495</v>
+      </c>
+      <c r="F371" t="n">
+        <v>97</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I371" t="n">
+        <v>11.73</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>c546c2a5-5fd7-465f-a2ea-af4f25ef49bd</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>53ef4842-e00b-4f4b-8768-707b0a2a6370</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="n">
+        <v>46068.13659741118</v>
+      </c>
+      <c r="F372" t="n">
+        <v>94</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I372" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>bdae556a-80e6-452e-8382-dc4a900879ec</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>96a62cd2-1fbb-42e7-a6c6-80117f8b68e6</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>46070.05326408425</v>
+      </c>
+      <c r="F373" t="n">
+        <v>256</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I373" t="n">
+        <v>18.78</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>c43fb852-5c32-41a3-9495-3859b8ad9093</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>be961253-cc99-42aa-8fca-b11a974c87ba</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="n">
+        <v>46073.01159743493</v>
+      </c>
+      <c r="F374" t="n">
+        <v>267</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I374" t="n">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>0342ee4c-1faf-4cbc-be60-a049d1413655</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>1fc1e725-31ae-4d22-b93a-45c1aa8f6f42</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="n">
+        <v>46082.67826410806</v>
+      </c>
+      <c r="F375" t="n">
+        <v>278</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I375" t="n">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>3a19c27b-7834-4fbb-9084-0dda36c001d2</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>809465fc-383a-4da2-81e1-852e4f415c41</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>46063.71993077818</v>
+      </c>
+      <c r="F376" t="n">
+        <v>92</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I376" t="n">
+        <v>15.29</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I376"/>
+  <dimension ref="A1:I396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15097,7 +15097,7 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>46065.38659728926</v>
+        <v>46065.38659729167</v>
       </c>
       <c r="F358" t="n">
         <v>190</v>
@@ -15138,7 +15138,7 @@
         </is>
       </c>
       <c r="E359" s="2" t="n">
-        <v>46089.88659729367</v>
+        <v>46089.88659729167</v>
       </c>
       <c r="F359" t="n">
         <v>135</v>
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>46077.05326397062</v>
+        <v>46077.05326396991</v>
       </c>
       <c r="F360" t="n">
         <v>200</v>
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>46061.6782639739</v>
+        <v>46061.67826396991</v>
       </c>
       <c r="F361" t="n">
         <v>41</v>
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>46090.13659731088</v>
+        <v>46090.13659731481</v>
       </c>
       <c r="F362" t="n">
         <v>75</v>
@@ -15302,7 +15302,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>46069.26159731727</v>
+        <v>46069.26159731481</v>
       </c>
       <c r="F363" t="n">
         <v>61</v>
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>46065.51159732063</v>
+        <v>46065.51159732639</v>
       </c>
       <c r="F364" t="n">
         <v>127</v>
@@ -15384,7 +15384,7 @@
         </is>
       </c>
       <c r="E365" s="2" t="n">
-        <v>46075.76159732725</v>
+        <v>46075.76159732639</v>
       </c>
       <c r="F365" t="n">
         <v>117</v>
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="E366" s="2" t="n">
-        <v>46079.88659733043</v>
+        <v>46079.88659732639</v>
       </c>
       <c r="F366" t="n">
         <v>55</v>
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="E367" s="2" t="n">
-        <v>46074.59493069621</v>
+        <v>46074.59493069445</v>
       </c>
       <c r="F367" t="n">
         <v>251</v>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>46085.13659736934</v>
+        <v>46085.13659737269</v>
       </c>
       <c r="F368" t="n">
         <v>112</v>
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>46083.09493070896</v>
+        <v>46083.09493070602</v>
       </c>
       <c r="F369" t="n">
         <v>220</v>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>46065.59493071572</v>
+        <v>46065.59493071759</v>
       </c>
       <c r="F370" t="n">
         <v>226</v>
@@ -15630,7 +15630,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>46072.84493073495</v>
+        <v>46072.84493072917</v>
       </c>
       <c r="F371" t="n">
         <v>97</v>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>46068.13659741118</v>
+        <v>46068.13659740741</v>
       </c>
       <c r="F372" t="n">
         <v>94</v>
@@ -15712,7 +15712,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>46070.05326408425</v>
+        <v>46070.05326408565</v>
       </c>
       <c r="F373" t="n">
         <v>256</v>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>46073.01159743493</v>
+        <v>46073.01159743056</v>
       </c>
       <c r="F374" t="n">
         <v>267</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>46082.67826410806</v>
+        <v>46082.6782641088</v>
       </c>
       <c r="F375" t="n">
         <v>278</v>
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>46063.71993077818</v>
+        <v>46063.71993077546</v>
       </c>
       <c r="F376" t="n">
         <v>92</v>
@@ -15852,6 +15852,826 @@
       </c>
       <c r="I376" t="n">
         <v>15.29</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>8fd06d81-aefb-429f-9348-58123252b1c1</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>875050a1-b0ef-4e94-86df-99e81c6c7ac8</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>46067.42783711882</v>
+      </c>
+      <c r="F377" t="n">
+        <v>284</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I377" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>251da395-c9f0-49c5-ab6e-8effa5cad045</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>d17de870-ea0d-4ca1-981f-7a372f1cc3ed</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="n">
+        <v>46085.26117045945</v>
+      </c>
+      <c r="F378" t="n">
+        <v>36</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>15.56</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>f34ff478-a6c7-42eb-ad60-5ebcb3bbfbb3</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>085d94d0-bba5-4ede-8990-ac9d7715c717</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>46066.17783712977</v>
+      </c>
+      <c r="F379" t="n">
+        <v>197</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>16.81</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>d93966bb-e9ff-4b23-9077-86b356cfbee5</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>dfc41205-7812-4be0-b610-292704959829</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="n">
+        <v>46074.09450379937</v>
+      </c>
+      <c r="F380" t="n">
+        <v>81</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>97ec7a10-16c3-4e34-8dee-9c9574b59a7f</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>34e52add-1e4c-4f41-9352-cb81d8e52b35</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>46079.55283713571</v>
+      </c>
+      <c r="F381" t="n">
+        <v>138</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I381" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>56102c21-ea73-431d-a1e7-2f63cd7f10a2</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>f2bc2587-8dfc-4747-8f1b-4f93a4a4b188</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="n">
+        <v>46067.09450382015</v>
+      </c>
+      <c r="F382" t="n">
+        <v>266</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I382" t="n">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>58cf189d-1c44-46e3-abf8-357e2fb8d6fd</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>5c13ff06-e031-42b0-9395-8136eb255c62</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>46061.55283715942</v>
+      </c>
+      <c r="F383" t="n">
+        <v>273</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I383" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>9cb55d30-1e15-48e0-b6da-6ea0474023b8</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>3c7f8b0c-0c18-4be1-9f2a-2025c68e1257</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>46088.96950383791</v>
+      </c>
+      <c r="F384" t="n">
+        <v>53</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I384" t="n">
+        <v>13.37</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2111a053-c3a8-4e07-b5a7-76929ee02b92</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2fbdead1-9d5c-499f-af78-1bf7785c6052</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>46074.17783719148</v>
+      </c>
+      <c r="F385" t="n">
+        <v>133</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I385" t="n">
+        <v>16.17</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>851092d7-6788-435a-9e0d-e24b4617eaa4</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>7ba5b19f-ee0e-4d03-b8fd-c9107a28308e</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="n">
+        <v>46067.80283719447</v>
+      </c>
+      <c r="F386" t="n">
+        <v>266</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I386" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>8ea2765f-f8e0-4c14-a0a9-f2eba2aad306</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>871552f8-cbb3-463f-9db0-e3aba46857ec</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>46067.59450386418</v>
+      </c>
+      <c r="F387" t="n">
+        <v>50</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I387" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>9275cff5-280c-460c-a108-e89b1b648796</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>85529bde-7020-4411-afb1-c1de2aee00a2</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>46075.92783720611</v>
+      </c>
+      <c r="F388" t="n">
+        <v>58</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>19.22</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>d48840c4-d3e6-49e3-88ea-0682b33e8cb8</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>da4fcc85-22ac-481b-addf-21e4047018ac</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="n">
+        <v>46078.51117054823</v>
+      </c>
+      <c r="F389" t="n">
+        <v>50</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I389" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>4f01fa7d-fee5-412e-b8b3-a097e539f2e6</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>8c099825-0e00-42ab-aed1-9bcc3ce88c9c</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>46088.26117055114</v>
+      </c>
+      <c r="F390" t="n">
+        <v>228</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ada923bd-586b-4309-b3f8-567e9360ccf4</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>73fc9a67-9098-4274-86cf-310aa345714e</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>46078.59450389317</v>
+      </c>
+      <c r="F391" t="n">
+        <v>77</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I391" t="n">
+        <v>18.51</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>d47866ea-7cbd-436e-acf2-1c9e8670e813</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>bcc971a8-905a-4f4b-b4aa-d274c37721f4</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>46075.84450389617</v>
+      </c>
+      <c r="F392" t="n">
+        <v>279</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I392" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>ab9e2d86-40c8-486d-ac93-8184edc4fa26</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>c206dd25-25cb-48f8-8fb2-f2e135c6db25</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>46081.969503902</v>
+      </c>
+      <c r="F393" t="n">
+        <v>61</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>63a5b87e-3fb5-4a8d-8092-b07586b92522</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ea18cdc6-44ec-4839-8a92-88e7dea25555</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>46066.26117058604</v>
+      </c>
+      <c r="F394" t="n">
+        <v>62</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>fdab87f8-bb13-4410-990c-e0691b53dcd8</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>514839d7-a1bd-43bf-938e-012c877db275</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="n">
+        <v>46077.30283725866</v>
+      </c>
+      <c r="F395" t="n">
+        <v>240</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>880f8a91-d51d-485f-8b26-ddf51041e784</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>033f7bb8-f6c4-4624-ac08-cac683c3d702</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="n">
+        <v>46075.34450392823</v>
+      </c>
+      <c r="F396" t="n">
+        <v>206</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I396"/>
+  <dimension ref="A1:I422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>46067.42783711882</v>
+        <v>46067.42783711806</v>
       </c>
       <c r="F377" t="n">
         <v>284</v>
@@ -15917,7 +15917,7 @@
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>46085.26117045945</v>
+        <v>46085.26117046296</v>
       </c>
       <c r="F378" t="n">
         <v>36</v>
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>46066.17783712977</v>
+        <v>46066.17783712963</v>
       </c>
       <c r="F379" t="n">
         <v>197</v>
@@ -15999,7 +15999,7 @@
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>46074.09450379937</v>
+        <v>46074.0945037963</v>
       </c>
       <c r="F380" t="n">
         <v>81</v>
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="E381" s="2" t="n">
-        <v>46079.55283713571</v>
+        <v>46079.5528371412</v>
       </c>
       <c r="F381" t="n">
         <v>138</v>
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="E382" s="2" t="n">
-        <v>46067.09450382015</v>
+        <v>46067.09450381945</v>
       </c>
       <c r="F382" t="n">
         <v>266</v>
@@ -16122,7 +16122,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>46061.55283715942</v>
+        <v>46061.55283716435</v>
       </c>
       <c r="F383" t="n">
         <v>273</v>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="E384" s="2" t="n">
-        <v>46088.96950383791</v>
+        <v>46088.96950384259</v>
       </c>
       <c r="F384" t="n">
         <v>53</v>
@@ -16204,7 +16204,7 @@
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>46074.17783719148</v>
+        <v>46074.1778371875</v>
       </c>
       <c r="F385" t="n">
         <v>133</v>
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>46067.80283719447</v>
+        <v>46067.80283719907</v>
       </c>
       <c r="F386" t="n">
         <v>266</v>
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>46067.59450386418</v>
+        <v>46067.59450386574</v>
       </c>
       <c r="F387" t="n">
         <v>50</v>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>46075.92783720611</v>
+        <v>46075.92783721065</v>
       </c>
       <c r="F388" t="n">
         <v>58</v>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>46078.51117054823</v>
+        <v>46078.51117054398</v>
       </c>
       <c r="F389" t="n">
         <v>50</v>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>46088.26117055114</v>
+        <v>46088.26117055555</v>
       </c>
       <c r="F390" t="n">
         <v>228</v>
@@ -16450,7 +16450,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>46078.59450389317</v>
+        <v>46078.59450388889</v>
       </c>
       <c r="F391" t="n">
         <v>77</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>46075.84450389617</v>
+        <v>46075.84450390047</v>
       </c>
       <c r="F392" t="n">
         <v>279</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>46081.969503902</v>
+        <v>46081.96950390047</v>
       </c>
       <c r="F393" t="n">
         <v>61</v>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>46066.26117058604</v>
+        <v>46066.26117059027</v>
       </c>
       <c r="F394" t="n">
         <v>62</v>
@@ -16614,7 +16614,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>46077.30283725866</v>
+        <v>46077.30283725695</v>
       </c>
       <c r="F395" t="n">
         <v>240</v>
@@ -16655,7 +16655,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>46075.34450392823</v>
+        <v>46075.34450392361</v>
       </c>
       <c r="F396" t="n">
         <v>206</v>
@@ -16672,6 +16672,1072 @@
       </c>
       <c r="I396" t="n">
         <v>4.4</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>3befdc06-76d2-413d-84aa-4a1074208feb</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>e16dabbd-1d2f-4339-b1cc-80a62f94afdf</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="n">
+        <v>46088.42765186141</v>
+      </c>
+      <c r="F397" t="n">
+        <v>121</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>8.210000000000001</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>3a7b9aa3-dcfa-47c9-8a10-70eb4dadf86e</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>75590bbb-a494-4465-808f-fb6b375fdadc</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>46066.88598520249</v>
+      </c>
+      <c r="F398" t="n">
+        <v>288</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>16.09</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>75a724e1-cac6-4266-9f23-3b5d9788f3c2</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>c05580c4-7618-4be4-bd64-e4761cfbd829</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n">
+        <v>46081.88598520584</v>
+      </c>
+      <c r="F399" t="n">
+        <v>292</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>10.37</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>9d4cfd27-5350-4f93-bf9d-b8eed1eb3933</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>5c262d93-398c-47a2-aaec-f5b18e59b71c</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>46076.1359852091</v>
+      </c>
+      <c r="F400" t="n">
+        <v>208</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>16.93</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>6d17a3ea-8cd5-4a76-bd68-8f8ba2a9186a</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>3a1e969f-61d3-4dfb-af1d-5f71b64e4e69</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>46064.63598521262</v>
+      </c>
+      <c r="F401" t="n">
+        <v>282</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>eb2fab7c-ee68-4bc3-bc59-4602fa8bef16</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>a5f22db9-f22c-48bf-8821-f090f0715fdc</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="n">
+        <v>46066.96931855869</v>
+      </c>
+      <c r="F402" t="n">
+        <v>150</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>65242059-1c9a-4236-9174-112fa877eab8</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>a0fc3a9a-6d1d-4ceb-a400-06e51faa868d</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>46076.26098522881</v>
+      </c>
+      <c r="F403" t="n">
+        <v>66</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>15.63</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>d8e60cff-0c28-4211-9336-08a512deb245</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>94a7a421-2c32-4eba-b98f-00028e8790ec</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>46070.46931856536</v>
+      </c>
+      <c r="F404" t="n">
+        <v>159</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>b9b52d4b-588a-4c77-affd-8a3bae308449</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2462299b-6b78-4a77-a0c9-eb548d12cbd8</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>46086.71931857229</v>
+      </c>
+      <c r="F405" t="n">
+        <v>115</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>d27791a1-5342-4438-935d-cc46d67bcad4</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>93cdd32c-822a-41a4-9bca-2ca6611ee24e</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>46071.13598524546</v>
+      </c>
+      <c r="F406" t="n">
+        <v>273</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>17.79</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>4adbc66a-857d-4fc3-a156-8d37745ae2aa</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>93c7e2e9-e4c5-45dd-8616-427bf268accb</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>46084.92765194014</v>
+      </c>
+      <c r="F407" t="n">
+        <v>77</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>8c973edc-3057-4a4f-97be-fc721e5d6e04</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>3d654124-fe83-462a-b82d-21e7a83e7995</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>46082.92765194343</v>
+      </c>
+      <c r="F408" t="n">
+        <v>162</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>4bedf1c5-7c76-4302-a033-d977a1e73ae0</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>1ef489b9-c0a7-4c55-802a-cf1b486c0db6</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>46076.30265195615</v>
+      </c>
+      <c r="F409" t="n">
+        <v>66</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>13.07</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>3e90ae57-80f3-40c4-943e-7225d387b3c0</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>84d4c225-14b3-4210-a713-ce6c3e0fadee</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>46080.96931862627</v>
+      </c>
+      <c r="F410" t="n">
+        <v>197</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>8b17adb3-b222-46b9-b890-ab5884ac6dfc</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>63a26f9a-9e9b-4368-9f9b-bd08332ec7a8</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>46075.63598529808</v>
+      </c>
+      <c r="F411" t="n">
+        <v>154</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>29723e0f-50c4-4b96-8d31-d824f2c7cb16</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>60b90ee6-b3ae-40ef-bdab-ec0bdd121f56</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>46072.6776519681</v>
+      </c>
+      <c r="F412" t="n">
+        <v>232</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2f2566d7-03eb-441b-84dc-1011a9dd706c</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>55b1e94d-9df6-4841-b5ee-5b412113e0bf</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>46071.13598530818</v>
+      </c>
+      <c r="F413" t="n">
+        <v>164</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>15.03</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>3f4d6e57-171d-4164-bcd6-6714be73f489</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>1f8b29aa-a9bd-4f76-b8d7-833c35008aaa</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>46075.88598531468</v>
+      </c>
+      <c r="F414" t="n">
+        <v>228</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>76f84a0e-1ebf-4a8e-850b-7c9e24aa55d6</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>eb796adf-6fff-4250-9bce-7f3a9570c6de</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>46062.71931865127</v>
+      </c>
+      <c r="F415" t="n">
+        <v>123</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>f0f4fe86-183d-4d4f-a5ad-d19c79489fce</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1a87ac9c-baa7-406b-9aff-83ff08e44c5c</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>46071.96931865447</v>
+      </c>
+      <c r="F416" t="n">
+        <v>203</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>37aac5e0-c378-481e-8a88-adcf59b80f43</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>3a903d55-0e13-45e3-8d8d-e28bbe73d6b6</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>46084.01098532767</v>
+      </c>
+      <c r="F417" t="n">
+        <v>73</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>ebf1cc9d-44c8-4593-b740-6671a0a8d131</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>b2c3c351-caf6-4ce5-9fc6-2d9a8d2e6d46</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>46083.38598533093</v>
+      </c>
+      <c r="F418" t="n">
+        <v>244</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>25f069cb-d54b-4387-8f06-cf8644724734</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>93b274b8-690e-4871-a1c3-36862a74250c</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>46065.17765200089</v>
+      </c>
+      <c r="F419" t="n">
+        <v>91</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>9.720000000000001</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>f1a56ec9-df63-4bd8-8aa9-29f126010290</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>355c8edc-4a3f-47a4-91ba-28bdbe68d261</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>46062.84431867089</v>
+      </c>
+      <c r="F420" t="n">
+        <v>242</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>528f0a0d-6494-418a-9cce-cdf5186ee75b</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ef4e1cc5-1f3e-4126-bc4f-0c0a79bf15c4</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>46062.67765200746</v>
+      </c>
+      <c r="F421" t="n">
+        <v>286</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>c7b4a4ed-72df-4fd6-a11a-6ffec4110d0d</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>6a5abde0-66d5-4855-bdcf-adfda2dd7fa9</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>46068.71931868397</v>
+      </c>
+      <c r="F422" t="n">
+        <v>172</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I422"/>
+  <dimension ref="A1:I451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16696,7 +16696,7 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>46088.42765186141</v>
+        <v>46088.42765186343</v>
       </c>
       <c r="F397" t="n">
         <v>121</v>
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>46066.88598520249</v>
+        <v>46066.88598519676</v>
       </c>
       <c r="F398" t="n">
         <v>288</v>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>46081.88598520584</v>
+        <v>46081.88598520833</v>
       </c>
       <c r="F399" t="n">
         <v>292</v>
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>46076.1359852091</v>
+        <v>46076.13598520833</v>
       </c>
       <c r="F400" t="n">
         <v>208</v>
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>46064.63598521262</v>
+        <v>46064.63598520833</v>
       </c>
       <c r="F401" t="n">
         <v>282</v>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>46066.96931855869</v>
+        <v>46066.96931855324</v>
       </c>
       <c r="F402" t="n">
         <v>150</v>
@@ -16942,7 +16942,7 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>46076.26098522881</v>
+        <v>46076.26098523148</v>
       </c>
       <c r="F403" t="n">
         <v>66</v>
@@ -16983,7 +16983,7 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>46070.46931856536</v>
+        <v>46070.46931856481</v>
       </c>
       <c r="F404" t="n">
         <v>159</v>
@@ -17024,7 +17024,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>46086.71931857229</v>
+        <v>46086.71931857639</v>
       </c>
       <c r="F405" t="n">
         <v>115</v>
@@ -17065,7 +17065,7 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>46071.13598524546</v>
+        <v>46071.13598524305</v>
       </c>
       <c r="F406" t="n">
         <v>273</v>
@@ -17106,7 +17106,7 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>46084.92765194014</v>
+        <v>46084.92765194445</v>
       </c>
       <c r="F407" t="n">
         <v>77</v>
@@ -17147,7 +17147,7 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>46082.92765194343</v>
+        <v>46082.92765194445</v>
       </c>
       <c r="F408" t="n">
         <v>162</v>
@@ -17188,7 +17188,7 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>46076.30265195615</v>
+        <v>46076.30265195602</v>
       </c>
       <c r="F409" t="n">
         <v>66</v>
@@ -17229,7 +17229,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>46080.96931862627</v>
+        <v>46080.96931862269</v>
       </c>
       <c r="F410" t="n">
         <v>197</v>
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>46075.63598529808</v>
+        <v>46075.63598530093</v>
       </c>
       <c r="F411" t="n">
         <v>154</v>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>46072.6776519681</v>
+        <v>46072.67765196759</v>
       </c>
       <c r="F412" t="n">
         <v>232</v>
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>46071.13598530818</v>
+        <v>46071.1359853125</v>
       </c>
       <c r="F413" t="n">
         <v>164</v>
@@ -17393,7 +17393,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>46075.88598531468</v>
+        <v>46075.8859853125</v>
       </c>
       <c r="F414" t="n">
         <v>228</v>
@@ -17434,7 +17434,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>46062.71931865127</v>
+        <v>46062.71931864583</v>
       </c>
       <c r="F415" t="n">
         <v>123</v>
@@ -17475,7 +17475,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>46071.96931865447</v>
+        <v>46071.96931865741</v>
       </c>
       <c r="F416" t="n">
         <v>203</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>46084.01098532767</v>
+        <v>46084.01098532407</v>
       </c>
       <c r="F417" t="n">
         <v>73</v>
@@ -17557,7 +17557,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>46083.38598533093</v>
+        <v>46083.38598533565</v>
       </c>
       <c r="F418" t="n">
         <v>244</v>
@@ -17598,7 +17598,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>46065.17765200089</v>
+        <v>46065.17765200231</v>
       </c>
       <c r="F419" t="n">
         <v>91</v>
@@ -17639,7 +17639,7 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>46062.84431867089</v>
+        <v>46062.84431866898</v>
       </c>
       <c r="F420" t="n">
         <v>242</v>
@@ -17680,7 +17680,7 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>46062.67765200746</v>
+        <v>46062.67765200231</v>
       </c>
       <c r="F421" t="n">
         <v>286</v>
@@ -17721,7 +17721,7 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>46068.71931868397</v>
+        <v>46068.71931868055</v>
       </c>
       <c r="F422" t="n">
         <v>172</v>
@@ -17738,6 +17738,1195 @@
       </c>
       <c r="I422" t="n">
         <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>742bbba6-93da-47a6-992d-38743bbd0a02</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>625f52a0-1520-4bd3-97b6-b0c003143539</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>46066.26118255514</v>
+      </c>
+      <c r="F423" t="n">
+        <v>35</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>16.71</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>97e23f1a-dd14-4206-b651-748a4034c646</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>07b46a48-c32d-491a-9210-a12786071a4a</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>46077.67784922865</v>
+      </c>
+      <c r="F424" t="n">
+        <v>109</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>9dd748e8-9bef-483f-9501-bc03ee42ce0e</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>21597957-c0db-41d6-bb3f-ac139cb59066</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>46065.63618256528</v>
+      </c>
+      <c r="F425" t="n">
+        <v>298</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>fd944fa2-d39f-4d56-b776-191e14b417a8</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>8ed4a7ac-c2b0-4df3-8f21-fd1cd62b1d69</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>46070.42784923852</v>
+      </c>
+      <c r="F426" t="n">
+        <v>41</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>3cb6c52a-6146-43b0-b902-56d992fe4704</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>c21bb342-4ef3-496e-8d68-0524a60aff18</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>46083.67784924832</v>
+      </c>
+      <c r="F427" t="n">
+        <v>90</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>0851b95e-fdd9-49eb-af78-983cc6912183</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>b458fe90-081c-4487-9d3c-18c13a5ba00c</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>46065.30284925168</v>
+      </c>
+      <c r="F428" t="n">
+        <v>88</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>4f30049a-0ad6-438c-948b-b32292ac8555</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>7247395f-ae70-4d17-869d-ba90f4071ca3</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>46068.51118259205</v>
+      </c>
+      <c r="F429" t="n">
+        <v>230</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>18.54</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>0453ba04-40c9-46b6-b0ba-ae7321763dbf</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>8e5661d9-114a-41c9-aefd-06f82e213f68</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>46086.30284926199</v>
+      </c>
+      <c r="F430" t="n">
+        <v>267</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>fb74104b-c7c5-4f1a-a7e7-5d0c10009147</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>4120ab62-081e-46e2-841a-b1c488ff23a1</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>46087.09451593523</v>
+      </c>
+      <c r="F431" t="n">
+        <v>233</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>94f916a3-4448-49c1-9925-48edc6c27c1d</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2a7e856a-a4d4-4689-9fb8-5b8ba31b3756</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>46077.42784927483</v>
+      </c>
+      <c r="F432" t="n">
+        <v>251</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>15.53</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>3a29e9bf-6fa7-46da-8d03-739f1ad41bf0</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>a1229b92-505f-4ab9-b33d-c478f6308440</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>46085.05284927809</v>
+      </c>
+      <c r="F433" t="n">
+        <v>77</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>19.02</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>662d4e2e-1bca-4d6f-9bc4-01bdea9b8f4a</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>e14b5a01-a9d3-494e-8a27-25ba8b85ee8e</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="n">
+        <v>46080.55284928159</v>
+      </c>
+      <c r="F434" t="n">
+        <v>181</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>fd6d1d42-0a9e-488f-90e7-578b3e63615b</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2e65af93-0eae-451b-9fb3-7912b544f47d</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>46075.92784928485</v>
+      </c>
+      <c r="F435" t="n">
+        <v>249</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>f3221ab3-4e4c-4b78-8424-a352cb7afd31</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>05cb4225-a92a-4b1c-ad0e-e6b4530089e8</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="n">
+        <v>46084.88618262453</v>
+      </c>
+      <c r="F436" t="n">
+        <v>268</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>e34a6680-32db-48d2-86c8-852224a66d16</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ab22b40c-6d45-4e73-a538-89c7cf7d755b</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="n">
+        <v>46086.71951596445</v>
+      </c>
+      <c r="F437" t="n">
+        <v>226</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>8aa8fed8-438b-4a11-aaa4-3f1491adc8a9</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>6dc962e0-af41-4d57-8529-0ebf8d4b407f</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="n">
+        <v>46061.5945159677</v>
+      </c>
+      <c r="F438" t="n">
+        <v>53</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>f7920bbf-fb88-465a-a502-1347fcd16537</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>0fcdccd1-01f3-4b93-a474-c9848e91901d</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="n">
+        <v>46061.5528493048</v>
+      </c>
+      <c r="F439" t="n">
+        <v>92</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>bbbfe89a-4a66-441d-8f11-adec421db590</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>443d6df9-8566-47a9-824d-5d34e62427cb</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="n">
+        <v>46073.42784930806</v>
+      </c>
+      <c r="F440" t="n">
+        <v>70</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>7d0d3269-ca8a-47e7-a273-5e7bd628e1dc</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>c62bf95e-c6c8-439b-b4cb-6e309c8411e4</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="n">
+        <v>46074.26118264463</v>
+      </c>
+      <c r="F441" t="n">
+        <v>33</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>18.14</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>8b8635dc-4921-4b90-b1b7-0ba103b926ce</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>9b20e40b-700b-4b39-a46b-ab9c2b223a71</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="n">
+        <v>46077.30284932105</v>
+      </c>
+      <c r="F442" t="n">
+        <v>61</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>17.96</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>7d810b14-a345-4157-a12f-840fd1241b53</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>129b97e9-ebb1-4bf0-b2f4-0eb5ccb772b6</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="n">
+        <v>46064.42784932427</v>
+      </c>
+      <c r="F443" t="n">
+        <v>118</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>8dcda335-55e5-4857-a135-46d2ace06bd9</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>7b860a4a-3b9d-44d3-8d59-89a0019578da</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="n">
+        <v>46086.80284933686</v>
+      </c>
+      <c r="F444" t="n">
+        <v>275</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>91fc52ed-53bc-482f-8cee-8288e2a1804b</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>e31a35e5-4a85-45f3-9102-4681e89d57f7</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="n">
+        <v>46072.38618267373</v>
+      </c>
+      <c r="F445" t="n">
+        <v>263</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>19.34</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>d025534f-cd65-4276-a8f8-ea16cea59e97</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2d4f2c47-efb3-405c-961e-8222f25fe1f9</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="n">
+        <v>46067.8028493436</v>
+      </c>
+      <c r="F446" t="n">
+        <v>185</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>0ac8e661-a9d6-46ac-9a94-253a74ac42e6</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>4f9bd536-2a22-48f1-b5f7-81168938ffa5</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="n">
+        <v>46066.21951601723</v>
+      </c>
+      <c r="F447" t="n">
+        <v>64</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>ba474a0b-94a8-4067-b3ba-3f4f981a1d65</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2202438b-1dff-42c1-9b7b-7c61b98889fc</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="n">
+        <v>46067.21951602664</v>
+      </c>
+      <c r="F448" t="n">
+        <v>39</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1355808d-e85c-4d2b-b826-d61f139fbb65</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>89576101-332f-4f69-939f-096d83372f1e</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="n">
+        <v>46062.88618269685</v>
+      </c>
+      <c r="F449" t="n">
+        <v>115</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>14.02</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ed37109a-8b4f-409b-b5df-6aed956cccaa</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>f1c14c1a-2da4-4d81-aae1-924627ac801c</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="n">
+        <v>46068.01118270647</v>
+      </c>
+      <c r="F450" t="n">
+        <v>234</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>b6957d4c-435f-408c-a80a-fa79106cd78b</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>d26d6c86-f71f-43f1-9755-3fdfea12200a</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="n">
+        <v>46066.80284937933</v>
+      </c>
+      <c r="F451" t="n">
+        <v>125</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>2.65</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I451"/>
+  <dimension ref="A1:I472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17762,7 +17762,7 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>46066.26118255514</v>
+        <v>46066.26118255787</v>
       </c>
       <c r="F423" t="n">
         <v>35</v>
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>46077.67784922865</v>
+        <v>46077.67784922454</v>
       </c>
       <c r="F424" t="n">
         <v>109</v>
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>46065.63618256528</v>
+        <v>46065.63618256945</v>
       </c>
       <c r="F425" t="n">
         <v>298</v>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>46070.42784923852</v>
+        <v>46070.42784923611</v>
       </c>
       <c r="F426" t="n">
         <v>41</v>
@@ -17926,7 +17926,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>46083.67784924832</v>
+        <v>46083.67784924769</v>
       </c>
       <c r="F427" t="n">
         <v>90</v>
@@ -17967,7 +17967,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>46065.30284925168</v>
+        <v>46065.30284924769</v>
       </c>
       <c r="F428" t="n">
         <v>88</v>
@@ -18008,7 +18008,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>46068.51118259205</v>
+        <v>46068.51118259259</v>
       </c>
       <c r="F429" t="n">
         <v>230</v>
@@ -18049,7 +18049,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>46086.30284926199</v>
+        <v>46086.30284925926</v>
       </c>
       <c r="F430" t="n">
         <v>267</v>
@@ -18090,7 +18090,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>46087.09451593523</v>
+        <v>46087.0945159375</v>
       </c>
       <c r="F431" t="n">
         <v>233</v>
@@ -18131,7 +18131,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>46077.42784927483</v>
+        <v>46077.42784927083</v>
       </c>
       <c r="F432" t="n">
         <v>251</v>
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>46085.05284927809</v>
+        <v>46085.05284928241</v>
       </c>
       <c r="F433" t="n">
         <v>77</v>
@@ -18213,7 +18213,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>46080.55284928159</v>
+        <v>46080.55284928241</v>
       </c>
       <c r="F434" t="n">
         <v>181</v>
@@ -18254,7 +18254,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>46075.92784928485</v>
+        <v>46075.92784928241</v>
       </c>
       <c r="F435" t="n">
         <v>249</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>46084.88618262453</v>
+        <v>46084.88618262731</v>
       </c>
       <c r="F436" t="n">
         <v>268</v>
@@ -18336,7 +18336,7 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>46086.71951596445</v>
+        <v>46086.71951596065</v>
       </c>
       <c r="F437" t="n">
         <v>226</v>
@@ -18377,7 +18377,7 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>46061.5945159677</v>
+        <v>46061.59451597223</v>
       </c>
       <c r="F438" t="n">
         <v>53</v>
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>46061.5528493048</v>
+        <v>46061.55284930555</v>
       </c>
       <c r="F439" t="n">
         <v>92</v>
@@ -18459,7 +18459,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>46073.42784930806</v>
+        <v>46073.42784930555</v>
       </c>
       <c r="F440" t="n">
         <v>70</v>
@@ -18500,7 +18500,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>46074.26118264463</v>
+        <v>46074.26118263889</v>
       </c>
       <c r="F441" t="n">
         <v>33</v>
@@ -18541,7 +18541,7 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>46077.30284932105</v>
+        <v>46077.30284931713</v>
       </c>
       <c r="F442" t="n">
         <v>61</v>
@@ -18582,7 +18582,7 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>46064.42784932427</v>
+        <v>46064.42784932871</v>
       </c>
       <c r="F443" t="n">
         <v>118</v>
@@ -18623,7 +18623,7 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>46086.80284933686</v>
+        <v>46086.80284934027</v>
       </c>
       <c r="F444" t="n">
         <v>275</v>
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>46072.38618267373</v>
+        <v>46072.38618267361</v>
       </c>
       <c r="F445" t="n">
         <v>263</v>
@@ -18705,7 +18705,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>46067.8028493436</v>
+        <v>46067.80284934027</v>
       </c>
       <c r="F446" t="n">
         <v>185</v>
@@ -18746,7 +18746,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>46066.21951601723</v>
+        <v>46066.21951601852</v>
       </c>
       <c r="F447" t="n">
         <v>64</v>
@@ -18787,7 +18787,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>46067.21951602664</v>
+        <v>46067.21951603009</v>
       </c>
       <c r="F448" t="n">
         <v>39</v>
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>46062.88618269685</v>
+        <v>46062.88618269676</v>
       </c>
       <c r="F449" t="n">
         <v>115</v>
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>46068.01118270647</v>
+        <v>46068.01118270833</v>
       </c>
       <c r="F450" t="n">
         <v>234</v>
@@ -18910,7 +18910,7 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>46066.80284937933</v>
+        <v>46066.802849375</v>
       </c>
       <c r="F451" t="n">
         <v>125</v>
@@ -18927,6 +18927,867 @@
       </c>
       <c r="I451" t="n">
         <v>2.65</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>cfd7c846-8925-4701-b2d3-8c7ea0b8b34c</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>19c89a45-aa5b-42a7-a4c4-f37c45aabfa6</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="n">
+        <v>46085.30567037634</v>
+      </c>
+      <c r="F452" t="n">
+        <v>100</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>d1448fab-54ad-4a42-a64e-e1ea225fbc8f</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>c836f447-2e61-4e2d-93e6-40c39cb154f4</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="n">
+        <v>46069.30567037963</v>
+      </c>
+      <c r="F453" t="n">
+        <v>109</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>14ad49f1-f0d8-4a89-b87e-bb614b694138</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>63ddbf74-1643-45a2-9ec6-d121cb1b59a1</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="n">
+        <v>46084.34733708126</v>
+      </c>
+      <c r="F454" t="n">
+        <v>132</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>17.06</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>6920db7f-1826-45d9-8754-c39cdb63ce77</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>b4477b36-8d6b-4bfa-8342-f947487f970d</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="n">
+        <v>46091.18067041774</v>
+      </c>
+      <c r="F455" t="n">
+        <v>293</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>82207ae5-fa0f-4482-a902-856a8ef3486e</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>4a9cb2bb-1014-48da-9937-60401e10b680</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="n">
+        <v>46069.63900375443</v>
+      </c>
+      <c r="F456" t="n">
+        <v>125</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>df8e3e3c-d43d-4cab-abd4-e3b092d7b4ec</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>0d6bfacf-0d3c-4e53-8b7d-c70341d3949a</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="n">
+        <v>46089.59733710044</v>
+      </c>
+      <c r="F457" t="n">
+        <v>126</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>31d089e5-57ee-47a9-9a9f-f35646490c53</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>c5ace0d9-ce34-4d25-94c8-c819aef3c171</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="n">
+        <v>46067.13900378929</v>
+      </c>
+      <c r="F458" t="n">
+        <v>201</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>5de2cbf2-9e7d-4c51-ba2e-86cda6bf4fc0</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>c0568aea-d541-4170-ba5b-38da5ce5ae4f</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="n">
+        <v>46069.30567046218</v>
+      </c>
+      <c r="F459" t="n">
+        <v>271</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>16efca68-fc1f-4a11-a961-8e9557c426c1</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>3f1b1d8a-1e2c-4b9d-8dd8-936c29080361</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="n">
+        <v>46072.38900379881</v>
+      </c>
+      <c r="F460" t="n">
+        <v>49</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>b4d84b68-ff3f-4cb7-828f-3423478f91f7</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>b8c0a864-7562-46c7-894c-47370b646b8c</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="n">
+        <v>46076.30567046876</v>
+      </c>
+      <c r="F461" t="n">
+        <v>32</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>13.68</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>79b6695f-88eb-4c79-96c0-5240c1671f9f</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>7f883c33-d214-4625-b546-6d594d62c7ac</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="n">
+        <v>46063.43067047193</v>
+      </c>
+      <c r="F462" t="n">
+        <v>96</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>16988602-e514-4125-a264-5811efbbe594</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>5cae1cf4-f2db-4493-aa63-af54df75d896</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="n">
+        <v>46072.01400381183</v>
+      </c>
+      <c r="F463" t="n">
+        <v>221</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>837362c8-3fd4-4766-9fc2-76244b469f47</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>0bb142ac-6ba7-4e2e-acae-c5ac023342df</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="n">
+        <v>46084.38900381498</v>
+      </c>
+      <c r="F464" t="n">
+        <v>55</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>11.16</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>134a085a-865c-40af-b0e3-e92f941868d7</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>f712fc12-f343-4248-8ce4-8649ce06a500</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="n">
+        <v>46081.22233715445</v>
+      </c>
+      <c r="F465" t="n">
+        <v>106</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>12.24</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>c8739490-4e29-4cd6-a531-28f0811583f2</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>26b04a3b-76b1-4ffa-ba1a-982a51f09914</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="n">
+        <v>46065.80567049114</v>
+      </c>
+      <c r="F466" t="n">
+        <v>172</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>66760467-9ada-44a0-88e3-1cc03d25a03a</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ed88fb44-c86b-4715-a767-834c2848c74e</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="n">
+        <v>46089.80567049731</v>
+      </c>
+      <c r="F467" t="n">
+        <v>112</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>a1983074-9104-42b3-9b51-550ef98a7c14</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>3f17a970-39db-4117-85be-a95d593c2536</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="n">
+        <v>46076.26400383394</v>
+      </c>
+      <c r="F468" t="n">
+        <v>133</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>13.95</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>26543b4e-61de-4b09-9fda-281c2c12f891</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>843a114b-443f-4556-b73b-2876fcff2f82</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="n">
+        <v>46062.05567050973</v>
+      </c>
+      <c r="F469" t="n">
+        <v>289</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>bd60e08d-9c48-4540-991b-7f4c2424d4d2</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>e55383eb-f12d-4688-ad53-c70b1cbcae49</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="n">
+        <v>46071.38900384946</v>
+      </c>
+      <c r="F470" t="n">
+        <v>286</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>13.63</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>712c29a7-39be-46aa-abb3-026fcf76dca3</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>57c46f50-a180-4588-9da7-adac5f8b862e</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="n">
+        <v>46069.51400385255</v>
+      </c>
+      <c r="F471" t="n">
+        <v>238</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>4cb7228b-9b50-45d0-9209-399c1d51f541</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>9c6e2f28-7db4-4bd1-8fce-f4b1fb405422</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="n">
+        <v>46077.76400385931</v>
+      </c>
+      <c r="F472" t="n">
+        <v>274</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>5.05</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I472"/>
+  <dimension ref="A1:I489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18951,7 +18951,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>46085.30567037634</v>
+        <v>46085.30567038195</v>
       </c>
       <c r="F452" t="n">
         <v>100</v>
@@ -18992,7 +18992,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>46069.30567037963</v>
+        <v>46069.30567038195</v>
       </c>
       <c r="F453" t="n">
         <v>109</v>
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>46084.34733708126</v>
+        <v>46084.34733708333</v>
       </c>
       <c r="F454" t="n">
         <v>132</v>
@@ -19074,7 +19074,7 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>46091.18067041774</v>
+        <v>46091.18067041667</v>
       </c>
       <c r="F455" t="n">
         <v>293</v>
@@ -19115,7 +19115,7 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>46069.63900375443</v>
+        <v>46069.63900375</v>
       </c>
       <c r="F456" t="n">
         <v>125</v>
@@ -19156,7 +19156,7 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>46089.59733710044</v>
+        <v>46089.59733709491</v>
       </c>
       <c r="F457" t="n">
         <v>126</v>
@@ -19197,7 +19197,7 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>46067.13900378929</v>
+        <v>46067.13900378472</v>
       </c>
       <c r="F458" t="n">
         <v>201</v>
@@ -19238,7 +19238,7 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>46069.30567046218</v>
+        <v>46069.30567046296</v>
       </c>
       <c r="F459" t="n">
         <v>271</v>
@@ -19279,7 +19279,7 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>46072.38900379881</v>
+        <v>46072.3890037963</v>
       </c>
       <c r="F460" t="n">
         <v>49</v>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>46076.30567046876</v>
+        <v>46076.30567047454</v>
       </c>
       <c r="F461" t="n">
         <v>32</v>
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>46063.43067047193</v>
+        <v>46063.43067047454</v>
       </c>
       <c r="F462" t="n">
         <v>96</v>
@@ -19402,7 +19402,7 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>46072.01400381183</v>
+        <v>46072.01400380787</v>
       </c>
       <c r="F463" t="n">
         <v>221</v>
@@ -19443,7 +19443,7 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>46084.38900381498</v>
+        <v>46084.38900381944</v>
       </c>
       <c r="F464" t="n">
         <v>55</v>
@@ -19484,7 +19484,7 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>46081.22233715445</v>
+        <v>46081.22233715278</v>
       </c>
       <c r="F465" t="n">
         <v>106</v>
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>46065.80567049114</v>
+        <v>46065.80567048611</v>
       </c>
       <c r="F466" t="n">
         <v>172</v>
@@ -19566,7 +19566,7 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>46089.80567049731</v>
+        <v>46089.80567049768</v>
       </c>
       <c r="F467" t="n">
         <v>112</v>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>46076.26400383394</v>
+        <v>46076.26400383102</v>
       </c>
       <c r="F468" t="n">
         <v>133</v>
@@ -19648,7 +19648,7 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>46062.05567050973</v>
+        <v>46062.05567050926</v>
       </c>
       <c r="F469" t="n">
         <v>289</v>
@@ -19689,7 +19689,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>46071.38900384946</v>
+        <v>46071.38900385416</v>
       </c>
       <c r="F470" t="n">
         <v>286</v>
@@ -19730,7 +19730,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>46069.51400385255</v>
+        <v>46069.51400385416</v>
       </c>
       <c r="F471" t="n">
         <v>238</v>
@@ -19771,7 +19771,7 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>46077.76400385931</v>
+        <v>46077.76400385416</v>
       </c>
       <c r="F472" t="n">
         <v>274</v>
@@ -19788,6 +19788,703 @@
       </c>
       <c r="I472" t="n">
         <v>5.05</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>bef846be-90f6-475c-b0b9-6b82113e83b2</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>6eb81ee1-6e66-41bc-9aed-38095788779f</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="n">
+        <v>46060.83983111622</v>
+      </c>
+      <c r="F473" t="n">
+        <v>197</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>af675207-0344-452e-8a04-baacf345219c</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>f021a564-f38d-4a0a-b157-17e169e61a38</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="n">
+        <v>46062.42316446183</v>
+      </c>
+      <c r="F474" t="n">
+        <v>147</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>f5f7dc07-13c2-4cca-91cd-9aba76c1b99f</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ac1cc16c-c20a-4c98-827a-b36c83d66644</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="n">
+        <v>46087.50649780969</v>
+      </c>
+      <c r="F475" t="n">
+        <v>111</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>13.66</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>3a81aaa1-ea69-498e-aee1-64b2ba72f89f</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>91b0138d-aecb-43cc-b23d-5d29a1db951f</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="n">
+        <v>46076.29816448507</v>
+      </c>
+      <c r="F476" t="n">
+        <v>261</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>3721214f-a030-4966-8546-c0c42dbbecdf</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>177bf079-0211-4389-8503-686b1f1a1a6d</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="n">
+        <v>46077.08983116035</v>
+      </c>
+      <c r="F477" t="n">
+        <v>142</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>73a2bfb4-4c00-45ee-9e57-835acbaa72ca</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>bfc165f5-879e-485f-a379-7a153e0cb1f7</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="n">
+        <v>46082.42316450816</v>
+      </c>
+      <c r="F478" t="n">
+        <v>35</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>19.68</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>01992c3d-3fdd-4e72-9e3d-66e2c028e1a3</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>c49fa654-d4bc-423d-9713-72190c1a1eb5</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="n">
+        <v>46068.58983117773</v>
+      </c>
+      <c r="F479" t="n">
+        <v>63</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>a693ab1b-d034-40be-8574-a9b8f52b9f52</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>d17e70c4-6cfb-4fcb-ab96-cf70cb5d3c51</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="n">
+        <v>46081.33983118348</v>
+      </c>
+      <c r="F480" t="n">
+        <v>288</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>a4750816-96d1-4929-8015-5609e24969e6</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>87536869-7fa6-422f-825f-36f07177e404</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="n">
+        <v>46083.33983120374</v>
+      </c>
+      <c r="F481" t="n">
+        <v>118</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>e7ef7f68-f343-4d9c-a4c4-d9706fa7ca24</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>7da06451-7637-4e8e-a945-bbd0f9c4c823</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="n">
+        <v>46071.3398312125</v>
+      </c>
+      <c r="F482" t="n">
+        <v>107</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>14.22</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>167fe122-e34f-46bb-8fcd-be10b0e8cefd</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>03edb0d7-86ad-4298-85bb-d8383182d0e5</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="n">
+        <v>46070.71483122668</v>
+      </c>
+      <c r="F483" t="n">
+        <v>32</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>11.04</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>a512c82e-84ee-449b-871e-8e3a0220f20f</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>4c573721-54ef-44ec-b407-144c237e2596</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="n">
+        <v>46062.42316456295</v>
+      </c>
+      <c r="F484" t="n">
+        <v>230</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>5218954c-8e4e-4ca8-a208-f3412c413f70</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>53d03aa6-8b91-4402-afc5-18e0a2422c7d</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="n">
+        <v>46071.83983123826</v>
+      </c>
+      <c r="F485" t="n">
+        <v>246</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>13.73</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>5abe27bd-139b-4f9a-9ef3-f9aaf767a326</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>be6fbd69-e5c9-47ac-94c5-a6eddb3ee14c</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="n">
+        <v>46082.71483124405</v>
+      </c>
+      <c r="F486" t="n">
+        <v>38</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>857485d6-d1ff-4b71-ade6-be67b26b84bb</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>0bdb2e56-1f52-4ed9-a45a-a0069354e994</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="n">
+        <v>46069.04816458028</v>
+      </c>
+      <c r="F487" t="n">
+        <v>233</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>41d1634e-bd05-4330-bfbb-ef0ecf2a98ab</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>c559c979-3a78-4837-9383-c508d34515c8</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="n">
+        <v>46063.71483125272</v>
+      </c>
+      <c r="F488" t="n">
+        <v>230</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>18.59</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>04efdc69-67d3-4bd2-89a6-0a7b29f81c30</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>db3046ee-b42d-4d8f-86d3-2f3c746bcd21</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="n">
+        <v>46073.92316458908</v>
+      </c>
+      <c r="F489" t="n">
+        <v>114</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>12.86</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I489"/>
+  <dimension ref="A1:I508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>46060.83983111622</v>
+        <v>46060.83983111111</v>
       </c>
       <c r="F473" t="n">
         <v>197</v>
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>46062.42316446183</v>
+        <v>46062.42316446759</v>
       </c>
       <c r="F474" t="n">
         <v>147</v>
@@ -19894,7 +19894,7 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>46087.50649780969</v>
+        <v>46087.5064978125</v>
       </c>
       <c r="F475" t="n">
         <v>111</v>
@@ -19935,7 +19935,7 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>46076.29816448507</v>
+        <v>46076.29816449074</v>
       </c>
       <c r="F476" t="n">
         <v>261</v>
@@ -19976,7 +19976,7 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>46077.08983116035</v>
+        <v>46077.08983115741</v>
       </c>
       <c r="F477" t="n">
         <v>142</v>
@@ -20017,7 +20017,7 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>46082.42316450816</v>
+        <v>46082.42316451389</v>
       </c>
       <c r="F478" t="n">
         <v>35</v>
@@ -20058,7 +20058,7 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>46068.58983117773</v>
+        <v>46068.58983118056</v>
       </c>
       <c r="F479" t="n">
         <v>63</v>
@@ -20099,7 +20099,7 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>46081.33983118348</v>
+        <v>46081.33983118056</v>
       </c>
       <c r="F480" t="n">
         <v>288</v>
@@ -20140,7 +20140,7 @@
         </is>
       </c>
       <c r="E481" s="2" t="n">
-        <v>46083.33983120374</v>
+        <v>46083.3398312037</v>
       </c>
       <c r="F481" t="n">
         <v>118</v>
@@ -20181,7 +20181,7 @@
         </is>
       </c>
       <c r="E482" s="2" t="n">
-        <v>46071.3398312125</v>
+        <v>46071.33983121528</v>
       </c>
       <c r="F482" t="n">
         <v>107</v>
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="E483" s="2" t="n">
-        <v>46070.71483122668</v>
+        <v>46070.71483122685</v>
       </c>
       <c r="F483" t="n">
         <v>32</v>
@@ -20263,7 +20263,7 @@
         </is>
       </c>
       <c r="E484" s="2" t="n">
-        <v>46062.42316456295</v>
+        <v>46062.42316456018</v>
       </c>
       <c r="F484" t="n">
         <v>230</v>
@@ -20304,7 +20304,7 @@
         </is>
       </c>
       <c r="E485" s="2" t="n">
-        <v>46071.83983123826</v>
+        <v>46071.83983123842</v>
       </c>
       <c r="F485" t="n">
         <v>246</v>
@@ -20345,7 +20345,7 @@
         </is>
       </c>
       <c r="E486" s="2" t="n">
-        <v>46082.71483124405</v>
+        <v>46082.71483123842</v>
       </c>
       <c r="F486" t="n">
         <v>38</v>
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="E487" s="2" t="n">
-        <v>46069.04816458028</v>
+        <v>46069.04816458334</v>
       </c>
       <c r="F487" t="n">
         <v>233</v>
@@ -20427,7 +20427,7 @@
         </is>
       </c>
       <c r="E488" s="2" t="n">
-        <v>46063.71483125272</v>
+        <v>46063.71483125</v>
       </c>
       <c r="F488" t="n">
         <v>230</v>
@@ -20468,7 +20468,7 @@
         </is>
       </c>
       <c r="E489" s="2" t="n">
-        <v>46073.92316458908</v>
+        <v>46073.92316458334</v>
       </c>
       <c r="F489" t="n">
         <v>114</v>
@@ -20485,6 +20485,785 @@
       </c>
       <c r="I489" t="n">
         <v>12.86</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>12ac5c84-7f67-46a8-a927-51a14d1c415e</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>c1afc87a-643f-4914-a4a9-ffc8466f3eb3</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="n">
+        <v>46088.49482821159</v>
+      </c>
+      <c r="F490" t="n">
+        <v>138</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>14.61</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>41d368dd-fc3e-46d6-9b0d-042354a42e74</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>13273bba-d933-4a91-938a-a7f7b28e8890</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="n">
+        <v>46081.82816155596</v>
+      </c>
+      <c r="F491" t="n">
+        <v>192</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>f16b9a11-f59e-4680-911a-87bc8d1e52d3</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>09a0a469-10fd-41c9-b065-4effe35e04bb</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="n">
+        <v>46084.45316156915</v>
+      </c>
+      <c r="F492" t="n">
+        <v>158</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>18426bfb-b198-4edd-89be-ede8b8d1aef5</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>41781fb9-cd8a-47b8-9969-51c7327ca9b0</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="n">
+        <v>46071.78649490578</v>
+      </c>
+      <c r="F493" t="n">
+        <v>162</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>17.55</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>b491dcc9-04bc-407a-9d7d-9a311b93575f</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2e77154a-a2df-42fc-bd9b-331b1db91f45</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="n">
+        <v>46085.99482824239</v>
+      </c>
+      <c r="F494" t="n">
+        <v>105</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>18.81</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>4dffd7c9-0ada-40f4-bd76-ff63cd2b079f</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>8508e6e9-6400-4104-bda2-c827580f5781</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="n">
+        <v>46074.28649491249</v>
+      </c>
+      <c r="F495" t="n">
+        <v>263</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>13.36</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>95f7b019-6aed-482b-b1c6-4d092fb4d2af</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>a1c8ebe8-e479-481d-9f8d-bab0fbefd54e</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="n">
+        <v>46082.78649492214</v>
+      </c>
+      <c r="F496" t="n">
+        <v>181</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>369942c4-0dd6-4241-826b-f55924e60235</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>3e3e5545-d4d8-4bfa-bbfd-cd13ac788188</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="n">
+        <v>46088.03649493169</v>
+      </c>
+      <c r="F497" t="n">
+        <v>98</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>73991c4b-a969-4df5-9461-7f9808c58c77</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>10924f7b-09ee-4478-bc3b-610693f8af29</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="n">
+        <v>46061.86982827468</v>
+      </c>
+      <c r="F498" t="n">
+        <v>212</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>9f7eb8c0-d615-40e6-95f8-f558a003b10d</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>817f4449-3843-4f1f-9e20-196f05093068</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="n">
+        <v>46086.82816161124</v>
+      </c>
+      <c r="F499" t="n">
+        <v>199</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>7.66</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>f3e14fd4-d575-41e4-9bd6-bddfa903ecc2</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>e02efd50-472d-423a-9220-99fcc0ff11e3</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="n">
+        <v>46081.03649494795</v>
+      </c>
+      <c r="F500" t="n">
+        <v>185</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>fb781356-87c3-45a4-9925-8cec9714a4e6</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>7363adaa-9a64-4f4b-912e-34a85500526c</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="n">
+        <v>46079.11982829705</v>
+      </c>
+      <c r="F501" t="n">
+        <v>100</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>16.97</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>fbf79842-b44b-4c3a-a798-d993dbfe9b39</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>d8244b87-6537-433a-955c-1acb09861283</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="n">
+        <v>46063.7864949732</v>
+      </c>
+      <c r="F502" t="n">
+        <v>111</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>6cfbc732-bb5e-413d-bc13-575a35cbe624</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>570f9ac6-f58d-4d2f-8e67-ef269695365e</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="n">
+        <v>46069.41149497663</v>
+      </c>
+      <c r="F503" t="n">
+        <v>292</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>16.45</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>98ac2bf3-5725-4b92-81ac-b77ffb7dc10b</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>e4b8ea04-4e72-4fcf-9a43-a9fba34f0fa8</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="n">
+        <v>46087.57816164652</v>
+      </c>
+      <c r="F504" t="n">
+        <v>226</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>8.710000000000001</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>7ab1c66b-a1a6-45ef-a8e9-ad21b4f16e77</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>7ebc5a2d-c96b-47bb-8e15-ebe133d899da</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="n">
+        <v>46085.03649499911</v>
+      </c>
+      <c r="F505" t="n">
+        <v>287</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>19.56</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>5371a197-f9a1-4c64-a656-57b162b132bc</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>73d3ee13-8936-43d6-bee6-e28a6201e3ab</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="n">
+        <v>46074.7031616722</v>
+      </c>
+      <c r="F506" t="n">
+        <v>99</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I506" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>8fe0d440-c063-468d-94d5-dc0ef2c8b820</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>6d8619e4-69a3-4338-9b21-791a88a2b35c</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="n">
+        <v>46072.41149500881</v>
+      </c>
+      <c r="F507" t="n">
+        <v>298</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I507" t="n">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>58e50f7f-d379-4823-aba8-bfe4cf0cdb63</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>ef79e2a1-f6c9-476b-952f-969c4cb4b643</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="n">
+        <v>46073.11982835824</v>
+      </c>
+      <c r="F508" t="n">
+        <v>292</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I508" t="n">
+        <v>2.66</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I508"/>
+  <dimension ref="A1:I534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20509,7 +20509,7 @@
         </is>
       </c>
       <c r="E490" s="2" t="n">
-        <v>46088.49482821159</v>
+        <v>46088.49482820602</v>
       </c>
       <c r="F490" t="n">
         <v>138</v>
@@ -20550,7 +20550,7 @@
         </is>
       </c>
       <c r="E491" s="2" t="n">
-        <v>46081.82816155596</v>
+        <v>46081.82816155093</v>
       </c>
       <c r="F491" t="n">
         <v>192</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="E492" s="2" t="n">
-        <v>46084.45316156915</v>
+        <v>46084.45316157407</v>
       </c>
       <c r="F492" t="n">
         <v>158</v>
@@ -20632,7 +20632,7 @@
         </is>
       </c>
       <c r="E493" s="2" t="n">
-        <v>46071.78649490578</v>
+        <v>46071.78649490741</v>
       </c>
       <c r="F493" t="n">
         <v>162</v>
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="E494" s="2" t="n">
-        <v>46085.99482824239</v>
+        <v>46085.99482824074</v>
       </c>
       <c r="F494" t="n">
         <v>105</v>
@@ -20714,7 +20714,7 @@
         </is>
       </c>
       <c r="E495" s="2" t="n">
-        <v>46074.28649491249</v>
+        <v>46074.28649490741</v>
       </c>
       <c r="F495" t="n">
         <v>263</v>
@@ -20755,7 +20755,7 @@
         </is>
       </c>
       <c r="E496" s="2" t="n">
-        <v>46082.78649492214</v>
+        <v>46082.78649491898</v>
       </c>
       <c r="F496" t="n">
         <v>181</v>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="E497" s="2" t="n">
-        <v>46088.03649493169</v>
+        <v>46088.03649493056</v>
       </c>
       <c r="F497" t="n">
         <v>98</v>
@@ -20837,7 +20837,7 @@
         </is>
       </c>
       <c r="E498" s="2" t="n">
-        <v>46061.86982827468</v>
+        <v>46061.86982827546</v>
       </c>
       <c r="F498" t="n">
         <v>212</v>
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E499" s="2" t="n">
-        <v>46086.82816161124</v>
+        <v>46086.8281616088</v>
       </c>
       <c r="F499" t="n">
         <v>199</v>
@@ -20919,7 +20919,7 @@
         </is>
       </c>
       <c r="E500" s="2" t="n">
-        <v>46081.03649494795</v>
+        <v>46081.0364949537</v>
       </c>
       <c r="F500" t="n">
         <v>185</v>
@@ -20960,7 +20960,7 @@
         </is>
       </c>
       <c r="E501" s="2" t="n">
-        <v>46079.11982829705</v>
+        <v>46079.11982829861</v>
       </c>
       <c r="F501" t="n">
         <v>100</v>
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="E502" s="2" t="n">
-        <v>46063.7864949732</v>
+        <v>46063.78649497686</v>
       </c>
       <c r="F502" t="n">
         <v>111</v>
@@ -21042,7 +21042,7 @@
         </is>
       </c>
       <c r="E503" s="2" t="n">
-        <v>46069.41149497663</v>
+        <v>46069.41149497686</v>
       </c>
       <c r="F503" t="n">
         <v>292</v>
@@ -21083,7 +21083,7 @@
         </is>
       </c>
       <c r="E504" s="2" t="n">
-        <v>46087.57816164652</v>
+        <v>46087.57816164352</v>
       </c>
       <c r="F504" t="n">
         <v>226</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="E505" s="2" t="n">
-        <v>46085.03649499911</v>
+        <v>46085.036495</v>
       </c>
       <c r="F505" t="n">
         <v>287</v>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="E506" s="2" t="n">
-        <v>46074.7031616722</v>
+        <v>46074.70316166666</v>
       </c>
       <c r="F506" t="n">
         <v>99</v>
@@ -21206,7 +21206,7 @@
         </is>
       </c>
       <c r="E507" s="2" t="n">
-        <v>46072.41149500881</v>
+        <v>46072.41149501158</v>
       </c>
       <c r="F507" t="n">
         <v>298</v>
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="E508" s="2" t="n">
-        <v>46073.11982835824</v>
+        <v>46073.11982835648</v>
       </c>
       <c r="F508" t="n">
         <v>292</v>
@@ -21264,6 +21264,1072 @@
       </c>
       <c r="I508" t="n">
         <v>2.66</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>820ac52a-b331-4fe5-8654-20b1274c6413</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>9b2fe321-2c99-4766-bf76-030845ae0a1d</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="n">
+        <v>46065.28641162244</v>
+      </c>
+      <c r="F509" t="n">
+        <v>186</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I509" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>6f75a963-811f-4ce2-934c-2d777210f546</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>9d84f1d3-9ade-4269-b2ae-7c452cf014fd</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="n">
+        <v>46091.66141163242</v>
+      </c>
+      <c r="F510" t="n">
+        <v>57</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I510" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>4eaeac62-be9c-49fc-8c7d-caaa08402b0e</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>7c4e7a82-1f01-46ad-96d0-56f9ef7ae577</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="n">
+        <v>46065.3697449691</v>
+      </c>
+      <c r="F511" t="n">
+        <v>215</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I511" t="n">
+        <v>13.85</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>903f8491-79d9-4410-ac78-5804f3207eb4</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>3f4421ff-1261-427e-944e-2671b034212e</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="n">
+        <v>46074.32807830565</v>
+      </c>
+      <c r="F512" t="n">
+        <v>252</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>13.21</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>7c6017db-f642-475c-b025-70063ae29455</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>4af20b6a-3945-44ce-903a-613eca25acdb</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="n">
+        <v>46072.49474497589</v>
+      </c>
+      <c r="F513" t="n">
+        <v>288</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>14.58</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>484c92d4-4609-4e15-ab17-2c7fe90ed0af</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>b0dac955-6769-4d1f-b623-491b7e33dcb0</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="n">
+        <v>46063.03641164579</v>
+      </c>
+      <c r="F514" t="n">
+        <v>275</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I514" t="n">
+        <v>19.43</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>d5f2f541-519b-415b-8d49-57e9c14d3837</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>014902fb-6dee-40fe-87c8-882e3172cf74</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="n">
+        <v>46083.70307831562</v>
+      </c>
+      <c r="F515" t="n">
+        <v>119</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>19.64</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>440bcf7a-4f4f-4e79-aea6-4e36abc4ccc9</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>0458c646-6470-4be2-b304-40de35f43fdb</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="n">
+        <v>46078.07807832849</v>
+      </c>
+      <c r="F516" t="n">
+        <v>242</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>16.07</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>58b00773-7876-4a12-b536-57f6580686d9</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>86418913-14b6-44cb-a8af-87109b9e0d46</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="n">
+        <v>46092.11974499856</v>
+      </c>
+      <c r="F517" t="n">
+        <v>180</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I517" t="n">
+        <v>17.34</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>681f28dc-69a6-4690-ae3b-8812f190c1d5</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>ab708a6c-697e-4ca9-b36f-95faf07403a8</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="n">
+        <v>46089.61974500485</v>
+      </c>
+      <c r="F518" t="n">
+        <v>213</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I518" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>0b1f29de-5d5f-4f11-857b-1bd7afe0f513</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>32761a91-cda4-4b00-87f6-2607f212de2e</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="n">
+        <v>46073.57807834455</v>
+      </c>
+      <c r="F519" t="n">
+        <v>217</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I519" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>d37293a5-c4c0-4667-9af1-15495ec14e48</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ea9c5664-f75b-4a88-bd7e-2f74275746ba</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="n">
+        <v>46065.74474501749</v>
+      </c>
+      <c r="F520" t="n">
+        <v>122</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I520" t="n">
+        <v>14.81</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>798da334-6624-48b3-b015-2d87eed90dd3</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>b2bb4ac7-06a7-42db-b132-a871e334a877</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="n">
+        <v>46070.28641168836</v>
+      </c>
+      <c r="F521" t="n">
+        <v>181</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I521" t="n">
+        <v>16.83</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>99506b88-2468-4186-a930-ee01a6255beb</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>6c69b523-65b3-46c3-a792-c6ac665b3114</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="n">
+        <v>46075.2030783644</v>
+      </c>
+      <c r="F522" t="n">
+        <v>162</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I522" t="n">
+        <v>19.78</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>161d7f17-1219-4bfd-a10e-c583627229b3</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>49f28af4-1cb9-47b6-9c10-b4ac3cc1fece</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="n">
+        <v>46090.24474503446</v>
+      </c>
+      <c r="F523" t="n">
+        <v>296</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I523" t="n">
+        <v>16.49</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>fadaa025-22d2-4aba-a79e-5d96c64dbf0e</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>3e30eee4-0eaa-4b65-a121-1ba9d2501417</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="n">
+        <v>46064.91141170741</v>
+      </c>
+      <c r="F524" t="n">
+        <v>237</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I524" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>3cdbe1ce-31bf-4206-9da2-ffc624ee822b</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>0682c165-3967-4c80-854d-3d7e4e158fbe</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="n">
+        <v>46062.49474504391</v>
+      </c>
+      <c r="F525" t="n">
+        <v>192</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I525" t="n">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>df172bf8-5317-465b-9813-3d47c6eb1b84</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>15f2ec6e-3f14-41f8-9570-7155c28f11e1</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="n">
+        <v>46082.0780783806</v>
+      </c>
+      <c r="F526" t="n">
+        <v>142</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I526" t="n">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>5b1bef2e-48c0-4417-8ea7-bfcf33096cf4</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>f75fa40f-8655-45c6-b5b8-c5357845776b</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="n">
+        <v>46072.4114117327</v>
+      </c>
+      <c r="F527" t="n">
+        <v>166</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I527" t="n">
+        <v>14.48</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>f6d49b80-089a-4703-96a0-5263533dd2b2</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>e2daa030-a550-4b12-aadb-ddc1a4c36032</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="n">
+        <v>46069.61974507861</v>
+      </c>
+      <c r="F528" t="n">
+        <v>126</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I528" t="n">
+        <v>17.58</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>abcb33f6-2efd-41bd-92a9-af9c97fbc614</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>8239e330-26a6-4cfe-b592-0f782f98a731</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="n">
+        <v>46067.03641174863</v>
+      </c>
+      <c r="F529" t="n">
+        <v>226</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I529" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>3477476b-8b33-4e15-bbdf-a99880bce8e9</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>e9f4f7bb-f29c-479c-8729-dd71ab1729b7</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="n">
+        <v>46085.6197450883</v>
+      </c>
+      <c r="F530" t="n">
+        <v>190</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I530" t="n">
+        <v>15.91</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>33999472-1585-4dc3-ac64-f76649b4b5b5</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>1987d7dd-e960-4872-babc-c54f3e81ba88</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="n">
+        <v>46070.16141175831</v>
+      </c>
+      <c r="F531" t="n">
+        <v>265</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I531" t="n">
+        <v>15.68</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>904bbb59-d91c-4f0e-9a7f-804a92b84751</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>b8b8a080-ebee-4b4e-987c-611dfb3353a1</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="n">
+        <v>46088.03641176457</v>
+      </c>
+      <c r="F532" t="n">
+        <v>59</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I532" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>b3d89697-0e79-4281-98af-c2f4b79d8e78</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>ab43e0bd-22ed-4136-a721-ea7d489fccbe</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="n">
+        <v>46084.36974510436</v>
+      </c>
+      <c r="F533" t="n">
+        <v>145</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I533" t="n">
+        <v>8.289999999999999</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>9046ac97-a2d7-45e0-ad8c-45e4acc4de8a</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>0f5dca8e-067c-425d-b7bc-42ae7a8e4374</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="n">
+        <v>46083.78641177717</v>
+      </c>
+      <c r="F534" t="n">
+        <v>247</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I534" t="n">
+        <v>11.52</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I534"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21288,7 +21288,7 @@
         </is>
       </c>
       <c r="E509" s="2" t="n">
-        <v>46065.28641162244</v>
+        <v>46065.28641162037</v>
       </c>
       <c r="F509" t="n">
         <v>186</v>
@@ -21329,7 +21329,7 @@
         </is>
       </c>
       <c r="E510" s="2" t="n">
-        <v>46091.66141163242</v>
+        <v>46091.66141163195</v>
       </c>
       <c r="F510" t="n">
         <v>57</v>
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="E511" s="2" t="n">
-        <v>46065.3697449691</v>
+        <v>46065.36974496528</v>
       </c>
       <c r="F511" t="n">
         <v>215</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="E512" s="2" t="n">
-        <v>46074.32807830565</v>
+        <v>46074.32807831019</v>
       </c>
       <c r="F512" t="n">
         <v>252</v>
@@ -21452,7 +21452,7 @@
         </is>
       </c>
       <c r="E513" s="2" t="n">
-        <v>46072.49474497589</v>
+        <v>46072.49474497685</v>
       </c>
       <c r="F513" t="n">
         <v>288</v>
@@ -21493,7 +21493,7 @@
         </is>
       </c>
       <c r="E514" s="2" t="n">
-        <v>46063.03641164579</v>
+        <v>46063.03641164352</v>
       </c>
       <c r="F514" t="n">
         <v>275</v>
@@ -21534,7 +21534,7 @@
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>46083.70307831562</v>
+        <v>46083.70307831019</v>
       </c>
       <c r="F515" t="n">
         <v>119</v>
@@ -21575,7 +21575,7 @@
         </is>
       </c>
       <c r="E516" s="2" t="n">
-        <v>46078.07807832849</v>
+        <v>46078.07807833333</v>
       </c>
       <c r="F516" t="n">
         <v>242</v>
@@ -21616,7 +21616,7 @@
         </is>
       </c>
       <c r="E517" s="2" t="n">
-        <v>46092.11974499856</v>
+        <v>46092.119745</v>
       </c>
       <c r="F517" t="n">
         <v>180</v>
@@ -21657,7 +21657,7 @@
         </is>
       </c>
       <c r="E518" s="2" t="n">
-        <v>46089.61974500485</v>
+        <v>46089.619745</v>
       </c>
       <c r="F518" t="n">
         <v>213</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E519" s="2" t="n">
-        <v>46073.57807834455</v>
+        <v>46073.57807834491</v>
       </c>
       <c r="F519" t="n">
         <v>217</v>
@@ -21739,7 +21739,7 @@
         </is>
       </c>
       <c r="E520" s="2" t="n">
-        <v>46065.74474501749</v>
+        <v>46065.74474502315</v>
       </c>
       <c r="F520" t="n">
         <v>122</v>
@@ -21780,7 +21780,7 @@
         </is>
       </c>
       <c r="E521" s="2" t="n">
-        <v>46070.28641168836</v>
+        <v>46070.28641168981</v>
       </c>
       <c r="F521" t="n">
         <v>181</v>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="E522" s="2" t="n">
-        <v>46075.2030783644</v>
+        <v>46075.20307836805</v>
       </c>
       <c r="F522" t="n">
         <v>162</v>
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="E523" s="2" t="n">
-        <v>46090.24474503446</v>
+        <v>46090.24474503472</v>
       </c>
       <c r="F523" t="n">
         <v>296</v>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="E524" s="2" t="n">
-        <v>46064.91141170741</v>
+        <v>46064.91141171296</v>
       </c>
       <c r="F524" t="n">
         <v>237</v>
@@ -21944,7 +21944,7 @@
         </is>
       </c>
       <c r="E525" s="2" t="n">
-        <v>46062.49474504391</v>
+        <v>46062.49474504629</v>
       </c>
       <c r="F525" t="n">
         <v>192</v>
@@ -21985,7 +21985,7 @@
         </is>
       </c>
       <c r="E526" s="2" t="n">
-        <v>46082.0780783806</v>
+        <v>46082.07807837963</v>
       </c>
       <c r="F526" t="n">
         <v>142</v>
@@ -22026,7 +22026,7 @@
         </is>
       </c>
       <c r="E527" s="2" t="n">
-        <v>46072.4114117327</v>
+        <v>46072.41141173611</v>
       </c>
       <c r="F527" t="n">
         <v>166</v>
@@ -22067,7 +22067,7 @@
         </is>
       </c>
       <c r="E528" s="2" t="n">
-        <v>46069.61974507861</v>
+        <v>46069.61974508102</v>
       </c>
       <c r="F528" t="n">
         <v>126</v>
@@ -22108,7 +22108,7 @@
         </is>
       </c>
       <c r="E529" s="2" t="n">
-        <v>46067.03641174863</v>
+        <v>46067.03641174769</v>
       </c>
       <c r="F529" t="n">
         <v>226</v>
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="E530" s="2" t="n">
-        <v>46085.6197450883</v>
+        <v>46085.61974509259</v>
       </c>
       <c r="F530" t="n">
         <v>190</v>
@@ -22190,7 +22190,7 @@
         </is>
       </c>
       <c r="E531" s="2" t="n">
-        <v>46070.16141175831</v>
+        <v>46070.16141175926</v>
       </c>
       <c r="F531" t="n">
         <v>265</v>
@@ -22231,7 +22231,7 @@
         </is>
       </c>
       <c r="E532" s="2" t="n">
-        <v>46088.03641176457</v>
+        <v>46088.03641175926</v>
       </c>
       <c r="F532" t="n">
         <v>59</v>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="E533" s="2" t="n">
-        <v>46084.36974510436</v>
+        <v>46084.36974510417</v>
       </c>
       <c r="F533" t="n">
         <v>145</v>
@@ -22313,7 +22313,7 @@
         </is>
       </c>
       <c r="E534" s="2" t="n">
-        <v>46083.78641177717</v>
+        <v>46083.78641178241</v>
       </c>
       <c r="F534" t="n">
         <v>247</v>
@@ -22330,6 +22330,908 @@
       </c>
       <c r="I534" t="n">
         <v>11.52</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>e6f26c6c-72e6-44c3-994d-a57412779b20</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>d89801b1-f7ce-452a-9967-c9e0646f5f20</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="n">
+        <v>46063.19785992941</v>
+      </c>
+      <c r="F535" t="n">
+        <v>241</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I535" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>f2959436-f8c7-408e-a74b-f639ccfaef88</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>07f0b4c3-3055-4059-bfc8-e5982f74dd40</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="n">
+        <v>46078.98952659949</v>
+      </c>
+      <c r="F536" t="n">
+        <v>257</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I536" t="n">
+        <v>16.74</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>4b43a6f8-9fd1-421c-9b2e-e6ee3dfbb218</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2bd5f778-63a7-41fe-b7ed-e7c08ef1a386</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="n">
+        <v>46079.69785993961</v>
+      </c>
+      <c r="F537" t="n">
+        <v>233</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I537" t="n">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>006d4301-f7a5-4129-90ac-04468ac81af1</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>eeba8993-98e2-4388-b4b6-e59f9469684b</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="n">
+        <v>46090.73952662585</v>
+      </c>
+      <c r="F538" t="n">
+        <v>117</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I538" t="n">
+        <v>7.93</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>f48e25f8-1b6f-46c8-bccb-4833c143971c</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>d413c626-7ec8-4ad4-9674-c399a597c62c</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="n">
+        <v>46081.86452662906</v>
+      </c>
+      <c r="F539" t="n">
+        <v>32</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I539" t="n">
+        <v>13.89</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>c7633374-a3be-42a5-9f79-de785b537808</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>7cf7806f-dce3-429d-97a8-e0b9bd41b8ed</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="n">
+        <v>46063.03119330619</v>
+      </c>
+      <c r="F540" t="n">
+        <v>150</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I540" t="n">
+        <v>16.65</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>b6e5a0c5-579f-42ca-95dc-51a58f7b418a</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>a9c1bb20-6bb7-4b54-9b8e-2c47eb726682</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="n">
+        <v>46085.90619331602</v>
+      </c>
+      <c r="F541" t="n">
+        <v>116</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I541" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>fdbc8a8b-8c16-49b1-b804-aeeb96052e78</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>96a1a977-9b51-417f-99ed-aae66d9a89d9</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="n">
+        <v>46071.23952666226</v>
+      </c>
+      <c r="F542" t="n">
+        <v>116</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I542" t="n">
+        <v>14.18</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>11f5490a-1ee9-4c72-9242-5b6c9da0e3d5</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>b2b466d4-7975-4ff3-99ce-87742466c525</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="n">
+        <v>46074.07286000525</v>
+      </c>
+      <c r="F543" t="n">
+        <v>53</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I543" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>75e0e6b1-c1e3-486e-afc6-921038d0ccd7</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>531462a2-3085-4d1f-9780-eaebcdaaf18b</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="n">
+        <v>46077.65619334196</v>
+      </c>
+      <c r="F544" t="n">
+        <v>84</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I544" t="n">
+        <v>14.63</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>5efbdcbd-e694-4785-bd60-68b89ce18354</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2b4799c4-3670-4808-8778-eae82aeb1763</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="n">
+        <v>46065.53119334519</v>
+      </c>
+      <c r="F545" t="n">
+        <v>249</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I545" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>26e5b703-c6b3-4c9b-9405-6eb0c9237834</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>b202a867-d31d-487b-8ec5-5ca805a2f47b</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="n">
+        <v>46089.48952669524</v>
+      </c>
+      <c r="F546" t="n">
+        <v>134</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I546" t="n">
+        <v>9.73</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>341f86f5-4aac-47e2-8915-b95512203e2d</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>a14edb41-93ce-4614-a48e-79d6f7af4eb2</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="n">
+        <v>46082.61452670155</v>
+      </c>
+      <c r="F547" t="n">
+        <v>74</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I547" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>3c5acbac-0c47-4ebd-8729-f2b2341217e1</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>09129bc0-e031-451a-ba2c-557552e4613a</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="n">
+        <v>46078.98952670841</v>
+      </c>
+      <c r="F548" t="n">
+        <v>129</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I548" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>da03fce0-856b-4297-9fb0-f891ded73073</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>f97556a6-39e3-4c1c-99f9-89869070319b</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="n">
+        <v>46077.36452671797</v>
+      </c>
+      <c r="F549" t="n">
+        <v>206</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I549" t="n">
+        <v>16.18</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>6c0cabb1-bb86-4d6b-a263-7809828022d2</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>784fa69c-0ef3-4ef4-977b-2be19f7ba08d</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="n">
+        <v>46064.69786006435</v>
+      </c>
+      <c r="F550" t="n">
+        <v>195</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I550" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>4d4ddf73-bfa6-407f-b277-f11e75ddc037</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>6195dead-f130-41dd-a558-02f38456b2cc</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="n">
+        <v>46071.57286006756</v>
+      </c>
+      <c r="F551" t="n">
+        <v>171</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I551" t="n">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>8b002d26-6faf-4d2e-9e86-f391b9642d63</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>9c6e90b1-dff2-4b78-ae67-cf32817d5df4</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="n">
+        <v>46075.53119340763</v>
+      </c>
+      <c r="F552" t="n">
+        <v>59</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I552" t="n">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>12d9f639-3cf1-4a06-9b2d-4e3986f14761</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>6c608919-9b21-4924-8ffa-05693147aed7</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="n">
+        <v>46087.69786007755</v>
+      </c>
+      <c r="F553" t="n">
+        <v>154</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I553" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>9203b0d5-2c73-4491-9815-5268241b0aa6</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>45ac5b49-4ae9-40ba-816a-20f768a2d408</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="n">
+        <v>46089.73952674748</v>
+      </c>
+      <c r="F554" t="n">
+        <v>60</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I554" t="n">
+        <v>18.64</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2d127bd3-cfad-4141-89a5-22b24b4af79b</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>d66a44be-271b-4e19-b4fa-fb2b86a67062</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="n">
+        <v>46069.78119341761</v>
+      </c>
+      <c r="F555" t="n">
+        <v>121</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I555" t="n">
+        <v>14.46</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>d32357f9-e223-4af1-b4ef-5a0bfa33ac2f</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>3e97200b-aff4-476f-9ae6-ad2ce4d611a1</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="n">
+        <v>46065.32286008786</v>
+      </c>
+      <c r="F556" t="n">
+        <v>95</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>13.45</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I556"/>
+  <dimension ref="A1:I573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="E535" s="2" t="n">
-        <v>46063.19785992941</v>
+        <v>46063.19785993056</v>
       </c>
       <c r="F535" t="n">
         <v>241</v>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="E536" s="2" t="n">
-        <v>46078.98952659949</v>
+        <v>46078.98952659722</v>
       </c>
       <c r="F536" t="n">
         <v>257</v>
@@ -22436,7 +22436,7 @@
         </is>
       </c>
       <c r="E537" s="2" t="n">
-        <v>46079.69785993961</v>
+        <v>46079.69785994213</v>
       </c>
       <c r="F537" t="n">
         <v>233</v>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="E538" s="2" t="n">
-        <v>46090.73952662585</v>
+        <v>46090.73952662037</v>
       </c>
       <c r="F538" t="n">
         <v>117</v>
@@ -22518,7 +22518,7 @@
         </is>
       </c>
       <c r="E539" s="2" t="n">
-        <v>46081.86452662906</v>
+        <v>46081.86452663194</v>
       </c>
       <c r="F539" t="n">
         <v>32</v>
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="E540" s="2" t="n">
-        <v>46063.03119330619</v>
+        <v>46063.03119331018</v>
       </c>
       <c r="F540" t="n">
         <v>150</v>
@@ -22600,7 +22600,7 @@
         </is>
       </c>
       <c r="E541" s="2" t="n">
-        <v>46085.90619331602</v>
+        <v>46085.90619332176</v>
       </c>
       <c r="F541" t="n">
         <v>116</v>
@@ -22641,7 +22641,7 @@
         </is>
       </c>
       <c r="E542" s="2" t="n">
-        <v>46071.23952666226</v>
+        <v>46071.23952666666</v>
       </c>
       <c r="F542" t="n">
         <v>116</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="E543" s="2" t="n">
-        <v>46074.07286000525</v>
+        <v>46074.07286</v>
       </c>
       <c r="F543" t="n">
         <v>53</v>
@@ -22723,7 +22723,7 @@
         </is>
       </c>
       <c r="E544" s="2" t="n">
-        <v>46077.65619334196</v>
+        <v>46077.6561933449</v>
       </c>
       <c r="F544" t="n">
         <v>84</v>
@@ -22764,7 +22764,7 @@
         </is>
       </c>
       <c r="E545" s="2" t="n">
-        <v>46065.53119334519</v>
+        <v>46065.5311933449</v>
       </c>
       <c r="F545" t="n">
         <v>249</v>
@@ -22805,7 +22805,7 @@
         </is>
       </c>
       <c r="E546" s="2" t="n">
-        <v>46089.48952669524</v>
+        <v>46089.48952668982</v>
       </c>
       <c r="F546" t="n">
         <v>134</v>
@@ -22846,7 +22846,7 @@
         </is>
       </c>
       <c r="E547" s="2" t="n">
-        <v>46082.61452670155</v>
+        <v>46082.61452670139</v>
       </c>
       <c r="F547" t="n">
         <v>74</v>
@@ -22887,7 +22887,7 @@
         </is>
       </c>
       <c r="E548" s="2" t="n">
-        <v>46078.98952670841</v>
+        <v>46078.98952671296</v>
       </c>
       <c r="F548" t="n">
         <v>129</v>
@@ -22928,7 +22928,7 @@
         </is>
       </c>
       <c r="E549" s="2" t="n">
-        <v>46077.36452671797</v>
+        <v>46077.36452671296</v>
       </c>
       <c r="F549" t="n">
         <v>206</v>
@@ -22969,7 +22969,7 @@
         </is>
       </c>
       <c r="E550" s="2" t="n">
-        <v>46064.69786006435</v>
+        <v>46064.69786006944</v>
       </c>
       <c r="F550" t="n">
         <v>195</v>
@@ -23010,7 +23010,7 @@
         </is>
       </c>
       <c r="E551" s="2" t="n">
-        <v>46071.57286006756</v>
+        <v>46071.57286006944</v>
       </c>
       <c r="F551" t="n">
         <v>171</v>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="E552" s="2" t="n">
-        <v>46075.53119340763</v>
+        <v>46075.53119340278</v>
       </c>
       <c r="F552" t="n">
         <v>59</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="E553" s="2" t="n">
-        <v>46087.69786007755</v>
+        <v>46087.69786008102</v>
       </c>
       <c r="F553" t="n">
         <v>154</v>
@@ -23133,7 +23133,7 @@
         </is>
       </c>
       <c r="E554" s="2" t="n">
-        <v>46089.73952674748</v>
+        <v>46089.73952674768</v>
       </c>
       <c r="F554" t="n">
         <v>60</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="E555" s="2" t="n">
-        <v>46069.78119341761</v>
+        <v>46069.78119341435</v>
       </c>
       <c r="F555" t="n">
         <v>121</v>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="E556" s="2" t="n">
-        <v>46065.32286008786</v>
+        <v>46065.32286009259</v>
       </c>
       <c r="F556" t="n">
         <v>95</v>
@@ -23232,6 +23232,703 @@
       </c>
       <c r="I556" t="n">
         <v>13.45</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>7f9fe44f-d666-4ca8-991e-a8fce8e912ee</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>315233ab-de09-4dae-98c5-60b6571801ec</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="n">
+        <v>46078.69120367298</v>
+      </c>
+      <c r="F557" t="n">
+        <v>283</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>18.08</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>7306ed97-2720-4b20-88db-b6f3d60c9c0f</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>c8cddf37-cf9c-4eb8-938d-5a84537c9fb2</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="n">
+        <v>46087.85787034714</v>
+      </c>
+      <c r="F558" t="n">
+        <v>75</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>11.28</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>75ac22f9-821c-4658-b3bc-3e0317162654</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>c15ff324-436b-4f2d-8f6b-5f3f9986a0e7</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="n">
+        <v>46076.27453703021</v>
+      </c>
+      <c r="F559" t="n">
+        <v>83</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I559" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>529f37f3-8e24-40ef-a323-093546de9b69</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>92ca576c-ffe6-4381-b759-c6121480811f</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="n">
+        <v>46090.3995370366</v>
+      </c>
+      <c r="F560" t="n">
+        <v>172</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I560" t="n">
+        <v>18.46</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>b0a18ba4-cc14-4040-b4db-22c62ad3ab0d</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>c0dd2dfd-3ea2-4b9a-9783-bf0889f8bff1</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="n">
+        <v>46073.89953704643</v>
+      </c>
+      <c r="F561" t="n">
+        <v>111</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I561" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>99497060-ac1c-4836-b1af-647bbb07375f</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>b03112af-9a3b-459f-b875-2ecc7d9fba8c</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="n">
+        <v>46087.19120371649</v>
+      </c>
+      <c r="F562" t="n">
+        <v>200</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I562" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>4a9ed203-b425-4dce-bc9d-8bc3b30a8e0d</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>8dcd002e-a0e7-4018-b0de-e4c4fd212841</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="n">
+        <v>46074.85787038643</v>
+      </c>
+      <c r="F563" t="n">
+        <v>200</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I563" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>b7fce51d-e668-4ebc-89b6-3ff11456c439</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>09bedb2b-2ea0-4eb3-af78-bbc3c28ade61</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="n">
+        <v>46069.02453706586</v>
+      </c>
+      <c r="F564" t="n">
+        <v>265</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I564" t="n">
+        <v>18.84</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>637b8783-6206-4acd-abdb-8be45b44d43f</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>fdb0626c-e24c-4cf5-bdc1-a8d380425e08</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="n">
+        <v>46073.69120374206</v>
+      </c>
+      <c r="F565" t="n">
+        <v>142</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I565" t="n">
+        <v>16.78</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>6b999299-f7f8-4d33-a450-032be3510c25</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>f2ed00f5-36cb-478f-99be-63cead244709</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="n">
+        <v>46064.31620374526</v>
+      </c>
+      <c r="F566" t="n">
+        <v>245</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I566" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>1a735bd3-46bc-4b3b-9daf-fe4e57cb21f0</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>d78dba12-9afe-48e4-9c3f-55269b2dc908</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="n">
+        <v>46074.56620374847</v>
+      </c>
+      <c r="F567" t="n">
+        <v>183</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I567" t="n">
+        <v>10.69</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>97b960e5-dafa-4cb4-8ff5-4413f0dd9474</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>edc89045-64eb-47e4-b5e3-41dbe705b88d</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="n">
+        <v>46081.60787041856</v>
+      </c>
+      <c r="F568" t="n">
+        <v>276</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I568" t="n">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>8360d677-6da7-4fe9-b837-20a7d4e5cb24</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>b882e698-7840-4ca0-b55d-395ac2b45bf6</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="n">
+        <v>46076.27453709151</v>
+      </c>
+      <c r="F569" t="n">
+        <v>131</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I569" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>fc8f22e9-66f1-488d-8593-92f2edd3939c</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>a227ebea-f21b-4d04-a2b7-4ab954d1d161</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="n">
+        <v>46064.94120377398</v>
+      </c>
+      <c r="F570" t="n">
+        <v>277</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I570" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>bbf2b0be-8d4d-4098-8e78-cc2cb8e99134</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>a9103f53-c513-45e3-a226-ab4e3265da6d</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="n">
+        <v>46083.73287046605</v>
+      </c>
+      <c r="F571" t="n">
+        <v>193</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I571" t="n">
+        <v>11.41</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2df22f71-0472-4082-a45f-cc6ba5027acb</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>41fab8da-6513-4c74-8f8b-d27c5ef456d5</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="n">
+        <v>46068.69120380253</v>
+      </c>
+      <c r="F572" t="n">
+        <v>241</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I572" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>13f8e6b3-302b-4b78-8e73-f99a03e7a2c0</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>cdf7124e-bcf9-4481-818e-c51d0ee94887</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="n">
+        <v>46082.10787047545</v>
+      </c>
+      <c r="F573" t="n">
+        <v>210</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I573" t="n">
+        <v>18.37</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I573"/>
+  <dimension ref="A1:I589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23256,7 +23256,7 @@
         </is>
       </c>
       <c r="E557" s="2" t="n">
-        <v>46078.69120367298</v>
+        <v>46078.69120366898</v>
       </c>
       <c r="F557" t="n">
         <v>283</v>
@@ -23297,7 +23297,7 @@
         </is>
       </c>
       <c r="E558" s="2" t="n">
-        <v>46087.85787034714</v>
+        <v>46087.85787034722</v>
       </c>
       <c r="F558" t="n">
         <v>75</v>
@@ -23338,7 +23338,7 @@
         </is>
       </c>
       <c r="E559" s="2" t="n">
-        <v>46076.27453703021</v>
+        <v>46076.27453702546</v>
       </c>
       <c r="F559" t="n">
         <v>83</v>
@@ -23379,7 +23379,7 @@
         </is>
       </c>
       <c r="E560" s="2" t="n">
-        <v>46090.3995370366</v>
+        <v>46090.39953703704</v>
       </c>
       <c r="F560" t="n">
         <v>172</v>
@@ -23420,7 +23420,7 @@
         </is>
       </c>
       <c r="E561" s="2" t="n">
-        <v>46073.89953704643</v>
+        <v>46073.89953704861</v>
       </c>
       <c r="F561" t="n">
         <v>111</v>
@@ -23461,7 +23461,7 @@
         </is>
       </c>
       <c r="E562" s="2" t="n">
-        <v>46087.19120371649</v>
+        <v>46087.19120371528</v>
       </c>
       <c r="F562" t="n">
         <v>200</v>
@@ -23502,7 +23502,7 @@
         </is>
       </c>
       <c r="E563" s="2" t="n">
-        <v>46074.85787038643</v>
+        <v>46074.85787038194</v>
       </c>
       <c r="F563" t="n">
         <v>200</v>
@@ -23543,7 +23543,7 @@
         </is>
       </c>
       <c r="E564" s="2" t="n">
-        <v>46069.02453706586</v>
+        <v>46069.02453706018</v>
       </c>
       <c r="F564" t="n">
         <v>265</v>
@@ -23584,7 +23584,7 @@
         </is>
       </c>
       <c r="E565" s="2" t="n">
-        <v>46073.69120374206</v>
+        <v>46073.69120373842</v>
       </c>
       <c r="F565" t="n">
         <v>142</v>
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="E566" s="2" t="n">
-        <v>46064.31620374526</v>
+        <v>46064.31620375</v>
       </c>
       <c r="F566" t="n">
         <v>245</v>
@@ -23666,7 +23666,7 @@
         </is>
       </c>
       <c r="E567" s="2" t="n">
-        <v>46074.56620374847</v>
+        <v>46074.56620375</v>
       </c>
       <c r="F567" t="n">
         <v>183</v>
@@ -23707,7 +23707,7 @@
         </is>
       </c>
       <c r="E568" s="2" t="n">
-        <v>46081.60787041856</v>
+        <v>46081.60787041666</v>
       </c>
       <c r="F568" t="n">
         <v>276</v>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="E569" s="2" t="n">
-        <v>46076.27453709151</v>
+        <v>46076.27453709491</v>
       </c>
       <c r="F569" t="n">
         <v>131</v>
@@ -23789,7 +23789,7 @@
         </is>
       </c>
       <c r="E570" s="2" t="n">
-        <v>46064.94120377398</v>
+        <v>46064.94120377315</v>
       </c>
       <c r="F570" t="n">
         <v>277</v>
@@ -23830,7 +23830,7 @@
         </is>
       </c>
       <c r="E571" s="2" t="n">
-        <v>46083.73287046605</v>
+        <v>46083.73287046296</v>
       </c>
       <c r="F571" t="n">
         <v>193</v>
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="E572" s="2" t="n">
-        <v>46068.69120380253</v>
+        <v>46068.69120380787</v>
       </c>
       <c r="F572" t="n">
         <v>241</v>
@@ -23912,7 +23912,7 @@
         </is>
       </c>
       <c r="E573" s="2" t="n">
-        <v>46082.10787047545</v>
+        <v>46082.10787047454</v>
       </c>
       <c r="F573" t="n">
         <v>210</v>
@@ -23929,6 +23929,662 @@
       </c>
       <c r="I573" t="n">
         <v>18.37</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>00e08cba-156c-4323-a246-b3dffa441a39</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>6cef5e0a-eebb-4fc2-8f07-8993e3eaf566</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="n">
+        <v>46090.52831800817</v>
+      </c>
+      <c r="F574" t="n">
+        <v>269</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>ee3ead3e-0988-4098-a0a6-b21207fe1348</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>707d7704-d0a9-44c7-9be2-ded67341a1fb</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="n">
+        <v>46072.86165136145</v>
+      </c>
+      <c r="F575" t="n">
+        <v>282</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>18.16</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>87c5e14b-c37b-4ce1-ae1a-249a497e328c</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>b5722f70-9126-4a23-8dea-e47e792fc988</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="n">
+        <v>46083.65331803136</v>
+      </c>
+      <c r="F576" t="n">
+        <v>206</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>8b94f2f4-ffdb-4d5c-9444-9ff1146d7f91</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>8e81bcf0-c5a6-4abf-b964-dd993289e4f2</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="n">
+        <v>46069.06998470155</v>
+      </c>
+      <c r="F577" t="n">
+        <v>63</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>15.32</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>67e902ad-f257-422c-97fb-ef27fbcd3f9a</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>3bcb3e2b-3fcf-475e-b9a3-7abe86678f59</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="n">
+        <v>46061.1116513965</v>
+      </c>
+      <c r="F578" t="n">
+        <v>37</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>8f43a2fc-2b9b-492b-946e-4b4bae8848e4</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>64563d3d-0a1d-4eb5-8a3e-36f31c8da6cb</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="n">
+        <v>46075.77831807279</v>
+      </c>
+      <c r="F579" t="n">
+        <v>205</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>15.13</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>21dedefc-892f-4155-9690-83a9d08e7b8e</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>b0f04673-935e-4e30-99ec-1b107bc70620</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="n">
+        <v>46087.94498475021</v>
+      </c>
+      <c r="F580" t="n">
+        <v>290</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>e0f6235b-57c4-428a-9a53-73baa4e707be</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>ec14a453-5157-4578-9df0-17e1bbc0429b</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="n">
+        <v>46076.19498475341</v>
+      </c>
+      <c r="F581" t="n">
+        <v>255</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>69ef4899-7d40-4b46-afca-22f4506dd5a4</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>b7574b04-197e-4a71-9339-47ba35108319</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="n">
+        <v>46063.44498476941</v>
+      </c>
+      <c r="F582" t="n">
+        <v>78</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>32885b57-d4a0-4830-99c2-e0df24476522</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>f44ed429-f41f-4e20-b349-351fad8f9293</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="n">
+        <v>46079.40331810607</v>
+      </c>
+      <c r="F583" t="n">
+        <v>176</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>9166efe3-08c2-4479-a602-746f03836694</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>73b57c8d-e51b-413f-881c-71a7dffb4179</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="n">
+        <v>46074.52831810926</v>
+      </c>
+      <c r="F584" t="n">
+        <v>243</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>38163a9b-2694-4c57-8733-c0707ee8f428</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>29df2464-ee11-4264-a02a-add31b6b7684</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="n">
+        <v>46070.61165145234</v>
+      </c>
+      <c r="F585" t="n">
+        <v>298</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>47b3ec8e-d3ac-4c89-b0ea-50f24f0c1857</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>cde54da0-c63c-4291-a137-0de6b67688c5</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="n">
+        <v>46067.81998478885</v>
+      </c>
+      <c r="F586" t="n">
+        <v>94</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>fbcfcdb1-e425-46cb-ad31-8956d35057c0</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>30a4ff7d-c883-42fe-bb8d-5b5e5da4cff2</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="n">
+        <v>46078.86165146495</v>
+      </c>
+      <c r="F587" t="n">
+        <v>232</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>46337070-9af5-42c2-b44f-c38cb59f2291</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>c10197a7-2631-4208-ad01-fa12f8608570</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="n">
+        <v>46078.27831813797</v>
+      </c>
+      <c r="F588" t="n">
+        <v>33</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I588" t="n">
+        <v>12.07</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>ecf0d7f9-7ccd-4791-ad25-7e56f5d068a5</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>41541b51-5d3a-441e-80c4-7bc5f6f2c5fc</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="n">
+        <v>46080.73665149286</v>
+      </c>
+      <c r="F589" t="n">
+        <v>79</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I589" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I589"/>
+  <dimension ref="A1:I608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23953,7 +23953,7 @@
         </is>
       </c>
       <c r="E574" s="2" t="n">
-        <v>46090.52831800817</v>
+        <v>46090.52831800926</v>
       </c>
       <c r="F574" t="n">
         <v>269</v>
@@ -23994,7 +23994,7 @@
         </is>
       </c>
       <c r="E575" s="2" t="n">
-        <v>46072.86165136145</v>
+        <v>46072.86165136574</v>
       </c>
       <c r="F575" t="n">
         <v>282</v>
@@ -24035,7 +24035,7 @@
         </is>
       </c>
       <c r="E576" s="2" t="n">
-        <v>46083.65331803136</v>
+        <v>46083.6533180324</v>
       </c>
       <c r="F576" t="n">
         <v>206</v>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="E577" s="2" t="n">
-        <v>46069.06998470155</v>
+        <v>46069.06998469908</v>
       </c>
       <c r="F577" t="n">
         <v>63</v>
@@ -24117,7 +24117,7 @@
         </is>
       </c>
       <c r="E578" s="2" t="n">
-        <v>46061.1116513965</v>
+        <v>46061.11165140046</v>
       </c>
       <c r="F578" t="n">
         <v>37</v>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="E579" s="2" t="n">
-        <v>46075.77831807279</v>
+        <v>46075.77831806713</v>
       </c>
       <c r="F579" t="n">
         <v>205</v>
@@ -24199,7 +24199,7 @@
         </is>
       </c>
       <c r="E580" s="2" t="n">
-        <v>46087.94498475021</v>
+        <v>46087.94498474537</v>
       </c>
       <c r="F580" t="n">
         <v>290</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="E581" s="2" t="n">
-        <v>46076.19498475341</v>
+        <v>46076.19498475694</v>
       </c>
       <c r="F581" t="n">
         <v>255</v>
@@ -24281,7 +24281,7 @@
         </is>
       </c>
       <c r="E582" s="2" t="n">
-        <v>46063.44498476941</v>
+        <v>46063.44498476852</v>
       </c>
       <c r="F582" t="n">
         <v>78</v>
@@ -24322,7 +24322,7 @@
         </is>
       </c>
       <c r="E583" s="2" t="n">
-        <v>46079.40331810607</v>
+        <v>46079.40331810185</v>
       </c>
       <c r="F583" t="n">
         <v>176</v>
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="E584" s="2" t="n">
-        <v>46074.52831810926</v>
+        <v>46074.52831811343</v>
       </c>
       <c r="F584" t="n">
         <v>243</v>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="E585" s="2" t="n">
-        <v>46070.61165145234</v>
+        <v>46070.61165144676</v>
       </c>
       <c r="F585" t="n">
         <v>298</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="E586" s="2" t="n">
-        <v>46067.81998478885</v>
+        <v>46067.81998479167</v>
       </c>
       <c r="F586" t="n">
         <v>94</v>
@@ -24486,7 +24486,7 @@
         </is>
       </c>
       <c r="E587" s="2" t="n">
-        <v>46078.86165146495</v>
+        <v>46078.86165146991</v>
       </c>
       <c r="F587" t="n">
         <v>232</v>
@@ -24527,7 +24527,7 @@
         </is>
       </c>
       <c r="E588" s="2" t="n">
-        <v>46078.27831813797</v>
+        <v>46078.27831813657</v>
       </c>
       <c r="F588" t="n">
         <v>33</v>
@@ -24568,7 +24568,7 @@
         </is>
       </c>
       <c r="E589" s="2" t="n">
-        <v>46080.73665149286</v>
+        <v>46080.73665149305</v>
       </c>
       <c r="F589" t="n">
         <v>79</v>
@@ -24585,6 +24585,785 @@
       </c>
       <c r="I589" t="n">
         <v>3.1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>5e9205cd-a237-49e7-af22-7d6a4f77ea5a</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>ac67a1e0-8f9d-4da3-ac13-3938417523d7</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="n">
+        <v>46079.98479248568</v>
+      </c>
+      <c r="F590" t="n">
+        <v>163</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I590" t="n">
+        <v>18.24</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>39135631-e2cf-4868-858f-b736be08fea0</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>460ae794-5de5-43a2-9fb7-a5ddadf804a0</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="n">
+        <v>46074.6097924923</v>
+      </c>
+      <c r="F591" t="n">
+        <v>174</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I591" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>4d847d85-a98e-4b18-9672-720cb4c97fa7</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>404f2c56-b24b-4538-86d7-660edac1076e</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="n">
+        <v>46083.60979250196</v>
+      </c>
+      <c r="F592" t="n">
+        <v>86</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I592" t="n">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>24632c37-c13c-434d-afa7-3c2337e5cb3a</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>af909e78-6d84-4e73-95c6-7816f8f19772</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="n">
+        <v>46080.77645917836</v>
+      </c>
+      <c r="F593" t="n">
+        <v>216</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I593" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>c548d365-f7b9-40cb-9898-996280bb02e0</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>fa8dd032-10c7-420f-bc7e-cad5db014adb</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="n">
+        <v>46082.60979251795</v>
+      </c>
+      <c r="F594" t="n">
+        <v>230</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I594" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>680a7d1c-f1e2-49be-9764-c86642b19a94</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>fe69e734-7888-4b9e-9932-8190010df45e</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="n">
+        <v>46090.98479252449</v>
+      </c>
+      <c r="F595" t="n">
+        <v>113</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I595" t="n">
+        <v>15.27</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>e947e3da-c5f9-4207-b1ea-fceb927463a9</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>f95a8bcf-3bf1-4449-bcef-894d85f72918</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="n">
+        <v>46069.40145921921</v>
+      </c>
+      <c r="F596" t="n">
+        <v>31</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I596" t="n">
+        <v>10.13</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>5b60f2d9-a210-408f-8170-43f432deb1c9</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>903e0975-c5bb-4cbc-bd34-5958da4c5476</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="n">
+        <v>46075.15145922238</v>
+      </c>
+      <c r="F597" t="n">
+        <v>102</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I597" t="n">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>bae663bf-e068-4cf1-80d3-86314be5b2dc</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>5cbec4d9-11b0-49c3-85bd-78c356084d53</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="n">
+        <v>46081.94312590487</v>
+      </c>
+      <c r="F598" t="n">
+        <v>298</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I598" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>543149c8-e6ed-4c91-b9eb-3ba0495d3c23</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>075238b2-a36b-474f-9705-e6766faac0d5</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="n">
+        <v>46083.10979257478</v>
+      </c>
+      <c r="F599" t="n">
+        <v>98</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I599" t="n">
+        <v>11.22</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>d386bf0d-26f1-415b-a71d-9e85bbe05393</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>9ea13220-e54c-4951-8e76-d130654c4c37</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="n">
+        <v>46084.52645925103</v>
+      </c>
+      <c r="F600" t="n">
+        <v>239</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I600" t="n">
+        <v>16.94</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>9769f37e-d546-49ac-a192-43b675d1c3fd</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>c1886a20-3adb-4dcd-b1cd-11a253aefda1</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="n">
+        <v>46075.15145925416</v>
+      </c>
+      <c r="F601" t="n">
+        <v>257</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I601" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>5fd19d5c-1f9e-43f6-8ae8-c361d69b0879</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>28612b0a-bc11-4198-aec4-ad60e16c15cd</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="n">
+        <v>46074.7347926002</v>
+      </c>
+      <c r="F602" t="n">
+        <v>287</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I602" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>cbdc3e11-404b-458f-a791-7a1d1e23d34f</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>388562b1-f2ec-45d3-9a5c-4d989d6a1681</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="n">
+        <v>46071.85979260664</v>
+      </c>
+      <c r="F603" t="n">
+        <v>244</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I603" t="n">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>7e02caf1-6889-4f5f-a341-ca7d23d4f596</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>cb529afb-515f-4ace-b3de-bb143aed65c5</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="n">
+        <v>46082.94312594321</v>
+      </c>
+      <c r="F604" t="n">
+        <v>180</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I604" t="n">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>43cc7c6b-3aec-42c3-a452-39167bea5217</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>6708345b-4eaf-4bc0-852d-27808640263e</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="n">
+        <v>46066.85979261299</v>
+      </c>
+      <c r="F605" t="n">
+        <v>224</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I605" t="n">
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>a5d5e662-5e94-4817-ad78-0daf29adc9e5</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>789a2e54-11f1-40ab-88d9-5de9af64a414</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="n">
+        <v>46077.6514592861</v>
+      </c>
+      <c r="F606" t="n">
+        <v>248</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I606" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>81230ff9-09f7-4773-a970-2fa296f38587</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>e21b025c-9608-45b0-8548-3fd14ae75f2a</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="n">
+        <v>46075.609792629</v>
+      </c>
+      <c r="F607" t="n">
+        <v>185</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I607" t="n">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>dfc7a4d8-8f01-4600-8951-a5d66832b61a</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>3522ebf8-6440-454d-85cc-59c762d79052</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="n">
+        <v>46078.15145930197</v>
+      </c>
+      <c r="F608" t="n">
+        <v>242</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I608" t="n">
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I608"/>
+  <dimension ref="A1:I627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24609,7 +24609,7 @@
         </is>
       </c>
       <c r="E590" s="2" t="n">
-        <v>46079.98479248568</v>
+        <v>46079.98479248842</v>
       </c>
       <c r="F590" t="n">
         <v>163</v>
@@ -24650,7 +24650,7 @@
         </is>
       </c>
       <c r="E591" s="2" t="n">
-        <v>46074.6097924923</v>
+        <v>46074.60979248842</v>
       </c>
       <c r="F591" t="n">
         <v>174</v>
@@ -24691,7 +24691,7 @@
         </is>
       </c>
       <c r="E592" s="2" t="n">
-        <v>46083.60979250196</v>
+        <v>46083.6097925</v>
       </c>
       <c r="F592" t="n">
         <v>86</v>
@@ -24732,7 +24732,7 @@
         </is>
       </c>
       <c r="E593" s="2" t="n">
-        <v>46080.77645917836</v>
+        <v>46080.77645917824</v>
       </c>
       <c r="F593" t="n">
         <v>216</v>
@@ -24773,7 +24773,7 @@
         </is>
       </c>
       <c r="E594" s="2" t="n">
-        <v>46082.60979251795</v>
+        <v>46082.60979252315</v>
       </c>
       <c r="F594" t="n">
         <v>230</v>
@@ -24814,7 +24814,7 @@
         </is>
       </c>
       <c r="E595" s="2" t="n">
-        <v>46090.98479252449</v>
+        <v>46090.98479252315</v>
       </c>
       <c r="F595" t="n">
         <v>113</v>
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="E596" s="2" t="n">
-        <v>46069.40145921921</v>
+        <v>46069.40145922454</v>
       </c>
       <c r="F596" t="n">
         <v>31</v>
@@ -24896,7 +24896,7 @@
         </is>
       </c>
       <c r="E597" s="2" t="n">
-        <v>46075.15145922238</v>
+        <v>46075.15145922454</v>
       </c>
       <c r="F597" t="n">
         <v>102</v>
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="E598" s="2" t="n">
-        <v>46081.94312590487</v>
+        <v>46081.94312590278</v>
       </c>
       <c r="F598" t="n">
         <v>298</v>
@@ -24978,7 +24978,7 @@
         </is>
       </c>
       <c r="E599" s="2" t="n">
-        <v>46083.10979257478</v>
+        <v>46083.10979256944</v>
       </c>
       <c r="F599" t="n">
         <v>98</v>
@@ -25019,7 +25019,7 @@
         </is>
       </c>
       <c r="E600" s="2" t="n">
-        <v>46084.52645925103</v>
+        <v>46084.52645924769</v>
       </c>
       <c r="F600" t="n">
         <v>239</v>
@@ -25060,7 +25060,7 @@
         </is>
       </c>
       <c r="E601" s="2" t="n">
-        <v>46075.15145925416</v>
+        <v>46075.15145925926</v>
       </c>
       <c r="F601" t="n">
         <v>257</v>
@@ -25101,7 +25101,7 @@
         </is>
       </c>
       <c r="E602" s="2" t="n">
-        <v>46074.7347926002</v>
+        <v>46074.73479260417</v>
       </c>
       <c r="F602" t="n">
         <v>287</v>
@@ -25142,7 +25142,7 @@
         </is>
       </c>
       <c r="E603" s="2" t="n">
-        <v>46071.85979260664</v>
+        <v>46071.85979260417</v>
       </c>
       <c r="F603" t="n">
         <v>244</v>
@@ -25183,7 +25183,7 @@
         </is>
       </c>
       <c r="E604" s="2" t="n">
-        <v>46082.94312594321</v>
+        <v>46082.9431259375</v>
       </c>
       <c r="F604" t="n">
         <v>180</v>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="E605" s="2" t="n">
-        <v>46066.85979261299</v>
+        <v>46066.85979261574</v>
       </c>
       <c r="F605" t="n">
         <v>224</v>
@@ -25265,7 +25265,7 @@
         </is>
       </c>
       <c r="E606" s="2" t="n">
-        <v>46077.6514592861</v>
+        <v>46077.65145928241</v>
       </c>
       <c r="F606" t="n">
         <v>248</v>
@@ -25306,7 +25306,7 @@
         </is>
       </c>
       <c r="E607" s="2" t="n">
-        <v>46075.609792629</v>
+        <v>46075.60979262731</v>
       </c>
       <c r="F607" t="n">
         <v>185</v>
@@ -25347,7 +25347,7 @@
         </is>
       </c>
       <c r="E608" s="2" t="n">
-        <v>46078.15145930197</v>
+        <v>46078.15145930555</v>
       </c>
       <c r="F608" t="n">
         <v>242</v>
@@ -25364,6 +25364,785 @@
       </c>
       <c r="I608" t="n">
         <v>18.6</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>51871dc8-1dd3-4e7b-9f35-714867513b8a</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>82a04c67-3eb9-4673-88bf-14fe0b9482d0</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="n">
+        <v>46065.93731605494</v>
+      </c>
+      <c r="F609" t="n">
+        <v>192</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I609" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>05c2823e-2f3c-48b8-81a0-67bbb86be46b</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>bc321edc-229c-4a48-8a7a-7ccdfa5dae42</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="n">
+        <v>46075.5206493928</v>
+      </c>
+      <c r="F610" t="n">
+        <v>208</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I610" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2c5a65e6-e0b1-4636-8f28-ca2ee380a7da</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>6a15ed7f-1488-43dc-9bcd-f89dc4094bb7</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="n">
+        <v>46079.27064939943</v>
+      </c>
+      <c r="F611" t="n">
+        <v>200</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I611" t="n">
+        <v>19.53</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>486527da-bf6a-4e7b-be80-6fef241cd54e</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>719684b9-50eb-4921-8d7d-df59fbf67eb1</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="n">
+        <v>46071.68731607262</v>
+      </c>
+      <c r="F612" t="n">
+        <v>296</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I612" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>0fc8512e-fc67-46f5-8afe-015c5ef82a68</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>0764d7a0-740e-4595-b8f4-a312b615c481</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="n">
+        <v>46071.06231608841</v>
+      </c>
+      <c r="F613" t="n">
+        <v>284</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I613" t="n">
+        <v>17.39</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>0fe5a03f-f61b-4a5a-a68b-d652907a7276</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>16d47716-e177-4925-85d6-3e3b3b47f9e5</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="n">
+        <v>46079.39564945974</v>
+      </c>
+      <c r="F614" t="n">
+        <v>261</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I614" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>d0129bb7-4efb-4c06-9de5-9baf3deca2bd</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>502664f9-7266-48cd-90d2-f3367666cbc8</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="n">
+        <v>46074.81231612948</v>
+      </c>
+      <c r="F615" t="n">
+        <v>168</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I615" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>4ff45ae0-c68e-427a-b10a-f58aa9004a90</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>e9d3dd75-88ee-4c15-98bf-2aa2dfcdd8a9</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="n">
+        <v>46090.72898280869</v>
+      </c>
+      <c r="F616" t="n">
+        <v>182</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I616" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>f4c5951e-14c5-470e-965c-5112463cc869</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>5290939c-4ef1-4dec-b2fd-79ecd4a0c8f4</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="n">
+        <v>46069.56231614838</v>
+      </c>
+      <c r="F617" t="n">
+        <v>142</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I617" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>7c605736-e9f5-4018-9484-45fdf210d664</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>c9e2e540-1006-48f0-936a-c96df820744d</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="n">
+        <v>46083.14564948797</v>
+      </c>
+      <c r="F618" t="n">
+        <v>233</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I618" t="n">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>a7d0e017-2382-4461-be72-a48f4032e35a</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>b91551f5-2bd3-4247-9bfc-33cd1149855d</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="n">
+        <v>46071.06231615783</v>
+      </c>
+      <c r="F619" t="n">
+        <v>178</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I619" t="n">
+        <v>10.74</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>be821378-0914-4afb-b584-76db194eb46a</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>8b635b57-5a39-4409-85a4-930bcbe379bc</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="n">
+        <v>46080.72898282779</v>
+      </c>
+      <c r="F620" t="n">
+        <v>42</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I620" t="n">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2b571559-b6a0-47cf-b82a-5e34bad8f456</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>28baa84b-0ac2-4aea-aa21-2e15271c2448</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="n">
+        <v>46068.93731616739</v>
+      </c>
+      <c r="F621" t="n">
+        <v>98</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I621" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>cb7177dd-a107-48e0-b477-1e55a6c4b906</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>ec72b444-4f6f-4213-ba14-fae0813369f7</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="n">
+        <v>46066.06231617376</v>
+      </c>
+      <c r="F622" t="n">
+        <v>185</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I622" t="n">
+        <v>15.36</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>8af6f512-45a1-42e4-8338-9ce47bb5d9b8</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>a96c54e6-05b1-41e9-b2a2-af1197dfb230</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="n">
+        <v>46072.1873161769</v>
+      </c>
+      <c r="F623" t="n">
+        <v>78</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I623" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>db454617-b131-4f06-aabb-1a3a6c61a57a</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>87009d6e-a488-4d92-8aec-f096f0c3402c</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="n">
+        <v>46082.43731618626</v>
+      </c>
+      <c r="F624" t="n">
+        <v>45</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I624" t="n">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>b87c0c9f-f228-4fbe-87b5-ca44123d58bf</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>1797cd90-3237-4bf7-9f2d-930a28ce0af5</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="n">
+        <v>46089.43731619242</v>
+      </c>
+      <c r="F625" t="n">
+        <v>153</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I625" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>ef73a3ff-3873-4481-89c8-cc24315e80ff</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>53c97ff1-4f0f-4243-aee9-b8db6686cbc9</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="n">
+        <v>46077.56231619621</v>
+      </c>
+      <c r="F626" t="n">
+        <v>116</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I626" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>6ba64849-9ea4-476a-bb6a-a67c924debd3</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>009aab46-bbae-408d-898f-aff157ab4e90</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="n">
+        <v>46076.35398287535</v>
+      </c>
+      <c r="F627" t="n">
+        <v>182</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I627" t="n">
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I627"/>
+  <dimension ref="A1:I644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25388,7 +25388,7 @@
         </is>
       </c>
       <c r="E609" s="2" t="n">
-        <v>46065.93731605494</v>
+        <v>46065.93731605324</v>
       </c>
       <c r="F609" t="n">
         <v>192</v>
@@ -25429,7 +25429,7 @@
         </is>
       </c>
       <c r="E610" s="2" t="n">
-        <v>46075.5206493928</v>
+        <v>46075.52064939815</v>
       </c>
       <c r="F610" t="n">
         <v>208</v>
@@ -25470,7 +25470,7 @@
         </is>
       </c>
       <c r="E611" s="2" t="n">
-        <v>46079.27064939943</v>
+        <v>46079.27064939815</v>
       </c>
       <c r="F611" t="n">
         <v>200</v>
@@ -25511,7 +25511,7 @@
         </is>
       </c>
       <c r="E612" s="2" t="n">
-        <v>46071.68731607262</v>
+        <v>46071.68731607639</v>
       </c>
       <c r="F612" t="n">
         <v>296</v>
@@ -25552,7 +25552,7 @@
         </is>
       </c>
       <c r="E613" s="2" t="n">
-        <v>46071.06231608841</v>
+        <v>46071.06231608796</v>
       </c>
       <c r="F613" t="n">
         <v>284</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="E614" s="2" t="n">
-        <v>46079.39564945974</v>
+        <v>46079.39564945602</v>
       </c>
       <c r="F614" t="n">
         <v>261</v>
@@ -25634,7 +25634,7 @@
         </is>
       </c>
       <c r="E615" s="2" t="n">
-        <v>46074.81231612948</v>
+        <v>46074.81231613426</v>
       </c>
       <c r="F615" t="n">
         <v>168</v>
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E616" s="2" t="n">
-        <v>46090.72898280869</v>
+        <v>46090.7289828125</v>
       </c>
       <c r="F616" t="n">
         <v>182</v>
@@ -25716,7 +25716,7 @@
         </is>
       </c>
       <c r="E617" s="2" t="n">
-        <v>46069.56231614838</v>
+        <v>46069.56231614584</v>
       </c>
       <c r="F617" t="n">
         <v>142</v>
@@ -25757,7 +25757,7 @@
         </is>
       </c>
       <c r="E618" s="2" t="n">
-        <v>46083.14564948797</v>
+        <v>46083.14564949074</v>
       </c>
       <c r="F618" t="n">
         <v>233</v>
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="E619" s="2" t="n">
-        <v>46071.06231615783</v>
+        <v>46071.0623161574</v>
       </c>
       <c r="F619" t="n">
         <v>178</v>
@@ -25839,7 +25839,7 @@
         </is>
       </c>
       <c r="E620" s="2" t="n">
-        <v>46080.72898282779</v>
+        <v>46080.72898282408</v>
       </c>
       <c r="F620" t="n">
         <v>42</v>
@@ -25880,7 +25880,7 @@
         </is>
       </c>
       <c r="E621" s="2" t="n">
-        <v>46068.93731616739</v>
+        <v>46068.93731616898</v>
       </c>
       <c r="F621" t="n">
         <v>98</v>
@@ -25921,7 +25921,7 @@
         </is>
       </c>
       <c r="E622" s="2" t="n">
-        <v>46066.06231617376</v>
+        <v>46066.06231616898</v>
       </c>
       <c r="F622" t="n">
         <v>185</v>
@@ -25962,7 +25962,7 @@
         </is>
       </c>
       <c r="E623" s="2" t="n">
-        <v>46072.1873161769</v>
+        <v>46072.18731618056</v>
       </c>
       <c r="F623" t="n">
         <v>78</v>
@@ -26003,7 +26003,7 @@
         </is>
       </c>
       <c r="E624" s="2" t="n">
-        <v>46082.43731618626</v>
+        <v>46082.43731618056</v>
       </c>
       <c r="F624" t="n">
         <v>45</v>
@@ -26044,7 +26044,7 @@
         </is>
       </c>
       <c r="E625" s="2" t="n">
-        <v>46089.43731619242</v>
+        <v>46089.43731619213</v>
       </c>
       <c r="F625" t="n">
         <v>153</v>
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="E626" s="2" t="n">
-        <v>46077.56231619621</v>
+        <v>46077.56231619213</v>
       </c>
       <c r="F626" t="n">
         <v>116</v>
@@ -26126,7 +26126,7 @@
         </is>
       </c>
       <c r="E627" s="2" t="n">
-        <v>46076.35398287535</v>
+        <v>46076.35398287037</v>
       </c>
       <c r="F627" t="n">
         <v>182</v>
@@ -26143,6 +26143,703 @@
       </c>
       <c r="I627" t="n">
         <v>2.05</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>6f0be026-de9f-4555-b467-07b9a6b9508e</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>f8ebd807-a83d-48ef-922f-350303dc643c</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="n">
+        <v>46084.82037809934</v>
+      </c>
+      <c r="F628" t="n">
+        <v>197</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I628" t="n">
+        <v>15.45</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>3f7c2327-b354-4cee-83eb-70f713847b1e</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>165c2050-dd0b-4d08-bac7-cd9b837c7876</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="n">
+        <v>46068.82037810552</v>
+      </c>
+      <c r="F629" t="n">
+        <v>209</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I629" t="n">
+        <v>18.85</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>b5a4fdd4-d8fb-49d5-a855-a97dd4b5d778</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>4ccf7ba1-aab8-4a4f-8072-14e2df78904b</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="n">
+        <v>46089.65371144508</v>
+      </c>
+      <c r="F630" t="n">
+        <v>176</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I630" t="n">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>b8adebeb-3326-464e-a7de-171a2181e659</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>aac7b5b9-d2a6-44af-a9ce-62e197ef6ba1</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="n">
+        <v>46087.07037811475</v>
+      </c>
+      <c r="F631" t="n">
+        <v>241</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I631" t="n">
+        <v>13.71</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>8b095fa5-e987-4d2e-b5ce-431bf3866e6c</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>324a63d0-6a77-4c68-b7fc-b0ed62bdf894</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="n">
+        <v>46083.90371145992</v>
+      </c>
+      <c r="F632" t="n">
+        <v>144</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I632" t="n">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>976ec45a-e969-4965-8f5b-91009ef7206a</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>51b23182-54fe-408e-b79d-d8a6767491c5</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="n">
+        <v>46083.40371146572</v>
+      </c>
+      <c r="F633" t="n">
+        <v>199</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I633" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>0716375c-6918-46d2-9d64-d4049fecb03d</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>00a450c1-b452-49f8-8ffd-44980fbab741</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="n">
+        <v>46074.82037814111</v>
+      </c>
+      <c r="F634" t="n">
+        <v>149</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I634" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>295bec43-76dd-46ed-9d07-98eaef0f2af5</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>235b0eee-0e97-4f9a-8430-ff35d8f66e2a</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="n">
+        <v>46066.82037816406</v>
+      </c>
+      <c r="F635" t="n">
+        <v>47</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I635" t="n">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>37ad6d20-b932-43d7-9ea8-2eaf84fd7c39</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>15d3c483-b65b-46bd-9541-fcf711d1c507</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="n">
+        <v>46089.69537817298</v>
+      </c>
+      <c r="F636" t="n">
+        <v>211</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I636" t="n">
+        <v>11.79</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>e846094b-ae10-416c-8bba-7331e23c4a90</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>bfaed988-53d0-48bb-8972-f6cd027f8079</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="n">
+        <v>46077.98704484252</v>
+      </c>
+      <c r="F637" t="n">
+        <v>122</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I637" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>729ad42a-29c6-4d40-b9e9-647ed9968d04</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2938f337-2cc1-4b8b-9a68-34337776f600</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="n">
+        <v>46075.4453781789</v>
+      </c>
+      <c r="F638" t="n">
+        <v>187</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I638" t="n">
+        <v>12.12</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>da6d4943-151d-4e7d-999e-3b91f32ba1a4</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>594bc6c5-c9d8-40cd-9c24-17d7a0085ab8</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="n">
+        <v>46089.69537818477</v>
+      </c>
+      <c r="F639" t="n">
+        <v>36</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I639" t="n">
+        <v>11.93</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>e06649f5-590d-4fb1-84d1-658c4c8ea36e</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>5e3e0231-2d14-411e-9b47-bca184c4aa5d</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="n">
+        <v>46083.65371152671</v>
+      </c>
+      <c r="F640" t="n">
+        <v>198</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I640" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>029dcec3-1f0d-49cc-89a8-7b501429880b</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>e985b288-8447-478e-9c29-dee339fc3912</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="n">
+        <v>46082.90371154983</v>
+      </c>
+      <c r="F641" t="n">
+        <v>204</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I641" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>4b266e71-41bf-4064-a0a8-1282f31e24d6</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>518bf301-5c1c-48a3-b60c-60db3add2b43</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="n">
+        <v>46070.32037822221</v>
+      </c>
+      <c r="F642" t="n">
+        <v>227</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I642" t="n">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>3758201d-bfd1-4f32-8c12-cc3d7ae2b7d3</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>8c7dcd58-00b9-44fe-b999-e3a10c1a0d40</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="n">
+        <v>46075.7370448975</v>
+      </c>
+      <c r="F643" t="n">
+        <v>287</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I643" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>6fd55d62-0084-42f7-a642-01e92225a72a</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>3db46911-742e-4c93-b385-83fa04a7b668</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="n">
+        <v>46063.11204490314</v>
+      </c>
+      <c r="F644" t="n">
+        <v>225</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I644" t="n">
+        <v>5.16</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I644"/>
+  <dimension ref="A1:I670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26167,7 +26167,7 @@
         </is>
       </c>
       <c r="E628" s="2" t="n">
-        <v>46084.82037809934</v>
+        <v>46084.82037810185</v>
       </c>
       <c r="F628" t="n">
         <v>197</v>
@@ -26208,7 +26208,7 @@
         </is>
       </c>
       <c r="E629" s="2" t="n">
-        <v>46068.82037810552</v>
+        <v>46068.82037810185</v>
       </c>
       <c r="F629" t="n">
         <v>209</v>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="E630" s="2" t="n">
-        <v>46089.65371144508</v>
+        <v>46089.65371144676</v>
       </c>
       <c r="F630" t="n">
         <v>176</v>
@@ -26290,7 +26290,7 @@
         </is>
       </c>
       <c r="E631" s="2" t="n">
-        <v>46087.07037811475</v>
+        <v>46087.07037811343</v>
       </c>
       <c r="F631" t="n">
         <v>241</v>
@@ -26331,7 +26331,7 @@
         </is>
       </c>
       <c r="E632" s="2" t="n">
-        <v>46083.90371145992</v>
+        <v>46083.90371145833</v>
       </c>
       <c r="F632" t="n">
         <v>144</v>
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="E633" s="2" t="n">
-        <v>46083.40371146572</v>
+        <v>46083.40371146991</v>
       </c>
       <c r="F633" t="n">
         <v>199</v>
@@ -26413,7 +26413,7 @@
         </is>
       </c>
       <c r="E634" s="2" t="n">
-        <v>46074.82037814111</v>
+        <v>46074.82037813657</v>
       </c>
       <c r="F634" t="n">
         <v>149</v>
@@ -26454,7 +26454,7 @@
         </is>
       </c>
       <c r="E635" s="2" t="n">
-        <v>46066.82037816406</v>
+        <v>46066.82037815973</v>
       </c>
       <c r="F635" t="n">
         <v>47</v>
@@ -26495,7 +26495,7 @@
         </is>
       </c>
       <c r="E636" s="2" t="n">
-        <v>46089.69537817298</v>
+        <v>46089.69537817129</v>
       </c>
       <c r="F636" t="n">
         <v>211</v>
@@ -26536,7 +26536,7 @@
         </is>
       </c>
       <c r="E637" s="2" t="n">
-        <v>46077.98704484252</v>
+        <v>46077.98704483797</v>
       </c>
       <c r="F637" t="n">
         <v>122</v>
@@ -26577,7 +26577,7 @@
         </is>
       </c>
       <c r="E638" s="2" t="n">
-        <v>46075.4453781789</v>
+        <v>46075.44537818287</v>
       </c>
       <c r="F638" t="n">
         <v>187</v>
@@ -26618,7 +26618,7 @@
         </is>
       </c>
       <c r="E639" s="2" t="n">
-        <v>46089.69537818477</v>
+        <v>46089.69537818287</v>
       </c>
       <c r="F639" t="n">
         <v>36</v>
@@ -26659,7 +26659,7 @@
         </is>
       </c>
       <c r="E640" s="2" t="n">
-        <v>46083.65371152671</v>
+        <v>46083.65371152778</v>
       </c>
       <c r="F640" t="n">
         <v>198</v>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="E641" s="2" t="n">
-        <v>46082.90371154983</v>
+        <v>46082.90371155093</v>
       </c>
       <c r="F641" t="n">
         <v>204</v>
@@ -26741,7 +26741,7 @@
         </is>
       </c>
       <c r="E642" s="2" t="n">
-        <v>46070.32037822221</v>
+        <v>46070.32037821759</v>
       </c>
       <c r="F642" t="n">
         <v>227</v>
@@ -26782,7 +26782,7 @@
         </is>
       </c>
       <c r="E643" s="2" t="n">
-        <v>46075.7370448975</v>
+        <v>46075.73704489583</v>
       </c>
       <c r="F643" t="n">
         <v>287</v>
@@ -26823,7 +26823,7 @@
         </is>
       </c>
       <c r="E644" s="2" t="n">
-        <v>46063.11204490314</v>
+        <v>46063.11204490741</v>
       </c>
       <c r="F644" t="n">
         <v>225</v>
@@ -26840,6 +26840,1072 @@
       </c>
       <c r="I644" t="n">
         <v>5.16</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>6581aef5-d303-40b5-afb1-75cd700ffcd5</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>57ab6d74-f2aa-4832-9eb1-6ff9d5bf8e3e</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="n">
+        <v>46080.0535767574</v>
+      </c>
+      <c r="F645" t="n">
+        <v>196</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I645" t="n">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>5696ec00-dee4-4407-b758-0e1d04c6e064</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>7923be07-ca5a-46e1-b54f-99074ef66e2c</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="n">
+        <v>46077.01191009585</v>
+      </c>
+      <c r="F646" t="n">
+        <v>37</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I646" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>cb9da114-f6ed-4a74-ae23-bdfeef567115</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>4d898aa9-1c65-4b1e-a54b-38b41cea9839</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="n">
+        <v>46084.01191009995</v>
+      </c>
+      <c r="F647" t="n">
+        <v>107</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I647" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>0056bf23-5e8c-4573-a2c9-94a535f8ebc3</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>b85720b9-16f7-4d68-9800-f5099246c862</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="n">
+        <v>46088.05357678317</v>
+      </c>
+      <c r="F648" t="n">
+        <v>120</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I648" t="n">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>05eec657-7b50-4a70-a046-ca678f834a7d</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>b76145ac-2cca-45d8-8027-848e5228b265</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="n">
+        <v>46083.97024345986</v>
+      </c>
+      <c r="F649" t="n">
+        <v>250</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I649" t="n">
+        <v>17.35</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>4cf79573-78c5-49a5-a189-bbe79c86ffcd</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>21084d39-cd0e-4b0a-8312-fe2471e2ad13</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="n">
+        <v>46071.76191014628</v>
+      </c>
+      <c r="F650" t="n">
+        <v>205</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I650" t="n">
+        <v>18.62</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>c0e8dc3d-bcbc-4ff8-9630-e01202f8dbaa</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>5c60f1ac-e406-4d09-8556-1b3ee905ebf8</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="n">
+        <v>46072.01191015267</v>
+      </c>
+      <c r="F651" t="n">
+        <v>236</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I651" t="n">
+        <v>13.36</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>47338e60-080d-411c-9cbd-36b0c097e65b</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>ef6a45c5-4825-49f2-876f-92cb78724d7c</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="n">
+        <v>46082.92857682281</v>
+      </c>
+      <c r="F652" t="n">
+        <v>125</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I652" t="n">
+        <v>14.71</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>ec70b249-04e2-44bc-bef3-9100defce744</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>0c5f752e-b73b-4645-bf37-c3bbfd9cb7d8</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="n">
+        <v>46065.97024349581</v>
+      </c>
+      <c r="F653" t="n">
+        <v>240</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I653" t="n">
+        <v>12.86</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>a0c71fc9-5569-4293-af42-7669ef342814</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2449b7e5-78fc-40d4-b51c-7a641035fd87</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="n">
+        <v>46091.51191016587</v>
+      </c>
+      <c r="F654" t="n">
+        <v>271</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I654" t="n">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>18ca39b0-ae2d-4808-9be5-daa71af39f85</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>8fd0e957-b0e0-48c7-b5cb-937a005f8741</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="n">
+        <v>46072.92857683581</v>
+      </c>
+      <c r="F655" t="n">
+        <v>123</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I655" t="n">
+        <v>12.78</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>ec9b42f1-cbe8-4c9f-9005-49f3f8b86e9a</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>70dfe2fc-eeb1-43d9-929d-de1432f0debe</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="n">
+        <v>46063.0119101755</v>
+      </c>
+      <c r="F656" t="n">
+        <v>156</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I656" t="n">
+        <v>15.07</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>274b414a-827a-48ba-816f-939f69937440</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>5e4c6806-f63b-48b6-bcb1-715e65bc82fe</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="n">
+        <v>46073.8869101822</v>
+      </c>
+      <c r="F657" t="n">
+        <v>73</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I657" t="n">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>f8a6e4ea-3d59-4451-87de-7ce684d4a881</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>6b6a2616-8905-478f-a523-6cc7cc7e9975</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="n">
+        <v>46081.88691018544</v>
+      </c>
+      <c r="F658" t="n">
+        <v>125</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I658" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>0b9c5663-1263-455c-9b3c-55c004b2d8a1</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>92459525-16a6-4d67-805f-6fdf96fcf29d</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="n">
+        <v>46070.97024352251</v>
+      </c>
+      <c r="F659" t="n">
+        <v>46</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I659" t="n">
+        <v>19.77</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>dfc05acf-e593-4f7d-bbb7-0b9754e8ac52</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>c7dd6d71-5a7a-4f0d-a69b-881815587ddf</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="n">
+        <v>46082.88691019875</v>
+      </c>
+      <c r="F660" t="n">
+        <v>271</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I660" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>5a52a3f8-9969-4ce3-a4b8-6a7eed412837</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>794b3f5d-2b87-45f8-9f5d-540c3ccbb0c9</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="n">
+        <v>46077.17857688169</v>
+      </c>
+      <c r="F661" t="n">
+        <v>122</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I661" t="n">
+        <v>15.31</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>5277041d-d330-43c2-8e1c-b56487870ca4</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>dd2423ec-5c50-4b40-8941-591a214a1726</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="n">
+        <v>46080.47024355155</v>
+      </c>
+      <c r="F662" t="n">
+        <v>75</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I662" t="n">
+        <v>17.09</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>24e18678-0779-4ef0-8dc3-5c07e001e0cd</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>4a4bd5ff-b415-4f34-ac73-d84b8e657757</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="n">
+        <v>46091.13691022486</v>
+      </c>
+      <c r="F663" t="n">
+        <v>146</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I663" t="n">
+        <v>15.33</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>3b62a5a7-24fb-4c63-ab33-02f7328a44a9</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>0f9bc35e-a2cd-4f1d-8d76-3e1d23bf416b</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="n">
+        <v>46073.09524356141</v>
+      </c>
+      <c r="F664" t="n">
+        <v>129</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I664" t="n">
+        <v>13.48</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>41716cf2-dc1c-4706-b613-39f033036755</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>1d279b40-4d75-4083-8567-f2de1634e430</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="n">
+        <v>46090.05357689804</v>
+      </c>
+      <c r="F665" t="n">
+        <v>39</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I665" t="n">
+        <v>12.98</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>ba1e55c3-8b86-4aa5-b6a7-84994b037eff</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2fb1608f-059c-42f9-8705-575d4c58a877</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="n">
+        <v>46076.72024356789</v>
+      </c>
+      <c r="F666" t="n">
+        <v>67</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I666" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>e7e63eda-3bf4-4404-8ea2-0494df611a28</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>949ebc06-2a8a-4987-a932-6fd616a8aa81</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="n">
+        <v>46069.05357690811</v>
+      </c>
+      <c r="F667" t="n">
+        <v>202</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I667" t="n">
+        <v>17.61</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>757e2847-eeba-4697-ace3-27a661bf5bbd</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>6a1a7d08-fada-4ce2-a11f-5245489f4c6f</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="n">
+        <v>46085.38691024464</v>
+      </c>
+      <c r="F668" t="n">
+        <v>63</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I668" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>cc92f6f9-80cb-4e85-ae72-c03bf7ac3534</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>944c66d7-f53a-4cd6-9511-159698cd4419</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="n">
+        <v>46089.26191024825</v>
+      </c>
+      <c r="F669" t="n">
+        <v>107</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I669" t="n">
+        <v>11.48</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>04a9f8db-7fb0-48d3-ad32-60a0d8dfa45a</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>41a4f48d-0e68-4c42-9660-515a903adaa2</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="n">
+        <v>46086.6785769181</v>
+      </c>
+      <c r="F670" t="n">
+        <v>159</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I670" t="n">
+        <v>10.14</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I670"/>
+  <dimension ref="A1:I686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="E645" s="2" t="n">
-        <v>46080.0535767574</v>
+        <v>46080.05357675926</v>
       </c>
       <c r="F645" t="n">
         <v>196</v>
@@ -26905,7 +26905,7 @@
         </is>
       </c>
       <c r="E646" s="2" t="n">
-        <v>46077.01191009585</v>
+        <v>46077.01191009259</v>
       </c>
       <c r="F646" t="n">
         <v>37</v>
@@ -26946,7 +26946,7 @@
         </is>
       </c>
       <c r="E647" s="2" t="n">
-        <v>46084.01191009995</v>
+        <v>46084.01191010416</v>
       </c>
       <c r="F647" t="n">
         <v>107</v>
@@ -26987,7 +26987,7 @@
         </is>
       </c>
       <c r="E648" s="2" t="n">
-        <v>46088.05357678317</v>
+        <v>46088.0535767824</v>
       </c>
       <c r="F648" t="n">
         <v>120</v>
@@ -27028,7 +27028,7 @@
         </is>
       </c>
       <c r="E649" s="2" t="n">
-        <v>46083.97024345986</v>
+        <v>46083.97024346065</v>
       </c>
       <c r="F649" t="n">
         <v>250</v>
@@ -27069,7 +27069,7 @@
         </is>
       </c>
       <c r="E650" s="2" t="n">
-        <v>46071.76191014628</v>
+        <v>46071.76191015046</v>
       </c>
       <c r="F650" t="n">
         <v>205</v>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="E651" s="2" t="n">
-        <v>46072.01191015267</v>
+        <v>46072.01191015046</v>
       </c>
       <c r="F651" t="n">
         <v>236</v>
@@ -27151,7 +27151,7 @@
         </is>
       </c>
       <c r="E652" s="2" t="n">
-        <v>46082.92857682281</v>
+        <v>46082.92857681713</v>
       </c>
       <c r="F652" t="n">
         <v>125</v>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="E653" s="2" t="n">
-        <v>46065.97024349581</v>
+        <v>46065.97024349537</v>
       </c>
       <c r="F653" t="n">
         <v>240</v>
@@ -27233,7 +27233,7 @@
         </is>
       </c>
       <c r="E654" s="2" t="n">
-        <v>46091.51191016587</v>
+        <v>46091.51191016204</v>
       </c>
       <c r="F654" t="n">
         <v>271</v>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="E655" s="2" t="n">
-        <v>46072.92857683581</v>
+        <v>46072.92857684028</v>
       </c>
       <c r="F655" t="n">
         <v>123</v>
@@ -27315,7 +27315,7 @@
         </is>
       </c>
       <c r="E656" s="2" t="n">
-        <v>46063.0119101755</v>
+        <v>46063.01191017361</v>
       </c>
       <c r="F656" t="n">
         <v>156</v>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="E657" s="2" t="n">
-        <v>46073.8869101822</v>
+        <v>46073.88691018519</v>
       </c>
       <c r="F657" t="n">
         <v>73</v>
@@ -27397,7 +27397,7 @@
         </is>
       </c>
       <c r="E658" s="2" t="n">
-        <v>46081.88691018544</v>
+        <v>46081.88691018519</v>
       </c>
       <c r="F658" t="n">
         <v>125</v>
@@ -27438,7 +27438,7 @@
         </is>
       </c>
       <c r="E659" s="2" t="n">
-        <v>46070.97024352251</v>
+        <v>46070.97024351852</v>
       </c>
       <c r="F659" t="n">
         <v>46</v>
@@ -27479,7 +27479,7 @@
         </is>
       </c>
       <c r="E660" s="2" t="n">
-        <v>46082.88691019875</v>
+        <v>46082.88691019676</v>
       </c>
       <c r="F660" t="n">
         <v>271</v>
@@ -27520,7 +27520,7 @@
         </is>
       </c>
       <c r="E661" s="2" t="n">
-        <v>46077.17857688169</v>
+        <v>46077.17857688657</v>
       </c>
       <c r="F661" t="n">
         <v>122</v>
@@ -27561,7 +27561,7 @@
         </is>
       </c>
       <c r="E662" s="2" t="n">
-        <v>46080.47024355155</v>
+        <v>46080.47024355324</v>
       </c>
       <c r="F662" t="n">
         <v>75</v>
@@ -27602,7 +27602,7 @@
         </is>
       </c>
       <c r="E663" s="2" t="n">
-        <v>46091.13691022486</v>
+        <v>46091.13691021991</v>
       </c>
       <c r="F663" t="n">
         <v>146</v>
@@ -27643,7 +27643,7 @@
         </is>
       </c>
       <c r="E664" s="2" t="n">
-        <v>46073.09524356141</v>
+        <v>46073.09524356481</v>
       </c>
       <c r="F664" t="n">
         <v>129</v>
@@ -27684,7 +27684,7 @@
         </is>
       </c>
       <c r="E665" s="2" t="n">
-        <v>46090.05357689804</v>
+        <v>46090.05357689815</v>
       </c>
       <c r="F665" t="n">
         <v>39</v>
@@ -27725,7 +27725,7 @@
         </is>
       </c>
       <c r="E666" s="2" t="n">
-        <v>46076.72024356789</v>
+        <v>46076.72024356481</v>
       </c>
       <c r="F666" t="n">
         <v>67</v>
@@ -27766,7 +27766,7 @@
         </is>
       </c>
       <c r="E667" s="2" t="n">
-        <v>46069.05357690811</v>
+        <v>46069.05357690972</v>
       </c>
       <c r="F667" t="n">
         <v>202</v>
@@ -27807,7 +27807,7 @@
         </is>
       </c>
       <c r="E668" s="2" t="n">
-        <v>46085.38691024464</v>
+        <v>46085.38691024305</v>
       </c>
       <c r="F668" t="n">
         <v>63</v>
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="E669" s="2" t="n">
-        <v>46089.26191024825</v>
+        <v>46089.26191024305</v>
       </c>
       <c r="F669" t="n">
         <v>107</v>
@@ -27889,7 +27889,7 @@
         </is>
       </c>
       <c r="E670" s="2" t="n">
-        <v>46086.6785769181</v>
+        <v>46086.67857692129</v>
       </c>
       <c r="F670" t="n">
         <v>159</v>
@@ -27906,6 +27906,662 @@
       </c>
       <c r="I670" t="n">
         <v>10.14</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>7c341fa3-92ab-4b13-8326-7209f6283a19</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>bf74494f-051e-4574-9a1a-aec3f3e9208d</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="n">
+        <v>46077.226888145</v>
+      </c>
+      <c r="F671" t="n">
+        <v>58</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I671" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>479e9279-c507-41eb-8759-353a8aa695e7</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>a1ed0d99-f814-4a34-b2aa-19694f92df1d</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="n">
+        <v>46087.39355482769</v>
+      </c>
+      <c r="F672" t="n">
+        <v>99</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I672" t="n">
+        <v>13.95</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>cd7ca003-ec1c-47c5-b06e-914ebbe9493a</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>503b913b-7f84-4634-bbee-f0de199efaf1</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="n">
+        <v>46081.01855483129</v>
+      </c>
+      <c r="F673" t="n">
+        <v>214</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I673" t="n">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>b184e682-6d09-46e9-9e0a-0e10a547cf81</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>90931d55-9c18-42d6-b45f-545f8c04a3c5</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="n">
+        <v>46076.14355483816</v>
+      </c>
+      <c r="F674" t="n">
+        <v>226</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I674" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>6233d740-2bc1-48c1-b920-d6a5b402dd7d</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>d16cd225-39dc-4a14-9a3b-090e0b8e587c</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="n">
+        <v>46078.2685548571</v>
+      </c>
+      <c r="F675" t="n">
+        <v>167</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I675" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>e88cd020-db01-4ed9-84cc-ff7291d2dec0</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>d1459ffa-93b9-4965-96f5-46458a9e59ef</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="n">
+        <v>46089.39355486338</v>
+      </c>
+      <c r="F676" t="n">
+        <v>235</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I676" t="n">
+        <v>11.63</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>af75ca0f-9bde-4f9b-be00-d4c0e7866b01</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>e54b6ca7-1b45-4ac2-990d-37c8a27bdd17</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="n">
+        <v>46073.4352215332</v>
+      </c>
+      <c r="F677" t="n">
+        <v>78</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I677" t="n">
+        <v>11.47</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>e6f94c59-5c98-4e1d-b3a6-dcf068fde7ed</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>8f46e708-fb90-4fb9-b75a-2331ddbd7ab4</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="n">
+        <v>46065.97688821566</v>
+      </c>
+      <c r="F678" t="n">
+        <v>265</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I678" t="n">
+        <v>17.47</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>4919bef2-f721-401b-8476-1ba37b44f462</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>b86e336f-cf03-4875-90ac-bc8c94d1abb2</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="n">
+        <v>46061.85188821885</v>
+      </c>
+      <c r="F679" t="n">
+        <v>91</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I679" t="n">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>b7ce1c5c-5170-4ab3-ac66-68e618626248</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>f2784152-1332-4324-8269-cd162b8bba8c</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="n">
+        <v>46064.64355488874</v>
+      </c>
+      <c r="F680" t="n">
+        <v>44</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I680" t="n">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>fc74598b-dbe8-47de-8bf0-3d7b5ae99a24</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>8a4462d1-a0ce-4637-931e-963e3e2c0fdc</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="n">
+        <v>46081.81022156178</v>
+      </c>
+      <c r="F681" t="n">
+        <v>120</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I681" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>274b780d-38cd-4ea2-94b1-9ee4cf363b89</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>25076df8-400f-4109-8e22-1bc52e8eccac</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E682" s="2" t="n">
+        <v>46069.76855490782</v>
+      </c>
+      <c r="F682" t="n">
+        <v>290</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I682" t="n">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>ecf1317e-b752-4c1b-abc6-498f021bf838</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>dd112ac8-d264-499c-a23d-e018926e1a43</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="n">
+        <v>46089.01855491417</v>
+      </c>
+      <c r="F683" t="n">
+        <v>63</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I683" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>eb5dd109-1b0e-4595-9516-2fefd92e84a1</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>169ee050-8624-4623-93a3-395d634a3855</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="n">
+        <v>46072.14355493592</v>
+      </c>
+      <c r="F684" t="n">
+        <v>122</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I684" t="n">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2ca072e4-83f7-4e91-a38e-ffd37f3ce3c9</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>b4cb8dd2-62be-478d-b2f2-24fda97dfd4d</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="n">
+        <v>46062.72688828197</v>
+      </c>
+      <c r="F685" t="n">
+        <v>193</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I685" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>fc29f243-7782-48f6-a7b0-92bebbca11e2</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>0f4a82f0-8519-481c-9026-86692b20a125</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="n">
+        <v>46089.4352216246</v>
+      </c>
+      <c r="F686" t="n">
+        <v>282</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I686" t="n">
+        <v>18.82</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I686"/>
+  <dimension ref="A1:I703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27930,7 +27930,7 @@
         </is>
       </c>
       <c r="E671" s="2" t="n">
-        <v>46077.226888145</v>
+        <v>46077.22688814815</v>
       </c>
       <c r="F671" t="n">
         <v>58</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="E672" s="2" t="n">
-        <v>46087.39355482769</v>
+        <v>46087.39355482639</v>
       </c>
       <c r="F672" t="n">
         <v>99</v>
@@ -28012,7 +28012,7 @@
         </is>
       </c>
       <c r="E673" s="2" t="n">
-        <v>46081.01855483129</v>
+        <v>46081.01855482639</v>
       </c>
       <c r="F673" t="n">
         <v>214</v>
@@ -28053,7 +28053,7 @@
         </is>
       </c>
       <c r="E674" s="2" t="n">
-        <v>46076.14355483816</v>
+        <v>46076.14355483796</v>
       </c>
       <c r="F674" t="n">
         <v>226</v>
@@ -28094,7 +28094,7 @@
         </is>
       </c>
       <c r="E675" s="2" t="n">
-        <v>46078.2685548571</v>
+        <v>46078.26855486111</v>
       </c>
       <c r="F675" t="n">
         <v>167</v>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="E676" s="2" t="n">
-        <v>46089.39355486338</v>
+        <v>46089.39355486111</v>
       </c>
       <c r="F676" t="n">
         <v>235</v>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="E677" s="2" t="n">
-        <v>46073.4352215332</v>
+        <v>46073.43522152778</v>
       </c>
       <c r="F677" t="n">
         <v>78</v>
@@ -28217,7 +28217,7 @@
         </is>
       </c>
       <c r="E678" s="2" t="n">
-        <v>46065.97688821566</v>
+        <v>46065.97688821759</v>
       </c>
       <c r="F678" t="n">
         <v>265</v>
@@ -28258,7 +28258,7 @@
         </is>
       </c>
       <c r="E679" s="2" t="n">
-        <v>46061.85188821885</v>
+        <v>46061.85188821759</v>
       </c>
       <c r="F679" t="n">
         <v>91</v>
@@ -28299,7 +28299,7 @@
         </is>
       </c>
       <c r="E680" s="2" t="n">
-        <v>46064.64355488874</v>
+        <v>46064.64355488426</v>
       </c>
       <c r="F680" t="n">
         <v>44</v>
@@ -28340,7 +28340,7 @@
         </is>
       </c>
       <c r="E681" s="2" t="n">
-        <v>46081.81022156178</v>
+        <v>46081.8102215625</v>
       </c>
       <c r="F681" t="n">
         <v>120</v>
@@ -28381,7 +28381,7 @@
         </is>
       </c>
       <c r="E682" s="2" t="n">
-        <v>46069.76855490782</v>
+        <v>46069.76855490741</v>
       </c>
       <c r="F682" t="n">
         <v>290</v>
@@ -28422,7 +28422,7 @@
         </is>
       </c>
       <c r="E683" s="2" t="n">
-        <v>46089.01855491417</v>
+        <v>46089.01855491898</v>
       </c>
       <c r="F683" t="n">
         <v>63</v>
@@ -28463,7 +28463,7 @@
         </is>
       </c>
       <c r="E684" s="2" t="n">
-        <v>46072.14355493592</v>
+        <v>46072.14355493055</v>
       </c>
       <c r="F684" t="n">
         <v>122</v>
@@ -28504,7 +28504,7 @@
         </is>
       </c>
       <c r="E685" s="2" t="n">
-        <v>46062.72688828197</v>
+        <v>46062.72688828703</v>
       </c>
       <c r="F685" t="n">
         <v>193</v>
@@ -28545,7 +28545,7 @@
         </is>
       </c>
       <c r="E686" s="2" t="n">
-        <v>46089.4352216246</v>
+        <v>46089.43522162037</v>
       </c>
       <c r="F686" t="n">
         <v>282</v>
@@ -28562,6 +28562,703 @@
       </c>
       <c r="I686" t="n">
         <v>18.82</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>24d53e44-db23-467d-8f83-dd77da0ce638</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>74afb41f-0b93-40ff-a9fd-99c168e556e8</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="n">
+        <v>46066.1939722331</v>
+      </c>
+      <c r="F687" t="n">
+        <v>108</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I687" t="n">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>70d0eaf7-560d-4256-8248-3ecd20ed7d9e</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>c0cfd944-c7cd-4ca1-9deb-08176c2352d6</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="n">
+        <v>46075.11063891259</v>
+      </c>
+      <c r="F688" t="n">
+        <v>202</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I688" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>6ff28b7c-beba-4d8d-a0d7-f16d8adc5117</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>f9d666aa-c4de-43a8-9fa3-7865d5fccc56</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="n">
+        <v>46090.36063892905</v>
+      </c>
+      <c r="F689" t="n">
+        <v>94</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I689" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>18876a4a-8841-4a2c-ba1f-7462a6f638d6</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>2634c01f-3652-4f11-9402-abde766bbb0f</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E690" s="2" t="n">
+        <v>46087.23563893846</v>
+      </c>
+      <c r="F690" t="n">
+        <v>272</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I690" t="n">
+        <v>13.77</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>5c56cf72-bffc-4ed0-9c03-0a30ef026c87</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>11c08e16-1dce-482f-ad40-d8be8b67cdbf</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="n">
+        <v>46080.15230561166</v>
+      </c>
+      <c r="F691" t="n">
+        <v>50</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I691" t="n">
+        <v>16.42</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>861b9920-8925-4940-a4c9-ae05868c39aa</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>2d02b18a-3ade-402f-bf3b-9e23c29e5d3e</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="n">
+        <v>46089.15230561485</v>
+      </c>
+      <c r="F692" t="n">
+        <v>218</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I692" t="n">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>263cc241-1dca-4623-a579-67f737128923</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>c6e116af-5ee1-4d4a-a1b3-1118a5b9a178</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="n">
+        <v>46066.8189722911</v>
+      </c>
+      <c r="F693" t="n">
+        <v>53</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I693" t="n">
+        <v>15.32</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>1766af78-fe44-4760-a54d-1c7447e38dd5</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>7ee40d22-1f4f-4583-9500-9dcb76fe803b</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="n">
+        <v>46077.1523056277</v>
+      </c>
+      <c r="F694" t="n">
+        <v>125</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I694" t="n">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>b37c2fa0-0013-43a4-92bd-9bde452a4ea6</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>ed14d143-ae93-484f-95bb-f116b5c90a01</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="n">
+        <v>46084.77730564684</v>
+      </c>
+      <c r="F695" t="n">
+        <v>151</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I695" t="n">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>ec25e1cc-fdfc-455d-a0b4-e7b56a652530</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>b200f386-6524-48b2-a742-872dc159a39e</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="n">
+        <v>46077.81897232313</v>
+      </c>
+      <c r="F696" t="n">
+        <v>79</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I696" t="n">
+        <v>13.93</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>4e943048-2a4d-485c-a9e0-0f472ca7592c</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>86a1dc05-25d8-4ed1-8c8c-f3a46379ddf2</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="n">
+        <v>46091.94397234546</v>
+      </c>
+      <c r="F697" t="n">
+        <v>97</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I697" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2bba8090-73f0-4c22-89f0-1db5cbac829c</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>f7a792c3-13e8-46eb-b89b-6277ab4aa0a1</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="n">
+        <v>46068.23563901529</v>
+      </c>
+      <c r="F698" t="n">
+        <v>233</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I698" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>14989120-0b72-46de-9ade-91f61be782f3</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>d14ade62-f764-487b-be12-7082714670a2</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="n">
+        <v>46063.6939723551</v>
+      </c>
+      <c r="F699" t="n">
+        <v>298</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I699" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>6a2a3c73-3787-4279-ab71-d4a02512c0d2</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>067ba303-2e1f-440d-b282-609925848884</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="n">
+        <v>46071.56897236143</v>
+      </c>
+      <c r="F700" t="n">
+        <v>158</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I700" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>04321294-8006-43d3-b777-0c6d5d467ff8</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>c1c850de-9c05-4e3c-a681-66c9f6257780</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="n">
+        <v>46092.19397236464</v>
+      </c>
+      <c r="F701" t="n">
+        <v>108</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I701" t="n">
+        <v>15.27</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>53e41fad-e8ac-4ae7-a300-5867e9196190</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>f1188708-c6c6-42ae-affd-e5a13c8ec51a</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="n">
+        <v>46068.11063904161</v>
+      </c>
+      <c r="F702" t="n">
+        <v>245</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I702" t="n">
+        <v>17.29</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>fbe1449b-20ec-412d-a47d-d2939b52cfc8</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>592cd027-c468-4054-824b-dbc7b81af69a</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="n">
+        <v>46062.7773057181</v>
+      </c>
+      <c r="F703" t="n">
+        <v>89</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I703" t="n">
+        <v>3.68</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I703"/>
+  <dimension ref="A1:I723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28586,7 +28586,7 @@
         </is>
       </c>
       <c r="E687" s="2" t="n">
-        <v>46066.1939722331</v>
+        <v>46066.1939722338</v>
       </c>
       <c r="F687" t="n">
         <v>108</v>
@@ -28627,7 +28627,7 @@
         </is>
       </c>
       <c r="E688" s="2" t="n">
-        <v>46075.11063891259</v>
+        <v>46075.11063891204</v>
       </c>
       <c r="F688" t="n">
         <v>202</v>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="E689" s="2" t="n">
-        <v>46090.36063892905</v>
+        <v>46090.36063892361</v>
       </c>
       <c r="F689" t="n">
         <v>94</v>
@@ -28709,7 +28709,7 @@
         </is>
       </c>
       <c r="E690" s="2" t="n">
-        <v>46087.23563893846</v>
+        <v>46087.23563893518</v>
       </c>
       <c r="F690" t="n">
         <v>272</v>
@@ -28750,7 +28750,7 @@
         </is>
       </c>
       <c r="E691" s="2" t="n">
-        <v>46080.15230561166</v>
+        <v>46080.15230561342</v>
       </c>
       <c r="F691" t="n">
         <v>50</v>
@@ -28791,7 +28791,7 @@
         </is>
       </c>
       <c r="E692" s="2" t="n">
-        <v>46089.15230561485</v>
+        <v>46089.15230561342</v>
       </c>
       <c r="F692" t="n">
         <v>218</v>
@@ -28832,7 +28832,7 @@
         </is>
       </c>
       <c r="E693" s="2" t="n">
-        <v>46066.8189722911</v>
+        <v>46066.81897229166</v>
       </c>
       <c r="F693" t="n">
         <v>53</v>
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="E694" s="2" t="n">
-        <v>46077.1523056277</v>
+        <v>46077.152305625</v>
       </c>
       <c r="F694" t="n">
         <v>125</v>
@@ -28914,7 +28914,7 @@
         </is>
       </c>
       <c r="E695" s="2" t="n">
-        <v>46084.77730564684</v>
+        <v>46084.77730564815</v>
       </c>
       <c r="F695" t="n">
         <v>151</v>
@@ -28955,7 +28955,7 @@
         </is>
       </c>
       <c r="E696" s="2" t="n">
-        <v>46077.81897232313</v>
+        <v>46077.81897232639</v>
       </c>
       <c r="F696" t="n">
         <v>79</v>
@@ -28996,7 +28996,7 @@
         </is>
       </c>
       <c r="E697" s="2" t="n">
-        <v>46091.94397234546</v>
+        <v>46091.94397234954</v>
       </c>
       <c r="F697" t="n">
         <v>97</v>
@@ -29037,7 +29037,7 @@
         </is>
       </c>
       <c r="E698" s="2" t="n">
-        <v>46068.23563901529</v>
+        <v>46068.2356390162</v>
       </c>
       <c r="F698" t="n">
         <v>233</v>
@@ -29078,7 +29078,7 @@
         </is>
       </c>
       <c r="E699" s="2" t="n">
-        <v>46063.6939723551</v>
+        <v>46063.69397234954</v>
       </c>
       <c r="F699" t="n">
         <v>298</v>
@@ -29119,7 +29119,7 @@
         </is>
       </c>
       <c r="E700" s="2" t="n">
-        <v>46071.56897236143</v>
+        <v>46071.56897236111</v>
       </c>
       <c r="F700" t="n">
         <v>158</v>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="E701" s="2" t="n">
-        <v>46092.19397236464</v>
+        <v>46092.19397236111</v>
       </c>
       <c r="F701" t="n">
         <v>108</v>
@@ -29201,7 +29201,7 @@
         </is>
       </c>
       <c r="E702" s="2" t="n">
-        <v>46068.11063904161</v>
+        <v>46068.11063903935</v>
       </c>
       <c r="F702" t="n">
         <v>245</v>
@@ -29242,7 +29242,7 @@
         </is>
       </c>
       <c r="E703" s="2" t="n">
-        <v>46062.7773057181</v>
+        <v>46062.77730571759</v>
       </c>
       <c r="F703" t="n">
         <v>89</v>
@@ -29259,6 +29259,826 @@
       </c>
       <c r="I703" t="n">
         <v>3.68</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>48a7eade-f777-46c8-9432-0f72f31af211</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>66dd239a-54b2-4ce9-8a63-e24729d86c9e</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="n">
+        <v>46068.23422471475</v>
+      </c>
+      <c r="F704" t="n">
+        <v>267</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I704" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>1543c334-bcab-4db1-9016-591f3d88c3e0</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>3f29d64d-9c4a-4fd3-b9cf-fe8aaac6005a</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="n">
+        <v>46077.5675580612</v>
+      </c>
+      <c r="F705" t="n">
+        <v>187</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I705" t="n">
+        <v>12.21</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>369d8ca6-947a-4c7f-b9e4-003149ee5e04</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>3b848b4e-57b3-486c-847c-bbe64e631818</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="n">
+        <v>46082.19255806503</v>
+      </c>
+      <c r="F706" t="n">
+        <v>167</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I706" t="n">
+        <v>17.71</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>483f01d3-af85-48b4-90cf-126b27cb147c</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>6dc487af-7e77-4d23-a9b9-3db228a18371</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="n">
+        <v>46082.90089141442</v>
+      </c>
+      <c r="F707" t="n">
+        <v>191</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I707" t="n">
+        <v>19.05</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>7bb0ee22-f02f-4f3b-8010-5686f60e025e</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>7a01a05b-895c-498b-9ff8-4a57efa27c97</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="n">
+        <v>46086.52589142705</v>
+      </c>
+      <c r="F708" t="n">
+        <v>158</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I708" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>c2235a52-80c6-42fa-bf2f-7b4a537e082b</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>f7f36eda-5a23-4f3a-91d6-c7f8880a740a</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="n">
+        <v>46090.19255809703</v>
+      </c>
+      <c r="F709" t="n">
+        <v>262</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I709" t="n">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>dfb0e9f0-76f4-4ad1-96b4-812cf753a73e</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>7f18fcec-46a1-45ad-be91-e91c90f37edb</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="n">
+        <v>46073.35922477006</v>
+      </c>
+      <c r="F710" t="n">
+        <v>220</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I710" t="n">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>02809e03-2bd2-4a9c-903f-c71ad3837b1a</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>5f336d17-545c-4752-bc61-5f6bc5175d74</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="n">
+        <v>46063.52589143992</v>
+      </c>
+      <c r="F711" t="n">
+        <v>248</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I711" t="n">
+        <v>18.87</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>77a4ee56-a45e-4d4e-b37b-e941b6c994de</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>c6db83ed-0aa0-45c7-8454-68e4289ec1e7</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="n">
+        <v>46077.81755811304</v>
+      </c>
+      <c r="F712" t="n">
+        <v>211</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I712" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>97ccd94d-2642-43d3-a7ad-5e0d5f27fe6d</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>eff03056-3aac-4cfe-a6e8-96d378958383</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="n">
+        <v>46067.48422478294</v>
+      </c>
+      <c r="F713" t="n">
+        <v>102</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I713" t="n">
+        <v>19.09</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>85e5e323-7f4a-4960-9872-8025979708c3</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2bd4c63b-92a8-44fd-9c2f-6729e6dbbb41</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="n">
+        <v>46066.10922479541</v>
+      </c>
+      <c r="F714" t="n">
+        <v>214</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I714" t="n">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2260abfa-f76b-4a8e-b01b-bd54feb9076d</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>71a48183-f332-4d9d-a4d9-257631c5f356</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="n">
+        <v>46079.73422481463</v>
+      </c>
+      <c r="F715" t="n">
+        <v>247</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I715" t="n">
+        <v>14.47</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>d786870f-8350-4c30-ab75-3d8e03a55241</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>6aaf2cce-13ab-48ed-9854-a6edba1c05dc</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="n">
+        <v>46084.48422482406</v>
+      </c>
+      <c r="F716" t="n">
+        <v>169</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I716" t="n">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2dd6e076-8bac-47b8-bf60-09733006482e</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>b3351198-7b92-4a8c-a751-f5b2c9812b39</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="n">
+        <v>46080.69255816057</v>
+      </c>
+      <c r="F717" t="n">
+        <v>270</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I717" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>11751227-3f6c-45eb-808c-22d2142a87dc</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>6b1a44d1-55d4-44bc-9194-a185b2353f31</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="n">
+        <v>46068.81755816381</v>
+      </c>
+      <c r="F718" t="n">
+        <v>155</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I718" t="n">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>d8c8d185-217c-4961-b91b-728d5258bbcf</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>1a86857f-b308-4a75-aa76-57ad3b696117</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="n">
+        <v>46080.31755816709</v>
+      </c>
+      <c r="F719" t="n">
+        <v>88</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I719" t="n">
+        <v>15.61</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>f802cb49-a3f6-436b-b685-e1b8637de2b5</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>ecf78c76-b34e-48e4-8f45-d00b3d463bcf</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="n">
+        <v>46071.35922484336</v>
+      </c>
+      <c r="F720" t="n">
+        <v>292</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I720" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>f4aa5d5d-5ee6-4fd3-8635-2847ccfd3a5d</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>ec142984-bffb-4424-bfc8-841f464be685</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="n">
+        <v>46064.65089151944</v>
+      </c>
+      <c r="F721" t="n">
+        <v>249</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I721" t="n">
+        <v>16.73</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>9542fb03-e624-473c-b924-1833dc17de54</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>e928e269-a868-4aed-90ac-825c329ba67b</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="n">
+        <v>46065.23422485922</v>
+      </c>
+      <c r="F722" t="n">
+        <v>296</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I722" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>811e58df-890e-4538-8d6a-eb3cda00ae28</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>e839981c-6ffd-4a01-9152-89db0f32775a</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="n">
+        <v>46089.48422486539</v>
+      </c>
+      <c r="F723" t="n">
+        <v>290</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I723" t="n">
+        <v>4.93</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I723"/>
+  <dimension ref="A1:I745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29283,7 +29283,7 @@
         </is>
       </c>
       <c r="E704" s="2" t="n">
-        <v>46068.23422471475</v>
+        <v>46068.23422471065</v>
       </c>
       <c r="F704" t="n">
         <v>267</v>
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="E705" s="2" t="n">
-        <v>46077.5675580612</v>
+        <v>46077.56755805555</v>
       </c>
       <c r="F705" t="n">
         <v>187</v>
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="E706" s="2" t="n">
-        <v>46082.19255806503</v>
+        <v>46082.19255806713</v>
       </c>
       <c r="F706" t="n">
         <v>167</v>
@@ -29406,7 +29406,7 @@
         </is>
       </c>
       <c r="E707" s="2" t="n">
-        <v>46082.90089141442</v>
+        <v>46082.90089141203</v>
       </c>
       <c r="F707" t="n">
         <v>191</v>
@@ -29447,7 +29447,7 @@
         </is>
       </c>
       <c r="E708" s="2" t="n">
-        <v>46086.52589142705</v>
+        <v>46086.52589142361</v>
       </c>
       <c r="F708" t="n">
         <v>158</v>
@@ -29488,7 +29488,7 @@
         </is>
       </c>
       <c r="E709" s="2" t="n">
-        <v>46090.19255809703</v>
+        <v>46090.19255810185</v>
       </c>
       <c r="F709" t="n">
         <v>262</v>
@@ -29529,7 +29529,7 @@
         </is>
       </c>
       <c r="E710" s="2" t="n">
-        <v>46073.35922477006</v>
+        <v>46073.35922476852</v>
       </c>
       <c r="F710" t="n">
         <v>220</v>
@@ -29570,7 +29570,7 @@
         </is>
       </c>
       <c r="E711" s="2" t="n">
-        <v>46063.52589143992</v>
+        <v>46063.52589143519</v>
       </c>
       <c r="F711" t="n">
         <v>248</v>
@@ -29611,7 +29611,7 @@
         </is>
       </c>
       <c r="E712" s="2" t="n">
-        <v>46077.81755811304</v>
+        <v>46077.81755811343</v>
       </c>
       <c r="F712" t="n">
         <v>211</v>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="E713" s="2" t="n">
-        <v>46067.48422478294</v>
+        <v>46067.48422478009</v>
       </c>
       <c r="F713" t="n">
         <v>102</v>
@@ -29693,7 +29693,7 @@
         </is>
       </c>
       <c r="E714" s="2" t="n">
-        <v>46066.10922479541</v>
+        <v>46066.10922479167</v>
       </c>
       <c r="F714" t="n">
         <v>214</v>
@@ -29734,7 +29734,7 @@
         </is>
       </c>
       <c r="E715" s="2" t="n">
-        <v>46079.73422481463</v>
+        <v>46079.73422481481</v>
       </c>
       <c r="F715" t="n">
         <v>247</v>
@@ -29775,7 +29775,7 @@
         </is>
       </c>
       <c r="E716" s="2" t="n">
-        <v>46084.48422482406</v>
+        <v>46084.48422482639</v>
       </c>
       <c r="F716" t="n">
         <v>169</v>
@@ -29816,7 +29816,7 @@
         </is>
       </c>
       <c r="E717" s="2" t="n">
-        <v>46080.69255816057</v>
+        <v>46080.69255815972</v>
       </c>
       <c r="F717" t="n">
         <v>270</v>
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="E718" s="2" t="n">
-        <v>46068.81755816381</v>
+        <v>46068.81755815972</v>
       </c>
       <c r="F718" t="n">
         <v>155</v>
@@ -29898,7 +29898,7 @@
         </is>
       </c>
       <c r="E719" s="2" t="n">
-        <v>46080.31755816709</v>
+        <v>46080.31755817129</v>
       </c>
       <c r="F719" t="n">
         <v>88</v>
@@ -29939,7 +29939,7 @@
         </is>
       </c>
       <c r="E720" s="2" t="n">
-        <v>46071.35922484336</v>
+        <v>46071.35922483796</v>
       </c>
       <c r="F720" t="n">
         <v>292</v>
@@ -29980,7 +29980,7 @@
         </is>
       </c>
       <c r="E721" s="2" t="n">
-        <v>46064.65089151944</v>
+        <v>46064.6508915162</v>
       </c>
       <c r="F721" t="n">
         <v>249</v>
@@ -30021,7 +30021,7 @@
         </is>
       </c>
       <c r="E722" s="2" t="n">
-        <v>46065.23422485922</v>
+        <v>46065.23422486111</v>
       </c>
       <c r="F722" t="n">
         <v>296</v>
@@ -30062,7 +30062,7 @@
         </is>
       </c>
       <c r="E723" s="2" t="n">
-        <v>46089.48422486539</v>
+        <v>46089.48422486111</v>
       </c>
       <c r="F723" t="n">
         <v>290</v>
@@ -30079,6 +30079,908 @@
       </c>
       <c r="I723" t="n">
         <v>4.93</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>668d09cc-e7bf-4afe-ae02-dfa5fc492f28</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>aa84d5be-7207-428d-b3fb-f7508d8f7987</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="n">
+        <v>46067.10597591585</v>
+      </c>
+      <c r="F724" t="n">
+        <v>258</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I724" t="n">
+        <v>15.58</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>5393c4a7-a6a5-4e67-9349-ac0120ab56f2</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>0c73f1e6-6b2f-4d6f-9590-3e1f5ef81877</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="n">
+        <v>46069.43930925251</v>
+      </c>
+      <c r="F725" t="n">
+        <v>158</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I725" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>a23ba822-6d9c-4acc-9e4e-680e97ed1dcc</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>cd308a27-e094-4370-8bed-1c443c24eebc</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="n">
+        <v>46075.06430925896</v>
+      </c>
+      <c r="F726" t="n">
+        <v>191</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I726" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>1d43965a-6ccc-4bee-8a97-b293616556f6</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>3b3038db-30e1-4c62-b331-4b1db6ddc522</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="n">
+        <v>46074.4809759324</v>
+      </c>
+      <c r="F727" t="n">
+        <v>30</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I727" t="n">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>f9cd6ce6-649e-45db-a88e-85f23a67bc80</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9a50a567-91d5-4ed1-b8d9-5c7bd4a13547</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="n">
+        <v>46089.52264261209</v>
+      </c>
+      <c r="F728" t="n">
+        <v>68</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I728" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>8e66cd9e-a6a0-4f6d-a099-9069f266e5c4</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>7c918f57-9203-406e-b7ba-ee20a5b8d84d</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="n">
+        <v>46084.10597595514</v>
+      </c>
+      <c r="F729" t="n">
+        <v>95</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I729" t="n">
+        <v>16.22</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>c0b198b1-1cf0-414b-a93b-ce7d1cc9579b</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>74c79a26-6731-4fca-a084-8c7c9c1701a5</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="n">
+        <v>46088.85597595836</v>
+      </c>
+      <c r="F730" t="n">
+        <v>280</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I730" t="n">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>d0fd67c1-4dd7-4a63-9ad9-04cbd327f960</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>f6252cc0-7331-4e30-9955-0ddc9bdc33be</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="n">
+        <v>46075.73097597437</v>
+      </c>
+      <c r="F731" t="n">
+        <v>249</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I731" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>a157f796-716a-4a0f-8662-0c5f2fcbaecc</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>5ffa703c-e429-4c82-9c3c-2b418eac78d5</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="n">
+        <v>46068.93930931124</v>
+      </c>
+      <c r="F732" t="n">
+        <v>75</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I732" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>39b4e3d3-f5a5-45d9-bf3d-f9efc16ca07b</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>0a3adaf2-1cb7-4baf-9683-26086f06f87a</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="n">
+        <v>46072.35597598121</v>
+      </c>
+      <c r="F733" t="n">
+        <v>118</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I733" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>5db9d1bc-0b79-4f41-a92e-ef70dd9ba97a</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>b176f2f9-d443-4b5e-92bf-def333af20bd</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="n">
+        <v>46077.98097598441</v>
+      </c>
+      <c r="F734" t="n">
+        <v>279</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I734" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>477b37aa-4184-4394-9cc7-4141d8743c9a</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>e125722d-bdbc-4a8d-bd32-a5f8f99b3d39</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="n">
+        <v>46071.56430932119</v>
+      </c>
+      <c r="F735" t="n">
+        <v>259</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I735" t="n">
+        <v>14.17</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>4e5142f2-4879-481a-b0ff-bb0824d3c6b0</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>c79c2fd7-1198-45d3-8ed9-a1b14d9750db</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="n">
+        <v>46086.5226426672</v>
+      </c>
+      <c r="F736" t="n">
+        <v>182</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I736" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>0f96f2ff-339a-4b83-b78b-a5ebfde3bef5</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>48ddbc7e-0e46-426f-80f2-baf4958622c1</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="n">
+        <v>46081.35597600374</v>
+      </c>
+      <c r="F737" t="n">
+        <v>144</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I737" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>7f430714-2f40-4a66-ba3c-792df8521c53</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>e92811c2-b197-43cf-ae14-6669da8505b4</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="n">
+        <v>46071.23097601035</v>
+      </c>
+      <c r="F738" t="n">
+        <v>191</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I738" t="n">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>04488e88-c60e-4072-ba18-f71e5f88786f</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>437dde84-2a87-48e1-b135-a4faca60d0cb</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="n">
+        <v>46067.77264268652</v>
+      </c>
+      <c r="F739" t="n">
+        <v>251</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I739" t="n">
+        <v>15.88</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>1bb64865-d67d-4fa5-bdd7-025164f39262</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>feaafd77-9dc3-4fd6-b588-fa3836d8f985</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="n">
+        <v>46091.77264268977</v>
+      </c>
+      <c r="F740" t="n">
+        <v>81</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I740" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>6cd721fe-5fa1-477f-8862-19e75ea3ed8f</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>5dca3b0f-add6-4da1-9107-636410c0b346</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="n">
+        <v>46067.31430935964</v>
+      </c>
+      <c r="F741" t="n">
+        <v>80</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I741" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>73094085-e92b-4b33-8794-c41e715069e2</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>a7eae0fd-f5f9-481d-9934-3b8eed490fcb</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="n">
+        <v>46085.27264271185</v>
+      </c>
+      <c r="F742" t="n">
+        <v>136</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I742" t="n">
+        <v>10.73</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>94a62891-c9af-4ed7-bdb7-310851a029a4</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>83f1637e-02e2-46fe-ae19-73cfd90ac1c8</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="n">
+        <v>46093.64764271503</v>
+      </c>
+      <c r="F743" t="n">
+        <v>182</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I743" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>5446c4e1-c08d-4b9d-ba8a-c8be95707b64</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>4f9639c8-42b2-4f56-af7e-10e6bcc81300</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="n">
+        <v>46066.23097605485</v>
+      </c>
+      <c r="F744" t="n">
+        <v>215</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I744" t="n">
+        <v>14.88</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>bc8ff286-430a-4509-a9cd-446e4bfae597</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>790b9a5d-f145-4d81-85d8-a60f7acb03b2</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="n">
+        <v>46091.43930940087</v>
+      </c>
+      <c r="F745" t="n">
+        <v>58</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I745" t="n">
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I745"/>
+  <dimension ref="A1:I763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30103,7 +30103,7 @@
         </is>
       </c>
       <c r="E724" s="2" t="n">
-        <v>46067.10597591585</v>
+        <v>46067.10597591435</v>
       </c>
       <c r="F724" t="n">
         <v>258</v>
@@ -30144,7 +30144,7 @@
         </is>
       </c>
       <c r="E725" s="2" t="n">
-        <v>46069.43930925251</v>
+        <v>46069.43930924768</v>
       </c>
       <c r="F725" t="n">
         <v>158</v>
@@ -30185,7 +30185,7 @@
         </is>
       </c>
       <c r="E726" s="2" t="n">
-        <v>46075.06430925896</v>
+        <v>46075.06430925926</v>
       </c>
       <c r="F726" t="n">
         <v>191</v>
@@ -30226,7 +30226,7 @@
         </is>
       </c>
       <c r="E727" s="2" t="n">
-        <v>46074.4809759324</v>
+        <v>46074.4809759375</v>
       </c>
       <c r="F727" t="n">
         <v>30</v>
@@ -30267,7 +30267,7 @@
         </is>
       </c>
       <c r="E728" s="2" t="n">
-        <v>46089.52264261209</v>
+        <v>46089.52264261574</v>
       </c>
       <c r="F728" t="n">
         <v>68</v>
@@ -30308,7 +30308,7 @@
         </is>
       </c>
       <c r="E729" s="2" t="n">
-        <v>46084.10597595514</v>
+        <v>46084.10597596065</v>
       </c>
       <c r="F729" t="n">
         <v>95</v>
@@ -30349,7 +30349,7 @@
         </is>
       </c>
       <c r="E730" s="2" t="n">
-        <v>46088.85597595836</v>
+        <v>46088.85597596065</v>
       </c>
       <c r="F730" t="n">
         <v>280</v>
@@ -30390,7 +30390,7 @@
         </is>
       </c>
       <c r="E731" s="2" t="n">
-        <v>46075.73097597437</v>
+        <v>46075.73097597222</v>
       </c>
       <c r="F731" t="n">
         <v>249</v>
@@ -30431,7 +30431,7 @@
         </is>
       </c>
       <c r="E732" s="2" t="n">
-        <v>46068.93930931124</v>
+        <v>46068.93930930556</v>
       </c>
       <c r="F732" t="n">
         <v>75</v>
@@ -30472,7 +30472,7 @@
         </is>
       </c>
       <c r="E733" s="2" t="n">
-        <v>46072.35597598121</v>
+        <v>46072.3559759838</v>
       </c>
       <c r="F733" t="n">
         <v>118</v>
@@ -30513,7 +30513,7 @@
         </is>
       </c>
       <c r="E734" s="2" t="n">
-        <v>46077.98097598441</v>
+        <v>46077.9809759838</v>
       </c>
       <c r="F734" t="n">
         <v>279</v>
@@ -30554,7 +30554,7 @@
         </is>
       </c>
       <c r="E735" s="2" t="n">
-        <v>46071.56430932119</v>
+        <v>46071.56430931713</v>
       </c>
       <c r="F735" t="n">
         <v>259</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="E736" s="2" t="n">
-        <v>46086.5226426672</v>
+        <v>46086.52264266204</v>
       </c>
       <c r="F736" t="n">
         <v>182</v>
@@ -30636,7 +30636,7 @@
         </is>
       </c>
       <c r="E737" s="2" t="n">
-        <v>46081.35597600374</v>
+        <v>46081.35597600695</v>
       </c>
       <c r="F737" t="n">
         <v>144</v>
@@ -30677,7 +30677,7 @@
         </is>
       </c>
       <c r="E738" s="2" t="n">
-        <v>46071.23097601035</v>
+        <v>46071.23097600695</v>
       </c>
       <c r="F738" t="n">
         <v>191</v>
@@ -30718,7 +30718,7 @@
         </is>
       </c>
       <c r="E739" s="2" t="n">
-        <v>46067.77264268652</v>
+        <v>46067.77264268519</v>
       </c>
       <c r="F739" t="n">
         <v>251</v>
@@ -30759,7 +30759,7 @@
         </is>
       </c>
       <c r="E740" s="2" t="n">
-        <v>46091.77264268977</v>
+        <v>46091.77264268519</v>
       </c>
       <c r="F740" t="n">
         <v>81</v>
@@ -30800,7 +30800,7 @@
         </is>
       </c>
       <c r="E741" s="2" t="n">
-        <v>46067.31430935964</v>
+        <v>46067.31430936343</v>
       </c>
       <c r="F741" t="n">
         <v>80</v>
@@ -30841,7 +30841,7 @@
         </is>
       </c>
       <c r="E742" s="2" t="n">
-        <v>46085.27264271185</v>
+        <v>46085.27264270833</v>
       </c>
       <c r="F742" t="n">
         <v>136</v>
@@ -30882,7 +30882,7 @@
         </is>
       </c>
       <c r="E743" s="2" t="n">
-        <v>46093.64764271503</v>
+        <v>46093.64764271991</v>
       </c>
       <c r="F743" t="n">
         <v>182</v>
@@ -30923,7 +30923,7 @@
         </is>
       </c>
       <c r="E744" s="2" t="n">
-        <v>46066.23097605485</v>
+        <v>46066.23097605324</v>
       </c>
       <c r="F744" t="n">
         <v>215</v>
@@ -30964,7 +30964,7 @@
         </is>
       </c>
       <c r="E745" s="2" t="n">
-        <v>46091.43930940087</v>
+        <v>46091.43930939815</v>
       </c>
       <c r="F745" t="n">
         <v>58</v>
@@ -30981,6 +30981,744 @@
       </c>
       <c r="I745" t="n">
         <v>14.3</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>65dcbd00-d437-45a3-b188-bab2ab093abf</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>9cae9438-2d6f-475f-8908-724a90753160</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="n">
+        <v>46079.27136491858</v>
+      </c>
+      <c r="F746" t="n">
+        <v>158</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I746" t="n">
+        <v>19.84</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>72e0bfb0-8a83-4873-8434-d498abcf8f72</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>3a5b84b3-f5f0-4964-9fde-58aaddeb58ff</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="n">
+        <v>46086.06303160238</v>
+      </c>
+      <c r="F747" t="n">
+        <v>147</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I747" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>9311b965-ffe2-44e9-b507-3dd68bf062cf</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>b865e09d-4db0-4f4c-999a-144f911fd47d</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="n">
+        <v>46069.77136494197</v>
+      </c>
+      <c r="F748" t="n">
+        <v>63</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I748" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>87764510-2df2-4b85-bc20-9e3caab3d5a5</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>5fa317e1-d049-4166-9cf7-69f6691b9b71</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="n">
+        <v>46078.47969828514</v>
+      </c>
+      <c r="F749" t="n">
+        <v>60</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I749" t="n">
+        <v>19.66</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>bc11519c-ebfd-4f6a-b7a3-0c190d922501</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>b5e8660a-cd9b-4730-aa01-88a641a347ee</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="n">
+        <v>46075.93803163142</v>
+      </c>
+      <c r="F750" t="n">
+        <v>181</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I750" t="n">
+        <v>19.86</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>0db48bdc-507d-4811-845a-7b82a9a8253b</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2d3e6f5b-9550-4a29-bee8-189496eb6796</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="n">
+        <v>46087.72969830448</v>
+      </c>
+      <c r="F751" t="n">
+        <v>294</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I751" t="n">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>81c21abf-2894-4470-93ea-412801c0bae6</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>77f95eb5-e8d3-4b4c-b00e-a6055d80b6bc</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="n">
+        <v>46087.31303164407</v>
+      </c>
+      <c r="F752" t="n">
+        <v>30</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I752" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>39248575-c038-45fa-bc84-addd656093d8</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>1f562e3f-de12-49a6-9ec8-07cc11c47bec</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="n">
+        <v>46087.2713649807</v>
+      </c>
+      <c r="F753" t="n">
+        <v>281</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I753" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2f829d3c-fe79-4b74-80eb-af05c58e6bdc</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>5a91b0fc-6197-41a7-9126-f071451f217f</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="n">
+        <v>46065.81303165048</v>
+      </c>
+      <c r="F754" t="n">
+        <v>273</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I754" t="n">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>35a5554d-fbb3-4862-ae0b-f39a694b681b</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>da8d9990-bcf5-4346-b382-458d688af1ca</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="n">
+        <v>46082.18803166286</v>
+      </c>
+      <c r="F755" t="n">
+        <v>237</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I755" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>b5814631-9780-452b-a8c2-e25717782368</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>80a89430-4d89-478c-83af-33922193c816</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="n">
+        <v>46072.97969833275</v>
+      </c>
+      <c r="F756" t="n">
+        <v>101</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I756" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>eb5a1875-4164-4128-9681-276ef1292909</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>a69f9295-2385-4682-8e4a-e39936a92d43</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="n">
+        <v>46073.85469833589</v>
+      </c>
+      <c r="F757" t="n">
+        <v>127</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I757" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>dd8202c3-93c8-4179-a888-f47d8f0644d1</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>b77be1bb-2a94-4004-9c28-01d029717973</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="n">
+        <v>46076.47969835497</v>
+      </c>
+      <c r="F758" t="n">
+        <v>179</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I758" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>8ab9a700-c7c2-43b4-9c58-552d18b8f648</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>fde4fbcc-af3d-4687-a8a1-51eb5cb99240</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="n">
+        <v>46089.81303169762</v>
+      </c>
+      <c r="F759" t="n">
+        <v>256</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I759" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>7b1b140b-6213-4024-97e7-63ed5c022d63</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>49443ecb-b3eb-4a0f-8114-33f471474506</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="n">
+        <v>46072.8963650433</v>
+      </c>
+      <c r="F760" t="n">
+        <v>206</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I760" t="n">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>1e0ce4e5-07f6-4542-bde6-cc4be7d9c71d</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>59fdcdd0-c519-42d6-b48a-3fad7f372bef</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="n">
+        <v>46077.10469839242</v>
+      </c>
+      <c r="F761" t="n">
+        <v>79</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I761" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>bbf58bbd-9d9a-44ec-aefc-55754b8e3894</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>e02808a6-6ac0-4e2e-b966-d1ec6ff7ed5a</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="n">
+        <v>46063.39636506246</v>
+      </c>
+      <c r="F762" t="n">
+        <v>50</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I762" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>49ebdf1c-409d-4824-96f0-794ef9893e24</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>2cf1c7b2-8580-407b-a13e-cc263bec6411</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="n">
+        <v>46083.47969840227</v>
+      </c>
+      <c r="F763" t="n">
+        <v>53</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I763" t="n">
+        <v>19.23</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I763"/>
+  <dimension ref="A1:I780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31005,7 +31005,7 @@
         </is>
       </c>
       <c r="E746" s="2" t="n">
-        <v>46079.27136491858</v>
+        <v>46079.27136491898</v>
       </c>
       <c r="F746" t="n">
         <v>158</v>
@@ -31046,7 +31046,7 @@
         </is>
       </c>
       <c r="E747" s="2" t="n">
-        <v>46086.06303160238</v>
+        <v>46086.06303159722</v>
       </c>
       <c r="F747" t="n">
         <v>147</v>
@@ -31087,7 +31087,7 @@
         </is>
       </c>
       <c r="E748" s="2" t="n">
-        <v>46069.77136494197</v>
+        <v>46069.77136494213</v>
       </c>
       <c r="F748" t="n">
         <v>63</v>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="E749" s="2" t="n">
-        <v>46078.47969828514</v>
+        <v>46078.47969828704</v>
       </c>
       <c r="F749" t="n">
         <v>60</v>
@@ -31169,7 +31169,7 @@
         </is>
       </c>
       <c r="E750" s="2" t="n">
-        <v>46075.93803163142</v>
+        <v>46075.93803163194</v>
       </c>
       <c r="F750" t="n">
         <v>181</v>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="E751" s="2" t="n">
-        <v>46087.72969830448</v>
+        <v>46087.72969831018</v>
       </c>
       <c r="F751" t="n">
         <v>294</v>
@@ -31251,7 +31251,7 @@
         </is>
       </c>
       <c r="E752" s="2" t="n">
-        <v>46087.31303164407</v>
+        <v>46087.31303164352</v>
       </c>
       <c r="F752" t="n">
         <v>30</v>
@@ -31292,7 +31292,7 @@
         </is>
       </c>
       <c r="E753" s="2" t="n">
-        <v>46087.2713649807</v>
+        <v>46087.27136497685</v>
       </c>
       <c r="F753" t="n">
         <v>281</v>
@@ -31333,7 +31333,7 @@
         </is>
       </c>
       <c r="E754" s="2" t="n">
-        <v>46065.81303165048</v>
+        <v>46065.8130316551</v>
       </c>
       <c r="F754" t="n">
         <v>273</v>
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="E755" s="2" t="n">
-        <v>46082.18803166286</v>
+        <v>46082.18803166666</v>
       </c>
       <c r="F755" t="n">
         <v>237</v>
@@ -31415,7 +31415,7 @@
         </is>
       </c>
       <c r="E756" s="2" t="n">
-        <v>46072.97969833275</v>
+        <v>46072.97969833334</v>
       </c>
       <c r="F756" t="n">
         <v>101</v>
@@ -31456,7 +31456,7 @@
         </is>
       </c>
       <c r="E757" s="2" t="n">
-        <v>46073.85469833589</v>
+        <v>46073.85469833334</v>
       </c>
       <c r="F757" t="n">
         <v>127</v>
@@ -31497,7 +31497,7 @@
         </is>
       </c>
       <c r="E758" s="2" t="n">
-        <v>46076.47969835497</v>
+        <v>46076.47969835648</v>
       </c>
       <c r="F758" t="n">
         <v>179</v>
@@ -31538,7 +31538,7 @@
         </is>
       </c>
       <c r="E759" s="2" t="n">
-        <v>46089.81303169762</v>
+        <v>46089.81303170139</v>
       </c>
       <c r="F759" t="n">
         <v>256</v>
@@ -31579,7 +31579,7 @@
         </is>
       </c>
       <c r="E760" s="2" t="n">
-        <v>46072.8963650433</v>
+        <v>46072.8963650463</v>
       </c>
       <c r="F760" t="n">
         <v>206</v>
@@ -31620,7 +31620,7 @@
         </is>
       </c>
       <c r="E761" s="2" t="n">
-        <v>46077.10469839242</v>
+        <v>46077.1046983912</v>
       </c>
       <c r="F761" t="n">
         <v>79</v>
@@ -31661,7 +31661,7 @@
         </is>
       </c>
       <c r="E762" s="2" t="n">
-        <v>46063.39636506246</v>
+        <v>46063.39636505787</v>
       </c>
       <c r="F762" t="n">
         <v>50</v>
@@ -31702,7 +31702,7 @@
         </is>
       </c>
       <c r="E763" s="2" t="n">
-        <v>46083.47969840227</v>
+        <v>46083.47969840278</v>
       </c>
       <c r="F763" t="n">
         <v>53</v>
@@ -31719,6 +31719,703 @@
       </c>
       <c r="I763" t="n">
         <v>19.23</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>8e188aac-6f6f-4659-b66f-ec964671086d</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>7243cab6-5d8f-47cb-a027-8ba269247d74</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="n">
+        <v>46068.31616564016</v>
+      </c>
+      <c r="F764" t="n">
+        <v>111</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I764" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>d185257e-e77b-4db5-8ddf-fb6aac551c3e</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>d8b3a84c-ebe3-4f7d-a9ee-11c921b7a51c</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="n">
+        <v>46074.77449898252</v>
+      </c>
+      <c r="F765" t="n">
+        <v>194</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I765" t="n">
+        <v>9.539999999999999</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>054cb21b-5f68-4c99-a79d-5873b4800199</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>2325aa40-69c2-41a8-922b-8a0bda2ad7ed</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="n">
+        <v>46092.27449899985</v>
+      </c>
+      <c r="F766" t="n">
+        <v>70</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I766" t="n">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>94811057-7765-4a34-907e-003e0467f4b2</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>ae56f9ea-e16a-4b3e-8b8b-3ca2cfd5ab97</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="n">
+        <v>46086.77449902004</v>
+      </c>
+      <c r="F767" t="n">
+        <v>127</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I767" t="n">
+        <v>19.78</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>5b283e66-8c1f-438b-aae2-8dd4b2f70796</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>27b61076-ce80-48ab-a16a-d7e5f7789397</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="n">
+        <v>46067.2328323564</v>
+      </c>
+      <c r="F768" t="n">
+        <v>280</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I768" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>dc0148e0-6a54-43ae-94e7-e1426f7c6d18</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>800a7a7c-043c-4beb-bb1f-c5eb62d717ae</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="n">
+        <v>46065.69116569277</v>
+      </c>
+      <c r="F769" t="n">
+        <v>72</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I769" t="n">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>64cf29f4-98e4-4615-a27d-8586b7dd8edc</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>b448bccd-e187-4f92-b931-31a650dba3e2</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="n">
+        <v>46064.02449903472</v>
+      </c>
+      <c r="F770" t="n">
+        <v>52</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I770" t="n">
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>50583fd0-80b7-4d04-afc2-5bbb1b5a2a70</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>224ee8a3-4d7b-4de2-85d0-d56b94d263a2</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="n">
+        <v>46084.89949904069</v>
+      </c>
+      <c r="F771" t="n">
+        <v>230</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I771" t="n">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>74783a81-6b2d-4b3a-a04e-ccc649620011</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>ea7c0426-b996-45cc-a465-1077bb17cb8a</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="n">
+        <v>46091.73283237693</v>
+      </c>
+      <c r="F772" t="n">
+        <v>257</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I772" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>be18b39d-7131-4e71-8242-a8e1c757894c</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>d600776c-0197-46c8-8b60-62b89d332466</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="n">
+        <v>46077.14949904947</v>
+      </c>
+      <c r="F773" t="n">
+        <v>165</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I773" t="n">
+        <v>19.33</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>36e830f4-42cd-45c3-90dc-08a43dfa1d03</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>dbcf8f2b-abf3-4a0e-940d-74d8b053c70b</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="n">
+        <v>46089.23283239429</v>
+      </c>
+      <c r="F774" t="n">
+        <v>188</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I774" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>67be2989-51c9-43c3-957a-bc0ff8e200cd</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>18b97689-8265-4500-82bf-c1c9a5fb0001</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="n">
+        <v>46071.2744990667</v>
+      </c>
+      <c r="F775" t="n">
+        <v>140</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I775" t="n">
+        <v>19.89</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>108d5377-b43c-494b-91d9-fe1a5aac9d35</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>e220f895-7e66-4d4c-9064-89814e079e0c</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="n">
+        <v>46066.60783240589</v>
+      </c>
+      <c r="F776" t="n">
+        <v>124</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I776" t="n">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>994da3e9-335f-4347-83ff-ee6342ffa884</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>acdc337c-712a-4d83-b41f-2b1d839258f0</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="n">
+        <v>46079.69116574505</v>
+      </c>
+      <c r="F777" t="n">
+        <v>71</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I777" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>9552f2c4-1b71-4e2b-ae7b-808d0801ab51</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>318e3450-d48a-4a75-bf6d-51783234c03b</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="n">
+        <v>46068.94116574799</v>
+      </c>
+      <c r="F778" t="n">
+        <v>157</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I778" t="n">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>0391a3fb-66b3-44f4-9496-426b72cc82f5</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>a7df247c-43ed-4a2f-875f-3a270546003d</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="n">
+        <v>46080.69116575106</v>
+      </c>
+      <c r="F779" t="n">
+        <v>200</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I779" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>6b6ddfc6-16dd-47a7-9983-17f8cbd1c022</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>f3f6d821-b359-41f2-9cb0-c9ffb72a2b7d</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="n">
+        <v>46064.02449909023</v>
+      </c>
+      <c r="F780" t="n">
+        <v>266</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I780" t="n">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I780"/>
+  <dimension ref="A1:I801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31743,7 +31743,7 @@
         </is>
       </c>
       <c r="E764" s="2" t="n">
-        <v>46068.31616564016</v>
+        <v>46068.31616563658</v>
       </c>
       <c r="F764" t="n">
         <v>111</v>
@@ -31784,7 +31784,7 @@
         </is>
       </c>
       <c r="E765" s="2" t="n">
-        <v>46074.77449898252</v>
+        <v>46074.77449898148</v>
       </c>
       <c r="F765" t="n">
         <v>194</v>
@@ -31825,7 +31825,7 @@
         </is>
       </c>
       <c r="E766" s="2" t="n">
-        <v>46092.27449899985</v>
+        <v>46092.27449900463</v>
       </c>
       <c r="F766" t="n">
         <v>70</v>
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="E767" s="2" t="n">
-        <v>46086.77449902004</v>
+        <v>46086.7744990162</v>
       </c>
       <c r="F767" t="n">
         <v>127</v>
@@ -31907,7 +31907,7 @@
         </is>
       </c>
       <c r="E768" s="2" t="n">
-        <v>46067.2328323564</v>
+        <v>46067.23283236111</v>
       </c>
       <c r="F768" t="n">
         <v>280</v>
@@ -31948,7 +31948,7 @@
         </is>
       </c>
       <c r="E769" s="2" t="n">
-        <v>46065.69116569277</v>
+        <v>46065.69116569444</v>
       </c>
       <c r="F769" t="n">
         <v>72</v>
@@ -31989,7 +31989,7 @@
         </is>
       </c>
       <c r="E770" s="2" t="n">
-        <v>46064.02449903472</v>
+        <v>46064.02449903935</v>
       </c>
       <c r="F770" t="n">
         <v>52</v>
@@ -32030,7 +32030,7 @@
         </is>
       </c>
       <c r="E771" s="2" t="n">
-        <v>46084.89949904069</v>
+        <v>46084.89949903935</v>
       </c>
       <c r="F771" t="n">
         <v>230</v>
@@ -32071,7 +32071,7 @@
         </is>
       </c>
       <c r="E772" s="2" t="n">
-        <v>46091.73283237693</v>
+        <v>46091.73283237268</v>
       </c>
       <c r="F772" t="n">
         <v>257</v>
@@ -32112,7 +32112,7 @@
         </is>
       </c>
       <c r="E773" s="2" t="n">
-        <v>46077.14949904947</v>
+        <v>46077.14949905092</v>
       </c>
       <c r="F773" t="n">
         <v>165</v>
@@ -32153,7 +32153,7 @@
         </is>
       </c>
       <c r="E774" s="2" t="n">
-        <v>46089.23283239429</v>
+        <v>46089.23283239584</v>
       </c>
       <c r="F774" t="n">
         <v>188</v>
@@ -32194,7 +32194,7 @@
         </is>
       </c>
       <c r="E775" s="2" t="n">
-        <v>46071.2744990667</v>
+        <v>46071.2744990625</v>
       </c>
       <c r="F775" t="n">
         <v>140</v>
@@ -32235,7 +32235,7 @@
         </is>
       </c>
       <c r="E776" s="2" t="n">
-        <v>46066.60783240589</v>
+        <v>46066.6078324074</v>
       </c>
       <c r="F776" t="n">
         <v>124</v>
@@ -32276,7 +32276,7 @@
         </is>
       </c>
       <c r="E777" s="2" t="n">
-        <v>46079.69116574505</v>
+        <v>46079.69116574074</v>
       </c>
       <c r="F777" t="n">
         <v>71</v>
@@ -32317,7 +32317,7 @@
         </is>
       </c>
       <c r="E778" s="2" t="n">
-        <v>46068.94116574799</v>
+        <v>46068.94116575232</v>
       </c>
       <c r="F778" t="n">
         <v>157</v>
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="E779" s="2" t="n">
-        <v>46080.69116575106</v>
+        <v>46080.69116575232</v>
       </c>
       <c r="F779" t="n">
         <v>200</v>
@@ -32399,7 +32399,7 @@
         </is>
       </c>
       <c r="E780" s="2" t="n">
-        <v>46064.02449909023</v>
+        <v>46064.02449908565</v>
       </c>
       <c r="F780" t="n">
         <v>266</v>
@@ -32416,6 +32416,867 @@
       </c>
       <c r="I780" t="n">
         <v>5.5</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>95b71417-21f5-42ae-b094-2c2a3be4e43e</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>d6962470-d22a-46dc-94b9-ad2a8e1973b9</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="n">
+        <v>46071.5628169697</v>
+      </c>
+      <c r="F781" t="n">
+        <v>205</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I781" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>b8801d2a-1b47-422d-80bf-585b2df73efb</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>f909aeaf-5210-4c7d-98d4-8f2bb3dfd37f</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="n">
+        <v>46067.52115032687</v>
+      </c>
+      <c r="F782" t="n">
+        <v>228</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I782" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>d980f77b-7b57-438d-81ad-c0920652e893</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>9ad126d7-613c-469c-a162-6b4449305ea7</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="n">
+        <v>46092.77115033026</v>
+      </c>
+      <c r="F783" t="n">
+        <v>183</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I783" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>f280fc40-6d44-4750-8f6e-cd38f42b60d7</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>bea60411-3170-48bb-9de3-4030fcc563e4</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="n">
+        <v>46085.5211503336</v>
+      </c>
+      <c r="F784" t="n">
+        <v>204</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I784" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>7139832d-dc74-4c27-b4ef-7404b7ce5035</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>a39d0f42-a7ee-4622-8f78-2e0e39e6bf5e</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="n">
+        <v>46088.18781700351</v>
+      </c>
+      <c r="F785" t="n">
+        <v>32</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I785" t="n">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>53dad3eb-334e-4d0b-8ca2-63aaa7be3f6e</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>a7ecf256-f1cf-4e1f-83bc-4becc43136fd</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="n">
+        <v>46081.89615035267</v>
+      </c>
+      <c r="F786" t="n">
+        <v>243</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I786" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>57d0dc5a-3f5d-4fe4-8dcf-2c75e43a6727</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>83e9e65a-9c70-4898-8730-3c2bad35fcd9</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="n">
+        <v>46086.81281702552</v>
+      </c>
+      <c r="F787" t="n">
+        <v>244</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I787" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>1456155d-de5d-472c-9362-12af909fe2a5</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>d87036af-d8c0-4313-af57-6f4f66d1f268</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="n">
+        <v>46089.06281702872</v>
+      </c>
+      <c r="F788" t="n">
+        <v>280</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I788" t="n">
+        <v>18.66</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>40ddd5ed-8332-4c5a-9f36-5e0dc960512b</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>836a5808-43fb-47cb-8345-5f8cf16d5270</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="n">
+        <v>46091.35448370175</v>
+      </c>
+      <c r="F789" t="n">
+        <v>285</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I789" t="n">
+        <v>18.19</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>b416da0c-04fe-4638-930b-5ef3529ac398</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>4ef79430-7e01-4b11-97ac-e279970fcf6e</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="n">
+        <v>46072.9794837049</v>
+      </c>
+      <c r="F790" t="n">
+        <v>68</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I790" t="n">
+        <v>14.03</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>83e522e3-27be-464b-a60d-a5d110bcb142</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>b64a8ea9-bc2b-4865-8a21-309a1aad9136</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="n">
+        <v>46065.77115037473</v>
+      </c>
+      <c r="F791" t="n">
+        <v>40</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I791" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>a3357bef-eabf-47af-9207-30812e5cdf25</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>5a1a04d7-e61c-4d71-91be-9bd81a5052b1</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="n">
+        <v>46068.81281704475</v>
+      </c>
+      <c r="F792" t="n">
+        <v>169</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I792" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>8e30634f-9a26-4821-bedf-9a0ff16b9926</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>777bf23e-675d-4a75-8289-c52c13ed558d</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="n">
+        <v>46082.52115038124</v>
+      </c>
+      <c r="F793" t="n">
+        <v>253</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I793" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>ac04374b-576a-4063-8efb-9eb502c6fa0b</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>39562986-b7a4-4577-8944-df37d1f6a10d</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E794" s="2" t="n">
+        <v>46089.56281706034</v>
+      </c>
+      <c r="F794" t="n">
+        <v>162</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I794" t="n">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>6169a2bb-0c93-46d3-b793-b0d0111599a9</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>68cc14fd-3b58-4c48-93f9-475f54764a81</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="n">
+        <v>46065.2294837366</v>
+      </c>
+      <c r="F795" t="n">
+        <v>44</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I795" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>56107f3e-36e1-4509-b162-49c9f32c414a</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>31976a4d-1897-42cf-899d-b3bc75381873</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="n">
+        <v>46071.31281707619</v>
+      </c>
+      <c r="F796" t="n">
+        <v>248</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I796" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>6843851e-d1ef-488a-aded-43bd64bc5570</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>76a883dc-3db9-45fe-9fc6-e2c8124da5e2</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="n">
+        <v>46080.43781708262</v>
+      </c>
+      <c r="F797" t="n">
+        <v>243</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I797" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>712ffb44-a1e4-4d97-a34c-7c09179120a8</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2fca88fb-2585-4813-9b2a-df955c039432</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="n">
+        <v>46080.43781709218</v>
+      </c>
+      <c r="F798" t="n">
+        <v>75</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I798" t="n">
+        <v>17.86</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>4045a261-74b1-4d98-ab45-b13383a68603</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>b8f872a9-86aa-4613-85d6-fe033fecca63</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="n">
+        <v>46082.896150438</v>
+      </c>
+      <c r="F799" t="n">
+        <v>233</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I799" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>4d9605ff-3600-4423-9103-8b2e3d48a853</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>0176c7bb-b2f2-4c7d-83d6-11524d8961f3</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="n">
+        <v>46073.14615045683</v>
+      </c>
+      <c r="F800" t="n">
+        <v>206</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I800" t="n">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>df07feb8-f776-4930-9174-bc8ad881fdab</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>49c715b6-6db3-4fdd-bff1-1b584d04d45e</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="n">
+        <v>46076.81281713021</v>
+      </c>
+      <c r="F801" t="n">
+        <v>98</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I801" t="n">
+        <v>11.49</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I801"/>
+  <dimension ref="A1:I821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32440,7 +32440,7 @@
         </is>
       </c>
       <c r="E781" s="2" t="n">
-        <v>46071.5628169697</v>
+        <v>46071.56281696759</v>
       </c>
       <c r="F781" t="n">
         <v>205</v>
@@ -32481,7 +32481,7 @@
         </is>
       </c>
       <c r="E782" s="2" t="n">
-        <v>46067.52115032687</v>
+        <v>46067.52115032407</v>
       </c>
       <c r="F782" t="n">
         <v>228</v>
@@ -32522,7 +32522,7 @@
         </is>
       </c>
       <c r="E783" s="2" t="n">
-        <v>46092.77115033026</v>
+        <v>46092.77115033565</v>
       </c>
       <c r="F783" t="n">
         <v>183</v>
@@ -32563,7 +32563,7 @@
         </is>
       </c>
       <c r="E784" s="2" t="n">
-        <v>46085.5211503336</v>
+        <v>46085.52115033565</v>
       </c>
       <c r="F784" t="n">
         <v>204</v>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="E785" s="2" t="n">
-        <v>46088.18781700351</v>
+        <v>46088.18781700231</v>
       </c>
       <c r="F785" t="n">
         <v>32</v>
@@ -32645,7 +32645,7 @@
         </is>
       </c>
       <c r="E786" s="2" t="n">
-        <v>46081.89615035267</v>
+        <v>46081.89615034722</v>
       </c>
       <c r="F786" t="n">
         <v>243</v>
@@ -32686,7 +32686,7 @@
         </is>
       </c>
       <c r="E787" s="2" t="n">
-        <v>46086.81281702552</v>
+        <v>46086.81281702546</v>
       </c>
       <c r="F787" t="n">
         <v>244</v>
@@ -32727,7 +32727,7 @@
         </is>
       </c>
       <c r="E788" s="2" t="n">
-        <v>46089.06281702872</v>
+        <v>46089.06281702546</v>
       </c>
       <c r="F788" t="n">
         <v>280</v>
@@ -32768,7 +32768,7 @@
         </is>
       </c>
       <c r="E789" s="2" t="n">
-        <v>46091.35448370175</v>
+        <v>46091.3544837037</v>
       </c>
       <c r="F789" t="n">
         <v>285</v>
@@ -32809,7 +32809,7 @@
         </is>
       </c>
       <c r="E790" s="2" t="n">
-        <v>46072.9794837049</v>
+        <v>46072.9794837037</v>
       </c>
       <c r="F790" t="n">
         <v>68</v>
@@ -32850,7 +32850,7 @@
         </is>
       </c>
       <c r="E791" s="2" t="n">
-        <v>46065.77115037473</v>
+        <v>46065.77115037037</v>
       </c>
       <c r="F791" t="n">
         <v>40</v>
@@ -32891,7 +32891,7 @@
         </is>
       </c>
       <c r="E792" s="2" t="n">
-        <v>46068.81281704475</v>
+        <v>46068.81281704861</v>
       </c>
       <c r="F792" t="n">
         <v>169</v>
@@ -32932,7 +32932,7 @@
         </is>
       </c>
       <c r="E793" s="2" t="n">
-        <v>46082.52115038124</v>
+        <v>46082.52115038194</v>
       </c>
       <c r="F793" t="n">
         <v>253</v>
@@ -32973,7 +32973,7 @@
         </is>
       </c>
       <c r="E794" s="2" t="n">
-        <v>46089.56281706034</v>
+        <v>46089.56281706018</v>
       </c>
       <c r="F794" t="n">
         <v>162</v>
@@ -33014,7 +33014,7 @@
         </is>
       </c>
       <c r="E795" s="2" t="n">
-        <v>46065.2294837366</v>
+        <v>46065.22948373843</v>
       </c>
       <c r="F795" t="n">
         <v>44</v>
@@ -33055,7 +33055,7 @@
         </is>
       </c>
       <c r="E796" s="2" t="n">
-        <v>46071.31281707619</v>
+        <v>46071.31281707176</v>
       </c>
       <c r="F796" t="n">
         <v>248</v>
@@ -33096,7 +33096,7 @@
         </is>
       </c>
       <c r="E797" s="2" t="n">
-        <v>46080.43781708262</v>
+        <v>46080.43781708333</v>
       </c>
       <c r="F797" t="n">
         <v>243</v>
@@ -33137,7 +33137,7 @@
         </is>
       </c>
       <c r="E798" s="2" t="n">
-        <v>46080.43781709218</v>
+        <v>46080.43781709491</v>
       </c>
       <c r="F798" t="n">
         <v>75</v>
@@ -33178,7 +33178,7 @@
         </is>
       </c>
       <c r="E799" s="2" t="n">
-        <v>46082.896150438</v>
+        <v>46082.89615043982</v>
       </c>
       <c r="F799" t="n">
         <v>233</v>
@@ -33219,7 +33219,7 @@
         </is>
       </c>
       <c r="E800" s="2" t="n">
-        <v>46073.14615045683</v>
+        <v>46073.14615045139</v>
       </c>
       <c r="F800" t="n">
         <v>206</v>
@@ -33260,7 +33260,7 @@
         </is>
       </c>
       <c r="E801" s="2" t="n">
-        <v>46076.81281713021</v>
+        <v>46076.81281712963</v>
       </c>
       <c r="F801" t="n">
         <v>98</v>
@@ -33277,6 +33277,826 @@
       </c>
       <c r="I801" t="n">
         <v>11.49</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2a89eb02-6796-4263-b09b-b719a04d1d45</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>b2c54bf1-f437-465a-b709-e9db501ce6a0</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E802" s="2" t="n">
+        <v>46073.72634565126</v>
+      </c>
+      <c r="F802" t="n">
+        <v>279</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I802" t="n">
+        <v>19.85</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>7d342796-202b-43c1-b529-374f4457e2d3</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>6b6f7f35-0752-489f-a52a-b4ab07a2d1c2</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="n">
+        <v>46072.68467899886</v>
+      </c>
+      <c r="F803" t="n">
+        <v>179</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I803" t="n">
+        <v>17.58</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>fa65d685-e3af-4dc6-b722-d0141f075c46</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>c1fa47de-d377-4d2d-b260-4d558bc7a49b</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E804" s="2" t="n">
+        <v>46069.55967900548</v>
+      </c>
+      <c r="F804" t="n">
+        <v>54</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I804" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>d1b6bc40-bb78-4bb7-afc7-53a9c571fede</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>9fe46a46-09b4-4125-8940-a123b25cdaaa</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="n">
+        <v>46080.14301234509</v>
+      </c>
+      <c r="F805" t="n">
+        <v>220</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I805" t="n">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>3d9a58ef-76cb-451d-b232-d40e9ed5d441</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>6622a0bf-51af-443a-a92c-d8e161fc8220</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E806" s="2" t="n">
+        <v>46064.76801234834</v>
+      </c>
+      <c r="F806" t="n">
+        <v>195</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I806" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>ff85984b-faaf-46ac-8b98-63bfc9c4c317</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>e2edd1a4-0bc6-47f3-9e70-20f69d830103</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="n">
+        <v>46078.43467902156</v>
+      </c>
+      <c r="F807" t="n">
+        <v>277</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I807" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>faa6538a-8f52-41f6-b2d7-46383e440756</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>c4b4b7de-7878-4e07-877e-0fba370386fd</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="n">
+        <v>46089.93467902479</v>
+      </c>
+      <c r="F808" t="n">
+        <v>185</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I808" t="n">
+        <v>18.27</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>896255d7-a8ec-485d-8322-eba000e2f7a8</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>e05e5f23-3bb2-4e82-8f1d-38fd3bdcc47f</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="n">
+        <v>46082.10134569499</v>
+      </c>
+      <c r="F809" t="n">
+        <v>157</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I809" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>f5cefa5c-ce40-4027-a789-2db0d93944a8</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>48dad3a6-0dcc-4b9f-a3dc-8f687fc52ce3</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E810" s="2" t="n">
+        <v>46063.72634571111</v>
+      </c>
+      <c r="F810" t="n">
+        <v>251</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I810" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>1598fbb5-0289-4b28-a0a2-ad0077d43750</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>1f071330-7213-475f-8e39-c92361552732</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="n">
+        <v>46086.85134571734</v>
+      </c>
+      <c r="F811" t="n">
+        <v>31</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I811" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>c20b8282-d6ad-4b45-b846-29fc671c5ca4</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>862398e3-c060-4bd5-b55a-52fc82624a4e</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="n">
+        <v>46070.47634573025</v>
+      </c>
+      <c r="F812" t="n">
+        <v>151</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I812" t="n">
+        <v>16.64</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>abc1ba4a-6353-4fce-81c7-2202979b4176</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>170705d8-00c4-44bd-b018-d25961290ad6</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="n">
+        <v>46069.0180124062</v>
+      </c>
+      <c r="F813" t="n">
+        <v>50</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I813" t="n">
+        <v>14.94</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>db667000-3463-4a25-92cf-3e49aee5a648</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>7138cd71-18a4-46c8-9683-2f1102b770bd</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="n">
+        <v>46081.47634575884</v>
+      </c>
+      <c r="F814" t="n">
+        <v>36</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I814" t="n">
+        <v>14.97</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>a321d833-8b68-493e-b8c8-0e840b5bb2a0</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>51a2a8a4-901a-4fd1-bcb6-9112bd88ef9e</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="n">
+        <v>46072.47634576831</v>
+      </c>
+      <c r="F815" t="n">
+        <v>80</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I815" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>0890e8fe-9776-497d-8fc1-6f82f4fb95fb</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>d9af0d63-293e-4bf1-93c8-8a29d08eac3a</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="n">
+        <v>46064.3096791048</v>
+      </c>
+      <c r="F816" t="n">
+        <v>44</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I816" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>af387291-c46e-41e3-a957-64263abe700c</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>e66d46aa-a3a8-484c-ae36-899e711944db</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="n">
+        <v>46087.1846791202</v>
+      </c>
+      <c r="F817" t="n">
+        <v>187</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I817" t="n">
+        <v>10.83</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>e961c49a-f7e5-41b8-8593-a0847cd0d6d7</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>f4388d7d-1f5d-4190-ba49-8ceeb5ea3117</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E818" s="2" t="n">
+        <v>46062.72634579032</v>
+      </c>
+      <c r="F818" t="n">
+        <v>170</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I818" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>515eaa44-db39-4466-bbff-e11d8eada275</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>bcd6743c-c8b2-4a37-a960-5f3fed50b6e1</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="n">
+        <v>46066.68467912688</v>
+      </c>
+      <c r="F819" t="n">
+        <v>47</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I819" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>89ae5406-7799-4844-8ee8-313d5a92b3f8</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>d7c25c9c-16d7-4f99-b1f6-ff8f8fb625e0</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="n">
+        <v>46091.64301246336</v>
+      </c>
+      <c r="F820" t="n">
+        <v>174</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I820" t="n">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>8819dc20-c8a9-4a42-9cef-3a4545594c92</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>7d2865f1-7d4f-4bb6-b300-fe31f6752dcc</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="n">
+        <v>46092.97634580639</v>
+      </c>
+      <c r="F821" t="n">
+        <v>291</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I821" t="n">
+        <v>19.52</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I821"/>
+  <dimension ref="A1:I839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33301,7 +33301,7 @@
         </is>
       </c>
       <c r="E802" s="2" t="n">
-        <v>46073.72634565126</v>
+        <v>46073.72634564815</v>
       </c>
       <c r="F802" t="n">
         <v>279</v>
@@ -33342,7 +33342,7 @@
         </is>
       </c>
       <c r="E803" s="2" t="n">
-        <v>46072.68467899886</v>
+        <v>46072.68467900463</v>
       </c>
       <c r="F803" t="n">
         <v>179</v>
@@ -33383,7 +33383,7 @@
         </is>
       </c>
       <c r="E804" s="2" t="n">
-        <v>46069.55967900548</v>
+        <v>46069.55967900463</v>
       </c>
       <c r="F804" t="n">
         <v>54</v>
@@ -33424,7 +33424,7 @@
         </is>
       </c>
       <c r="E805" s="2" t="n">
-        <v>46080.14301234509</v>
+        <v>46080.14301234954</v>
       </c>
       <c r="F805" t="n">
         <v>220</v>
@@ -33465,7 +33465,7 @@
         </is>
       </c>
       <c r="E806" s="2" t="n">
-        <v>46064.76801234834</v>
+        <v>46064.76801234954</v>
       </c>
       <c r="F806" t="n">
         <v>195</v>
@@ -33506,7 +33506,7 @@
         </is>
       </c>
       <c r="E807" s="2" t="n">
-        <v>46078.43467902156</v>
+        <v>46078.4346790162</v>
       </c>
       <c r="F807" t="n">
         <v>277</v>
@@ -33547,7 +33547,7 @@
         </is>
       </c>
       <c r="E808" s="2" t="n">
-        <v>46089.93467902479</v>
+        <v>46089.93467902778</v>
       </c>
       <c r="F808" t="n">
         <v>185</v>
@@ -33588,7 +33588,7 @@
         </is>
       </c>
       <c r="E809" s="2" t="n">
-        <v>46082.10134569499</v>
+        <v>46082.10134569444</v>
       </c>
       <c r="F809" t="n">
         <v>157</v>
@@ -33629,7 +33629,7 @@
         </is>
       </c>
       <c r="E810" s="2" t="n">
-        <v>46063.72634571111</v>
+        <v>46063.72634570602</v>
       </c>
       <c r="F810" t="n">
         <v>251</v>
@@ -33670,7 +33670,7 @@
         </is>
       </c>
       <c r="E811" s="2" t="n">
-        <v>46086.85134571734</v>
+        <v>46086.85134571759</v>
       </c>
       <c r="F811" t="n">
         <v>31</v>
@@ -33711,7 +33711,7 @@
         </is>
       </c>
       <c r="E812" s="2" t="n">
-        <v>46070.47634573025</v>
+        <v>46070.47634572917</v>
       </c>
       <c r="F812" t="n">
         <v>151</v>
@@ -33752,7 +33752,7 @@
         </is>
       </c>
       <c r="E813" s="2" t="n">
-        <v>46069.0180124062</v>
+        <v>46069.01801240741</v>
       </c>
       <c r="F813" t="n">
         <v>50</v>
@@ -33793,7 +33793,7 @@
         </is>
       </c>
       <c r="E814" s="2" t="n">
-        <v>46081.47634575884</v>
+        <v>46081.47634576389</v>
       </c>
       <c r="F814" t="n">
         <v>36</v>
@@ -33834,7 +33834,7 @@
         </is>
       </c>
       <c r="E815" s="2" t="n">
-        <v>46072.47634576831</v>
+        <v>46072.47634576389</v>
       </c>
       <c r="F815" t="n">
         <v>80</v>
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="E816" s="2" t="n">
-        <v>46064.3096791048</v>
+        <v>46064.3096791088</v>
       </c>
       <c r="F816" t="n">
         <v>44</v>
@@ -33916,7 +33916,7 @@
         </is>
       </c>
       <c r="E817" s="2" t="n">
-        <v>46087.1846791202</v>
+        <v>46087.18467912037</v>
       </c>
       <c r="F817" t="n">
         <v>187</v>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="E818" s="2" t="n">
-        <v>46062.72634579032</v>
+        <v>46062.72634578704</v>
       </c>
       <c r="F818" t="n">
         <v>170</v>
@@ -33998,7 +33998,7 @@
         </is>
       </c>
       <c r="E819" s="2" t="n">
-        <v>46066.68467912688</v>
+        <v>46066.68467913195</v>
       </c>
       <c r="F819" t="n">
         <v>47</v>
@@ -34039,7 +34039,7 @@
         </is>
       </c>
       <c r="E820" s="2" t="n">
-        <v>46091.64301246336</v>
+        <v>46091.64301246528</v>
       </c>
       <c r="F820" t="n">
         <v>174</v>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="E821" s="2" t="n">
-        <v>46092.97634580639</v>
+        <v>46092.97634581019</v>
       </c>
       <c r="F821" t="n">
         <v>291</v>
@@ -34097,6 +34097,744 @@
       </c>
       <c r="I821" t="n">
         <v>19.52</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>4bd3bde1-ce9e-47fe-9979-e319549c82c7</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>e40dcebb-e955-4c85-b7e0-a48e5ca40047</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="n">
+        <v>46076.3443310844</v>
+      </c>
+      <c r="F822" t="n">
+        <v>73</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I822" t="n">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>13193e76-2e27-4b5c-abae-20f2c95e8beb</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>bf6fd1e8-3bcd-4ce6-b093-787fa60dd0a4</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="n">
+        <v>46090.96933111817</v>
+      </c>
+      <c r="F823" t="n">
+        <v>288</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I823" t="n">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>27e07f7a-b482-409c-89a2-bf8988cce7b2</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>496f5bf2-9aa8-49dc-843e-381abbe652e2</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="n">
+        <v>46083.46933112144</v>
+      </c>
+      <c r="F824" t="n">
+        <v>179</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I824" t="n">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>7500aae1-4fca-40ba-bec0-43dd21007ec4</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>e2b22b9b-05c0-485b-9b4c-bcb0523a8180</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="n">
+        <v>46090.96933112788</v>
+      </c>
+      <c r="F825" t="n">
+        <v>280</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I825" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>9b5012eb-260c-4a30-91e9-c6bc0e172ed2</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>3f0aeb65-82ec-4578-93e9-e82b158f79d2</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E826" s="2" t="n">
+        <v>46077.76099779799</v>
+      </c>
+      <c r="F826" t="n">
+        <v>155</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I826" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>6663c602-893a-46d8-87f6-3ac0b8ecb75c</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>57a3de1d-0980-4816-8ee8-1962721ca820</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="n">
+        <v>46067.84433113461</v>
+      </c>
+      <c r="F827" t="n">
+        <v>131</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I827" t="n">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>cfa6e6bc-b92a-4467-87ea-c5339d8ca97c</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>df988a3e-551f-4672-9414-b7910077f50a</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="n">
+        <v>46082.63599780456</v>
+      </c>
+      <c r="F828" t="n">
+        <v>56</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I828" t="n">
+        <v>16.33</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>768f792e-4607-4674-a0c2-95a3d530219c</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>d0595f61-eeee-4fbf-9d30-d27876d7fe0b</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="n">
+        <v>46075.59433115059</v>
+      </c>
+      <c r="F829" t="n">
+        <v>165</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I829" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>5e54f55c-c7aa-486c-8446-e04f281e7599</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>fff11e19-4093-40bc-a826-73dc30fe22cd</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="n">
+        <v>46072.96933115714</v>
+      </c>
+      <c r="F830" t="n">
+        <v>216</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I830" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>349b72a1-663e-46b2-8016-c168505c9e6a</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>9f438f4e-90b4-4c99-aca3-8156625c1b65</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="n">
+        <v>46073.96933116354</v>
+      </c>
+      <c r="F831" t="n">
+        <v>249</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I831" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>3a8835be-b4f8-4d62-b667-251078e80453</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2761f052-058c-46ca-880d-6e9f4d12cb9e</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="n">
+        <v>46072.05266450235</v>
+      </c>
+      <c r="F832" t="n">
+        <v>98</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I832" t="n">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>76a8dcac-9025-4886-ba58-875067deddf9</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>48a3f3c0-2d42-4bbb-9665-69eef7309b76</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="n">
+        <v>46077.13599785489</v>
+      </c>
+      <c r="F833" t="n">
+        <v>214</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I833" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>6cf2cbdf-26a5-40f0-8e89-1b35b72eb8e0</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>f7ffa53f-19e1-4955-b99f-25f6e2307307</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="n">
+        <v>46068.46933121052</v>
+      </c>
+      <c r="F834" t="n">
+        <v>213</v>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I834" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>c704c584-79b7-4a58-8263-fb85621e2d2f</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>cd712b09-5fec-4cbc-99ef-04affc2184cb</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="n">
+        <v>46077.01099788346</v>
+      </c>
+      <c r="F835" t="n">
+        <v>191</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I835" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>c1874fb6-c1cc-4c29-ac60-cd83d9b68d86</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>7b7938f5-eb28-43a4-93a7-879440105e8c</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="n">
+        <v>46062.63599789296</v>
+      </c>
+      <c r="F836" t="n">
+        <v>49</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I836" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>17709fbb-8fd7-48f6-b328-e2b51d2621c0</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>271c28f9-7d77-41a1-88dc-531678f64ee0</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="n">
+        <v>46066.21933122957</v>
+      </c>
+      <c r="F837" t="n">
+        <v>126</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I837" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>199526dc-6b3e-4f21-b9f8-2c32fad7b37c</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>bcbe24ee-36f9-4bcb-9bd2-056996e0a523</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="n">
+        <v>46069.8859978996</v>
+      </c>
+      <c r="F838" t="n">
+        <v>146</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I838" t="n">
+        <v>16.11</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>72bf4235-23e4-4d6a-879e-9391c03ca732</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>987075a0-0883-43bf-a916-b52112048be4</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="n">
+        <v>46070.38599791293</v>
+      </c>
+      <c r="F839" t="n">
+        <v>238</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I839" t="n">
+        <v>7.95</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I839"/>
+  <dimension ref="A1:I856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34121,7 +34121,7 @@
         </is>
       </c>
       <c r="E822" s="2" t="n">
-        <v>46076.3443310844</v>
+        <v>46076.34433108797</v>
       </c>
       <c r="F822" t="n">
         <v>73</v>
@@ -34162,7 +34162,7 @@
         </is>
       </c>
       <c r="E823" s="2" t="n">
-        <v>46090.96933111817</v>
+        <v>46090.96933112269</v>
       </c>
       <c r="F823" t="n">
         <v>288</v>
@@ -34203,7 +34203,7 @@
         </is>
       </c>
       <c r="E824" s="2" t="n">
-        <v>46083.46933112144</v>
+        <v>46083.46933112269</v>
       </c>
       <c r="F824" t="n">
         <v>179</v>
@@ -34244,7 +34244,7 @@
         </is>
       </c>
       <c r="E825" s="2" t="n">
-        <v>46090.96933112788</v>
+        <v>46090.96933112269</v>
       </c>
       <c r="F825" t="n">
         <v>280</v>
@@ -34285,7 +34285,7 @@
         </is>
       </c>
       <c r="E826" s="2" t="n">
-        <v>46077.76099779799</v>
+        <v>46077.76099780093</v>
       </c>
       <c r="F826" t="n">
         <v>155</v>
@@ -34326,7 +34326,7 @@
         </is>
       </c>
       <c r="E827" s="2" t="n">
-        <v>46067.84433113461</v>
+        <v>46067.84433113426</v>
       </c>
       <c r="F827" t="n">
         <v>131</v>
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="E828" s="2" t="n">
-        <v>46082.63599780456</v>
+        <v>46082.63599780093</v>
       </c>
       <c r="F828" t="n">
         <v>56</v>
@@ -34408,7 +34408,7 @@
         </is>
       </c>
       <c r="E829" s="2" t="n">
-        <v>46075.59433115059</v>
+        <v>46075.59433114583</v>
       </c>
       <c r="F829" t="n">
         <v>165</v>
@@ -34449,7 +34449,7 @@
         </is>
       </c>
       <c r="E830" s="2" t="n">
-        <v>46072.96933115714</v>
+        <v>46072.96933115741</v>
       </c>
       <c r="F830" t="n">
         <v>216</v>
@@ -34490,7 +34490,7 @@
         </is>
       </c>
       <c r="E831" s="2" t="n">
-        <v>46073.96933116354</v>
+        <v>46073.96933116898</v>
       </c>
       <c r="F831" t="n">
         <v>249</v>
@@ -34531,7 +34531,7 @@
         </is>
       </c>
       <c r="E832" s="2" t="n">
-        <v>46072.05266450235</v>
+        <v>46072.05266450231</v>
       </c>
       <c r="F832" t="n">
         <v>98</v>
@@ -34572,7 +34572,7 @@
         </is>
       </c>
       <c r="E833" s="2" t="n">
-        <v>46077.13599785489</v>
+        <v>46077.13599785879</v>
       </c>
       <c r="F833" t="n">
         <v>214</v>
@@ -34613,7 +34613,7 @@
         </is>
       </c>
       <c r="E834" s="2" t="n">
-        <v>46068.46933121052</v>
+        <v>46068.46933121528</v>
       </c>
       <c r="F834" t="n">
         <v>213</v>
@@ -34654,7 +34654,7 @@
         </is>
       </c>
       <c r="E835" s="2" t="n">
-        <v>46077.01099788346</v>
+        <v>46077.01099788195</v>
       </c>
       <c r="F835" t="n">
         <v>191</v>
@@ -34695,7 +34695,7 @@
         </is>
       </c>
       <c r="E836" s="2" t="n">
-        <v>46062.63599789296</v>
+        <v>46062.63599789352</v>
       </c>
       <c r="F836" t="n">
         <v>49</v>
@@ -34736,7 +34736,7 @@
         </is>
       </c>
       <c r="E837" s="2" t="n">
-        <v>46066.21933122957</v>
+        <v>46066.21933122685</v>
       </c>
       <c r="F837" t="n">
         <v>126</v>
@@ -34777,7 +34777,7 @@
         </is>
       </c>
       <c r="E838" s="2" t="n">
-        <v>46069.8859978996</v>
+        <v>46069.88599790509</v>
       </c>
       <c r="F838" t="n">
         <v>146</v>
@@ -34818,7 +34818,7 @@
         </is>
       </c>
       <c r="E839" s="2" t="n">
-        <v>46070.38599791293</v>
+        <v>46070.38599791667</v>
       </c>
       <c r="F839" t="n">
         <v>238</v>
@@ -34835,6 +34835,703 @@
       </c>
       <c r="I839" t="n">
         <v>7.95</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>7630b21b-a8a5-4665-9de3-f84219197904</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>5eee4774-018b-4ba5-a86f-79b3cab028bc</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="n">
+        <v>46090.01838559285</v>
+      </c>
+      <c r="F840" t="n">
+        <v>298</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I840" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>b834bb17-112e-4497-82f7-7f6543ea62b4</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>8d37ff75-f7bf-453b-9f5b-1f277576e785</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="n">
+        <v>46070.64338559614</v>
+      </c>
+      <c r="F841" t="n">
+        <v>244</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I841" t="n">
+        <v>10.88</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>29ca37ff-432e-499d-a99a-ef79b45c464e</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>3308fcb2-9271-4d13-88c8-6e412e2ab43b</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="n">
+        <v>46080.43505226635</v>
+      </c>
+      <c r="F842" t="n">
+        <v>258</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I842" t="n">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>66fda483-fabb-4688-9107-6268458088b1</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>6d9d0614-8134-4385-bb3d-7b2495e367ef</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="n">
+        <v>46066.76838560605</v>
+      </c>
+      <c r="F843" t="n">
+        <v>287</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I843" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>7b7c6afd-077c-49f9-adaa-4315d09878e8</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>da4071cf-3d71-41ec-a07a-0ae0d142923f</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="n">
+        <v>46086.85171894635</v>
+      </c>
+      <c r="F844" t="n">
+        <v>98</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I844" t="n">
+        <v>16.01</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>86d5394a-0b05-479e-926f-a06c1e0adf6a</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>1b463568-f76e-4ec5-bb41-c6cf128fc41a</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="n">
+        <v>46075.47671894957</v>
+      </c>
+      <c r="F845" t="n">
+        <v>239</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I845" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>05722d08-3ec5-4bab-abfc-5ddaed91c53b</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>8832e022-50f7-4f55-92f8-8bdfade18bb2</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="n">
+        <v>46072.93505230208</v>
+      </c>
+      <c r="F846" t="n">
+        <v>290</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I846" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>886cefa9-fb7a-43bf-9867-f6bde54ce44b</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>eb3b6cbf-8faf-4a3a-a6b9-17ec1740b64a</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="n">
+        <v>46080.935052318</v>
+      </c>
+      <c r="F847" t="n">
+        <v>232</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I847" t="n">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>66e2e085-f9d4-4ba1-a4cc-54d8dcc4e1aa</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>8917caa0-1b5d-4cf0-8a1b-dd944fdcb4fc</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="n">
+        <v>46066.68505232743</v>
+      </c>
+      <c r="F848" t="n">
+        <v>167</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I848" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>b2524bbd-027c-42f8-ace5-f5c683045ec6</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>b51d9141-f138-4c13-bd33-840abdef0c56</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="n">
+        <v>46084.89338566395</v>
+      </c>
+      <c r="F849" t="n">
+        <v>216</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I849" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>1d8ae93f-1d6c-4db2-b8f2-3186dbb8c44e</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>f02b4194-8fef-406c-b397-730e5dfe6a3e</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="n">
+        <v>46069.35171900995</v>
+      </c>
+      <c r="F850" t="n">
+        <v>193</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I850" t="n">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>b3d22458-5736-4686-9e6e-8c1a8e37c3f7</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>05978b60-2fbf-493f-a9ce-359e7b9308e6</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="n">
+        <v>46069.51838567976</v>
+      </c>
+      <c r="F851" t="n">
+        <v>285</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I851" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>7c99a2d3-7714-43df-91a0-f99d580869fe</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>6a0f527b-8524-4a17-bc4b-450c137479f3</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="n">
+        <v>46090.76838569906</v>
+      </c>
+      <c r="F852" t="n">
+        <v>248</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I852" t="n">
+        <v>14.78</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>70cfc60d-a552-4972-9d7a-7a78d64b4a36</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>9d7fa90b-a2ca-4fff-93eb-8429e527391a</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="n">
+        <v>46074.18505237543</v>
+      </c>
+      <c r="F853" t="n">
+        <v>260</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I853" t="n">
+        <v>11.34</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2d9f5b2f-1e96-43b4-ab10-763b0ec513a3</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>d591c8d5-46b3-464b-a8ac-272c65cbfaaa</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="n">
+        <v>46083.51838572142</v>
+      </c>
+      <c r="F854" t="n">
+        <v>102</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I854" t="n">
+        <v>10.73</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>23e62939-2c8a-4a8f-8dad-21424ac52484</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>45e8137a-db7a-45c6-baaa-31b6dd0062f5</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="n">
+        <v>46082.93505239791</v>
+      </c>
+      <c r="F855" t="n">
+        <v>237</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I855" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>a4cbb055-a7e7-415d-9104-b783f62bab93</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>aff41e1b-d7d8-47ef-a566-16669b8cd752</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="n">
+        <v>46085.22671906773</v>
+      </c>
+      <c r="F856" t="n">
+        <v>248</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I856" t="n">
+        <v>19.51</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I856"/>
+  <dimension ref="A1:I873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="E840" s="2" t="n">
-        <v>46090.01838559285</v>
+        <v>46090.01838559028</v>
       </c>
       <c r="F840" t="n">
         <v>298</v>
@@ -34900,7 +34900,7 @@
         </is>
       </c>
       <c r="E841" s="2" t="n">
-        <v>46070.64338559614</v>
+        <v>46070.64338560185</v>
       </c>
       <c r="F841" t="n">
         <v>244</v>
@@ -34941,7 +34941,7 @@
         </is>
       </c>
       <c r="E842" s="2" t="n">
-        <v>46080.43505226635</v>
+        <v>46080.43505226852</v>
       </c>
       <c r="F842" t="n">
         <v>258</v>
@@ -34982,7 +34982,7 @@
         </is>
       </c>
       <c r="E843" s="2" t="n">
-        <v>46066.76838560605</v>
+        <v>46066.76838560185</v>
       </c>
       <c r="F843" t="n">
         <v>287</v>
@@ -35023,7 +35023,7 @@
         </is>
       </c>
       <c r="E844" s="2" t="n">
-        <v>46086.85171894635</v>
+        <v>46086.85171894676</v>
       </c>
       <c r="F844" t="n">
         <v>98</v>
@@ -35064,7 +35064,7 @@
         </is>
       </c>
       <c r="E845" s="2" t="n">
-        <v>46075.47671894957</v>
+        <v>46075.47671894676</v>
       </c>
       <c r="F845" t="n">
         <v>239</v>
@@ -35105,7 +35105,7 @@
         </is>
       </c>
       <c r="E846" s="2" t="n">
-        <v>46072.93505230208</v>
+        <v>46072.93505230324</v>
       </c>
       <c r="F846" t="n">
         <v>290</v>
@@ -35146,7 +35146,7 @@
         </is>
       </c>
       <c r="E847" s="2" t="n">
-        <v>46080.935052318</v>
+        <v>46080.93505231482</v>
       </c>
       <c r="F847" t="n">
         <v>232</v>
@@ -35187,7 +35187,7 @@
         </is>
       </c>
       <c r="E848" s="2" t="n">
-        <v>46066.68505232743</v>
+        <v>46066.68505232639</v>
       </c>
       <c r="F848" t="n">
         <v>167</v>
@@ -35228,7 +35228,7 @@
         </is>
       </c>
       <c r="E849" s="2" t="n">
-        <v>46084.89338566395</v>
+        <v>46084.89338565972</v>
       </c>
       <c r="F849" t="n">
         <v>216</v>
@@ -35269,7 +35269,7 @@
         </is>
       </c>
       <c r="E850" s="2" t="n">
-        <v>46069.35171900995</v>
+        <v>46069.35171900463</v>
       </c>
       <c r="F850" t="n">
         <v>193</v>
@@ -35310,7 +35310,7 @@
         </is>
       </c>
       <c r="E851" s="2" t="n">
-        <v>46069.51838567976</v>
+        <v>46069.51838568287</v>
       </c>
       <c r="F851" t="n">
         <v>285</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="E852" s="2" t="n">
-        <v>46090.76838569906</v>
+        <v>46090.76838569444</v>
       </c>
       <c r="F852" t="n">
         <v>248</v>
@@ -35392,7 +35392,7 @@
         </is>
       </c>
       <c r="E853" s="2" t="n">
-        <v>46074.18505237543</v>
+        <v>46074.18505237268</v>
       </c>
       <c r="F853" t="n">
         <v>260</v>
@@ -35433,7 +35433,7 @@
         </is>
       </c>
       <c r="E854" s="2" t="n">
-        <v>46083.51838572142</v>
+        <v>46083.51838571759</v>
       </c>
       <c r="F854" t="n">
         <v>102</v>
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="E855" s="2" t="n">
-        <v>46082.93505239791</v>
+        <v>46082.93505239583</v>
       </c>
       <c r="F855" t="n">
         <v>237</v>
@@ -35515,7 +35515,7 @@
         </is>
       </c>
       <c r="E856" s="2" t="n">
-        <v>46085.22671906773</v>
+        <v>46085.2267190625</v>
       </c>
       <c r="F856" t="n">
         <v>248</v>
@@ -35532,6 +35532,703 @@
       </c>
       <c r="I856" t="n">
         <v>19.51</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>0454c67c-df71-4eb3-9f24-4d6138289f81</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>cc1d5d90-aee6-4a6b-9996-673237cea8ab</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="n">
+        <v>46081.90782221168</v>
+      </c>
+      <c r="F857" t="n">
+        <v>192</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I857" t="n">
+        <v>11.34</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>4e6aefae-861e-4457-8282-955f4b773184</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>5ce527de-483c-4513-9666-9a95418f48f1</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="n">
+        <v>46093.6161555514</v>
+      </c>
+      <c r="F858" t="n">
+        <v>174</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I858" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>b7ab92ab-a79e-4d29-b534-8b85d8220bb6</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>9f2a6347-be91-4b5f-ab1e-72c101cea58d</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="n">
+        <v>46073.11615555801</v>
+      </c>
+      <c r="F859" t="n">
+        <v>272</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I859" t="n">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>40e2dc15-31af-47d7-a15e-a31aef127a74</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>7fcc7b05-587f-4da6-81ba-a8fd1b020f1e</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="n">
+        <v>46080.78282223095</v>
+      </c>
+      <c r="F860" t="n">
+        <v>105</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I860" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>a076fb4e-9ebe-4822-afeb-8ca6a96e0305</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>ca61044f-7eb9-4396-8860-7ad4c5667b97</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="n">
+        <v>46077.86615557402</v>
+      </c>
+      <c r="F861" t="n">
+        <v>56</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I861" t="n">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>e46d2fc9-9da0-48f0-8017-e3ef4a6abc25</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>f6dc9631-41f9-475f-bb4a-a1cda238dcab</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="n">
+        <v>46079.82448891387</v>
+      </c>
+      <c r="F862" t="n">
+        <v>145</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I862" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>8909f63d-e40f-4feb-afd3-9e0355033eb2</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>f2a83d93-a575-472c-8687-85b14b3a762c</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="n">
+        <v>46085.49115560574</v>
+      </c>
+      <c r="F863" t="n">
+        <v>112</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I863" t="n">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>bf32d800-c7a9-46c6-8804-75f4f395b928</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>bc6dbf78-8d60-499b-95f7-2034d99dc304</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="n">
+        <v>46064.86615561195</v>
+      </c>
+      <c r="F864" t="n">
+        <v>86</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I864" t="n">
+        <v>18.02</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>1fb412a3-8bed-42d0-a000-ce46ec465bb1</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>cc254c37-32a7-4215-9933-cab26199c795</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="n">
+        <v>46088.03282228186</v>
+      </c>
+      <c r="F865" t="n">
+        <v>35</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I865" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>5927cee8-bf86-4cac-b4b3-b3ac42cff46a</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>611b19a9-c093-4ffd-b178-a68fef68637e</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="n">
+        <v>46082.90782228502</v>
+      </c>
+      <c r="F866" t="n">
+        <v>137</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I866" t="n">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>46a60cbf-1262-45bf-b897-985e1391d99e</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>9b1cbf10-2f87-4950-a83e-2e0d1d40caf5</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="n">
+        <v>46088.24115562159</v>
+      </c>
+      <c r="F867" t="n">
+        <v>143</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I867" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>02a48c66-3577-4f70-8840-ce020e99877e</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2f902437-f306-41dd-9ed8-2eea15ef9c0a</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="n">
+        <v>46080.28282230424</v>
+      </c>
+      <c r="F868" t="n">
+        <v>261</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I868" t="n">
+        <v>17.61</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>0de489e7-531e-4929-a158-859442a7e42b</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>502b9740-dc11-4dc6-876b-02c85ec6dd3a</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="n">
+        <v>46065.19948898017</v>
+      </c>
+      <c r="F869" t="n">
+        <v>161</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I869" t="n">
+        <v>14.83</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>4d85c947-c91c-467a-8797-75ef2c733efc</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>59305006-2161-48d9-b539-cafa7636fdd1</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="n">
+        <v>46075.782822317</v>
+      </c>
+      <c r="F870" t="n">
+        <v>269</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I870" t="n">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>594137f2-e0c5-427f-8815-aa9d9cc313a2</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>5dd85d62-a5b9-4f29-b707-5e09b58b5805</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="n">
+        <v>46070.86615566887</v>
+      </c>
+      <c r="F871" t="n">
+        <v>248</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I871" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>15a79783-bc18-462d-9108-469660dd9454</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>5df3bc08-50e8-4b24-96c8-18a314dc764d</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="n">
+        <v>46071.82448901462</v>
+      </c>
+      <c r="F872" t="n">
+        <v>89</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I872" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>53a49096-ccec-45ae-8e5a-f128df6e4992</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>e9a9243d-86f5-4dd6-8747-95957fd6c3bf</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="n">
+        <v>46080.82448902094</v>
+      </c>
+      <c r="F873" t="n">
+        <v>86</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I873" t="n">
+        <v>18.79</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I873"/>
+  <dimension ref="A1:I892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="E857" s="2" t="n">
-        <v>46081.90782221168</v>
+        <v>46081.90782221065</v>
       </c>
       <c r="F857" t="n">
         <v>192</v>
@@ -35597,7 +35597,7 @@
         </is>
       </c>
       <c r="E858" s="2" t="n">
-        <v>46093.6161555514</v>
+        <v>46093.61615555556</v>
       </c>
       <c r="F858" t="n">
         <v>174</v>
@@ -35638,7 +35638,7 @@
         </is>
       </c>
       <c r="E859" s="2" t="n">
-        <v>46073.11615555801</v>
+        <v>46073.11615555556</v>
       </c>
       <c r="F859" t="n">
         <v>272</v>
@@ -35679,7 +35679,7 @@
         </is>
       </c>
       <c r="E860" s="2" t="n">
-        <v>46080.78282223095</v>
+        <v>46080.7828222338</v>
       </c>
       <c r="F860" t="n">
         <v>105</v>
@@ -35720,7 +35720,7 @@
         </is>
       </c>
       <c r="E861" s="2" t="n">
-        <v>46077.86615557402</v>
+        <v>46077.8661555787</v>
       </c>
       <c r="F861" t="n">
         <v>56</v>
@@ -35761,7 +35761,7 @@
         </is>
       </c>
       <c r="E862" s="2" t="n">
-        <v>46079.82448891387</v>
+        <v>46079.82448891204</v>
       </c>
       <c r="F862" t="n">
         <v>145</v>
@@ -35802,7 +35802,7 @@
         </is>
       </c>
       <c r="E863" s="2" t="n">
-        <v>46085.49115560574</v>
+        <v>46085.49115560185</v>
       </c>
       <c r="F863" t="n">
         <v>112</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="E864" s="2" t="n">
-        <v>46064.86615561195</v>
+        <v>46064.86615561342</v>
       </c>
       <c r="F864" t="n">
         <v>86</v>
@@ -35884,7 +35884,7 @@
         </is>
       </c>
       <c r="E865" s="2" t="n">
-        <v>46088.03282228186</v>
+        <v>46088.03282228009</v>
       </c>
       <c r="F865" t="n">
         <v>35</v>
@@ -35925,7 +35925,7 @@
         </is>
       </c>
       <c r="E866" s="2" t="n">
-        <v>46082.90782228502</v>
+        <v>46082.90782228009</v>
       </c>
       <c r="F866" t="n">
         <v>137</v>
@@ -35966,7 +35966,7 @@
         </is>
       </c>
       <c r="E867" s="2" t="n">
-        <v>46088.24115562159</v>
+        <v>46088.241155625</v>
       </c>
       <c r="F867" t="n">
         <v>143</v>
@@ -36007,7 +36007,7 @@
         </is>
       </c>
       <c r="E868" s="2" t="n">
-        <v>46080.28282230424</v>
+        <v>46080.28282230324</v>
       </c>
       <c r="F868" t="n">
         <v>261</v>
@@ -36048,7 +36048,7 @@
         </is>
       </c>
       <c r="E869" s="2" t="n">
-        <v>46065.19948898017</v>
+        <v>46065.19948898148</v>
       </c>
       <c r="F869" t="n">
         <v>161</v>
@@ -36089,7 +36089,7 @@
         </is>
       </c>
       <c r="E870" s="2" t="n">
-        <v>46075.782822317</v>
+        <v>46075.78282231482</v>
       </c>
       <c r="F870" t="n">
         <v>269</v>
@@ -36130,7 +36130,7 @@
         </is>
       </c>
       <c r="E871" s="2" t="n">
-        <v>46070.86615566887</v>
+        <v>46070.8661556713</v>
       </c>
       <c r="F871" t="n">
         <v>248</v>
@@ -36171,7 +36171,7 @@
         </is>
       </c>
       <c r="E872" s="2" t="n">
-        <v>46071.82448901462</v>
+        <v>46071.8244890162</v>
       </c>
       <c r="F872" t="n">
         <v>89</v>
@@ -36212,7 +36212,7 @@
         </is>
       </c>
       <c r="E873" s="2" t="n">
-        <v>46080.82448902094</v>
+        <v>46080.8244890162</v>
       </c>
       <c r="F873" t="n">
         <v>86</v>
@@ -36229,6 +36229,785 @@
       </c>
       <c r="I873" t="n">
         <v>18.79</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>6453c3a0-5a79-4c17-bd51-f78ceb5a8981</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>1e6951c1-f598-4ab6-8442-a0750c265751</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="n">
+        <v>46066.44649543845</v>
+      </c>
+      <c r="F874" t="n">
+        <v>281</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I874" t="n">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>161cae4d-9001-4a7e-92e2-3a672f496387</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>27689719-57a6-4887-9e2b-38d6cef2c0bd</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="n">
+        <v>46070.15482878957</v>
+      </c>
+      <c r="F875" t="n">
+        <v>49</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I875" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>da78dd3b-9f6e-4f63-bb4e-1fbf1793c853</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>4a37fedc-b464-4fb9-8ea0-90da1e29c5bc</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="n">
+        <v>46093.32149546904</v>
+      </c>
+      <c r="F876" t="n">
+        <v>113</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I876" t="n">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>45858749-6b6c-4644-ba1c-ec3fbc445b62</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>eaf3c3c2-4a0b-4095-b526-492ae01a6f72</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="n">
+        <v>46067.27982882118</v>
+      </c>
+      <c r="F877" t="n">
+        <v>117</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I877" t="n">
+        <v>18.89</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>8fe046d4-db39-4cc8-bec4-ff3b917ec2e7</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>15ee1d98-01d6-49c5-9465-d3b295bb69bf</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="n">
+        <v>46079.07149549173</v>
+      </c>
+      <c r="F878" t="n">
+        <v>104</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I878" t="n">
+        <v>13.92</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>5e70a501-afbe-478a-b3a4-18c4d2279087</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>f90f84d6-d1a6-4a25-9f3e-37bea9a84b1a</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="n">
+        <v>46090.82149550117</v>
+      </c>
+      <c r="F879" t="n">
+        <v>53</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I879" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>98ee5866-2039-411f-ae72-7edca314732d</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>8a5bdab3-96d8-4cc9-a096-fe6501830bad</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="n">
+        <v>46072.44649550878</v>
+      </c>
+      <c r="F880" t="n">
+        <v>136</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I880" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>962c0e54-4c28-40a6-9179-057cb9417fa0</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>047d7aaf-76e1-48ee-b2c3-4530cffa1db6</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="n">
+        <v>46092.94649551516</v>
+      </c>
+      <c r="F881" t="n">
+        <v>90</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I881" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>f61c65ca-a134-4add-8084-eb5711094e15</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>b9989966-62e3-4760-8802-b097eeec6cdc</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="n">
+        <v>46089.40482885166</v>
+      </c>
+      <c r="F882" t="n">
+        <v>254</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I882" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>523f6c58-61a5-4931-afca-4215e37fd0ea</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>1389c92b-3901-4921-ac11-c996ae19ea84</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="n">
+        <v>46063.23816219132</v>
+      </c>
+      <c r="F883" t="n">
+        <v>181</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I883" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>26468722-da8d-4845-aafd-86294dbec9fa</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>d3404a7d-b99f-4d8d-9351-f33e54831a37</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="n">
+        <v>46077.90482887752</v>
+      </c>
+      <c r="F884" t="n">
+        <v>191</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I884" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>330cb36f-6312-4d4b-9328-c96f00488996</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>5e31f4e7-0503-49b8-a957-f2a025cf8577</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="n">
+        <v>46078.90482888074</v>
+      </c>
+      <c r="F885" t="n">
+        <v>132</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I885" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>adb5ba9b-9e49-4231-8f11-e7add1262ca8</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>cb2eb52c-14ba-4424-8f7f-97b594d37bb7</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="n">
+        <v>46075.11316222404</v>
+      </c>
+      <c r="F886" t="n">
+        <v>291</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I886" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>01b96238-5646-4500-a32a-94644fe505df</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>1e93a7a8-a3d9-40ee-95e2-1bc98e9c8613</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="n">
+        <v>46076.86316223053</v>
+      </c>
+      <c r="F887" t="n">
+        <v>297</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I887" t="n">
+        <v>19.65</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2ec883b1-8763-4850-b109-39e119100668</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>84f4c07a-5985-43f0-941c-dab6ccdf33d4</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="n">
+        <v>46093.94649556707</v>
+      </c>
+      <c r="F888" t="n">
+        <v>203</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I888" t="n">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>4c426003-f12b-4eac-869d-5739ed01107e</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>51b8b468-cc7b-433c-acbe-e7db91774452</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="n">
+        <v>46075.61316224038</v>
+      </c>
+      <c r="F889" t="n">
+        <v>164</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I889" t="n">
+        <v>16.26</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>6875a5a0-fe74-4bc6-94f9-3470cd3bd4b9</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>c3d9d026-c031-4675-890d-48610f2c4ea1</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="n">
+        <v>46081.32149557994</v>
+      </c>
+      <c r="F890" t="n">
+        <v>94</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I890" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>6f082301-69cd-4203-ba0a-3ba7f6dac286</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>598bf867-908d-4207-bdeb-aae0576139df</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="n">
+        <v>46090.6964955833</v>
+      </c>
+      <c r="F891" t="n">
+        <v>104</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I891" t="n">
+        <v>19.35</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>7d972697-dfc6-49cd-a60a-949bbc9d54cb</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>5e33481d-99d0-45e9-a5eb-d4fb2917df41</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="n">
+        <v>46084.48816225928</v>
+      </c>
+      <c r="F892" t="n">
+        <v>246</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I892" t="n">
+        <v>18.66</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I892"/>
+  <dimension ref="A1:I916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36253,7 +36253,7 @@
         </is>
       </c>
       <c r="E874" s="2" t="n">
-        <v>46066.44649543845</v>
+        <v>46066.44649543981</v>
       </c>
       <c r="F874" t="n">
         <v>281</v>
@@ -36294,7 +36294,7 @@
         </is>
       </c>
       <c r="E875" s="2" t="n">
-        <v>46070.15482878957</v>
+        <v>46070.15482878473</v>
       </c>
       <c r="F875" t="n">
         <v>49</v>
@@ -36335,7 +36335,7 @@
         </is>
       </c>
       <c r="E876" s="2" t="n">
-        <v>46093.32149546904</v>
+        <v>46093.32149547453</v>
       </c>
       <c r="F876" t="n">
         <v>113</v>
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="E877" s="2" t="n">
-        <v>46067.27982882118</v>
+        <v>46067.27982881945</v>
       </c>
       <c r="F877" t="n">
         <v>117</v>
@@ -36417,7 +36417,7 @@
         </is>
       </c>
       <c r="E878" s="2" t="n">
-        <v>46079.07149549173</v>
+        <v>46079.07149548611</v>
       </c>
       <c r="F878" t="n">
         <v>104</v>
@@ -36458,7 +36458,7 @@
         </is>
       </c>
       <c r="E879" s="2" t="n">
-        <v>46090.82149550117</v>
+        <v>46090.82149549769</v>
       </c>
       <c r="F879" t="n">
         <v>53</v>
@@ -36499,7 +36499,7 @@
         </is>
       </c>
       <c r="E880" s="2" t="n">
-        <v>46072.44649550878</v>
+        <v>46072.44649550926</v>
       </c>
       <c r="F880" t="n">
         <v>136</v>
@@ -36540,7 +36540,7 @@
         </is>
       </c>
       <c r="E881" s="2" t="n">
-        <v>46092.94649551516</v>
+        <v>46092.94649552083</v>
       </c>
       <c r="F881" t="n">
         <v>90</v>
@@ -36581,7 +36581,7 @@
         </is>
       </c>
       <c r="E882" s="2" t="n">
-        <v>46089.40482885166</v>
+        <v>46089.40482885417</v>
       </c>
       <c r="F882" t="n">
         <v>254</v>
@@ -36622,7 +36622,7 @@
         </is>
       </c>
       <c r="E883" s="2" t="n">
-        <v>46063.23816219132</v>
+        <v>46063.2381621875</v>
       </c>
       <c r="F883" t="n">
         <v>181</v>
@@ -36663,7 +36663,7 @@
         </is>
       </c>
       <c r="E884" s="2" t="n">
-        <v>46077.90482887752</v>
+        <v>46077.90482887731</v>
       </c>
       <c r="F884" t="n">
         <v>191</v>
@@ -36704,7 +36704,7 @@
         </is>
       </c>
       <c r="E885" s="2" t="n">
-        <v>46078.90482888074</v>
+        <v>46078.90482887731</v>
       </c>
       <c r="F885" t="n">
         <v>132</v>
@@ -36745,7 +36745,7 @@
         </is>
       </c>
       <c r="E886" s="2" t="n">
-        <v>46075.11316222404</v>
+        <v>46075.11316222222</v>
       </c>
       <c r="F886" t="n">
         <v>291</v>
@@ -36786,7 +36786,7 @@
         </is>
       </c>
       <c r="E887" s="2" t="n">
-        <v>46076.86316223053</v>
+        <v>46076.8631622338</v>
       </c>
       <c r="F887" t="n">
         <v>297</v>
@@ -36827,7 +36827,7 @@
         </is>
       </c>
       <c r="E888" s="2" t="n">
-        <v>46093.94649556707</v>
+        <v>46093.94649556713</v>
       </c>
       <c r="F888" t="n">
         <v>203</v>
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="E889" s="2" t="n">
-        <v>46075.61316224038</v>
+        <v>46075.61316224537</v>
       </c>
       <c r="F889" t="n">
         <v>164</v>
@@ -36909,7 +36909,7 @@
         </is>
       </c>
       <c r="E890" s="2" t="n">
-        <v>46081.32149557994</v>
+        <v>46081.3214955787</v>
       </c>
       <c r="F890" t="n">
         <v>94</v>
@@ -36950,7 +36950,7 @@
         </is>
       </c>
       <c r="E891" s="2" t="n">
-        <v>46090.6964955833</v>
+        <v>46090.6964955787</v>
       </c>
       <c r="F891" t="n">
         <v>104</v>
@@ -36991,7 +36991,7 @@
         </is>
       </c>
       <c r="E892" s="2" t="n">
-        <v>46084.48816225928</v>
+        <v>46084.48816225694</v>
       </c>
       <c r="F892" t="n">
         <v>246</v>
@@ -37008,6 +37008,990 @@
       </c>
       <c r="I892" t="n">
         <v>18.66</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>981e0b17-342e-4113-be83-7c76e5259a29</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>6cbaff8f-e779-4410-a270-44f1b24d6790</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="n">
+        <v>46063.32957621248</v>
+      </c>
+      <c r="F893" t="n">
+        <v>74</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I893" t="n">
+        <v>16.66</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>acecc762-3846-4b42-b688-db7d0f463821</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>ac1a82ab-d1fa-4356-abb3-e0fa62693e5f</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="n">
+        <v>46075.45457622364</v>
+      </c>
+      <c r="F894" t="n">
+        <v>258</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I894" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>8697b735-863e-4fdf-a75d-bebb28f97320</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>452b3483-a519-4ee8-97ee-aa41e3518141</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="n">
+        <v>46081.37124289351</v>
+      </c>
+      <c r="F895" t="n">
+        <v>124</v>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I895" t="n">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>5ed1201b-b53c-407a-b20c-8d763254690a</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>5bfb0cc4-bc5a-4785-a923-72dba5785684</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="n">
+        <v>46072.03790956706</v>
+      </c>
+      <c r="F896" t="n">
+        <v>242</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I896" t="n">
+        <v>18.06</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>0210b4c6-9a2c-4ce0-b161-633e754973c4</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>dd05a3b0-15fa-42d1-82e6-d629446d7475</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="n">
+        <v>46087.87124290369</v>
+      </c>
+      <c r="F897" t="n">
+        <v>217</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I897" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2b650cbf-b353-4515-90a8-69b0d56e29db</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>e7877c05-9483-45fd-8705-4c2ea876eacc</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="n">
+        <v>46082.03790957366</v>
+      </c>
+      <c r="F898" t="n">
+        <v>105</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I898" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>5b9486da-06e8-4037-80e9-b024e2488ec5</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>1929eb70-7d3b-455b-ab13-934fdd9120ff</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="n">
+        <v>46080.28790958641</v>
+      </c>
+      <c r="F899" t="n">
+        <v>71</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I899" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>77008f62-d80d-4a6f-93bf-d4174f9f8478</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>817ba1f6-f97e-4c78-832f-fda58dbac078</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="n">
+        <v>46067.0379095959</v>
+      </c>
+      <c r="F900" t="n">
+        <v>119</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I900" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>f7cb1208-173d-4ed4-952c-ad8ce6de9c38</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>e5affd22-4972-408c-ba7e-2a9015a7a859</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="n">
+        <v>46090.87124293559</v>
+      </c>
+      <c r="F901" t="n">
+        <v>69</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I901" t="n">
+        <v>17.07</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>a31e886e-9d13-4d5e-be7c-e74de0637176</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>3c045790-a9ef-4a3b-ad78-c30e0d72ce7a</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="n">
+        <v>46091.20457627216</v>
+      </c>
+      <c r="F902" t="n">
+        <v>162</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I902" t="n">
+        <v>19.48</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>11aa990e-7ab4-4eab-bad3-65801d32a9e9</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>583390b3-44d5-43ef-b65a-86093ce85588</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="n">
+        <v>46091.24624294198</v>
+      </c>
+      <c r="F903" t="n">
+        <v>80</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I903" t="n">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>c28bd299-43b4-4030-ad45-9c78614a0ca9</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>0967913f-89e4-4f17-8a39-79ea3194c3c3</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="n">
+        <v>46064.53790961545</v>
+      </c>
+      <c r="F904" t="n">
+        <v>90</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I904" t="n">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>d08cbd9a-f7b0-4701-8b07-1c0219946d73</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>2732eac1-aabc-4d99-8d07-4aeefd50528e</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="n">
+        <v>46090.74624296809</v>
+      </c>
+      <c r="F905" t="n">
+        <v>62</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I905" t="n">
+        <v>18.54</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>dd8311c5-d2bc-4092-9d28-e938d9e13611</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>62a76233-a35c-43f0-976f-8849a7461a08</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="n">
+        <v>46078.91290963793</v>
+      </c>
+      <c r="F906" t="n">
+        <v>129</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I906" t="n">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>a2ece125-a567-4fb2-a5a7-685cb89961fc</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>fe23df8f-caea-4bd8-a871-fed9ccbe14c4</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="n">
+        <v>46089.91290964109</v>
+      </c>
+      <c r="F907" t="n">
+        <v>74</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I907" t="n">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>161f47e3-84ec-463f-800d-fac177e43fe5</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>8d84fd1f-af80-4348-a90e-a5625cef2683</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="n">
+        <v>46081.57957631107</v>
+      </c>
+      <c r="F908" t="n">
+        <v>274</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I908" t="n">
+        <v>19.84</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>e078ce27-f201-4501-bb87-f8db7e5c9f52</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>a4b5b38d-d66c-40f7-b304-5fa65f9938ad</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="n">
+        <v>46063.07957631467</v>
+      </c>
+      <c r="F909" t="n">
+        <v>55</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I909" t="n">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>db6f073f-805d-4e20-b452-4bbdf655a87d</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>5b2d358a-489a-4911-96e0-fdf9a9c8a1eb</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="n">
+        <v>46085.66290965427</v>
+      </c>
+      <c r="F910" t="n">
+        <v>198</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I910" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>c5b2a4ef-9ee9-4279-9c6e-3503479b54c9</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>5e90a8a1-e230-4e51-bcfe-c1aae6d9642f</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="n">
+        <v>46066.12124300704</v>
+      </c>
+      <c r="F911" t="n">
+        <v>196</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I911" t="n">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>b3f37da1-569b-4e61-8302-d566138d63b6</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>84dd387b-3539-4550-8575-181bf1bc8746</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="n">
+        <v>46085.07957634347</v>
+      </c>
+      <c r="F912" t="n">
+        <v>156</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I912" t="n">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>9c31d1d7-2d32-42f5-9b87-06a042b9a99d</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>020ec405-a29a-4371-adec-a2e0f626ea17</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="n">
+        <v>46074.70457635065</v>
+      </c>
+      <c r="F913" t="n">
+        <v>296</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I913" t="n">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>aa4809bf-6a76-4764-b5c5-ce0f87ea415c</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>5cae5db7-bfe1-42c3-92d3-70e24c389ff2</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="n">
+        <v>46083.74624302046</v>
+      </c>
+      <c r="F914" t="n">
+        <v>289</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I914" t="n">
+        <v>18.66</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>b308a64f-f387-4f50-a05d-8a3fdf6628dc</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>16f3ed75-63ac-4039-a36e-4c8ce4640a92</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="n">
+        <v>46065.03790969027</v>
+      </c>
+      <c r="F915" t="n">
+        <v>83</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I915" t="n">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>e8225f07-32c2-48e5-a0ff-9fada8493ac3</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>1ea1f901-3f79-49aa-b848-6194430629a3</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E916" s="2" t="n">
+        <v>46082.57957636673</v>
+      </c>
+      <c r="F916" t="n">
+        <v>226</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I916" t="n">
+        <v>18.92</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I916"/>
+  <dimension ref="A1:I939"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="E893" s="2" t="n">
-        <v>46063.32957621248</v>
+        <v>46063.32957621528</v>
       </c>
       <c r="F893" t="n">
         <v>74</v>
@@ -37073,7 +37073,7 @@
         </is>
       </c>
       <c r="E894" s="2" t="n">
-        <v>46075.45457622364</v>
+        <v>46075.45457622685</v>
       </c>
       <c r="F894" t="n">
         <v>258</v>
@@ -37114,7 +37114,7 @@
         </is>
       </c>
       <c r="E895" s="2" t="n">
-        <v>46081.37124289351</v>
+        <v>46081.37124289352</v>
       </c>
       <c r="F895" t="n">
         <v>124</v>
@@ -37155,7 +37155,7 @@
         </is>
       </c>
       <c r="E896" s="2" t="n">
-        <v>46072.03790956706</v>
+        <v>46072.03790957176</v>
       </c>
       <c r="F896" t="n">
         <v>242</v>
@@ -37196,7 +37196,7 @@
         </is>
       </c>
       <c r="E897" s="2" t="n">
-        <v>46087.87124290369</v>
+        <v>46087.87124290509</v>
       </c>
       <c r="F897" t="n">
         <v>217</v>
@@ -37237,7 +37237,7 @@
         </is>
       </c>
       <c r="E898" s="2" t="n">
-        <v>46082.03790957366</v>
+        <v>46082.03790957176</v>
       </c>
       <c r="F898" t="n">
         <v>105</v>
@@ -37278,7 +37278,7 @@
         </is>
       </c>
       <c r="E899" s="2" t="n">
-        <v>46080.28790958641</v>
+        <v>46080.28790958333</v>
       </c>
       <c r="F899" t="n">
         <v>71</v>
@@ -37319,7 +37319,7 @@
         </is>
       </c>
       <c r="E900" s="2" t="n">
-        <v>46067.0379095959</v>
+        <v>46067.03790959491</v>
       </c>
       <c r="F900" t="n">
         <v>119</v>
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="E901" s="2" t="n">
-        <v>46090.87124293559</v>
+        <v>46090.87124293981</v>
       </c>
       <c r="F901" t="n">
         <v>69</v>
@@ -37401,7 +37401,7 @@
         </is>
       </c>
       <c r="E902" s="2" t="n">
-        <v>46091.20457627216</v>
+        <v>46091.20457627315</v>
       </c>
       <c r="F902" t="n">
         <v>162</v>
@@ -37442,7 +37442,7 @@
         </is>
       </c>
       <c r="E903" s="2" t="n">
-        <v>46091.24624294198</v>
+        <v>46091.24624293981</v>
       </c>
       <c r="F903" t="n">
         <v>80</v>
@@ -37483,7 +37483,7 @@
         </is>
       </c>
       <c r="E904" s="2" t="n">
-        <v>46064.53790961545</v>
+        <v>46064.53790961805</v>
       </c>
       <c r="F904" t="n">
         <v>90</v>
@@ -37524,7 +37524,7 @@
         </is>
       </c>
       <c r="E905" s="2" t="n">
-        <v>46090.74624296809</v>
+        <v>46090.74624296296</v>
       </c>
       <c r="F905" t="n">
         <v>62</v>
@@ -37565,7 +37565,7 @@
         </is>
       </c>
       <c r="E906" s="2" t="n">
-        <v>46078.91290963793</v>
+        <v>46078.91290964121</v>
       </c>
       <c r="F906" t="n">
         <v>129</v>
@@ -37606,7 +37606,7 @@
         </is>
       </c>
       <c r="E907" s="2" t="n">
-        <v>46089.91290964109</v>
+        <v>46089.91290964121</v>
       </c>
       <c r="F907" t="n">
         <v>74</v>
@@ -37647,7 +37647,7 @@
         </is>
       </c>
       <c r="E908" s="2" t="n">
-        <v>46081.57957631107</v>
+        <v>46081.57957630787</v>
       </c>
       <c r="F908" t="n">
         <v>274</v>
@@ -37688,7 +37688,7 @@
         </is>
       </c>
       <c r="E909" s="2" t="n">
-        <v>46063.07957631467</v>
+        <v>46063.07957631945</v>
       </c>
       <c r="F909" t="n">
         <v>55</v>
@@ -37729,7 +37729,7 @@
         </is>
       </c>
       <c r="E910" s="2" t="n">
-        <v>46085.66290965427</v>
+        <v>46085.66290965278</v>
       </c>
       <c r="F910" t="n">
         <v>198</v>
@@ -37770,7 +37770,7 @@
         </is>
       </c>
       <c r="E911" s="2" t="n">
-        <v>46066.12124300704</v>
+        <v>46066.12124300926</v>
       </c>
       <c r="F911" t="n">
         <v>196</v>
@@ -37811,7 +37811,7 @@
         </is>
       </c>
       <c r="E912" s="2" t="n">
-        <v>46085.07957634347</v>
+        <v>46085.07957634259</v>
       </c>
       <c r="F912" t="n">
         <v>156</v>
@@ -37852,7 +37852,7 @@
         </is>
       </c>
       <c r="E913" s="2" t="n">
-        <v>46074.70457635065</v>
+        <v>46074.70457635417</v>
       </c>
       <c r="F913" t="n">
         <v>296</v>
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="E914" s="2" t="n">
-        <v>46083.74624302046</v>
+        <v>46083.74624302083</v>
       </c>
       <c r="F914" t="n">
         <v>289</v>
@@ -37934,7 +37934,7 @@
         </is>
       </c>
       <c r="E915" s="2" t="n">
-        <v>46065.03790969027</v>
+        <v>46065.0379096875</v>
       </c>
       <c r="F915" t="n">
         <v>83</v>
@@ -37975,7 +37975,7 @@
         </is>
       </c>
       <c r="E916" s="2" t="n">
-        <v>46082.57957636673</v>
+        <v>46082.57957636574</v>
       </c>
       <c r="F916" t="n">
         <v>226</v>
@@ -37992,6 +37992,949 @@
       </c>
       <c r="I916" t="n">
         <v>18.92</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>270a6a35-3b6e-44b1-a907-5cedb9c3cb69</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>5fdcc6b8-cfd3-453c-b2c0-05a7d5970b49</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="n">
+        <v>46088.69755768512</v>
+      </c>
+      <c r="F917" t="n">
+        <v>147</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I917" t="n">
+        <v>17.19</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>840c38f9-6901-4db4-bf66-254b32a3e0cf</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>563c08df-a4ab-4b6a-bc4f-6a55406a1efb</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="n">
+        <v>46087.69755769501</v>
+      </c>
+      <c r="F918" t="n">
+        <v>216</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I918" t="n">
+        <v>16.08</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>cdd9082a-aa1a-4296-9ea9-cae64d69204a</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>e88c669b-0165-46b0-a624-706f17ed899a</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="n">
+        <v>46077.94755769839</v>
+      </c>
+      <c r="F919" t="n">
+        <v>136</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I919" t="n">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>459cedbc-5bba-4cdf-964d-612bbdf760f9</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>545b967f-d66d-4c52-81ba-3d33eaf5aecb</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="n">
+        <v>46073.4892243779</v>
+      </c>
+      <c r="F920" t="n">
+        <v>250</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I920" t="n">
+        <v>10.13</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>bdc16618-c57d-485d-ab50-1876cfad7f93</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>c625a015-dd88-4d06-b2a0-aef1a164483a</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="n">
+        <v>46091.19755771443</v>
+      </c>
+      <c r="F921" t="n">
+        <v>286</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I921" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>cf66af94-a5df-43e1-b455-c20820e11a64</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>a0eec741-d1b6-4ae5-bec7-ffdcb194b7f2</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="n">
+        <v>46074.57255771765</v>
+      </c>
+      <c r="F922" t="n">
+        <v>280</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I922" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>4b22de1e-de42-4301-a30b-133affe96490</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>17956eb1-a53c-4dd9-9d6f-117df8c2019a</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="n">
+        <v>46085.98922438783</v>
+      </c>
+      <c r="F923" t="n">
+        <v>258</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I923" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>8b305baf-3130-468e-9935-760b59821687</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>ca7b7f10-f5d0-4288-b8b2-8d71d5b7f2c1</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E924" s="2" t="n">
+        <v>46084.11422439109</v>
+      </c>
+      <c r="F924" t="n">
+        <v>276</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I924" t="n">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>bd176dda-5293-48b8-85a7-4608fc33f665</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>29ec5eb3-96fb-48ab-b1c0-18c40e58a1a9</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="n">
+        <v>46090.1975577276</v>
+      </c>
+      <c r="F925" t="n">
+        <v>105</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I925" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>3e3b3622-163c-4f56-b39c-aad0565fd01b</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>8787d25e-fb77-4ea4-939c-12f1c0fa7957</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E926" s="2" t="n">
+        <v>46079.94755773411</v>
+      </c>
+      <c r="F926" t="n">
+        <v>278</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I926" t="n">
+        <v>16.77</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>c7b7120d-2c83-4041-8a26-ee1615c98c10</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>b560c6e4-517a-4a3b-a643-041c169c4d9b</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E927" s="2" t="n">
+        <v>46087.23922440725</v>
+      </c>
+      <c r="F927" t="n">
+        <v>110</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I927" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>acbebe96-1935-4090-a3b6-cdc3068db79b</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>82c3ceae-3cae-452b-ae21-8e182e3eafff</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E928" s="2" t="n">
+        <v>46070.98922441064</v>
+      </c>
+      <c r="F928" t="n">
+        <v>278</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I928" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>62fffb60-785b-4c1a-ba90-97c2e33862ab</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>9f8575ec-dc9a-4ea0-b12b-1b5347ccc8cb</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E929" s="2" t="n">
+        <v>46072.19755775029</v>
+      </c>
+      <c r="F929" t="n">
+        <v>221</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I929" t="n">
+        <v>17.67</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>ab16bfc1-48ac-40a0-bf05-96adeb0afe1e</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>d94cb259-7a3f-4296-ac2f-8f19a2a5ac16</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E930" s="2" t="n">
+        <v>46071.86422443926</v>
+      </c>
+      <c r="F930" t="n">
+        <v>168</v>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I930" t="n">
+        <v>16.55</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>34f9c02e-9fd8-4d8b-a2c3-0d84b0c3ccb8</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>58c1e21f-b64d-4c7a-b385-c5e0ff5ac63a</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E931" s="2" t="n">
+        <v>46081.03089111625</v>
+      </c>
+      <c r="F931" t="n">
+        <v>96</v>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I931" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>bb058c61-a946-4efc-9e81-37c28c1cc6b6</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>ad3bd7e7-0637-4efd-90c2-caea62717344</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E932" s="2" t="n">
+        <v>46091.28089111949</v>
+      </c>
+      <c r="F932" t="n">
+        <v>179</v>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I932" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>0866a124-fcf9-412f-9cb5-ea3844a73481</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>93dbde4d-8c8c-4289-a46d-dd8c08cbe862</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E933" s="2" t="n">
+        <v>46091.36422445606</v>
+      </c>
+      <c r="F933" t="n">
+        <v>178</v>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I933" t="n">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>e82fd749-30f4-4345-8639-0e2fa26b2ef5</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>4a26d1be-1adc-4ce4-ba57-c86fae5ce1e3</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E934" s="2" t="n">
+        <v>46073.69755779609</v>
+      </c>
+      <c r="F934" t="n">
+        <v>121</v>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I934" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>ccf2ffd8-d726-4243-896f-cb6c43e282ef</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>8041be33-7439-47b7-bff2-b240a37e8f00</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E935" s="2" t="n">
+        <v>46077.78089113588</v>
+      </c>
+      <c r="F935" t="n">
+        <v>61</v>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I935" t="n">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>7b182c2f-1dbe-4639-b306-ae15468c7a84</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>a707730f-2d23-4299-95ab-0578b89410a4</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E936" s="2" t="n">
+        <v>46072.11422448188</v>
+      </c>
+      <c r="F936" t="n">
+        <v>153</v>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I936" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>a466ca52-1869-439a-a37e-d752d2e3dc3c</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>4fc79177-fb8f-4956-b3fd-d5aa2e4990fc</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E937" s="2" t="n">
+        <v>46078.98922448815</v>
+      </c>
+      <c r="F937" t="n">
+        <v>84</v>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I937" t="n">
+        <v>12.16</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>33d1cef3-6ef4-4594-91b5-47b0b91db496</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>ef0cd6a6-bcce-4f0d-971b-303624ae411f</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E938" s="2" t="n">
+        <v>46089.03089115801</v>
+      </c>
+      <c r="F938" t="n">
+        <v>126</v>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I938" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>c2bd886d-76b2-4d72-873a-e284a1a6236d</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>f23c30b6-0274-4df2-b763-c85e77ce4017</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E939" s="2" t="n">
+        <v>46074.4892244982</v>
+      </c>
+      <c r="F939" t="n">
+        <v>215</v>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I939" t="n">
+        <v>15.61</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I939"/>
+  <dimension ref="A1:I954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38016,7 +38016,7 @@
         </is>
       </c>
       <c r="E917" s="2" t="n">
-        <v>46088.69755768512</v>
+        <v>46088.69755768518</v>
       </c>
       <c r="F917" t="n">
         <v>147</v>
@@ -38057,7 +38057,7 @@
         </is>
       </c>
       <c r="E918" s="2" t="n">
-        <v>46087.69755769501</v>
+        <v>46087.69755769676</v>
       </c>
       <c r="F918" t="n">
         <v>216</v>
@@ -38098,7 +38098,7 @@
         </is>
       </c>
       <c r="E919" s="2" t="n">
-        <v>46077.94755769839</v>
+        <v>46077.94755769676</v>
       </c>
       <c r="F919" t="n">
         <v>136</v>
@@ -38139,7 +38139,7 @@
         </is>
       </c>
       <c r="E920" s="2" t="n">
-        <v>46073.4892243779</v>
+        <v>46073.489224375</v>
       </c>
       <c r="F920" t="n">
         <v>250</v>
@@ -38180,7 +38180,7 @@
         </is>
       </c>
       <c r="E921" s="2" t="n">
-        <v>46091.19755771443</v>
+        <v>46091.1975577199</v>
       </c>
       <c r="F921" t="n">
         <v>286</v>
@@ -38221,7 +38221,7 @@
         </is>
       </c>
       <c r="E922" s="2" t="n">
-        <v>46074.57255771765</v>
+        <v>46074.5725577199</v>
       </c>
       <c r="F922" t="n">
         <v>280</v>
@@ -38262,7 +38262,7 @@
         </is>
       </c>
       <c r="E923" s="2" t="n">
-        <v>46085.98922438783</v>
+        <v>46085.98922438658</v>
       </c>
       <c r="F923" t="n">
         <v>258</v>
@@ -38303,7 +38303,7 @@
         </is>
       </c>
       <c r="E924" s="2" t="n">
-        <v>46084.11422439109</v>
+        <v>46084.11422438658</v>
       </c>
       <c r="F924" t="n">
         <v>276</v>
@@ -38344,7 +38344,7 @@
         </is>
       </c>
       <c r="E925" s="2" t="n">
-        <v>46090.1975577276</v>
+        <v>46090.19755773148</v>
       </c>
       <c r="F925" t="n">
         <v>105</v>
@@ -38385,7 +38385,7 @@
         </is>
       </c>
       <c r="E926" s="2" t="n">
-        <v>46079.94755773411</v>
+        <v>46079.94755773148</v>
       </c>
       <c r="F926" t="n">
         <v>278</v>
@@ -38426,7 +38426,7 @@
         </is>
       </c>
       <c r="E927" s="2" t="n">
-        <v>46087.23922440725</v>
+        <v>46087.23922440972</v>
       </c>
       <c r="F927" t="n">
         <v>110</v>
@@ -38467,7 +38467,7 @@
         </is>
       </c>
       <c r="E928" s="2" t="n">
-        <v>46070.98922441064</v>
+        <v>46070.98922440972</v>
       </c>
       <c r="F928" t="n">
         <v>278</v>
@@ -38508,7 +38508,7 @@
         </is>
       </c>
       <c r="E929" s="2" t="n">
-        <v>46072.19755775029</v>
+        <v>46072.19755775463</v>
       </c>
       <c r="F929" t="n">
         <v>221</v>
@@ -38549,7 +38549,7 @@
         </is>
       </c>
       <c r="E930" s="2" t="n">
-        <v>46071.86422443926</v>
+        <v>46071.86422444444</v>
       </c>
       <c r="F930" t="n">
         <v>168</v>
@@ -38590,7 +38590,7 @@
         </is>
       </c>
       <c r="E931" s="2" t="n">
-        <v>46081.03089111625</v>
+        <v>46081.03089111111</v>
       </c>
       <c r="F931" t="n">
         <v>96</v>
@@ -38631,7 +38631,7 @@
         </is>
       </c>
       <c r="E932" s="2" t="n">
-        <v>46091.28089111949</v>
+        <v>46091.28089112268</v>
       </c>
       <c r="F932" t="n">
         <v>179</v>
@@ -38672,7 +38672,7 @@
         </is>
       </c>
       <c r="E933" s="2" t="n">
-        <v>46091.36422445606</v>
+        <v>46091.36422445602</v>
       </c>
       <c r="F933" t="n">
         <v>178</v>
@@ -38713,7 +38713,7 @@
         </is>
       </c>
       <c r="E934" s="2" t="n">
-        <v>46073.69755779609</v>
+        <v>46073.69755780092</v>
       </c>
       <c r="F934" t="n">
         <v>121</v>
@@ -38754,7 +38754,7 @@
         </is>
       </c>
       <c r="E935" s="2" t="n">
-        <v>46077.78089113588</v>
+        <v>46077.78089113426</v>
       </c>
       <c r="F935" t="n">
         <v>61</v>
@@ -38795,7 +38795,7 @@
         </is>
       </c>
       <c r="E936" s="2" t="n">
-        <v>46072.11422448188</v>
+        <v>46072.11422447917</v>
       </c>
       <c r="F936" t="n">
         <v>153</v>
@@ -38836,7 +38836,7 @@
         </is>
       </c>
       <c r="E937" s="2" t="n">
-        <v>46078.98922448815</v>
+        <v>46078.98922449074</v>
       </c>
       <c r="F937" t="n">
         <v>84</v>
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="E938" s="2" t="n">
-        <v>46089.03089115801</v>
+        <v>46089.03089115741</v>
       </c>
       <c r="F938" t="n">
         <v>126</v>
@@ -38918,7 +38918,7 @@
         </is>
       </c>
       <c r="E939" s="2" t="n">
-        <v>46074.4892244982</v>
+        <v>46074.48922450231</v>
       </c>
       <c r="F939" t="n">
         <v>215</v>
@@ -38935,6 +38935,621 @@
       </c>
       <c r="I939" t="n">
         <v>15.61</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>09090ce7-d659-413e-b4ad-39210a801959</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>9f9299b7-5b94-4000-90c6-4761fc6bd124</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E940" s="2" t="n">
+        <v>46089.97386649226</v>
+      </c>
+      <c r="F940" t="n">
+        <v>292</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I940" t="n">
+        <v>13.14</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>10c3f739-f871-457d-b96b-aa0698b706aa</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>a0e4fbef-f6cc-4ac9-9095-b9732953e0ce</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="n">
+        <v>46063.93219982853</v>
+      </c>
+      <c r="F941" t="n">
+        <v>74</v>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I941" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>81f3921e-2d6a-4772-88f4-62412f06bf69</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>da9fca0b-1c40-42c3-a735-59e6cb0cf343</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E942" s="2" t="n">
+        <v>46092.3488665013</v>
+      </c>
+      <c r="F942" t="n">
+        <v>272</v>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I942" t="n">
+        <v>14.31</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>a6b5996a-6d32-40a7-afa5-d65581d6e3e6</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>cb3742fd-c3d1-43ee-813f-02c4fe0057b3</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E943" s="2" t="n">
+        <v>46084.22386651049</v>
+      </c>
+      <c r="F943" t="n">
+        <v>191</v>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I943" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>003489d7-1dcc-4462-81a4-b589dad1a971</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>15ba3b94-e7d2-4c5b-9226-02a613abdd85</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E944" s="2" t="n">
+        <v>46091.34886651627</v>
+      </c>
+      <c r="F944" t="n">
+        <v>58</v>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I944" t="n">
+        <v>19.61</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>7fdd3182-b9c1-41c4-83a4-1959c490bae0</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>fb2a3646-ccaf-4f66-8fc8-153e864c707d</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="n">
+        <v>46085.26553319156</v>
+      </c>
+      <c r="F945" t="n">
+        <v>300</v>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I945" t="n">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>1d7d4a03-0d0f-45ee-b89b-028536e4013d</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>3328a968-1fde-4ef0-a9d0-23167ea27668</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E946" s="2" t="n">
+        <v>46075.51553319449</v>
+      </c>
+      <c r="F946" t="n">
+        <v>270</v>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I946" t="n">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>526e5449-154a-4014-a453-ce420e5299e5</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>af55e2e4-0c2a-49d6-83c8-0956a3023db5</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E947" s="2" t="n">
+        <v>46066.76553320061</v>
+      </c>
+      <c r="F947" t="n">
+        <v>139</v>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I947" t="n">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>158308e1-4776-4ec7-9c4b-9f2952a1cfc0</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>9d4d43ba-54ba-4303-b8ed-9b0800989f98</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E948" s="2" t="n">
+        <v>46067.80719987879</v>
+      </c>
+      <c r="F948" t="n">
+        <v>114</v>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I948" t="n">
+        <v>19.08</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>6d9a8faa-d25a-45fd-9b6e-be2db64c7787</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>3a1d9b59-8d89-4b62-a2ef-157574e7a80d</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E949" s="2" t="n">
+        <v>46088.39053322918</v>
+      </c>
+      <c r="F949" t="n">
+        <v>167</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I949" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>ca07fa86-133f-48fd-ab00-56b79a1e9686</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>7035fc72-ba05-4325-a63c-6895776f04c9</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E950" s="2" t="n">
+        <v>46063.84886659442</v>
+      </c>
+      <c r="F950" t="n">
+        <v>42</v>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I950" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>a6030617-cebb-44b0-9656-074228b94451</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>65676154-590c-4467-b7f5-45dba31a4159</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E951" s="2" t="n">
+        <v>46082.22386660008</v>
+      </c>
+      <c r="F951" t="n">
+        <v>248</v>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I951" t="n">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>77aa8113-b791-4a1d-b19c-f91b3083a15a</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>c238bd6a-5062-4373-bfa6-2112ee4ee671</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E952" s="2" t="n">
+        <v>46087.97386660307</v>
+      </c>
+      <c r="F952" t="n">
+        <v>262</v>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I952" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>8214e60b-f470-46a3-a5a7-e47b0b184b28</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>55e095da-14fc-4b66-a7ad-aa8052c20812</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="n">
+        <v>46086.64053327261</v>
+      </c>
+      <c r="F953" t="n">
+        <v>210</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I953" t="n">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>85479a9c-38ed-44c8-b68b-17b605ebd8ec</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>dd7c38fb-8e35-41bd-8e9c-ce8e1f6ccbe4</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E954" s="2" t="n">
+        <v>46067.0155332783</v>
+      </c>
+      <c r="F954" t="n">
+        <v>241</v>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I954" t="n">
+        <v>6.46</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I954"/>
+  <dimension ref="A1:I972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38959,7 +38959,7 @@
         </is>
       </c>
       <c r="E940" s="2" t="n">
-        <v>46089.97386649226</v>
+        <v>46089.97386649306</v>
       </c>
       <c r="F940" t="n">
         <v>292</v>
@@ -39000,7 +39000,7 @@
         </is>
       </c>
       <c r="E941" s="2" t="n">
-        <v>46063.93219982853</v>
+        <v>46063.93219982639</v>
       </c>
       <c r="F941" t="n">
         <v>74</v>
@@ -39041,7 +39041,7 @@
         </is>
       </c>
       <c r="E942" s="2" t="n">
-        <v>46092.3488665013</v>
+        <v>46092.34886650463</v>
       </c>
       <c r="F942" t="n">
         <v>272</v>
@@ -39082,7 +39082,7 @@
         </is>
       </c>
       <c r="E943" s="2" t="n">
-        <v>46084.22386651049</v>
+        <v>46084.2238665162</v>
       </c>
       <c r="F943" t="n">
         <v>191</v>
@@ -39123,7 +39123,7 @@
         </is>
       </c>
       <c r="E944" s="2" t="n">
-        <v>46091.34886651627</v>
+        <v>46091.3488665162</v>
       </c>
       <c r="F944" t="n">
         <v>58</v>
@@ -39164,7 +39164,7 @@
         </is>
       </c>
       <c r="E945" s="2" t="n">
-        <v>46085.26553319156</v>
+        <v>46085.26553319445</v>
       </c>
       <c r="F945" t="n">
         <v>300</v>
@@ -39205,7 +39205,7 @@
         </is>
       </c>
       <c r="E946" s="2" t="n">
-        <v>46075.51553319449</v>
+        <v>46075.51553319445</v>
       </c>
       <c r="F946" t="n">
         <v>270</v>
@@ -39246,7 +39246,7 @@
         </is>
       </c>
       <c r="E947" s="2" t="n">
-        <v>46066.76553320061</v>
+        <v>46066.76553320602</v>
       </c>
       <c r="F947" t="n">
         <v>139</v>
@@ -39287,7 +39287,7 @@
         </is>
       </c>
       <c r="E948" s="2" t="n">
-        <v>46067.80719987879</v>
+        <v>46067.80719988426</v>
       </c>
       <c r="F948" t="n">
         <v>114</v>
@@ -39328,7 +39328,7 @@
         </is>
       </c>
       <c r="E949" s="2" t="n">
-        <v>46088.39053322918</v>
+        <v>46088.39053322917</v>
       </c>
       <c r="F949" t="n">
         <v>167</v>
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="E950" s="2" t="n">
-        <v>46063.84886659442</v>
+        <v>46063.84886659723</v>
       </c>
       <c r="F950" t="n">
         <v>42</v>
@@ -39410,7 +39410,7 @@
         </is>
       </c>
       <c r="E951" s="2" t="n">
-        <v>46082.22386660008</v>
+        <v>46082.22386659723</v>
       </c>
       <c r="F951" t="n">
         <v>248</v>
@@ -39451,7 +39451,7 @@
         </is>
       </c>
       <c r="E952" s="2" t="n">
-        <v>46087.97386660307</v>
+        <v>46087.97386660879</v>
       </c>
       <c r="F952" t="n">
         <v>262</v>
@@ -39492,7 +39492,7 @@
         </is>
       </c>
       <c r="E953" s="2" t="n">
-        <v>46086.64053327261</v>
+        <v>46086.64053327547</v>
       </c>
       <c r="F953" t="n">
         <v>210</v>
@@ -39533,7 +39533,7 @@
         </is>
       </c>
       <c r="E954" s="2" t="n">
-        <v>46067.0155332783</v>
+        <v>46067.01553327547</v>
       </c>
       <c r="F954" t="n">
         <v>241</v>
@@ -39550,6 +39550,744 @@
       </c>
       <c r="I954" t="n">
         <v>6.46</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>34c48c98-3a9f-4ebd-8305-8c9c4fed168d</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>8bb544d8-970b-44b5-8c50-debe8bce6c1c</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E955" s="2" t="n">
+        <v>46079.55137104871</v>
+      </c>
+      <c r="F955" t="n">
+        <v>104</v>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I955" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>a5e67c17-65b0-4887-bae5-68cf0695cd6a</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>51225ce1-08d2-417e-a5fb-162a243152f0</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E956" s="2" t="n">
+        <v>46073.5097044139</v>
+      </c>
+      <c r="F956" t="n">
+        <v>117</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I956" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2afd7729-e912-42a6-a1d5-f400c0b8d3ac</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>bf7ceb15-b987-4891-9f6c-c2a0558937d6</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E957" s="2" t="n">
+        <v>46082.42637108702</v>
+      </c>
+      <c r="F957" t="n">
+        <v>282</v>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I957" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>d0dc9243-be3d-4490-8ccf-e54c7acec9bb</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>4e3227fc-bdfd-4205-80cc-e9d318e2952c</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E958" s="2" t="n">
+        <v>46079.59303775692</v>
+      </c>
+      <c r="F958" t="n">
+        <v>87</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I958" t="n">
+        <v>13.52</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>325e2f29-de5a-45ac-8ad8-46f1eda6ef93</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>5aa76050-b039-47f6-b160-971a0af3b0e2</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="n">
+        <v>46090.25970442694</v>
+      </c>
+      <c r="F959" t="n">
+        <v>298</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I959" t="n">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>e35ff459-63e2-43df-99bb-93580fe79e77</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>1e19be16-93a4-4e24-8b0a-566322e0b8ca</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E960" s="2" t="n">
+        <v>46074.13470443633</v>
+      </c>
+      <c r="F960" t="n">
+        <v>60</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I960" t="n">
+        <v>10.86</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>8d5369e9-ff96-4235-bd93-54abc47a4e5b</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>0ad32fea-dffe-4229-a25e-d42a4663998e</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E961" s="2" t="n">
+        <v>46070.30137110626</v>
+      </c>
+      <c r="F961" t="n">
+        <v>250</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I961" t="n">
+        <v>8.720000000000001</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>bb5f7e22-1433-4dee-a0d5-9077e296429d</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>461a52ed-7640-41ef-b455-1d8347e9f91c</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E962" s="2" t="n">
+        <v>46088.9263711095</v>
+      </c>
+      <c r="F962" t="n">
+        <v>251</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I962" t="n">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>ac1bcbcf-1b6f-4578-9820-0eeef458212c</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>d5362288-df39-41db-91d7-a9f0b7253b4f</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E963" s="2" t="n">
+        <v>46081.96803777938</v>
+      </c>
+      <c r="F963" t="n">
+        <v>70</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I963" t="n">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>b22f9e8a-a712-4e4d-a912-12f32f177b3f</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>99bce355-958e-4323-968c-a2dab0758887</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E964" s="2" t="n">
+        <v>46064.21803778585</v>
+      </c>
+      <c r="F964" t="n">
+        <v>159</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I964" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>3c13e076-92c6-4ae1-851e-5ab74b8fe146</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>623457d2-fef0-4c0f-992c-2981b7f2c2a0</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E965" s="2" t="n">
+        <v>46075.1763711224</v>
+      </c>
+      <c r="F965" t="n">
+        <v>66</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I965" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>634d4c61-c469-4e28-a7be-e26a79378dc1</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>53f67020-e844-43ca-a17d-be977e4dc3b9</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="n">
+        <v>46087.59303779222</v>
+      </c>
+      <c r="F966" t="n">
+        <v>197</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I966" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>dd9a104a-5fde-47ef-8785-7e228655107c</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>d7d658f8-c747-40fc-b190-79ac2b93cbbe</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E967" s="2" t="n">
+        <v>46089.00970446219</v>
+      </c>
+      <c r="F967" t="n">
+        <v>221</v>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I967" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>b81f6205-b737-4091-b371-0cccf4a2b5b3</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>1d458302-bef6-4da7-aac2-17b4e14cffb0</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E968" s="2" t="n">
+        <v>46082.88470447782</v>
+      </c>
+      <c r="F968" t="n">
+        <v>103</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I968" t="n">
+        <v>6.14</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>95f95f81-5fee-445a-8b61-44e7c88bdb5d</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>c3952d90-429a-400e-bf0e-45a1933175fd</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E969" s="2" t="n">
+        <v>46083.71803781436</v>
+      </c>
+      <c r="F969" t="n">
+        <v>295</v>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I969" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>eaf12681-3b6f-4275-832b-36d05ef48adf</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>b5c2359c-fb85-4c20-aa1c-b979a817c8f5</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E970" s="2" t="n">
+        <v>46067.84303784247</v>
+      </c>
+      <c r="F970" t="n">
+        <v>180</v>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I970" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>011c3025-9667-441e-bd47-729fd2994091</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>4456e32a-19f6-404a-9301-0edfa67874ae</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="n">
+        <v>46086.55137119148</v>
+      </c>
+      <c r="F971" t="n">
+        <v>191</v>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I971" t="n">
+        <v>12.08</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>4bda87f4-6eb2-4c8e-a68e-c198d1754908</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>6c1ca2a9-2955-4520-ac0a-68b590a96b59</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E972" s="2" t="n">
+        <v>46077.50970453115</v>
+      </c>
+      <c r="F972" t="n">
+        <v>116</v>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I972" t="n">
+        <v>3.64</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I972"/>
+  <dimension ref="A1:I990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39574,7 +39574,7 @@
         </is>
       </c>
       <c r="E955" s="2" t="n">
-        <v>46079.55137104871</v>
+        <v>46079.55137105324</v>
       </c>
       <c r="F955" t="n">
         <v>104</v>
@@ -39615,7 +39615,7 @@
         </is>
       </c>
       <c r="E956" s="2" t="n">
-        <v>46073.5097044139</v>
+        <v>46073.50970440972</v>
       </c>
       <c r="F956" t="n">
         <v>117</v>
@@ -39656,7 +39656,7 @@
         </is>
       </c>
       <c r="E957" s="2" t="n">
-        <v>46082.42637108702</v>
+        <v>46082.42637108796</v>
       </c>
       <c r="F957" t="n">
         <v>282</v>
@@ -39697,7 +39697,7 @@
         </is>
       </c>
       <c r="E958" s="2" t="n">
-        <v>46079.59303775692</v>
+        <v>46079.59303775463</v>
       </c>
       <c r="F958" t="n">
         <v>87</v>
@@ -39738,7 +39738,7 @@
         </is>
       </c>
       <c r="E959" s="2" t="n">
-        <v>46090.25970442694</v>
+        <v>46090.2597044213</v>
       </c>
       <c r="F959" t="n">
         <v>298</v>
@@ -39779,7 +39779,7 @@
         </is>
       </c>
       <c r="E960" s="2" t="n">
-        <v>46074.13470443633</v>
+        <v>46074.13470443287</v>
       </c>
       <c r="F960" t="n">
         <v>60</v>
@@ -39820,7 +39820,7 @@
         </is>
       </c>
       <c r="E961" s="2" t="n">
-        <v>46070.30137110626</v>
+        <v>46070.30137111111</v>
       </c>
       <c r="F961" t="n">
         <v>250</v>
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="E962" s="2" t="n">
-        <v>46088.9263711095</v>
+        <v>46088.92637111111</v>
       </c>
       <c r="F962" t="n">
         <v>251</v>
@@ -39902,7 +39902,7 @@
         </is>
       </c>
       <c r="E963" s="2" t="n">
-        <v>46081.96803777938</v>
+        <v>46081.96803777778</v>
       </c>
       <c r="F963" t="n">
         <v>70</v>
@@ -39943,7 +39943,7 @@
         </is>
       </c>
       <c r="E964" s="2" t="n">
-        <v>46064.21803778585</v>
+        <v>46064.21803778935</v>
       </c>
       <c r="F964" t="n">
         <v>159</v>
@@ -39984,7 +39984,7 @@
         </is>
       </c>
       <c r="E965" s="2" t="n">
-        <v>46075.1763711224</v>
+        <v>46075.17637112269</v>
       </c>
       <c r="F965" t="n">
         <v>66</v>
@@ -40025,7 +40025,7 @@
         </is>
       </c>
       <c r="E966" s="2" t="n">
-        <v>46087.59303779222</v>
+        <v>46087.59303778935</v>
       </c>
       <c r="F966" t="n">
         <v>197</v>
@@ -40066,7 +40066,7 @@
         </is>
       </c>
       <c r="E967" s="2" t="n">
-        <v>46089.00970446219</v>
+        <v>46089.00970446759</v>
       </c>
       <c r="F967" t="n">
         <v>221</v>
@@ -40107,7 +40107,7 @@
         </is>
       </c>
       <c r="E968" s="2" t="n">
-        <v>46082.88470447782</v>
+        <v>46082.88470447917</v>
       </c>
       <c r="F968" t="n">
         <v>103</v>
@@ -40148,7 +40148,7 @@
         </is>
       </c>
       <c r="E969" s="2" t="n">
-        <v>46083.71803781436</v>
+        <v>46083.7180378125</v>
       </c>
       <c r="F969" t="n">
         <v>295</v>
@@ -40189,7 +40189,7 @@
         </is>
       </c>
       <c r="E970" s="2" t="n">
-        <v>46067.84303784247</v>
+        <v>46067.84303784723</v>
       </c>
       <c r="F970" t="n">
         <v>180</v>
@@ -40230,7 +40230,7 @@
         </is>
       </c>
       <c r="E971" s="2" t="n">
-        <v>46086.55137119148</v>
+        <v>46086.55137119213</v>
       </c>
       <c r="F971" t="n">
         <v>191</v>
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="E972" s="2" t="n">
-        <v>46077.50970453115</v>
+        <v>46077.50970452547</v>
       </c>
       <c r="F972" t="n">
         <v>116</v>
@@ -40288,6 +40288,744 @@
       </c>
       <c r="I972" t="n">
         <v>3.64</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>6926066a-6a9b-44c4-b7b1-7f889f9599e3</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>739d2c34-86a1-4c1c-9c14-0a1e3cd4deca</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="n">
+        <v>46077.54489169428</v>
+      </c>
+      <c r="F973" t="n">
+        <v>188</v>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I973" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>747cc012-7bee-4007-b2cc-6398a8a56d8a</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>d0c71655-e40f-42a1-b97c-df8de2fcb032</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E974" s="2" t="n">
+        <v>46086.04489170236</v>
+      </c>
+      <c r="F974" t="n">
+        <v>70</v>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I974" t="n">
+        <v>19.45</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>319e2d9d-ccfc-430f-906f-a57314a45a26</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>ad3955f3-f8e1-4c6a-844c-f2c9948ca011</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="n">
+        <v>46092.12822503909</v>
+      </c>
+      <c r="F975" t="n">
+        <v>110</v>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I975" t="n">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>90456825-156a-42d5-9699-3dbdee6962fb</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>c96e94bf-dd55-4c73-9997-19555b71a086</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E976" s="2" t="n">
+        <v>46076.08655837901</v>
+      </c>
+      <c r="F976" t="n">
+        <v>99</v>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I976" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>da0ae979-e948-4dca-aafd-74edc40830fd</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>a171a7b8-63ef-4dd4-b70d-106a9129df7c</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E977" s="2" t="n">
+        <v>46079.16989175322</v>
+      </c>
+      <c r="F977" t="n">
+        <v>189</v>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I977" t="n">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>ecb658cd-da9b-4b40-b426-a1af7c2fc202</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>9de8e151-467c-4d87-aa98-f3e5624ce458</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E978" s="2" t="n">
+        <v>46075.71155842937</v>
+      </c>
+      <c r="F978" t="n">
+        <v>166</v>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I978" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>089c3f47-3936-4d85-abe5-183bfb3eff0a</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>b8be1af3-aaea-495e-921a-ff02a3a5707c</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E979" s="2" t="n">
+        <v>46087.75322511497</v>
+      </c>
+      <c r="F979" t="n">
+        <v>284</v>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I979" t="n">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2d674ae3-b6a1-4334-a996-08fc97ac23a2</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>50dc187c-b085-43d6-94e3-fdb828cd2603</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="n">
+        <v>46063.83655845799</v>
+      </c>
+      <c r="F980" t="n">
+        <v>51</v>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I980" t="n">
+        <v>18.87</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>cbc8e7ba-539a-40dc-85bc-511e1beeff2c</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>8c3e47e9-070c-4f4a-875d-3e4aeb60b4d8</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="n">
+        <v>46069.29489179448</v>
+      </c>
+      <c r="F981" t="n">
+        <v>85</v>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I981" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>83a23be8-73d9-4889-ae07-3b1576e9767c</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>d55d80e3-8df2-459b-8f5e-be6d34c1ab8e</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E982" s="2" t="n">
+        <v>46090.58655846764</v>
+      </c>
+      <c r="F982" t="n">
+        <v>273</v>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I982" t="n">
+        <v>13.53</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>5d614cc4-63c2-453d-b413-1f854339ac52</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>bb4bba52-bb13-4eec-94fa-ce037b60f21b</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="n">
+        <v>46083.91989180716</v>
+      </c>
+      <c r="F983" t="n">
+        <v>216</v>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I983" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>e91326aa-fb04-4797-8df8-d38e706553d4</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>67183120-5ab6-4113-98e4-e1fec0971ca2</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E984" s="2" t="n">
+        <v>46073.7948918103</v>
+      </c>
+      <c r="F984" t="n">
+        <v>120</v>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I984" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>d3096633-4997-4e1f-b027-9c6141eafbd4</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>7e2ac0c4-48ac-43f2-b69d-b7ec29bf9430</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="n">
+        <v>46070.16989181375</v>
+      </c>
+      <c r="F985" t="n">
+        <v>249</v>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I985" t="n">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2edda539-e256-4d14-aa18-b231d5d0485b</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>63cfc09c-18cd-42c9-9461-e89aec6de221</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E986" s="2" t="n">
+        <v>46083.37822515026</v>
+      </c>
+      <c r="F986" t="n">
+        <v>171</v>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I986" t="n">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2c2b5829-f305-4ef3-bbc9-6c8a62e5f358</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>49e471b7-7521-4361-b296-a1730d60121a</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E987" s="2" t="n">
+        <v>46089.08655849293</v>
+      </c>
+      <c r="F987" t="n">
+        <v>167</v>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I987" t="n">
+        <v>17.98</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>60488695-1391-4844-8f91-3180be4b7007</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>9e37bcd8-a2a3-4217-8b66-3e6fd2085a9e</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E988" s="2" t="n">
+        <v>46082.12822516583</v>
+      </c>
+      <c r="F988" t="n">
+        <v>297</v>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I988" t="n">
+        <v>19.89</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>1c085c42-3beb-473c-989e-6075901e9c96</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>3ac748eb-9cfe-4f51-8626-578eeeceba15</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E989" s="2" t="n">
+        <v>46087.41989183586</v>
+      </c>
+      <c r="F989" t="n">
+        <v>61</v>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I989" t="n">
+        <v>19.72</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>103a5413-aa23-4103-8ae5-74ce703a6619</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>d0d83647-283b-49aa-9d1a-de78594c5353</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E990" s="2" t="n">
+        <v>46071.83655851175</v>
+      </c>
+      <c r="F990" t="n">
+        <v>192</v>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I990" t="n">
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I990"/>
+  <dimension ref="A1:I1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40312,7 +40312,7 @@
         </is>
       </c>
       <c r="E973" s="2" t="n">
-        <v>46077.54489169428</v>
+        <v>46077.54489168982</v>
       </c>
       <c r="F973" t="n">
         <v>188</v>
@@ -40353,7 +40353,7 @@
         </is>
       </c>
       <c r="E974" s="2" t="n">
-        <v>46086.04489170236</v>
+        <v>46086.04489170139</v>
       </c>
       <c r="F974" t="n">
         <v>70</v>
@@ -40394,7 +40394,7 @@
         </is>
       </c>
       <c r="E975" s="2" t="n">
-        <v>46092.12822503909</v>
+        <v>46092.12822503472</v>
       </c>
       <c r="F975" t="n">
         <v>110</v>
@@ -40435,7 +40435,7 @@
         </is>
       </c>
       <c r="E976" s="2" t="n">
-        <v>46076.08655837901</v>
+        <v>46076.08655837963</v>
       </c>
       <c r="F976" t="n">
         <v>99</v>
@@ -40476,7 +40476,7 @@
         </is>
       </c>
       <c r="E977" s="2" t="n">
-        <v>46079.16989175322</v>
+        <v>46079.16989174768</v>
       </c>
       <c r="F977" t="n">
         <v>189</v>
@@ -40517,7 +40517,7 @@
         </is>
       </c>
       <c r="E978" s="2" t="n">
-        <v>46075.71155842937</v>
+        <v>46075.71155842592</v>
       </c>
       <c r="F978" t="n">
         <v>166</v>
@@ -40558,7 +40558,7 @@
         </is>
       </c>
       <c r="E979" s="2" t="n">
-        <v>46087.75322511497</v>
+        <v>46087.75322511574</v>
       </c>
       <c r="F979" t="n">
         <v>284</v>
@@ -40599,7 +40599,7 @@
         </is>
       </c>
       <c r="E980" s="2" t="n">
-        <v>46063.83655845799</v>
+        <v>46063.83655846065</v>
       </c>
       <c r="F980" t="n">
         <v>51</v>
@@ -40640,7 +40640,7 @@
         </is>
       </c>
       <c r="E981" s="2" t="n">
-        <v>46069.29489179448</v>
+        <v>46069.29489179398</v>
       </c>
       <c r="F981" t="n">
         <v>85</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="E982" s="2" t="n">
-        <v>46090.58655846764</v>
+        <v>46090.58655847222</v>
       </c>
       <c r="F982" t="n">
         <v>273</v>
@@ -40722,7 +40722,7 @@
         </is>
       </c>
       <c r="E983" s="2" t="n">
-        <v>46083.91989180716</v>
+        <v>46083.91989180556</v>
       </c>
       <c r="F983" t="n">
         <v>216</v>
@@ -40763,7 +40763,7 @@
         </is>
       </c>
       <c r="E984" s="2" t="n">
-        <v>46073.7948918103</v>
+        <v>46073.79489180556</v>
       </c>
       <c r="F984" t="n">
         <v>120</v>
@@ -40804,7 +40804,7 @@
         </is>
       </c>
       <c r="E985" s="2" t="n">
-        <v>46070.16989181375</v>
+        <v>46070.16989181713</v>
       </c>
       <c r="F985" t="n">
         <v>249</v>
@@ -40845,7 +40845,7 @@
         </is>
       </c>
       <c r="E986" s="2" t="n">
-        <v>46083.37822515026</v>
+        <v>46083.37822515046</v>
       </c>
       <c r="F986" t="n">
         <v>171</v>
@@ -40886,7 +40886,7 @@
         </is>
       </c>
       <c r="E987" s="2" t="n">
-        <v>46089.08655849293</v>
+        <v>46089.08655849537</v>
       </c>
       <c r="F987" t="n">
         <v>167</v>
@@ -40927,7 +40927,7 @@
         </is>
       </c>
       <c r="E988" s="2" t="n">
-        <v>46082.12822516583</v>
+        <v>46082.12822516204</v>
       </c>
       <c r="F988" t="n">
         <v>297</v>
@@ -40968,7 +40968,7 @@
         </is>
       </c>
       <c r="E989" s="2" t="n">
-        <v>46087.41989183586</v>
+        <v>46087.41989184028</v>
       </c>
       <c r="F989" t="n">
         <v>61</v>
@@ -41009,7 +41009,7 @@
         </is>
       </c>
       <c r="E990" s="2" t="n">
-        <v>46071.83655851175</v>
+        <v>46071.83655850695</v>
       </c>
       <c r="F990" t="n">
         <v>192</v>
@@ -41026,6 +41026,703 @@
       </c>
       <c r="I990" t="n">
         <v>9.09</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>aa1b9572-cd3c-4dbf-8b51-0274dfb7b516</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>5bac36b1-46e0-46e9-bbb4-bd2aafe0ae0f</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E991" s="2" t="n">
+        <v>46066.4126801281</v>
+      </c>
+      <c r="F991" t="n">
+        <v>64</v>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I991" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>b087463e-ddb5-4f66-a2da-577f6d89fcba</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>9e2ed0f4-39ee-4689-8abb-51149fc50217</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E992" s="2" t="n">
+        <v>46082.95434680893</v>
+      </c>
+      <c r="F992" t="n">
+        <v>250</v>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I992" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2cb9c270-3c86-4b1f-b623-0e3e3088e0f9</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>e19b2a5e-bb58-4058-adb3-2bb969a5d548</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E993" s="2" t="n">
+        <v>46071.66268014885</v>
+      </c>
+      <c r="F993" t="n">
+        <v>232</v>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I993" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>c445bbb6-7921-46a2-a9e2-5a633f84c811</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>971e65f4-5512-425b-959d-5aeb3be87e1d</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E994" s="2" t="n">
+        <v>46079.57934682194</v>
+      </c>
+      <c r="F994" t="n">
+        <v>206</v>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I994" t="n">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>6d69a4a2-c824-4df9-9ee5-0adf2f9b043a</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>6ecda695-dbcd-480c-bf96-4812c900e0a4</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E995" s="2" t="n">
+        <v>46074.28768015857</v>
+      </c>
+      <c r="F995" t="n">
+        <v>275</v>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I995" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>f74370bf-7e9b-4aff-b252-885b66cecccb</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>efde3251-20c3-4cda-854a-10bcfc3ddc90</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E996" s="2" t="n">
+        <v>46070.16268016823</v>
+      </c>
+      <c r="F996" t="n">
+        <v>169</v>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I996" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>b9cdf282-21e8-4c47-bd77-4823e9aa0af0</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>b0db4e63-b5a9-41fe-9ead-9169dfbbf336</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E997" s="2" t="n">
+        <v>46070.03768017521</v>
+      </c>
+      <c r="F997" t="n">
+        <v>182</v>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I997" t="n">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>3c36d9a8-bb0a-480c-80fd-8d26330caaad</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>19ec4670-a86d-4cf4-91c5-1dbdc4fdfbfd</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E998" s="2" t="n">
+        <v>46078.70434686097</v>
+      </c>
+      <c r="F998" t="n">
+        <v>40</v>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I998" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>f4ee28cb-fd1c-442c-a29d-376ee87f12f5</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>12e6c5c5-8c3a-4357-88cd-709cba3081d2</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E999" s="2" t="n">
+        <v>46072.70434686419</v>
+      </c>
+      <c r="F999" t="n">
+        <v>141</v>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I999" t="n">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>4b49bea5-4c74-4d58-bc6b-4f980dd9c98a</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>2592be31-6393-4d7f-8104-883d8c2350a9</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1000" s="2" t="n">
+        <v>46087.49601353413</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>254</v>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1000" t="n">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>6c699fc5-22b0-4a5c-9288-024deb9efa3e</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>30529180-0b0e-4229-a8ec-9a7bfcae8760</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1001" s="2" t="n">
+        <v>46064.8710135405</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>293</v>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1001" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>5ee2d3aa-05e7-41e3-8a7a-36d36baa4231</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>fdc80b58-f0cd-4838-bd7f-b7de0788ac12</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1002" s="2" t="n">
+        <v>46072.45434688954</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>240</v>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1002" t="n">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>f58305c2-104f-4ae1-af96-b52052e2359d</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>814ba699-a460-4358-acf5-8d6ed92fee7a</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1003" s="2" t="n">
+        <v>46064.24601356585</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1003" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>620af20f-7891-48f8-86db-edbf76f21568</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>e3791d8a-2eec-4cc4-8c55-a46d24864d19</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1004" s="2" t="n">
+        <v>46072.03768025507</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1004" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>bb88b333-b0a6-40ba-96ed-0fa97cf91e38</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>f5936f5e-b21d-4e2c-9834-bbd579234f22</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1005" s="2" t="n">
+        <v>46086.95434693732</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>221</v>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1005" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>f1109d17-80b1-44f5-8950-2cc359f6061d</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>ce7d574b-f31d-4f73-91f6-07179e702296</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1006" s="2" t="n">
+        <v>46066.0376802772</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1006" t="n">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>1ef11b16-d8b4-421d-88c6-47b436bab4ad</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>ac762f40-e1c2-424f-9baf-fc5465cefc7f</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1007" s="2" t="n">
+        <v>46086.57934694736</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1007" t="n">
+        <v>15.93</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1007"/>
+  <dimension ref="A1:I1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41050,7 +41050,7 @@
         </is>
       </c>
       <c r="E991" s="2" t="n">
-        <v>46066.4126801281</v>
+        <v>46066.41268012732</v>
       </c>
       <c r="F991" t="n">
         <v>64</v>
@@ -41091,7 +41091,7 @@
         </is>
       </c>
       <c r="E992" s="2" t="n">
-        <v>46082.95434680893</v>
+        <v>46082.95434680556</v>
       </c>
       <c r="F992" t="n">
         <v>250</v>
@@ -41132,7 +41132,7 @@
         </is>
       </c>
       <c r="E993" s="2" t="n">
-        <v>46071.66268014885</v>
+        <v>46071.66268015046</v>
       </c>
       <c r="F993" t="n">
         <v>232</v>
@@ -41173,7 +41173,7 @@
         </is>
       </c>
       <c r="E994" s="2" t="n">
-        <v>46079.57934682194</v>
+        <v>46079.57934681713</v>
       </c>
       <c r="F994" t="n">
         <v>206</v>
@@ -41214,7 +41214,7 @@
         </is>
       </c>
       <c r="E995" s="2" t="n">
-        <v>46074.28768015857</v>
+        <v>46074.28768016204</v>
       </c>
       <c r="F995" t="n">
         <v>275</v>
@@ -41255,7 +41255,7 @@
         </is>
       </c>
       <c r="E996" s="2" t="n">
-        <v>46070.16268016823</v>
+        <v>46070.16268017361</v>
       </c>
       <c r="F996" t="n">
         <v>169</v>
@@ -41296,7 +41296,7 @@
         </is>
       </c>
       <c r="E997" s="2" t="n">
-        <v>46070.03768017521</v>
+        <v>46070.03768017361</v>
       </c>
       <c r="F997" t="n">
         <v>182</v>
@@ -41337,7 +41337,7 @@
         </is>
       </c>
       <c r="E998" s="2" t="n">
-        <v>46078.70434686097</v>
+        <v>46078.70434686343</v>
       </c>
       <c r="F998" t="n">
         <v>40</v>
@@ -41378,7 +41378,7 @@
         </is>
       </c>
       <c r="E999" s="2" t="n">
-        <v>46072.70434686419</v>
+        <v>46072.70434686343</v>
       </c>
       <c r="F999" t="n">
         <v>141</v>
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="E1000" s="2" t="n">
-        <v>46087.49601353413</v>
+        <v>46087.49601353009</v>
       </c>
       <c r="F1000" t="n">
         <v>254</v>
@@ -41460,7 +41460,7 @@
         </is>
       </c>
       <c r="E1001" s="2" t="n">
-        <v>46064.8710135405</v>
+        <v>46064.87101354167</v>
       </c>
       <c r="F1001" t="n">
         <v>293</v>
@@ -41501,7 +41501,7 @@
         </is>
       </c>
       <c r="E1002" s="2" t="n">
-        <v>46072.45434688954</v>
+        <v>46072.45434688657</v>
       </c>
       <c r="F1002" t="n">
         <v>240</v>
@@ -41542,7 +41542,7 @@
         </is>
       </c>
       <c r="E1003" s="2" t="n">
-        <v>46064.24601356585</v>
+        <v>46064.24601356481</v>
       </c>
       <c r="F1003" t="n">
         <v>45</v>
@@ -41583,7 +41583,7 @@
         </is>
       </c>
       <c r="E1004" s="2" t="n">
-        <v>46072.03768025507</v>
+        <v>46072.03768025463</v>
       </c>
       <c r="F1004" t="n">
         <v>178</v>
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="E1005" s="2" t="n">
-        <v>46086.95434693732</v>
+        <v>46086.95434693287</v>
       </c>
       <c r="F1005" t="n">
         <v>221</v>
@@ -41665,7 +41665,7 @@
         </is>
       </c>
       <c r="E1006" s="2" t="n">
-        <v>46066.0376802772</v>
+        <v>46066.03768027778</v>
       </c>
       <c r="F1006" t="n">
         <v>165</v>
@@ -41706,7 +41706,7 @@
         </is>
       </c>
       <c r="E1007" s="2" t="n">
-        <v>46086.57934694736</v>
+        <v>46086.57934694445</v>
       </c>
       <c r="F1007" t="n">
         <v>250</v>
@@ -41723,6 +41723,908 @@
       </c>
       <c r="I1007" t="n">
         <v>15.93</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>cbd21a07-ccba-41d3-8bd7-d6a3aff66f45</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>345028c4-0bbd-4cc0-a16b-f161a18c0def</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1008" s="2" t="n">
+        <v>46067.66224924307</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1008" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>ac8f9fc9-7577-47d9-b3da-73894453dacd</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>b1a05618-f367-46c2-89f7-ebbdd9235b0f</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1009" s="2" t="n">
+        <v>46067.49558258491</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>158</v>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1009" t="n">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>a1a6422f-3c5c-40f2-a958-d3757036e866</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>a0b24b9e-356d-40de-bdab-453f476aa026</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1010" s="2" t="n">
+        <v>46076.62058259187</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>194</v>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1010" t="n">
+        <v>17.59</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>821a7ae9-52e0-4767-8474-f9c9d12803e5</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>c9711386-fb0f-46e0-b722-f6cbec141b53</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1011" s="2" t="n">
+        <v>46067.49558259518</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>271</v>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1011" t="n">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>9faecf2e-fb14-4383-b290-17d76ed74144</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>3bc5cbf8-f164-4407-aa29-9ea8682487b8</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1012" s="2" t="n">
+        <v>46093.70391593169</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1012" t="n">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>dcc98172-e623-4a59-9f1c-8389587f6262</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>26a84c2a-1201-49c1-a24c-ac61e697fa0d</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1013" s="2" t="n">
+        <v>46090.45391594488</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1013" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>dac9db3e-e265-4fda-aee7-a08989e92396</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>0e00782e-0089-4067-be17-463c25b39c86</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1014" s="2" t="n">
+        <v>46077.16224928151</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1014" t="n">
+        <v>18.07</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>a1e4eacf-5fb1-44b6-8b13-289deef0bf28</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>efe83dfd-bcd3-441e-a1d0-019361d2b814</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1015" s="2" t="n">
+        <v>46064.49558261804</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>153</v>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1015" t="n">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>12ce98de-91bf-46dd-a39d-85fa12df3816</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>407e2cd6-8607-4a74-8d2a-3eda60b9915a</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1016" s="2" t="n">
+        <v>46081.2455826307</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1016" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>e1754b5c-dc3b-493c-9a06-beb095904dbe</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>513acce9-10f1-4029-913c-a27b547d1ed4</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1017" s="2" t="n">
+        <v>46082.66224932244</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>258</v>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1017" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>10f2c4cc-7955-41a0-81b2-26cfbbaf3cab</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>ff7a3100-76e3-4847-82d5-ca835d33a10b</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1018" s="2" t="n">
+        <v>46090.8705826764</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1018" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>95a04f3b-8308-4d26-8890-c40a2566766d</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>25585ef2-58e9-467f-a944-764d69d3fdfb</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1019" s="2" t="n">
+        <v>46081.78724934621</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1019" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>fd472e8e-7f4f-4ae8-9b6f-b138ed50ac4a</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>d2e749a6-9177-434a-889e-8c0152a41c44</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1020" s="2" t="n">
+        <v>46086.20391601665</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1020" t="n">
+        <v>10.03</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>6b4f444e-cef6-46ee-b10b-71d85c629d6d</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>1921b0fb-c26d-457c-ba07-39bde6956fe4</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1021" s="2" t="n">
+        <v>46082.45391601986</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1021" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>705f6cb6-3f87-412e-b92c-5c70ecef3030</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>301828a9-bf02-4635-9fb2-532ac628c00c</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1022" s="2" t="n">
+        <v>46074.95391602298</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1022" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>3fbdb635-6589-4bbf-b431-027b4c2460d6</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>f6a5da99-d5aa-4fc6-bb61-7594c67ac4a3</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1023" s="2" t="n">
+        <v>46078.03724935969</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>146</v>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1023" t="n">
+        <v>15.94</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>cc85edcb-69cd-4288-ab44-8d0c780b551f</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>70cb24d9-2c60-48a0-9432-8e9b8369e039</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1024" s="2" t="n">
+        <v>46074.2039160298</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1024" t="n">
+        <v>13.54</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>1a8bad90-6c95-4bfd-91a3-e8dba8bfc5ac</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>8bf21daf-7eba-478f-bfd0-8b6bce25d630</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1025" s="2" t="n">
+        <v>46089.41224936951</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>299</v>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1025" t="n">
+        <v>19.31</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>9f679509-6808-44fe-a3b1-1cb821a9ce38</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>f36bb26d-14fc-449a-a1a2-8886236de4c4</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1026" s="2" t="n">
+        <v>46093.2455827126</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1026" t="n">
+        <v>11.76</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>1c072f80-3e38-4764-8bf6-ca9659f62e91</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>f4ea58af-025c-41c0-bf6c-1a6cab6cb070</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1027" s="2" t="n">
+        <v>46089.91224938873</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1027" t="n">
+        <v>18.77</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>20b48947-d51c-4ab1-9245-be708e4e78ab</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>c6855eca-f16d-45ba-af85-30049ec9f0f1</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1028" s="2" t="n">
+        <v>46081.66224939546</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1028" t="n">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>b38af0fe-2b88-42ac-bb45-7caffd2b3e0b</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>87c629c6-0d8c-4a82-a585-8b24c354fc00</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1029" s="2" t="n">
+        <v>46078.45391607149</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>151</v>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1029" t="n">
+        <v>16.03</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1029"/>
+  <dimension ref="A1:I1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41747,7 +41747,7 @@
         </is>
       </c>
       <c r="E1008" s="2" t="n">
-        <v>46067.66224924307</v>
+        <v>46067.66224924768</v>
       </c>
       <c r="F1008" t="n">
         <v>54</v>
@@ -41788,7 +41788,7 @@
         </is>
       </c>
       <c r="E1009" s="2" t="n">
-        <v>46067.49558258491</v>
+        <v>46067.49558258102</v>
       </c>
       <c r="F1009" t="n">
         <v>158</v>
@@ -41829,7 +41829,7 @@
         </is>
       </c>
       <c r="E1010" s="2" t="n">
-        <v>46076.62058259187</v>
+        <v>46076.62058259259</v>
       </c>
       <c r="F1010" t="n">
         <v>194</v>
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="E1011" s="2" t="n">
-        <v>46067.49558259518</v>
+        <v>46067.49558259259</v>
       </c>
       <c r="F1011" t="n">
         <v>271</v>
@@ -41911,7 +41911,7 @@
         </is>
       </c>
       <c r="E1012" s="2" t="n">
-        <v>46093.70391593169</v>
+        <v>46093.70391592593</v>
       </c>
       <c r="F1012" t="n">
         <v>215</v>
@@ -41952,7 +41952,7 @@
         </is>
       </c>
       <c r="E1013" s="2" t="n">
-        <v>46090.45391594488</v>
+        <v>46090.45391594907</v>
       </c>
       <c r="F1013" t="n">
         <v>259</v>
@@ -41993,7 +41993,7 @@
         </is>
       </c>
       <c r="E1014" s="2" t="n">
-        <v>46077.16224928151</v>
+        <v>46077.16224928241</v>
       </c>
       <c r="F1014" t="n">
         <v>203</v>
@@ -42034,7 +42034,7 @@
         </is>
       </c>
       <c r="E1015" s="2" t="n">
-        <v>46064.49558261804</v>
+        <v>46064.49558261574</v>
       </c>
       <c r="F1015" t="n">
         <v>153</v>
@@ -42075,7 +42075,7 @@
         </is>
       </c>
       <c r="E1016" s="2" t="n">
-        <v>46081.2455826307</v>
+        <v>46081.24558262731</v>
       </c>
       <c r="F1016" t="n">
         <v>84</v>
@@ -42116,7 +42116,7 @@
         </is>
       </c>
       <c r="E1017" s="2" t="n">
-        <v>46082.66224932244</v>
+        <v>46082.66224931713</v>
       </c>
       <c r="F1017" t="n">
         <v>258</v>
@@ -42157,7 +42157,7 @@
         </is>
       </c>
       <c r="E1018" s="2" t="n">
-        <v>46090.8705826764</v>
+        <v>46090.87058267361</v>
       </c>
       <c r="F1018" t="n">
         <v>216</v>
@@ -42198,7 +42198,7 @@
         </is>
       </c>
       <c r="E1019" s="2" t="n">
-        <v>46081.78724934621</v>
+        <v>46081.78724935185</v>
       </c>
       <c r="F1019" t="n">
         <v>224</v>
@@ -42239,7 +42239,7 @@
         </is>
       </c>
       <c r="E1020" s="2" t="n">
-        <v>46086.20391601665</v>
+        <v>46086.20391601852</v>
       </c>
       <c r="F1020" t="n">
         <v>124</v>
@@ -42280,7 +42280,7 @@
         </is>
       </c>
       <c r="E1021" s="2" t="n">
-        <v>46082.45391601986</v>
+        <v>46082.45391601852</v>
       </c>
       <c r="F1021" t="n">
         <v>107</v>
@@ -42321,7 +42321,7 @@
         </is>
       </c>
       <c r="E1022" s="2" t="n">
-        <v>46074.95391602298</v>
+        <v>46074.95391601852</v>
       </c>
       <c r="F1022" t="n">
         <v>99</v>
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="E1023" s="2" t="n">
-        <v>46078.03724935969</v>
+        <v>46078.03724936343</v>
       </c>
       <c r="F1023" t="n">
         <v>146</v>
@@ -42403,7 +42403,7 @@
         </is>
       </c>
       <c r="E1024" s="2" t="n">
-        <v>46074.2039160298</v>
+        <v>46074.20391603009</v>
       </c>
       <c r="F1024" t="n">
         <v>79</v>
@@ -42444,7 +42444,7 @@
         </is>
       </c>
       <c r="E1025" s="2" t="n">
-        <v>46089.41224936951</v>
+        <v>46089.412249375</v>
       </c>
       <c r="F1025" t="n">
         <v>299</v>
@@ -42485,7 +42485,7 @@
         </is>
       </c>
       <c r="E1026" s="2" t="n">
-        <v>46093.2455827126</v>
+        <v>46093.24558270833</v>
       </c>
       <c r="F1026" t="n">
         <v>50</v>
@@ -42526,7 +42526,7 @@
         </is>
       </c>
       <c r="E1027" s="2" t="n">
-        <v>46089.91224938873</v>
+        <v>46089.91224938657</v>
       </c>
       <c r="F1027" t="n">
         <v>33</v>
@@ -42567,7 +42567,7 @@
         </is>
       </c>
       <c r="E1028" s="2" t="n">
-        <v>46081.66224939546</v>
+        <v>46081.66224939815</v>
       </c>
       <c r="F1028" t="n">
         <v>100</v>
@@ -42608,7 +42608,7 @@
         </is>
       </c>
       <c r="E1029" s="2" t="n">
-        <v>46078.45391607149</v>
+        <v>46078.45391607639</v>
       </c>
       <c r="F1029" t="n">
         <v>151</v>
@@ -42625,6 +42625,703 @@
       </c>
       <c r="I1029" t="n">
         <v>16.03</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>41f1ca31-a61c-46fb-ba0c-c41f1a378696</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>3d0a3a00-7f19-43d9-bc1d-5e08c73de887</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1030" s="2" t="n">
+        <v>46092.5773500886</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>164</v>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1030" t="n">
+        <v>17.13</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>b16e3ac1-922c-449f-82ec-c6ac996555c6</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>cd8cd8b4-f45b-4d7f-81dd-5c826c9a3cf7</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1031" s="2" t="n">
+        <v>46074.7440167715</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>141</v>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1031" t="n">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>5280a7f0-02ad-4a2a-96ab-d1be2dd83e45</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>6f89cf71-8f70-4c6e-bce7-ab6bb74ab8b5</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1032" s="2" t="n">
+        <v>46062.9523501084</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>114</v>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1032" t="n">
+        <v>13.92</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>6f706ea6-b1ad-4db2-8656-022d5c8719d2</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>35296116-d625-47b6-9725-71b8c6b0df2d</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1033" s="2" t="n">
+        <v>46064.49401678182</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>237</v>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1033" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>a1492ceb-41aa-463f-b41b-078af549270b</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>0f7a3093-140f-4b39-81a0-1c11a72565c4</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1034" s="2" t="n">
+        <v>46085.66068345831</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>136</v>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1034" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>c58770f4-3112-44ff-9178-50d113927050</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>ec1b70a7-1719-4c71-b61f-9d02ba680565</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1035" s="2" t="n">
+        <v>46079.91068346766</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>87</v>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1035" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>aa9ddf4a-2dc9-4276-a038-78961b1554e4</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>9f3780f4-9e36-4d7f-a328-517e975d7d96</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1036" s="2" t="n">
+        <v>46074.74401680436</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1036" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2174c701-71e1-4ad7-9812-50bf5137f5b9</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>0fa5a106-8af6-4b6b-9045-613c16545e86</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1037" s="2" t="n">
+        <v>46086.82735014095</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>270</v>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1037" t="n">
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>8c579b45-0738-49ec-b8f5-4444c4ee13d7</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>55effac5-ee9c-48f3-bd8f-e9ce4fbc936b</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1038" s="2" t="n">
+        <v>46062.95235014714</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>249</v>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1038" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>93c60b50-8b03-4731-a01c-489a285b5cc9</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>57c91528-994c-49ac-bada-e0d28e9ebaf8</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1039" s="2" t="n">
+        <v>46080.74401681725</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>240</v>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1039" t="n">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>ce653205-8e11-4ad8-a8a8-52ef2bd78b03</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>2ef167a8-9d14-4493-a872-3397b70e971d</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1040" s="2" t="n">
+        <v>46091.41068350641</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>228</v>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1040" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>a1cecc07-5dc1-4a75-9973-082adf04e207</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>3e1634b1-b83b-451c-99f0-7d0b14623b35</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1041" s="2" t="n">
+        <v>46074.07735018601</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1041" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>e41184cc-ea29-4a77-b4a7-3cc821d9155b</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>96a306ac-d539-4f45-976e-5a3f5797e734</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1042" s="2" t="n">
+        <v>46082.78568352255</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>281</v>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1042" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>bcacd9d1-f19d-48d4-9b06-ab9cf0b4b3be</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>9ae407bf-a494-4636-854a-97b8e5790a45</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1043" s="2" t="n">
+        <v>46067.53568353189</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>130</v>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1043" t="n">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>7831a6b1-8ce6-4ffb-98b6-441c5aa5e2a8</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>148f8118-61cc-4033-8dc2-6fd7a5d12b94</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1044" s="2" t="n">
+        <v>46074.5356835351</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>275</v>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1044" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>1f47aa5e-824a-4b9c-9b0f-3ada6afe780c</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>b1e35a13-c62b-4eff-8939-f697ffbd9c41</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1045" s="2" t="n">
+        <v>46092.95235022081</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1045" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>591c80f6-f2ed-40ec-bb1b-4daae70f79c1</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>e1839c67-01f5-44be-bc9c-55626edee130</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1046" s="2" t="n">
+        <v>46067.74401690347</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>119</v>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1046" t="n">
+        <v>16.29</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1046"/>
+  <dimension ref="A1:I1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42649,7 +42649,7 @@
         </is>
       </c>
       <c r="E1030" s="2" t="n">
-        <v>46092.5773500886</v>
+        <v>46092.57735009259</v>
       </c>
       <c r="F1030" t="n">
         <v>164</v>
@@ -42690,7 +42690,7 @@
         </is>
       </c>
       <c r="E1031" s="2" t="n">
-        <v>46074.7440167715</v>
+        <v>46074.74401677083</v>
       </c>
       <c r="F1031" t="n">
         <v>141</v>
@@ -42731,7 +42731,7 @@
         </is>
       </c>
       <c r="E1032" s="2" t="n">
-        <v>46062.9523501084</v>
+        <v>46062.95235010417</v>
       </c>
       <c r="F1032" t="n">
         <v>114</v>
@@ -42772,7 +42772,7 @@
         </is>
       </c>
       <c r="E1033" s="2" t="n">
-        <v>46064.49401678182</v>
+        <v>46064.49401678241</v>
       </c>
       <c r="F1033" t="n">
         <v>237</v>
@@ -42813,7 +42813,7 @@
         </is>
       </c>
       <c r="E1034" s="2" t="n">
-        <v>46085.66068345831</v>
+        <v>46085.66068346065</v>
       </c>
       <c r="F1034" t="n">
         <v>136</v>
@@ -42854,7 +42854,7 @@
         </is>
       </c>
       <c r="E1035" s="2" t="n">
-        <v>46079.91068346766</v>
+        <v>46079.91068347222</v>
       </c>
       <c r="F1035" t="n">
         <v>87</v>
@@ -42895,7 +42895,7 @@
         </is>
       </c>
       <c r="E1036" s="2" t="n">
-        <v>46074.74401680436</v>
+        <v>46074.74401680555</v>
       </c>
       <c r="F1036" t="n">
         <v>280</v>
@@ -42936,7 +42936,7 @@
         </is>
       </c>
       <c r="E1037" s="2" t="n">
-        <v>46086.82735014095</v>
+        <v>46086.82735013889</v>
       </c>
       <c r="F1037" t="n">
         <v>270</v>
@@ -42977,7 +42977,7 @@
         </is>
       </c>
       <c r="E1038" s="2" t="n">
-        <v>46062.95235014714</v>
+        <v>46062.95235015047</v>
       </c>
       <c r="F1038" t="n">
         <v>249</v>
@@ -43018,7 +43018,7 @@
         </is>
       </c>
       <c r="E1039" s="2" t="n">
-        <v>46080.74401681725</v>
+        <v>46080.74401681713</v>
       </c>
       <c r="F1039" t="n">
         <v>240</v>
@@ -43059,7 +43059,7 @@
         </is>
       </c>
       <c r="E1040" s="2" t="n">
-        <v>46091.41068350641</v>
+        <v>46091.41068350695</v>
       </c>
       <c r="F1040" t="n">
         <v>228</v>
@@ -43100,7 +43100,7 @@
         </is>
       </c>
       <c r="E1041" s="2" t="n">
-        <v>46074.07735018601</v>
+        <v>46074.07735018519</v>
       </c>
       <c r="F1041" t="n">
         <v>42</v>
@@ -43141,7 +43141,7 @@
         </is>
       </c>
       <c r="E1042" s="2" t="n">
-        <v>46082.78568352255</v>
+        <v>46082.78568351852</v>
       </c>
       <c r="F1042" t="n">
         <v>281</v>
@@ -43182,7 +43182,7 @@
         </is>
       </c>
       <c r="E1043" s="2" t="n">
-        <v>46067.53568353189</v>
+        <v>46067.53568353009</v>
       </c>
       <c r="F1043" t="n">
         <v>130</v>
@@ -43223,7 +43223,7 @@
         </is>
       </c>
       <c r="E1044" s="2" t="n">
-        <v>46074.5356835351</v>
+        <v>46074.53568353009</v>
       </c>
       <c r="F1044" t="n">
         <v>275</v>
@@ -43264,7 +43264,7 @@
         </is>
       </c>
       <c r="E1045" s="2" t="n">
-        <v>46092.95235022081</v>
+        <v>46092.95235021991</v>
       </c>
       <c r="F1045" t="n">
         <v>61</v>
@@ -43305,7 +43305,7 @@
         </is>
       </c>
       <c r="E1046" s="2" t="n">
-        <v>46067.74401690347</v>
+        <v>46067.74401689815</v>
       </c>
       <c r="F1046" t="n">
         <v>119</v>
@@ -43322,6 +43322,785 @@
       </c>
       <c r="I1046" t="n">
         <v>16.29</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>270dee36-101f-41e6-81fc-89f9fb70c842</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>cebd8e98-d307-4b24-bb0d-df5234e23d24</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1047" s="2" t="n">
+        <v>46071.56933123962</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>242</v>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1047" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>1e6934f9-e460-4a18-9fc4-45c97be786de</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>3368bdba-55f5-4d5e-b640-2bd125767d03</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1048" s="2" t="n">
+        <v>46064.44433124316</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>254</v>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1048" t="n">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>5acdd9fe-efe2-453f-b824-390aef6fc0f8</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>0e71e12c-730d-4ac8-ac68-e514f41b455e</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1049" s="2" t="n">
+        <v>46077.73599791306</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1049" t="n">
+        <v>16.72</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>72f99dc3-7992-4ec9-b9d3-f924803ff79c</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>2bdea190-3789-47aa-9926-315659337b88</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1050" s="2" t="n">
+        <v>46064.86099793624</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>268</v>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1050" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>af913a83-d4bb-45d0-9fd2-473a98b5b7fd</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>9bd3c989-44c5-4fd9-aa64-3859ab094b7e</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1051" s="2" t="n">
+        <v>46090.48599793966</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>249</v>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1051" t="n">
+        <v>17.76</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>a52b9965-74c4-467b-a089-9464c57ff9f2</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>17a0f6a5-5642-4b8b-aff1-c9f162e93dc9</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1052" s="2" t="n">
+        <v>46064.19433128539</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>266</v>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1052" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>01a81755-8ef3-4e01-9156-4111ea9d280f</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>7a699c76-5edd-43e1-8a3e-e6a02e92508f</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1053" s="2" t="n">
+        <v>46090.94433129056</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1053" t="n">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>8b4407c4-5b69-4586-a328-0ebb08d088ff</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>d1b8fb88-fa53-49f8-b92a-0e4775c8fd57</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1054" s="2" t="n">
+        <v>46082.36099797378</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>296</v>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1054" t="n">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>8e4cce9a-1690-49d8-a761-ccf3bb68d89f</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>8d4428c7-0490-41ee-89fc-43c139254e21</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1055" s="2" t="n">
+        <v>46080.15266465023</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1055" t="n">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>71d95e6c-2bad-4974-9dd7-b11f77a0cd90</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>c1b96343-db61-4d53-9ca6-e8c8b82f62cd</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1056" s="2" t="n">
+        <v>46093.23599799361</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>202</v>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1056" t="n">
+        <v>9.119999999999999</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>e2997279-2cd0-477a-a6ba-ab1af9625fe4</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>6ab1584a-52cf-4a90-8728-3e22a7f66dd7</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1057" s="2" t="n">
+        <v>46066.69433133335</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>262</v>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1057" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>3f865194-6f41-4cf6-983d-c563f20415f9</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>74204722-d14c-46bf-8fa0-42eab3545795</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1058" s="2" t="n">
+        <v>46082.44433133992</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>163</v>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1058" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>b8011357-8986-4c5a-b332-ec24e923d9cc</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>7f2f8422-5e8c-49dd-a9e3-e483620e3ff9</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1059" s="2" t="n">
+        <v>46078.36099800983</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>269</v>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1059" t="n">
+        <v>16.16</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>e586ba66-e65c-4b79-82b9-0c8dfe0139b1</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>9c1fa475-84fb-4258-b083-4fb3b3dfd323</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1060" s="2" t="n">
+        <v>46069.94433135587</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>296</v>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1060" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>5c432696-aff0-43f7-a6d2-7d3055f86462</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>6c00cb31-8897-4ffa-b45c-f18f0e79bfa5</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1061" s="2" t="n">
+        <v>46092.27766469294</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>204</v>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1061" t="n">
+        <v>9.720000000000001</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>a29005f5-f577-4811-871c-db0eb75298d9</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>d4750d8c-f184-48ac-ae07-ce1fb50f74d8</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1062" s="2" t="n">
+        <v>46088.11099803892</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>146</v>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1062" t="n">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>635ed7bd-3359-46c0-b5de-4623b01f86e5</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>b03a3a0b-9b61-47da-b9e1-1b273b159df3</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1063" s="2" t="n">
+        <v>46065.27766471187</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1063" t="n">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>e955c326-b7f2-4969-a2a2-b5388719a243</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>de25645b-2f13-42a1-a421-3624e3c71735</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1064" s="2" t="n">
+        <v>46084.36099804864</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>241</v>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1064" t="n">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>94992b43-d4ed-4b12-88d5-a7d6f61f451a</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>ff42ebd4-b2f5-413a-90a0-55141e8e9e00</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1065" s="2" t="n">
+        <v>46068.19433138821</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1065" t="n">
+        <v>17.12</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1065"/>
+  <dimension ref="A1:I1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43346,7 +43346,7 @@
         </is>
       </c>
       <c r="E1047" s="2" t="n">
-        <v>46071.56933123962</v>
+        <v>46071.56933123842</v>
       </c>
       <c r="F1047" t="n">
         <v>242</v>
@@ -43387,7 +43387,7 @@
         </is>
       </c>
       <c r="E1048" s="2" t="n">
-        <v>46064.44433124316</v>
+        <v>46064.44433123842</v>
       </c>
       <c r="F1048" t="n">
         <v>254</v>
@@ -43428,7 +43428,7 @@
         </is>
       </c>
       <c r="E1049" s="2" t="n">
-        <v>46077.73599791306</v>
+        <v>46077.73599791666</v>
       </c>
       <c r="F1049" t="n">
         <v>132</v>
@@ -43469,7 +43469,7 @@
         </is>
       </c>
       <c r="E1050" s="2" t="n">
-        <v>46064.86099793624</v>
+        <v>46064.86099793982</v>
       </c>
       <c r="F1050" t="n">
         <v>268</v>
@@ -43510,7 +43510,7 @@
         </is>
       </c>
       <c r="E1051" s="2" t="n">
-        <v>46090.48599793966</v>
+        <v>46090.48599793982</v>
       </c>
       <c r="F1051" t="n">
         <v>249</v>
@@ -43551,7 +43551,7 @@
         </is>
       </c>
       <c r="E1052" s="2" t="n">
-        <v>46064.19433128539</v>
+        <v>46064.19433128472</v>
       </c>
       <c r="F1052" t="n">
         <v>266</v>
@@ -43592,7 +43592,7 @@
         </is>
       </c>
       <c r="E1053" s="2" t="n">
-        <v>46090.94433129056</v>
+        <v>46090.9443312963</v>
       </c>
       <c r="F1053" t="n">
         <v>273</v>
@@ -43633,7 +43633,7 @@
         </is>
       </c>
       <c r="E1054" s="2" t="n">
-        <v>46082.36099797378</v>
+        <v>46082.36099797454</v>
       </c>
       <c r="F1054" t="n">
         <v>296</v>
@@ -43674,7 +43674,7 @@
         </is>
       </c>
       <c r="E1055" s="2" t="n">
-        <v>46080.15266465023</v>
+        <v>46080.15266465278</v>
       </c>
       <c r="F1055" t="n">
         <v>282</v>
@@ -43715,7 +43715,7 @@
         </is>
       </c>
       <c r="E1056" s="2" t="n">
-        <v>46093.23599799361</v>
+        <v>46093.23599799768</v>
       </c>
       <c r="F1056" t="n">
         <v>202</v>
@@ -43756,7 +43756,7 @@
         </is>
       </c>
       <c r="E1057" s="2" t="n">
-        <v>46066.69433133335</v>
+        <v>46066.69433133102</v>
       </c>
       <c r="F1057" t="n">
         <v>262</v>
@@ -43797,7 +43797,7 @@
         </is>
       </c>
       <c r="E1058" s="2" t="n">
-        <v>46082.44433133992</v>
+        <v>46082.44433134259</v>
       </c>
       <c r="F1058" t="n">
         <v>163</v>
@@ -43838,7 +43838,7 @@
         </is>
       </c>
       <c r="E1059" s="2" t="n">
-        <v>46078.36099800983</v>
+        <v>46078.36099800926</v>
       </c>
       <c r="F1059" t="n">
         <v>269</v>
@@ -43879,7 +43879,7 @@
         </is>
       </c>
       <c r="E1060" s="2" t="n">
-        <v>46069.94433135587</v>
+        <v>46069.94433135416</v>
       </c>
       <c r="F1060" t="n">
         <v>296</v>
@@ -43920,7 +43920,7 @@
         </is>
       </c>
       <c r="E1061" s="2" t="n">
-        <v>46092.27766469294</v>
+        <v>46092.2776646875</v>
       </c>
       <c r="F1061" t="n">
         <v>204</v>
@@ -43961,7 +43961,7 @@
         </is>
       </c>
       <c r="E1062" s="2" t="n">
-        <v>46088.11099803892</v>
+        <v>46088.11099804398</v>
       </c>
       <c r="F1062" t="n">
         <v>146</v>
@@ -44002,7 +44002,7 @@
         </is>
       </c>
       <c r="E1063" s="2" t="n">
-        <v>46065.27766471187</v>
+        <v>46065.27766471065</v>
       </c>
       <c r="F1063" t="n">
         <v>229</v>
@@ -44043,7 +44043,7 @@
         </is>
       </c>
       <c r="E1064" s="2" t="n">
-        <v>46084.36099804864</v>
+        <v>46084.36099804398</v>
       </c>
       <c r="F1064" t="n">
         <v>241</v>
@@ -44084,7 +44084,7 @@
         </is>
       </c>
       <c r="E1065" s="2" t="n">
-        <v>46068.19433138821</v>
+        <v>46068.19433138889</v>
       </c>
       <c r="F1065" t="n">
         <v>186</v>
@@ -44101,6 +44101,990 @@
       </c>
       <c r="I1065" t="n">
         <v>17.12</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>af872b23-d5b9-4423-b3be-aae4623fd127</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>6192bea3-4ddc-4fc8-abe0-59cbc71690e9</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1066" s="2" t="n">
+        <v>46072.88758997415</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1066" t="n">
+        <v>14.06</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>dddb430f-1936-49ef-bd90-e1cea8f465be</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>fc4dfaf7-1abd-4e7a-bbf8-c46fdc3cb25b</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1067" s="2" t="n">
+        <v>46068.8459233108</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1067" t="n">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>7c7bf2d8-8c67-408c-a0d8-4ed54884ca75</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>4ae67f16-a297-4ba6-af7f-c8d8c114f7b3</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1068" s="2" t="n">
+        <v>46073.13758998416</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1068" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>073064a8-665f-4e84-8583-eb9ce507b0cd</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>5f0ed220-8b0b-4d31-a91c-f56c8391f119</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1069" s="2" t="n">
+        <v>46071.22092332714</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1069" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2eee2f3d-ce87-4b75-b4f7-c127e8f8ea5b</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>43cba866-b3bb-4042-8d3a-24c548f7bc25</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1070" s="2" t="n">
+        <v>46084.59592333037</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1070" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>955f62ba-1feb-477a-b01e-bbd7539e6018</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>d66e4228-c3cf-4275-8d69-fd2b4db2dd72</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1071" s="2" t="n">
+        <v>46087.80425666714</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>86</v>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1071" t="n">
+        <v>14.06</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>125bd11a-46c4-4152-9fbe-ccaa2f890060</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>7b8ec132-e23e-4d4d-89d2-2480ca758877</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1072" s="2" t="n">
+        <v>46082.76259000432</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>114</v>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1072" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2aa3db7e-4414-4205-b34b-1d651e97f7a5</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>09a391de-62fd-488c-837f-6cfec7a502b8</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1073" s="2" t="n">
+        <v>46071.47092334406</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1073" t="n">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>a374a106-9fa7-4193-95d2-d26e722e3574</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>5c1f7152-b159-4afd-af7b-2d78ea41587b</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1074" s="2" t="n">
+        <v>46081.17925668693</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>227</v>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1074" t="n">
+        <v>17.26</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>09876ff5-dfc6-45fc-b6eb-2e05ddf48bcb</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>799d9e95-165e-44f4-9b1b-d1e3e5bf7578</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1075" s="2" t="n">
+        <v>46064.84592335678</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>112</v>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1075" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>42da3881-d929-4dde-a1f6-858136371715</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>a5a45524-6c7b-4409-a3cf-36a88e40534c</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1076" s="2" t="n">
+        <v>46065.09592336323</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>66</v>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1076" t="n">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>ce74c4b0-1aa3-43a8-a411-890cec58e475</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>945623d9-e101-4f23-bd10-6f919fb79b7d</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1077" s="2" t="n">
+        <v>46071.80425670284</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>83</v>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1077" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>9cf5954e-bac5-44c8-ad6f-f764d56003c9</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>5ed48192-2205-48b9-a218-bd060a052e74</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1078" s="2" t="n">
+        <v>46090.80425670629</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1078" t="n">
+        <v>19.39</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>f60ff2e6-c44c-4cff-9359-ff47fad07ae2</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>540fc44f-32c1-4f76-bb00-c18abe42c900</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1079" s="2" t="n">
+        <v>46083.72092337926</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1079" t="n">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>ddb78a5a-6bd8-44fa-a0ce-08c19e954b4a</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>124f4c46-3bbe-442c-ba82-11fb3355e9b0</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1080" s="2" t="n">
+        <v>46086.8459233892</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>268</v>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1080" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>712fbf2a-ede5-4830-883d-19f8fa0ca150</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>fae01e61-84c4-4df6-8058-ab5f07f535e0</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1081" s="2" t="n">
+        <v>46079.72092339239</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1081" t="n">
+        <v>15.54</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>16844a21-f768-49ff-9160-f8926dd9146e</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>9d629e47-70c4-40b3-a57b-a80c8b5721a7</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1082" s="2" t="n">
+        <v>46063.26259006565</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>285</v>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1082" t="n">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>43e61065-6228-42df-81ba-499ba844ecd9</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>af3c6298-24a7-4f88-afe5-90300eb6ef8a</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1083" s="2" t="n">
+        <v>46069.88759007852</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>199</v>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1083" t="n">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>346ed7fd-ce7a-43af-9863-ca070522bcce</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>3b34d5b7-513f-423d-bae0-2762f8a792b2</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1084" s="2" t="n">
+        <v>46078.2209234151</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1084" t="n">
+        <v>14.94</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>4e9ed854-3b7a-4f7d-818e-cee1c4118079</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>6f33185c-593b-4fb8-9612-12ed3bb2b8f1</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1085" s="2" t="n">
+        <v>46066.88759008912</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1085" t="n">
+        <v>18.13</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>251d2b2a-f3ff-4ff8-9a7c-d62774ac5575</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>4afbfd3b-5826-489b-b098-e6252d03d0ec</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1086" s="2" t="n">
+        <v>46092.34592342562</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1086" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>0b523ea7-eb63-4ae0-b101-395d9bf6c2d6</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>53076464-881c-4d92-8d55-36bcb28f6dce</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1087" s="2" t="n">
+        <v>46068.8875901049</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1087" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>36bb433b-156a-4097-b873-3cd42f27d229</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>4d518828-6cb4-40c3-95ba-412c2d6103d7</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1088" s="2" t="n">
+        <v>46067.42925677798</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>68</v>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1088" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>31d3f6b7-2747-4803-a7c0-cc54a997dd26</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>23cab191-ab0b-42a0-8f0b-ffc383422454</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1089" s="2" t="n">
+        <v>46067.09592345436</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>97</v>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1089" t="n">
+        <v>11.81</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1089"/>
+  <dimension ref="A1:I1107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44125,7 +44125,7 @@
         </is>
       </c>
       <c r="E1066" s="2" t="n">
-        <v>46072.88758997415</v>
+        <v>46072.88758997685</v>
       </c>
       <c r="F1066" t="n">
         <v>239</v>
@@ -44166,7 +44166,7 @@
         </is>
       </c>
       <c r="E1067" s="2" t="n">
-        <v>46068.8459233108</v>
+        <v>46068.84592331018</v>
       </c>
       <c r="F1067" t="n">
         <v>74</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="E1068" s="2" t="n">
-        <v>46073.13758998416</v>
+        <v>46073.13758998842</v>
       </c>
       <c r="F1068" t="n">
         <v>99</v>
@@ -44248,7 +44248,7 @@
         </is>
       </c>
       <c r="E1069" s="2" t="n">
-        <v>46071.22092332714</v>
+        <v>46071.22092332176</v>
       </c>
       <c r="F1069" t="n">
         <v>206</v>
@@ -44289,7 +44289,7 @@
         </is>
       </c>
       <c r="E1070" s="2" t="n">
-        <v>46084.59592333037</v>
+        <v>46084.59592333333</v>
       </c>
       <c r="F1070" t="n">
         <v>50</v>
@@ -44330,7 +44330,7 @@
         </is>
       </c>
       <c r="E1071" s="2" t="n">
-        <v>46087.80425666714</v>
+        <v>46087.80425666667</v>
       </c>
       <c r="F1071" t="n">
         <v>86</v>
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="E1072" s="2" t="n">
-        <v>46082.76259000432</v>
+        <v>46082.76259</v>
       </c>
       <c r="F1072" t="n">
         <v>114</v>
@@ -44412,7 +44412,7 @@
         </is>
       </c>
       <c r="E1073" s="2" t="n">
-        <v>46071.47092334406</v>
+        <v>46071.47092334491</v>
       </c>
       <c r="F1073" t="n">
         <v>220</v>
@@ -44453,7 +44453,7 @@
         </is>
       </c>
       <c r="E1074" s="2" t="n">
-        <v>46081.17925668693</v>
+        <v>46081.17925668981</v>
       </c>
       <c r="F1074" t="n">
         <v>227</v>
@@ -44494,7 +44494,7 @@
         </is>
       </c>
       <c r="E1075" s="2" t="n">
-        <v>46064.84592335678</v>
+        <v>46064.84592335648</v>
       </c>
       <c r="F1075" t="n">
         <v>112</v>
@@ -44535,7 +44535,7 @@
         </is>
       </c>
       <c r="E1076" s="2" t="n">
-        <v>46065.09592336323</v>
+        <v>46065.09592336806</v>
       </c>
       <c r="F1076" t="n">
         <v>66</v>
@@ -44576,7 +44576,7 @@
         </is>
       </c>
       <c r="E1077" s="2" t="n">
-        <v>46071.80425670284</v>
+        <v>46071.80425670139</v>
       </c>
       <c r="F1077" t="n">
         <v>83</v>
@@ -44617,7 +44617,7 @@
         </is>
       </c>
       <c r="E1078" s="2" t="n">
-        <v>46090.80425670629</v>
+        <v>46090.80425670139</v>
       </c>
       <c r="F1078" t="n">
         <v>53</v>
@@ -44658,7 +44658,7 @@
         </is>
       </c>
       <c r="E1079" s="2" t="n">
-        <v>46083.72092337926</v>
+        <v>46083.72092337963</v>
       </c>
       <c r="F1079" t="n">
         <v>139</v>
@@ -44699,7 +44699,7 @@
         </is>
       </c>
       <c r="E1080" s="2" t="n">
-        <v>46086.8459233892</v>
+        <v>46086.84592339121</v>
       </c>
       <c r="F1080" t="n">
         <v>268</v>
@@ -44740,7 +44740,7 @@
         </is>
       </c>
       <c r="E1081" s="2" t="n">
-        <v>46079.72092339239</v>
+        <v>46079.72092339121</v>
       </c>
       <c r="F1081" t="n">
         <v>96</v>
@@ -44781,7 +44781,7 @@
         </is>
       </c>
       <c r="E1082" s="2" t="n">
-        <v>46063.26259006565</v>
+        <v>46063.26259006945</v>
       </c>
       <c r="F1082" t="n">
         <v>285</v>
@@ -44822,7 +44822,7 @@
         </is>
       </c>
       <c r="E1083" s="2" t="n">
-        <v>46069.88759007852</v>
+        <v>46069.88759008102</v>
       </c>
       <c r="F1083" t="n">
         <v>199</v>
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="E1084" s="2" t="n">
-        <v>46078.2209234151</v>
+        <v>46078.22092341435</v>
       </c>
       <c r="F1084" t="n">
         <v>298</v>
@@ -44904,7 +44904,7 @@
         </is>
       </c>
       <c r="E1085" s="2" t="n">
-        <v>46066.88759008912</v>
+        <v>46066.88759009259</v>
       </c>
       <c r="F1085" t="n">
         <v>73</v>
@@ -44945,7 +44945,7 @@
         </is>
       </c>
       <c r="E1086" s="2" t="n">
-        <v>46092.34592342562</v>
+        <v>46092.34592342593</v>
       </c>
       <c r="F1086" t="n">
         <v>89</v>
@@ -44986,7 +44986,7 @@
         </is>
       </c>
       <c r="E1087" s="2" t="n">
-        <v>46068.8875901049</v>
+        <v>46068.88759010417</v>
       </c>
       <c r="F1087" t="n">
         <v>44</v>
@@ -45027,7 +45027,7 @@
         </is>
       </c>
       <c r="E1088" s="2" t="n">
-        <v>46067.42925677798</v>
+        <v>46067.42925678241</v>
       </c>
       <c r="F1088" t="n">
         <v>68</v>
@@ -45068,7 +45068,7 @@
         </is>
       </c>
       <c r="E1089" s="2" t="n">
-        <v>46067.09592345436</v>
+        <v>46067.09592344907</v>
       </c>
       <c r="F1089" t="n">
         <v>97</v>
@@ -45085,6 +45085,744 @@
       </c>
       <c r="I1089" t="n">
         <v>11.81</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>81ab1bed-6d2f-40df-8d37-325e739381e8</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>928ed5d1-b0e7-4f2c-9bfc-12294fba56ad</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1090" s="2" t="n">
+        <v>46077.8720364043</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1090" t="n">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>01916968-80bd-4178-9651-3ed790592a7c</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>c56fd014-b749-4da6-b465-87044e352503</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1091" s="2" t="n">
+        <v>46070.49703641114</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>287</v>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1091" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>82b98224-57d6-407f-b5d0-9eceb85837c9</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>7c5c551d-01aa-40bc-b273-a6c7f92144cf</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1092" s="2" t="n">
+        <v>46086.41370309051</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>284</v>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1092" t="n">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>a885a54b-31e7-407c-b159-57397c315b60</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>781570b2-d6e6-4037-983d-625ae806fb0b</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1093" s="2" t="n">
+        <v>46064.28870309389</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>290</v>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1093" t="n">
+        <v>16.53</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>d0bc2896-a5f6-443c-9ad1-a5590e505d88</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>83a05272-437b-4b14-b0f9-c6330259aa2d</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1094" s="2" t="n">
+        <v>46085.37203643999</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1094" t="n">
+        <v>19.26</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>a5e439f3-b700-448f-a572-2296fabdc313</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>dfba0779-197d-4684-9084-927913a11f10</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1095" s="2" t="n">
+        <v>46085.70536977988</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1095" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>6f6e9992-4ce3-4dfe-8b49-2af84eda38ad</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>3ab32e90-3b7f-4fdc-932b-38af12d3b0d8</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1096" s="2" t="n">
+        <v>46068.53870311945</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>103</v>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1096" t="n">
+        <v>17.69</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>eec7709b-d715-4902-8082-983721a03a2b</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>c392ae6f-3101-4c00-84ca-396e1e9e1f8a</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1097" s="2" t="n">
+        <v>46063.41370312895</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>131</v>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1097" t="n">
+        <v>18.45</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>afbc6a61-308c-43a1-9135-7cc53632dca7</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>74f590ce-4674-4597-a20b-fd0b165cb6c7</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1098" s="2" t="n">
+        <v>46086.95536979898</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>242</v>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1098" t="n">
+        <v>17.41</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>dc1b2a74-e081-4b2c-aab6-524bbefff893</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>e3dc7b4d-4915-44dd-979c-df6000ea8cba</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1099" s="2" t="n">
+        <v>46092.95536980218</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1099" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>5d377e01-1c91-46b5-9c99-893a2d6c7327</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>e0392288-4ae9-4331-bec8-34c675b52581</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1100" s="2" t="n">
+        <v>46070.37203647836</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1100" t="n">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>81a131c3-9bc1-4e7c-a8f3-f8bddd85bf49</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>3a58f8f2-a80e-4c21-8030-58c9d8e6bbf8</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1101" s="2" t="n">
+        <v>46080.95536981494</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>243</v>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1101" t="n">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>913aa50a-5b45-448a-80bd-554bc606bbb2</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>27291940-5987-4051-a30d-18564541644a</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1102" s="2" t="n">
+        <v>46080.20536984898</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1102" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>91b34d5a-a270-4bb3-9078-77a9e9431d66</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>2c957a9a-27f3-49ee-bc54-8bfbaf0fdcb6</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1103" s="2" t="n">
+        <v>46085.03870318847</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1103" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>dae49b27-a10c-431c-8b96-14e695227872</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>d46a9c38-c914-42d8-8e8c-62f3b7ccf572</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1104" s="2" t="n">
+        <v>46067.58036986162</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1104" t="n">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>939dcbd3-1e33-4b9b-a925-77f5e0b298f2</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>07b2d4d8-b43e-440d-9e3f-a695dad70331</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1105" s="2" t="n">
+        <v>46067.87203653473</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>167</v>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1105" t="n">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>38a05344-4fb8-441f-ae78-db1a11a972dc</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>0a333125-a903-4096-af8a-ff93ed481ceb</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1106" s="2" t="n">
+        <v>46069.91370320765</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1106" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>723b795b-d46b-4b05-bcff-faad28cd304f</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>4b650b40-38c5-4836-bed9-6c240409408c</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1107" s="2" t="n">
+        <v>46093.3303698775</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>284</v>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1107" t="n">
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1107"/>
+  <dimension ref="A1:I1129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45109,7 +45109,7 @@
         </is>
       </c>
       <c r="E1090" s="2" t="n">
-        <v>46077.8720364043</v>
+        <v>46077.87203640046</v>
       </c>
       <c r="F1090" t="n">
         <v>176</v>
@@ -45150,7 +45150,7 @@
         </is>
       </c>
       <c r="E1091" s="2" t="n">
-        <v>46070.49703641114</v>
+        <v>46070.49703641204</v>
       </c>
       <c r="F1091" t="n">
         <v>287</v>
@@ -45191,7 +45191,7 @@
         </is>
       </c>
       <c r="E1092" s="2" t="n">
-        <v>46086.41370309051</v>
+        <v>46086.41370309028</v>
       </c>
       <c r="F1092" t="n">
         <v>284</v>
@@ -45232,7 +45232,7 @@
         </is>
       </c>
       <c r="E1093" s="2" t="n">
-        <v>46064.28870309389</v>
+        <v>46064.28870309028</v>
       </c>
       <c r="F1093" t="n">
         <v>290</v>
@@ -45273,7 +45273,7 @@
         </is>
       </c>
       <c r="E1094" s="2" t="n">
-        <v>46085.37203643999</v>
+        <v>46085.37203643518</v>
       </c>
       <c r="F1094" t="n">
         <v>124</v>
@@ -45314,7 +45314,7 @@
         </is>
       </c>
       <c r="E1095" s="2" t="n">
-        <v>46085.70536977988</v>
+        <v>46085.70536978009</v>
       </c>
       <c r="F1095" t="n">
         <v>62</v>
@@ -45355,7 +45355,7 @@
         </is>
       </c>
       <c r="E1096" s="2" t="n">
-        <v>46068.53870311945</v>
+        <v>46068.538703125</v>
       </c>
       <c r="F1096" t="n">
         <v>103</v>
@@ -45396,7 +45396,7 @@
         </is>
       </c>
       <c r="E1097" s="2" t="n">
-        <v>46063.41370312895</v>
+        <v>46063.413703125</v>
       </c>
       <c r="F1097" t="n">
         <v>131</v>
@@ -45437,7 +45437,7 @@
         </is>
       </c>
       <c r="E1098" s="2" t="n">
-        <v>46086.95536979898</v>
+        <v>46086.95536980324</v>
       </c>
       <c r="F1098" t="n">
         <v>242</v>
@@ -45478,7 +45478,7 @@
         </is>
       </c>
       <c r="E1099" s="2" t="n">
-        <v>46092.95536980218</v>
+        <v>46092.95536980324</v>
       </c>
       <c r="F1099" t="n">
         <v>212</v>
@@ -45519,7 +45519,7 @@
         </is>
       </c>
       <c r="E1100" s="2" t="n">
-        <v>46070.37203647836</v>
+        <v>46070.37203648148</v>
       </c>
       <c r="F1100" t="n">
         <v>102</v>
@@ -45560,7 +45560,7 @@
         </is>
       </c>
       <c r="E1101" s="2" t="n">
-        <v>46080.95536981494</v>
+        <v>46080.95536981482</v>
       </c>
       <c r="F1101" t="n">
         <v>243</v>
@@ -45601,7 +45601,7 @@
         </is>
       </c>
       <c r="E1102" s="2" t="n">
-        <v>46080.20536984898</v>
+        <v>46080.20536984954</v>
       </c>
       <c r="F1102" t="n">
         <v>31</v>
@@ -45642,7 +45642,7 @@
         </is>
       </c>
       <c r="E1103" s="2" t="n">
-        <v>46085.03870318847</v>
+        <v>46085.03870318287</v>
       </c>
       <c r="F1103" t="n">
         <v>31</v>
@@ -45683,7 +45683,7 @@
         </is>
       </c>
       <c r="E1104" s="2" t="n">
-        <v>46067.58036986162</v>
+        <v>46067.58036986111</v>
       </c>
       <c r="F1104" t="n">
         <v>62</v>
@@ -45724,7 +45724,7 @@
         </is>
       </c>
       <c r="E1105" s="2" t="n">
-        <v>46067.87203653473</v>
+        <v>46067.87203653935</v>
       </c>
       <c r="F1105" t="n">
         <v>167</v>
@@ -45765,7 +45765,7 @@
         </is>
       </c>
       <c r="E1106" s="2" t="n">
-        <v>46069.91370320765</v>
+        <v>46069.91370320602</v>
       </c>
       <c r="F1106" t="n">
         <v>62</v>
@@ -45806,7 +45806,7 @@
         </is>
       </c>
       <c r="E1107" s="2" t="n">
-        <v>46093.3303698775</v>
+        <v>46093.33036987269</v>
       </c>
       <c r="F1107" t="n">
         <v>284</v>
@@ -45823,6 +45823,908 @@
       </c>
       <c r="I1107" t="n">
         <v>13.96</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>0fa21737-8fef-4643-ae03-2e44636125be</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>7abc287e-dad9-48c0-b7b8-68e9d3c61ddc</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1108" s="2" t="n">
+        <v>46081.70661407271</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1108" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>cefb531e-6a6b-4d5c-ad7d-295f569a9bb9</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>5567d8fb-7248-48ce-a76c-0a0eebb3db22</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1109" s="2" t="n">
+        <v>46087.70661408664</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1109" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>53721e18-24c2-4e0b-951c-595e30255a9c</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>f375e5b3-d41a-4b5a-b9f6-fe22ea0bd479</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1110" s="2" t="n">
+        <v>46080.53994742639</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>275</v>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1110" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>c3b796b4-c3b7-4c33-bbd3-955fb0a4b65d</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>d167c051-5def-4f9f-9d21-b3fe733b2031</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1111" s="2" t="n">
+        <v>46083.99828076906</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1111" t="n">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>16d325cf-522d-41fa-9d4c-8020e8b921cd</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>c4cc8be3-e4e3-4d06-b70c-6133eb984846</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1112" s="2" t="n">
+        <v>46092.28994743925</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1112" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>504965a3-3edb-476e-9526-f91bd41ce167</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>ced1db52-4b63-4119-8272-123b9ec199dc</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1113" s="2" t="n">
+        <v>46094.83161412187</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>184</v>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1113" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>a697956a-ee71-4180-8432-ffe94f4befe0</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>66deac39-1980-4530-a3b5-6efe0ed67263</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1114" s="2" t="n">
+        <v>46094.53994745837</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1114" t="n">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>4509d4b7-f1e6-476d-a4f9-a333d780c9ba</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>97095476-8d43-474d-b21d-7d01b8207784</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1115" s="2" t="n">
+        <v>46071.6649474618</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1115" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>554ba030-a219-4f43-925e-8731fba02638</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>5e066322-514a-4169-9f0a-e0a2e2c76bcb</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1116" s="2" t="n">
+        <v>46082.2066141378</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>136</v>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1116" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2a820542-202a-4b57-9dd7-ab9358782338</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>b1484b0d-8a0d-4b91-81ff-ddf4fa333c7d</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1117" s="2" t="n">
+        <v>46079.4566141535</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1117" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>6c9c9b0f-7a84-4480-a34e-2f59b51538bb</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>8198ef9d-ad00-4223-bd99-6fe8539e401f</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1118" s="2" t="n">
+        <v>46067.53994749314</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1118" t="n">
+        <v>15.43</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>69452ff9-373f-4e90-bc83-7d55a5cf96ae</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>ddbc5b09-2ac9-4bad-82fb-53d5b5d8787e</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1119" s="2" t="n">
+        <v>46080.78994750293</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1119" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>8e1bf935-5b95-4232-8307-b811ab920548</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>52756081-e76b-4e9a-be15-d6ac1bfd4624</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1120" s="2" t="n">
+        <v>46074.74828084267</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>67</v>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1120" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>cdfb013c-49d1-40f8-9e64-1fd880a300c2</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>6fefad7d-cdb0-4076-b738-d9b3bae53f80</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1121" s="2" t="n">
+        <v>46076.37328085209</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>68</v>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1121" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>6e9f6be8-5b1f-410d-9233-59ff12471641</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>46917315-9ded-4d8c-9f2e-bc71f41caa82</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1122" s="2" t="n">
+        <v>46090.33161418857</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>255</v>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1122" t="n">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>d7e4d10e-7bae-49df-a508-e2af42ec4d66</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>d20638da-e8b8-433a-bebe-eea4053097f7</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1123" s="2" t="n">
+        <v>46089.41494752826</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>217</v>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1123" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>094283f7-89f7-42a3-b427-7437a3555cf4</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>95227093-7827-4b57-800e-8567978be55a</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1124" s="2" t="n">
+        <v>46067.7899475349</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>248</v>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1124" t="n">
+        <v>14.48</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>a792257a-237a-4f6f-a55c-b2724e06670e</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>903bc1bd-39b3-429a-880e-4ab5d6c83fcc</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1125" s="2" t="n">
+        <v>46091.83161420472</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>252</v>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1125" t="n">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>d41e130a-35d4-4f51-a1da-2472e1c80b71</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>f305358c-2d09-4946-967a-a40567005d64</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1126" s="2" t="n">
+        <v>46065.53994754479</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>179</v>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1126" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>43c872c7-eac9-47c7-a0f0-e9017c2f71a8</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>b55fd694-249b-43c5-8f48-0b4e795aa37e</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1127" s="2" t="n">
+        <v>46082.28994754823</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1127" t="n">
+        <v>11.88</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>60c7bdf6-0ae0-4909-adcb-749ed894b62c</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>a74a2acc-add3-4b76-b9ba-8b80bf35320f</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1128" s="2" t="n">
+        <v>46072.83161421804</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1128" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>aad4a530-2f46-4e9a-aef7-ff036fc8f5d5</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>dd9ed150-18e0-4b21-af58-e65963c3a181</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1129" s="2" t="n">
+        <v>46070.12328089122</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1129" t="n">
+        <v>15.26</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1129"/>
+  <dimension ref="A1:I1152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45847,7 +45847,7 @@
         </is>
       </c>
       <c r="E1108" s="2" t="n">
-        <v>46081.70661407271</v>
+        <v>46081.70661407407</v>
       </c>
       <c r="F1108" t="n">
         <v>107</v>
@@ -45888,7 +45888,7 @@
         </is>
       </c>
       <c r="E1109" s="2" t="n">
-        <v>46087.70661408664</v>
+        <v>46087.70661408565</v>
       </c>
       <c r="F1109" t="n">
         <v>110</v>
@@ -45929,7 +45929,7 @@
         </is>
       </c>
       <c r="E1110" s="2" t="n">
-        <v>46080.53994742639</v>
+        <v>46080.53994743055</v>
       </c>
       <c r="F1110" t="n">
         <v>275</v>
@@ -45970,7 +45970,7 @@
         </is>
       </c>
       <c r="E1111" s="2" t="n">
-        <v>46083.99828076906</v>
+        <v>46083.99828076389</v>
       </c>
       <c r="F1111" t="n">
         <v>272</v>
@@ -46011,7 +46011,7 @@
         </is>
       </c>
       <c r="E1112" s="2" t="n">
-        <v>46092.28994743925</v>
+        <v>46092.28994744213</v>
       </c>
       <c r="F1112" t="n">
         <v>61</v>
@@ -46052,7 +46052,7 @@
         </is>
       </c>
       <c r="E1113" s="2" t="n">
-        <v>46094.83161412187</v>
+        <v>46094.83161412037</v>
       </c>
       <c r="F1113" t="n">
         <v>184</v>
@@ -46093,7 +46093,7 @@
         </is>
       </c>
       <c r="E1114" s="2" t="n">
-        <v>46094.53994745837</v>
+        <v>46094.5399474537</v>
       </c>
       <c r="F1114" t="n">
         <v>161</v>
@@ -46134,7 +46134,7 @@
         </is>
       </c>
       <c r="E1115" s="2" t="n">
-        <v>46071.6649474618</v>
+        <v>46071.66494746528</v>
       </c>
       <c r="F1115" t="n">
         <v>77</v>
@@ -46175,7 +46175,7 @@
         </is>
       </c>
       <c r="E1116" s="2" t="n">
-        <v>46082.2066141378</v>
+        <v>46082.20661414352</v>
       </c>
       <c r="F1116" t="n">
         <v>136</v>
@@ -46216,7 +46216,7 @@
         </is>
       </c>
       <c r="E1117" s="2" t="n">
-        <v>46079.4566141535</v>
+        <v>46079.45661415509</v>
       </c>
       <c r="F1117" t="n">
         <v>203</v>
@@ -46257,7 +46257,7 @@
         </is>
       </c>
       <c r="E1118" s="2" t="n">
-        <v>46067.53994749314</v>
+        <v>46067.53994748843</v>
       </c>
       <c r="F1118" t="n">
         <v>54</v>
@@ -46298,7 +46298,7 @@
         </is>
       </c>
       <c r="E1119" s="2" t="n">
-        <v>46080.78994750293</v>
+        <v>46080.7899475</v>
       </c>
       <c r="F1119" t="n">
         <v>150</v>
@@ -46339,7 +46339,7 @@
         </is>
       </c>
       <c r="E1120" s="2" t="n">
-        <v>46074.74828084267</v>
+        <v>46074.74828084491</v>
       </c>
       <c r="F1120" t="n">
         <v>67</v>
@@ -46380,7 +46380,7 @@
         </is>
       </c>
       <c r="E1121" s="2" t="n">
-        <v>46076.37328085209</v>
+        <v>46076.37328085648</v>
       </c>
       <c r="F1121" t="n">
         <v>68</v>
@@ -46421,7 +46421,7 @@
         </is>
       </c>
       <c r="E1122" s="2" t="n">
-        <v>46090.33161418857</v>
+        <v>46090.33161418982</v>
       </c>
       <c r="F1122" t="n">
         <v>255</v>
@@ -46462,7 +46462,7 @@
         </is>
       </c>
       <c r="E1123" s="2" t="n">
-        <v>46089.41494752826</v>
+        <v>46089.41494752315</v>
       </c>
       <c r="F1123" t="n">
         <v>217</v>
@@ -46503,7 +46503,7 @@
         </is>
       </c>
       <c r="E1124" s="2" t="n">
-        <v>46067.7899475349</v>
+        <v>46067.78994753472</v>
       </c>
       <c r="F1124" t="n">
         <v>248</v>
@@ -46544,7 +46544,7 @@
         </is>
       </c>
       <c r="E1125" s="2" t="n">
-        <v>46091.83161420472</v>
+        <v>46091.83161420139</v>
       </c>
       <c r="F1125" t="n">
         <v>252</v>
@@ -46585,7 +46585,7 @@
         </is>
       </c>
       <c r="E1126" s="2" t="n">
-        <v>46065.53994754479</v>
+        <v>46065.5399475463</v>
       </c>
       <c r="F1126" t="n">
         <v>179</v>
@@ -46626,7 +46626,7 @@
         </is>
       </c>
       <c r="E1127" s="2" t="n">
-        <v>46082.28994754823</v>
+        <v>46082.2899475463</v>
       </c>
       <c r="F1127" t="n">
         <v>107</v>
@@ -46667,7 +46667,7 @@
         </is>
       </c>
       <c r="E1128" s="2" t="n">
-        <v>46072.83161421804</v>
+        <v>46072.83161421296</v>
       </c>
       <c r="F1128" t="n">
         <v>90</v>
@@ -46708,7 +46708,7 @@
         </is>
       </c>
       <c r="E1129" s="2" t="n">
-        <v>46070.12328089122</v>
+        <v>46070.1232808912</v>
       </c>
       <c r="F1129" t="n">
         <v>118</v>
@@ -46725,6 +46725,949 @@
       </c>
       <c r="I1129" t="n">
         <v>15.26</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>f2800379-d944-44ef-8a3b-6e5f08da483b</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>1165ec9b-be5f-44db-98a1-ba9371e27432</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1130" s="2" t="n">
+        <v>46064.46121908358</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>131</v>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1130" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>c97bf412-d029-456b-b40a-b26b165a743b</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>e95bb4e2-6e85-4d60-b0da-899ba250a9df</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1131" s="2" t="n">
+        <v>46070.0445524234</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1131" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>598bb6ee-1389-49de-8544-dc88f153b9af</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>95c46b29-e5ee-4fc8-9367-4f3aad0309f5</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1132" s="2" t="n">
+        <v>46082.21121909362</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>144</v>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1132" t="n">
+        <v>17.44</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>a4cbac68-e2d0-4aba-bd01-56f761bc4bd5</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>f2493090-5882-4d00-9109-6a371a84b8f8</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1133" s="2" t="n">
+        <v>46077.29455243028</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1133" t="n">
+        <v>11.84</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>63c9c0bf-bdd8-4269-a9ac-adc8e6cef532</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>5e25c0bd-de9c-41a3-a578-fdcfe98ff45a</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1134" s="2" t="n">
+        <v>46065.33621910017</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1134" t="n">
+        <v>9.02</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>98315692-7c11-4c1c-860e-3d4b2068c769</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>79065d73-73bd-4aa8-b2a2-5c7b7bf979ec</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1135" s="2" t="n">
+        <v>46089.0445524368</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>207</v>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1135" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>e1f38474-1eef-4d7b-8770-423e3bd353e9</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>248674de-e341-46dc-bde6-df6cff3e80a6</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1136" s="2" t="n">
+        <v>46091.12788578675</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1136" t="n">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>c6a3afe4-2eee-4773-b3a5-0a22c673833b</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>c8d3b2e5-420d-4f8b-bff1-31fa7509fa77</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1137" s="2" t="n">
+        <v>46069.96121912999</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>254</v>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1137" t="n">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>b8e5c499-8a57-4c1d-b13e-2f8dd9882a69</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>b717ca32-c555-4628-8b51-6cff2c90c08c</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1138" s="2" t="n">
+        <v>46088.6278857999</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>247</v>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1138" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>ee19c194-d544-4268-92fe-8957a6707176</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>4e1783fe-fca4-47b3-89da-8adb249a3c8e</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1139" s="2" t="n">
+        <v>46072.33621914298</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>299</v>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1139" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>0ccb8d84-47f8-4e41-84ba-8bdfd6c409cb</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>f3fce761-769f-4fbf-a75a-417f667222e9</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1140" s="2" t="n">
+        <v>46065.54455247954</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>286</v>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1140" t="n">
+        <v>17.38</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>7fb4055a-a62d-40cf-82a5-274f46f606c5</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>0f7fcc7b-98e8-4ebe-a70a-955c4c9a3554</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1141" s="2" t="n">
+        <v>46088.79455249562</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1141" t="n">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>bd1ad3c6-d30e-433f-b3e0-5aa978b07a5b</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>43980dfb-96f5-4b0b-8101-ebcd96953a53</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1142" s="2" t="n">
+        <v>46089.08621919421</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1142" t="n">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>ee7fd7b6-f0ab-434e-89c2-95e4cfb22358</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>d867a737-d9d7-4298-9ca8-5a40e100e7f8</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1143" s="2" t="n">
+        <v>46074.25288586756</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1143" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2141e0f8-b3fe-4fec-b8c6-35b285f5eddb</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>cd064638-7414-41c9-a298-54d3dc28fcc0</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1144" s="2" t="n">
+        <v>46091.50288587385</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>269</v>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1144" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>acc98f39-0f14-49d4-a3dd-f756ca276854</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>860bcb5d-12f6-4fd7-b9b7-3bdff03a5c23</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1145" s="2" t="n">
+        <v>46085.08621921075</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1145" t="n">
+        <v>19.43</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>368872d9-6369-4cc8-b004-1dc875e59a8e</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>8f0e9be4-bd70-42b4-87d1-ccd2d150eb59</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1146" s="2" t="n">
+        <v>46074.50288588063</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>256</v>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1146" t="n">
+        <v>14.78</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>729c5d74-ba9e-4091-bb61-b325e03bcc73</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>526d9d0a-bff6-41d6-9a58-6de5b030909a</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1147" s="2" t="n">
+        <v>46065.00288588392</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1147" t="n">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>207cf69c-dfec-4b28-907e-4e253d10459b</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>aab5a3b2-fdec-449b-9633-7270302cd2d9</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1148" s="2" t="n">
+        <v>46076.62788588744</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>189</v>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1148" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>9760eb3b-3108-416a-8bf6-c254e5ec5ead</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>39faa04a-b038-4fd5-8d2a-b42dbdad65f2</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1149" s="2" t="n">
+        <v>46088.25288589073</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1149" t="n">
+        <v>18.22</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>0f601613-c146-4908-a34f-9a7a4184e9d9</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>da70f950-8ebb-470c-946a-00e5e0809122</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1150" s="2" t="n">
+        <v>46077.54455256057</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1150" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>b056bf95-66f8-421f-b7d2-6904f4ac3eca</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>d65773ca-7539-4181-aa24-9b07ba568ced</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1151" s="2" t="n">
+        <v>46067.58621923042</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>159</v>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1151" t="n">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>4a856853-7632-4d07-9987-5370801257c6</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>230be6fa-6dd0-4370-b5c5-24495c9d25a5</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1152" s="2" t="n">
+        <v>46083.8362192338</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1152" t="n">
+        <v>18.35</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1152"/>
+  <dimension ref="A1:I1174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46749,7 +46749,7 @@
         </is>
       </c>
       <c r="E1130" s="2" t="n">
-        <v>46064.46121908358</v>
+        <v>46064.46121908565</v>
       </c>
       <c r="F1130" t="n">
         <v>131</v>
@@ -46790,7 +46790,7 @@
         </is>
       </c>
       <c r="E1131" s="2" t="n">
-        <v>46070.0445524234</v>
+        <v>46070.04455241898</v>
       </c>
       <c r="F1131" t="n">
         <v>111</v>
@@ -46831,7 +46831,7 @@
         </is>
       </c>
       <c r="E1132" s="2" t="n">
-        <v>46082.21121909362</v>
+        <v>46082.21121909723</v>
       </c>
       <c r="F1132" t="n">
         <v>144</v>
@@ -46872,7 +46872,7 @@
         </is>
       </c>
       <c r="E1133" s="2" t="n">
-        <v>46077.29455243028</v>
+        <v>46077.29455243055</v>
       </c>
       <c r="F1133" t="n">
         <v>220</v>
@@ -46913,7 +46913,7 @@
         </is>
       </c>
       <c r="E1134" s="2" t="n">
-        <v>46065.33621910017</v>
+        <v>46065.33621909723</v>
       </c>
       <c r="F1134" t="n">
         <v>200</v>
@@ -46954,7 +46954,7 @@
         </is>
       </c>
       <c r="E1135" s="2" t="n">
-        <v>46089.0445524368</v>
+        <v>46089.04455244213</v>
       </c>
       <c r="F1135" t="n">
         <v>207</v>
@@ -46995,7 +46995,7 @@
         </is>
       </c>
       <c r="E1136" s="2" t="n">
-        <v>46091.12788578675</v>
+        <v>46091.12788578703</v>
       </c>
       <c r="F1136" t="n">
         <v>229</v>
@@ -47036,7 +47036,7 @@
         </is>
       </c>
       <c r="E1137" s="2" t="n">
-        <v>46069.96121912999</v>
+        <v>46069.96121913195</v>
       </c>
       <c r="F1137" t="n">
         <v>254</v>
@@ -47077,7 +47077,7 @@
         </is>
       </c>
       <c r="E1138" s="2" t="n">
-        <v>46088.6278857999</v>
+        <v>46088.62788579861</v>
       </c>
       <c r="F1138" t="n">
         <v>247</v>
@@ -47118,7 +47118,7 @@
         </is>
       </c>
       <c r="E1139" s="2" t="n">
-        <v>46072.33621914298</v>
+        <v>46072.33621914352</v>
       </c>
       <c r="F1139" t="n">
         <v>299</v>
@@ -47159,7 +47159,7 @@
         </is>
       </c>
       <c r="E1140" s="2" t="n">
-        <v>46065.54455247954</v>
+        <v>46065.54455247685</v>
       </c>
       <c r="F1140" t="n">
         <v>286</v>
@@ -47200,7 +47200,7 @@
         </is>
       </c>
       <c r="E1141" s="2" t="n">
-        <v>46088.79455249562</v>
+        <v>46088.7945525</v>
       </c>
       <c r="F1141" t="n">
         <v>39</v>
@@ -47241,7 +47241,7 @@
         </is>
       </c>
       <c r="E1142" s="2" t="n">
-        <v>46089.08621919421</v>
+        <v>46089.08621918981</v>
       </c>
       <c r="F1142" t="n">
         <v>102</v>
@@ -47282,7 +47282,7 @@
         </is>
       </c>
       <c r="E1143" s="2" t="n">
-        <v>46074.25288586756</v>
+        <v>46074.25288586805</v>
       </c>
       <c r="F1143" t="n">
         <v>212</v>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="E1144" s="2" t="n">
-        <v>46091.50288587385</v>
+        <v>46091.50288587963</v>
       </c>
       <c r="F1144" t="n">
         <v>269</v>
@@ -47364,7 +47364,7 @@
         </is>
       </c>
       <c r="E1145" s="2" t="n">
-        <v>46085.08621921075</v>
+        <v>46085.08621921296</v>
       </c>
       <c r="F1145" t="n">
         <v>214</v>
@@ -47405,7 +47405,7 @@
         </is>
       </c>
       <c r="E1146" s="2" t="n">
-        <v>46074.50288588063</v>
+        <v>46074.50288587963</v>
       </c>
       <c r="F1146" t="n">
         <v>256</v>
@@ -47446,7 +47446,7 @@
         </is>
       </c>
       <c r="E1147" s="2" t="n">
-        <v>46065.00288588392</v>
+        <v>46065.00288587963</v>
       </c>
       <c r="F1147" t="n">
         <v>81</v>
@@ -47487,7 +47487,7 @@
         </is>
       </c>
       <c r="E1148" s="2" t="n">
-        <v>46076.62788588744</v>
+        <v>46076.6278858912</v>
       </c>
       <c r="F1148" t="n">
         <v>189</v>
@@ -47528,7 +47528,7 @@
         </is>
       </c>
       <c r="E1149" s="2" t="n">
-        <v>46088.25288589073</v>
+        <v>46088.2528858912</v>
       </c>
       <c r="F1149" t="n">
         <v>298</v>
@@ -47569,7 +47569,7 @@
         </is>
       </c>
       <c r="E1150" s="2" t="n">
-        <v>46077.54455256057</v>
+        <v>46077.54455255787</v>
       </c>
       <c r="F1150" t="n">
         <v>214</v>
@@ -47610,7 +47610,7 @@
         </is>
       </c>
       <c r="E1151" s="2" t="n">
-        <v>46067.58621923042</v>
+        <v>46067.58621923611</v>
       </c>
       <c r="F1151" t="n">
         <v>159</v>
@@ -47651,7 +47651,7 @@
         </is>
       </c>
       <c r="E1152" s="2" t="n">
-        <v>46083.8362192338</v>
+        <v>46083.83621923611</v>
       </c>
       <c r="F1152" t="n">
         <v>203</v>
@@ -47668,6 +47668,908 @@
       </c>
       <c r="I1152" t="n">
         <v>18.35</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>13747bfa-f051-415a-8e69-f7848e592b5b</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>0f8bfeb6-86f0-4ebe-873a-68f58cd22cd7</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1153" s="2" t="n">
+        <v>46087.75224205069</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1153" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>e6fff83d-c808-4d8d-b039-0b2792a47843</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>a1c93576-e30b-4290-a1c5-edb0c5b41301</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1154" s="2" t="n">
+        <v>46089.37724205502</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>295</v>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1154" t="n">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>7c59c754-91fa-4b4b-8f2d-45e5a197eb3f</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>666a1cda-4cd0-4b26-bd51-eda2084b35bd</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1155" s="2" t="n">
+        <v>46063.50224206178</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>142</v>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1155" t="n">
+        <v>12.21</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>494b69f7-9e3b-453f-ac76-df0d6c73ad8b</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>1e63b43e-d3fc-47cb-b17b-af333ece5d9e</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1156" s="2" t="n">
+        <v>46070.12724206501</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>159</v>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1156" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2f238dc3-a576-419c-8368-1b5163a948b7</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>e493cbe2-4e59-4693-8b61-2aea7448a9cf</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1157" s="2" t="n">
+        <v>46090.54390873826</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1157" t="n">
+        <v>16.29</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>879a8ea7-0796-4664-8891-c1daf0d6ff14</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>da888965-bae3-4731-bfad-7bb2aeb4ca8f</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1158" s="2" t="n">
+        <v>46076.04390876108</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1158" t="n">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>e5612177-f798-47b6-af40-959123aff821</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>d3661327-d656-49f5-8e39-88c629565ed7</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1159" s="2" t="n">
+        <v>46067.6689087643</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>177</v>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1159" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>5e09d015-e75c-4aa8-8db6-0a32b87ab87c</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>0a75f7e6-cca9-42a1-8584-32fa4430dde4</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1160" s="2" t="n">
+        <v>46093.75224210083</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1160" t="n">
+        <v>17.96</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>ecdb06f5-74ab-4eaa-9eb8-a253b2b93506</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>718ee365-1a0c-4696-94f6-e424d43371aa</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1161" s="2" t="n">
+        <v>46079.293908771</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>270</v>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1161" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>d99490e8-a833-4bf5-b4b8-5bb2a678d97e</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>a2673d2a-74a1-4bee-ba79-e3e5d2d75798</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1162" s="2" t="n">
+        <v>46084.08557544698</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>65</v>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1162" t="n">
+        <v>10.77</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>1b60f115-6739-4e0f-86bd-10a678752c4e</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>9ce8a0b4-6311-491b-bb2a-219f11e43c32</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1163" s="2" t="n">
+        <v>46072.08557545977</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1163" t="n">
+        <v>19.92</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>25b86073-329e-4587-be25-79aac26f2755</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>36e9cbc2-37ad-46ae-bf93-3246e58ef27b</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1164" s="2" t="n">
+        <v>46082.58557546917</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1164" t="n">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>8e5595f4-25d4-4c40-92f9-1af35db7ae5c</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>f2316e90-f10c-4f58-a576-a467c7a3ba5e</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1165" s="2" t="n">
+        <v>46085.21057547606</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1165" t="n">
+        <v>18.41</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>3104add7-953f-457b-bc06-25065dae695d</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>d0ac3878-15ce-4e45-aca9-1cbae32eceb7</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1166" s="2" t="n">
+        <v>46069.1272421561</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>196</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1166" t="n">
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>32bc8e75-5ff8-48ad-a3b8-0b856c57f833</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>30468a0c-b3a3-47c6-ac56-d1bf9104611f</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1167" s="2" t="n">
+        <v>46080.12724216878</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1167" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>295d061e-caa2-4cce-93bc-71a3805c5ffa</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>72aaf7f9-6965-4ca3-a4d8-6bca81ac1a4b</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1168" s="2" t="n">
+        <v>46073.75224217217</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>261</v>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1168" t="n">
+        <v>18.29</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>76f70399-cd41-414b-807f-0c8108641501</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>e43707cb-5a6c-4537-8e67-5c7805517578</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1169" s="2" t="n">
+        <v>46079.41890884202</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1169" t="n">
+        <v>8.710000000000001</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>8fcce01b-2659-472e-ac86-215d6c65cd5c</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>f62a2bbd-2287-45f3-8d6d-ddc5e44e2bde</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1170" s="2" t="n">
+        <v>46073.1272421816</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>115</v>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1170" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>c609c869-7a39-46c7-a972-a15b9e6d831f</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>6f905eb2-3cd9-4f05-b61c-18ae33fc149d</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1171" s="2" t="n">
+        <v>46073.25224219112</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1171" t="n">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>dea9b727-ac82-49ed-837f-24af4ab0a1a0</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>3914796b-fdfb-4e5b-85b9-20213ce77a81</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1172" s="2" t="n">
+        <v>46093.41890886442</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>226</v>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1172" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>e10e1865-4bf0-4632-b6f7-f7266fb06e9e</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>493c577c-dabb-40b9-9ee0-3bce2e0fe2d0</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1173" s="2" t="n">
+        <v>46091.91890886763</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>291</v>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1173" t="n">
+        <v>11.19</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>efb3b819-7a0d-48b3-8372-53cd7fe3f536</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>7763bd06-5199-4238-bb90-4c3e4d934c63</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1174" s="2" t="n">
+        <v>46088.29390887092</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>179</v>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1174" t="n">
+        <v>11.61</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1174"/>
+  <dimension ref="A1:I1199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47692,7 +47692,7 @@
         </is>
       </c>
       <c r="E1153" s="2" t="n">
-        <v>46087.75224205069</v>
+        <v>46087.75224204861</v>
       </c>
       <c r="F1153" t="n">
         <v>93</v>
@@ -47733,7 +47733,7 @@
         </is>
       </c>
       <c r="E1154" s="2" t="n">
-        <v>46089.37724205502</v>
+        <v>46089.37724206018</v>
       </c>
       <c r="F1154" t="n">
         <v>295</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="E1155" s="2" t="n">
-        <v>46063.50224206178</v>
+        <v>46063.50224206018</v>
       </c>
       <c r="F1155" t="n">
         <v>142</v>
@@ -47815,7 +47815,7 @@
         </is>
       </c>
       <c r="E1156" s="2" t="n">
-        <v>46070.12724206501</v>
+        <v>46070.12724206018</v>
       </c>
       <c r="F1156" t="n">
         <v>159</v>
@@ -47856,7 +47856,7 @@
         </is>
       </c>
       <c r="E1157" s="2" t="n">
-        <v>46090.54390873826</v>
+        <v>46090.54390873843</v>
       </c>
       <c r="F1157" t="n">
         <v>57</v>
@@ -47897,7 +47897,7 @@
         </is>
       </c>
       <c r="E1158" s="2" t="n">
-        <v>46076.04390876108</v>
+        <v>46076.04390876157</v>
       </c>
       <c r="F1158" t="n">
         <v>139</v>
@@ -47938,7 +47938,7 @@
         </is>
       </c>
       <c r="E1159" s="2" t="n">
-        <v>46067.6689087643</v>
+        <v>46067.66890876157</v>
       </c>
       <c r="F1159" t="n">
         <v>177</v>
@@ -47979,7 +47979,7 @@
         </is>
       </c>
       <c r="E1160" s="2" t="n">
-        <v>46093.75224210083</v>
+        <v>46093.75224210648</v>
       </c>
       <c r="F1160" t="n">
         <v>110</v>
@@ -48020,7 +48020,7 @@
         </is>
       </c>
       <c r="E1161" s="2" t="n">
-        <v>46079.293908771</v>
+        <v>46079.29390877315</v>
       </c>
       <c r="F1161" t="n">
         <v>270</v>
@@ -48061,7 +48061,7 @@
         </is>
       </c>
       <c r="E1162" s="2" t="n">
-        <v>46084.08557544698</v>
+        <v>46084.08557545139</v>
       </c>
       <c r="F1162" t="n">
         <v>65</v>
@@ -48102,7 +48102,7 @@
         </is>
       </c>
       <c r="E1163" s="2" t="n">
-        <v>46072.08557545977</v>
+        <v>46072.08557546297</v>
       </c>
       <c r="F1163" t="n">
         <v>298</v>
@@ -48143,7 +48143,7 @@
         </is>
       </c>
       <c r="E1164" s="2" t="n">
-        <v>46082.58557546917</v>
+        <v>46082.58557547454</v>
       </c>
       <c r="F1164" t="n">
         <v>53</v>
@@ -48184,7 +48184,7 @@
         </is>
       </c>
       <c r="E1165" s="2" t="n">
-        <v>46085.21057547606</v>
+        <v>46085.21057547454</v>
       </c>
       <c r="F1165" t="n">
         <v>229</v>
@@ -48225,7 +48225,7 @@
         </is>
       </c>
       <c r="E1166" s="2" t="n">
-        <v>46069.1272421561</v>
+        <v>46069.12724215278</v>
       </c>
       <c r="F1166" t="n">
         <v>196</v>
@@ -48266,7 +48266,7 @@
         </is>
       </c>
       <c r="E1167" s="2" t="n">
-        <v>46080.12724216878</v>
+        <v>46080.12724216435</v>
       </c>
       <c r="F1167" t="n">
         <v>38</v>
@@ -48307,7 +48307,7 @@
         </is>
       </c>
       <c r="E1168" s="2" t="n">
-        <v>46073.75224217217</v>
+        <v>46073.75224217593</v>
       </c>
       <c r="F1168" t="n">
         <v>261</v>
@@ -48348,7 +48348,7 @@
         </is>
       </c>
       <c r="E1169" s="2" t="n">
-        <v>46079.41890884202</v>
+        <v>46079.41890884259</v>
       </c>
       <c r="F1169" t="n">
         <v>214</v>
@@ -48389,7 +48389,7 @@
         </is>
       </c>
       <c r="E1170" s="2" t="n">
-        <v>46073.1272421816</v>
+        <v>46073.12724217593</v>
       </c>
       <c r="F1170" t="n">
         <v>115</v>
@@ -48430,7 +48430,7 @@
         </is>
       </c>
       <c r="E1171" s="2" t="n">
-        <v>46073.25224219112</v>
+        <v>46073.2522421875</v>
       </c>
       <c r="F1171" t="n">
         <v>39</v>
@@ -48471,7 +48471,7 @@
         </is>
       </c>
       <c r="E1172" s="2" t="n">
-        <v>46093.41890886442</v>
+        <v>46093.41890886574</v>
       </c>
       <c r="F1172" t="n">
         <v>226</v>
@@ -48512,7 +48512,7 @@
         </is>
       </c>
       <c r="E1173" s="2" t="n">
-        <v>46091.91890886763</v>
+        <v>46091.91890886574</v>
       </c>
       <c r="F1173" t="n">
         <v>291</v>
@@ -48553,7 +48553,7 @@
         </is>
       </c>
       <c r="E1174" s="2" t="n">
-        <v>46088.29390887092</v>
+        <v>46088.29390886574</v>
       </c>
       <c r="F1174" t="n">
         <v>179</v>
@@ -48570,6 +48570,1031 @@
       </c>
       <c r="I1174" t="n">
         <v>11.61</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>c3f5c780-b600-46c4-bdef-269c6d4c1884</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>8c2f189c-fc32-4833-81f1-f29dc0168770</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1175" s="2" t="n">
+        <v>46072.82038569958</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1175" t="n">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>f9d96a39-a995-4272-afc9-4c916e1fead1</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>b50218bd-db22-4e2c-91d5-84e03bda9622</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1176" s="2" t="n">
+        <v>46090.61205237433</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>197</v>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1176" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>6c22ad06-2190-4e99-8894-4045977d2223</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>9851acbd-0906-46b5-906b-24dbe14dfc52</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1177" s="2" t="n">
+        <v>46074.02871904743</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1177" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>5958470a-163b-4a5f-a30e-da6468599531</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>ac75041a-90cc-407a-99bb-028ee1ee4db5</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1178" s="2" t="n">
+        <v>46078.02871905406</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>240</v>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1178" t="n">
+        <v>18.06</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>806e1717-58c3-4e43-b263-5107065ae816</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>b090d8f4-197b-45aa-afb6-3dac76a67bf2</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1179" s="2" t="n">
+        <v>46070.65371906035</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1179" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>40a8d33c-ad95-48e4-8b84-c9b5562e2ac0</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>fd8e4983-0f25-425f-bd00-5af9af3bcc12</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1180" s="2" t="n">
+        <v>46072.82038573387</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1180" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2d62c41e-d2a6-40bb-9e29-a173526748a5</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>801a53c3-12c2-48d1-9308-a44cee82edfc</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1181" s="2" t="n">
+        <v>46083.48705241014</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1181" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>3e483cf1-fbb4-4fd7-830e-f49d2727264e</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>d270c12b-3495-4bbf-a4af-5ae6bf9b2193</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1182" s="2" t="n">
+        <v>46078.2370524319</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>253</v>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1182" t="n">
+        <v>16.26</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>a0dd418f-f209-4047-8bae-a0ce6a6f54c8</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>4b9d037f-c5e3-466a-9129-bcaf905ff2ac</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1183" s="2" t="n">
+        <v>46089.02871910484</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1183" t="n">
+        <v>10.79</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>97cb124d-36ce-40d6-a589-bb9b8aab8bf1</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>56bb9a74-4ce8-4742-a864-3a81d8a1748e</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1184" s="2" t="n">
+        <v>46081.52871910795</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1184" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>c22b8354-84bc-4fc3-8a2e-f9d66b0fa4dd</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>e3323080-b9ea-4507-b289-060fe40727fb</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1185" s="2" t="n">
+        <v>46081.48705244464</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1185" t="n">
+        <v>18.41</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>74e399c6-cabe-4d79-bd4e-0a2117196a23</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>a013b7f4-0fba-4024-a385-10a4045b048f</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1186" s="2" t="n">
+        <v>46081.48705245096</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>174</v>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1186" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>0deda5d7-37bf-4347-9b8f-10184fd7b220</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>908f8c52-27d7-4362-9975-31747a09891a</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1187" s="2" t="n">
+        <v>46081.82038578764</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>228</v>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1187" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>164aaee5-d6d8-491d-b7b6-ac47f4854d46</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>97dd0f01-f644-4840-8568-5a463d57ac8b</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1188" s="2" t="n">
+        <v>46086.9037191273</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1188" t="n">
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>421c6958-54b0-477b-9858-c0bc0591fee6</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>88e30b56-3fa6-4a4c-b29d-09b6b0043370</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1189" s="2" t="n">
+        <v>46065.9037191369</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1189" t="n">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>3f8d9dca-be30-4d52-a926-c32b121dca04</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>91d6f324-fa5c-4836-b0cb-13a25205732e</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1190" s="2" t="n">
+        <v>46064.15371914008</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1190" t="n">
+        <v>19.58</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>b88501d7-3ae6-432b-b43f-e8b9f2ec45c7</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>3e631c22-5ca5-4aff-ab29-b5082a847457</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1191" s="2" t="n">
+        <v>46069.36205247672</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1191" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>3821cee3-2cd8-4828-8fcc-8466e8075c08</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>c4b36bab-fd88-4dbd-b952-e9b259e91489</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1192" s="2" t="n">
+        <v>46087.3620524829</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1192" t="n">
+        <v>15.81</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>f34c1c39-e159-46a6-9987-8cc1f6450c04</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>49bf5a20-e167-4039-a9ac-7c255315f4d1</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1193" s="2" t="n">
+        <v>46067.82038582257</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>231</v>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1193" t="n">
+        <v>19.66</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>aabe37ea-2a96-49c4-b055-33468aa40739</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>d4c0a2f3-53f1-4809-8143-e3bdc3597b8a</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1194" s="2" t="n">
+        <v>46092.77871915904</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>154</v>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1194" t="n">
+        <v>10.11</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>82cf344f-c9ca-4156-8e40-4204f4997d43</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>26f4b197-9af3-4827-908a-1af9df5e36ae</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1195" s="2" t="n">
+        <v>46083.98705250181</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>122</v>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1195" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>bdc7670e-0ab4-490d-b58d-89cddccae27d</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>ebc55034-484c-48b7-8524-dd9542fc5f81</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1196" s="2" t="n">
+        <v>46083.11205250496</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>279</v>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1196" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>622265a0-d291-4de5-b6e7-5b943f2e7937</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>452e00fe-7343-4e8d-a89f-06e4f2e084c9</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1197" s="2" t="n">
+        <v>46075.69538584768</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1197" t="n">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>eb78c85d-12e0-48a8-a3d5-04c94b0aa7d8</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>3e676c3c-0c49-49c0-b7a8-8f478851a3be</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1198" s="2" t="n">
+        <v>46092.77871918424</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1198" t="n">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>97c644b3-1c6a-47ec-99a1-066625d29ce6</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>ee087035-be2c-4793-a1d0-2ba6b94a34ec</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1199" s="2" t="n">
+        <v>46072.86205252397</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>227</v>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1199" t="n">
+        <v>15.86</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1199"/>
+  <dimension ref="A1:I1215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48594,7 +48594,7 @@
         </is>
       </c>
       <c r="E1175" s="2" t="n">
-        <v>46072.82038569958</v>
+        <v>46072.82038569445</v>
       </c>
       <c r="F1175" t="n">
         <v>123</v>
@@ -48635,7 +48635,7 @@
         </is>
       </c>
       <c r="E1176" s="2" t="n">
-        <v>46090.61205237433</v>
+        <v>46090.61205237269</v>
       </c>
       <c r="F1176" t="n">
         <v>197</v>
@@ -48676,7 +48676,7 @@
         </is>
       </c>
       <c r="E1177" s="2" t="n">
-        <v>46074.02871904743</v>
+        <v>46074.02871905093</v>
       </c>
       <c r="F1177" t="n">
         <v>89</v>
@@ -48717,7 +48717,7 @@
         </is>
       </c>
       <c r="E1178" s="2" t="n">
-        <v>46078.02871905406</v>
+        <v>46078.02871905093</v>
       </c>
       <c r="F1178" t="n">
         <v>240</v>
@@ -48758,7 +48758,7 @@
         </is>
       </c>
       <c r="E1179" s="2" t="n">
-        <v>46070.65371906035</v>
+        <v>46070.6537190625</v>
       </c>
       <c r="F1179" t="n">
         <v>178</v>
@@ -48799,7 +48799,7 @@
         </is>
       </c>
       <c r="E1180" s="2" t="n">
-        <v>46072.82038573387</v>
+        <v>46072.82038572917</v>
       </c>
       <c r="F1180" t="n">
         <v>168</v>
@@ -48840,7 +48840,7 @@
         </is>
       </c>
       <c r="E1181" s="2" t="n">
-        <v>46083.48705241014</v>
+        <v>46083.48705240741</v>
       </c>
       <c r="F1181" t="n">
         <v>160</v>
@@ -48881,7 +48881,7 @@
         </is>
       </c>
       <c r="E1182" s="2" t="n">
-        <v>46078.2370524319</v>
+        <v>46078.23705243056</v>
       </c>
       <c r="F1182" t="n">
         <v>253</v>
@@ -48922,7 +48922,7 @@
         </is>
       </c>
       <c r="E1183" s="2" t="n">
-        <v>46089.02871910484</v>
+        <v>46089.0287191088</v>
       </c>
       <c r="F1183" t="n">
         <v>175</v>
@@ -48963,7 +48963,7 @@
         </is>
       </c>
       <c r="E1184" s="2" t="n">
-        <v>46081.52871910795</v>
+        <v>46081.5287191088</v>
       </c>
       <c r="F1184" t="n">
         <v>219</v>
@@ -49004,7 +49004,7 @@
         </is>
       </c>
       <c r="E1185" s="2" t="n">
-        <v>46081.48705244464</v>
+        <v>46081.48705244213</v>
       </c>
       <c r="F1185" t="n">
         <v>120</v>
@@ -49045,7 +49045,7 @@
         </is>
       </c>
       <c r="E1186" s="2" t="n">
-        <v>46081.48705245096</v>
+        <v>46081.4870524537</v>
       </c>
       <c r="F1186" t="n">
         <v>174</v>
@@ -49086,7 +49086,7 @@
         </is>
       </c>
       <c r="E1187" s="2" t="n">
-        <v>46081.82038578764</v>
+        <v>46081.82038578704</v>
       </c>
       <c r="F1187" t="n">
         <v>228</v>
@@ -49127,7 +49127,7 @@
         </is>
       </c>
       <c r="E1188" s="2" t="n">
-        <v>46086.9037191273</v>
+        <v>46086.90371913194</v>
       </c>
       <c r="F1188" t="n">
         <v>40</v>
@@ -49168,7 +49168,7 @@
         </is>
       </c>
       <c r="E1189" s="2" t="n">
-        <v>46065.9037191369</v>
+        <v>46065.90371913194</v>
       </c>
       <c r="F1189" t="n">
         <v>32</v>
@@ -49209,7 +49209,7 @@
         </is>
       </c>
       <c r="E1190" s="2" t="n">
-        <v>46064.15371914008</v>
+        <v>46064.15371914352</v>
       </c>
       <c r="F1190" t="n">
         <v>186</v>
@@ -49250,7 +49250,7 @@
         </is>
       </c>
       <c r="E1191" s="2" t="n">
-        <v>46069.36205247672</v>
+        <v>46069.36205247685</v>
       </c>
       <c r="F1191" t="n">
         <v>51</v>
@@ -49291,7 +49291,7 @@
         </is>
       </c>
       <c r="E1192" s="2" t="n">
-        <v>46087.3620524829</v>
+        <v>46087.36205248842</v>
       </c>
       <c r="F1192" t="n">
         <v>104</v>
@@ -49332,7 +49332,7 @@
         </is>
       </c>
       <c r="E1193" s="2" t="n">
-        <v>46067.82038582257</v>
+        <v>46067.82038582176</v>
       </c>
       <c r="F1193" t="n">
         <v>231</v>
@@ -49373,7 +49373,7 @@
         </is>
       </c>
       <c r="E1194" s="2" t="n">
-        <v>46092.77871915904</v>
+        <v>46092.7787191551</v>
       </c>
       <c r="F1194" t="n">
         <v>154</v>
@@ -49414,7 +49414,7 @@
         </is>
       </c>
       <c r="E1195" s="2" t="n">
-        <v>46083.98705250181</v>
+        <v>46083.9870525</v>
       </c>
       <c r="F1195" t="n">
         <v>122</v>
@@ -49455,7 +49455,7 @@
         </is>
       </c>
       <c r="E1196" s="2" t="n">
-        <v>46083.11205250496</v>
+        <v>46083.1120525</v>
       </c>
       <c r="F1196" t="n">
         <v>279</v>
@@ -49496,7 +49496,7 @@
         </is>
       </c>
       <c r="E1197" s="2" t="n">
-        <v>46075.69538584768</v>
+        <v>46075.69538584491</v>
       </c>
       <c r="F1197" t="n">
         <v>77</v>
@@ -49537,7 +49537,7 @@
         </is>
       </c>
       <c r="E1198" s="2" t="n">
-        <v>46092.77871918424</v>
+        <v>46092.77871918982</v>
       </c>
       <c r="F1198" t="n">
         <v>225</v>
@@ -49578,7 +49578,7 @@
         </is>
       </c>
       <c r="E1199" s="2" t="n">
-        <v>46072.86205252397</v>
+        <v>46072.86205252315</v>
       </c>
       <c r="F1199" t="n">
         <v>227</v>
@@ -49595,6 +49595,662 @@
       </c>
       <c r="I1199" t="n">
         <v>15.86</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>35977a1c-a59a-4e79-b902-2c90e7028457</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>ee21fff5-6cc3-4f1b-b152-75841fad8b08</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1200" s="2" t="n">
+        <v>46093.82020439481</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1200" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>83353204-31d6-4fcf-91a0-79c688cab814</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>bae36c9b-de75-4c65-8581-b4f7f5105437</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1201" s="2" t="n">
+        <v>46065.27853774111</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>119</v>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1201" t="n">
+        <v>15.03</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>037e3450-e6eb-4f20-a193-788d9da0e0e1</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>7191ff22-f75c-406c-ba09-0ed47008ec6e</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1202" s="2" t="n">
+        <v>46077.11187108453</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>243</v>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1202" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>75415d39-8ec0-4976-9a2e-77a796a42b67</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>87fa3cdb-b79a-4f2f-921e-92cc4d324662</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1203" s="2" t="n">
+        <v>46076.52853775767</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1203" t="n">
+        <v>15.31</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>dbfefb40-ecba-47b8-b2b4-f443d7c25456</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>a632c5b4-eaff-4ef9-b00d-281e8cf43bb3</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1204" s="2" t="n">
+        <v>46079.15353776721</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1204" t="n">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>d3ed2d8f-cc17-4811-967b-182515024697</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>1497dbd8-f24b-489f-b0ce-da107ee1ae4f</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1205" s="2" t="n">
+        <v>46088.07020444021</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>209</v>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1205" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>908cb424-6c82-4221-82af-2f39d7a87e95</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>f57b08f7-29dd-4f71-9642-5993bd44d509</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1206" s="2" t="n">
+        <v>46076.73687111031</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1206" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>3611640a-bc82-474d-a1e6-5aeb3965ed41</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>63ddc6ca-d61e-4491-a23b-d04339988c49</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1207" s="2" t="n">
+        <v>46070.19520445016</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1207" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>d8ee6c5e-52c8-44c2-8db3-4133f7badee4</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>e7ec3757-fe5e-4cbc-af03-65a527b94075</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1208" s="2" t="n">
+        <v>46078.15353778708</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>128</v>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1208" t="n">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>8818b90e-f862-4a3b-9fb3-bd85803a7173</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>6d6b56f8-3181-40cb-9741-349801c651dd</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1209" s="2" t="n">
+        <v>46077.4868711241</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>198</v>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1209" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>05f685c8-525d-4cb9-b1b6-d3a5d0c94a5c</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>42edeff1-aa3c-435f-a287-988ed7adbd55</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1210" s="2" t="n">
+        <v>46075.82020446399</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1210" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>27e33755-bd09-4e08-85aa-af2a6015035f</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>8922865c-aee8-40d7-a325-4ca196431957</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1211" s="2" t="n">
+        <v>46093.61187113383</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>141</v>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1211" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>d3124b7f-5e1e-4257-aaa2-591f70d75836</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>08e47223-08d0-4415-8f71-a83619be9e57</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1212" s="2" t="n">
+        <v>46077.32020447057</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>294</v>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1212" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>bd576b5c-f2f5-47a8-85fd-1aed4428c746</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>00cd0fc4-ddc1-434d-8c51-311c47ee5647</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1213" s="2" t="n">
+        <v>46073.77853781653</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>173</v>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1213" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>ec85bf2b-4153-4d76-9924-a686558dba30</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>92915742-7e67-4f4b-8ab4-800b15c490ec</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1214" s="2" t="n">
+        <v>46091.32020451521</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1214" t="n">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>098c7941-b53d-41cf-b8cf-c489cbced2e9</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>fadd5405-889e-40b7-802b-a12bc4e02d98</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1215" s="2" t="n">
+        <v>46070.69520451845</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>245</v>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1215" t="n">
+        <v>5.02</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1215"/>
+  <dimension ref="A1:I1232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49619,7 +49619,7 @@
         </is>
       </c>
       <c r="E1200" s="2" t="n">
-        <v>46093.82020439481</v>
+        <v>46093.82020439815</v>
       </c>
       <c r="F1200" t="n">
         <v>110</v>
@@ -49660,7 +49660,7 @@
         </is>
       </c>
       <c r="E1201" s="2" t="n">
-        <v>46065.27853774111</v>
+        <v>46065.27853774306</v>
       </c>
       <c r="F1201" t="n">
         <v>119</v>
@@ -49701,7 +49701,7 @@
         </is>
       </c>
       <c r="E1202" s="2" t="n">
-        <v>46077.11187108453</v>
+        <v>46077.11187108796</v>
       </c>
       <c r="F1202" t="n">
         <v>243</v>
@@ -49742,7 +49742,7 @@
         </is>
       </c>
       <c r="E1203" s="2" t="n">
-        <v>46076.52853775767</v>
+        <v>46076.52853775463</v>
       </c>
       <c r="F1203" t="n">
         <v>45</v>
@@ -49783,7 +49783,7 @@
         </is>
       </c>
       <c r="E1204" s="2" t="n">
-        <v>46079.15353776721</v>
+        <v>46079.1535377662</v>
       </c>
       <c r="F1204" t="n">
         <v>229</v>
@@ -49824,7 +49824,7 @@
         </is>
       </c>
       <c r="E1205" s="2" t="n">
-        <v>46088.07020444021</v>
+        <v>46088.07020444445</v>
       </c>
       <c r="F1205" t="n">
         <v>209</v>
@@ -49865,7 +49865,7 @@
         </is>
       </c>
       <c r="E1206" s="2" t="n">
-        <v>46076.73687111031</v>
+        <v>46076.73687111111</v>
       </c>
       <c r="F1206" t="n">
         <v>46</v>
@@ -49906,7 +49906,7 @@
         </is>
       </c>
       <c r="E1207" s="2" t="n">
-        <v>46070.19520445016</v>
+        <v>46070.19520444445</v>
       </c>
       <c r="F1207" t="n">
         <v>79</v>
@@ -49947,7 +49947,7 @@
         </is>
       </c>
       <c r="E1208" s="2" t="n">
-        <v>46078.15353778708</v>
+        <v>46078.15353778935</v>
       </c>
       <c r="F1208" t="n">
         <v>128</v>
@@ -49988,7 +49988,7 @@
         </is>
       </c>
       <c r="E1209" s="2" t="n">
-        <v>46077.4868711241</v>
+        <v>46077.48687112269</v>
       </c>
       <c r="F1209" t="n">
         <v>198</v>
@@ -50029,7 +50029,7 @@
         </is>
       </c>
       <c r="E1210" s="2" t="n">
-        <v>46075.82020446399</v>
+        <v>46075.82020446759</v>
       </c>
       <c r="F1210" t="n">
         <v>139</v>
@@ -50070,7 +50070,7 @@
         </is>
       </c>
       <c r="E1211" s="2" t="n">
-        <v>46093.61187113383</v>
+        <v>46093.61187113426</v>
       </c>
       <c r="F1211" t="n">
         <v>141</v>
@@ -50111,7 +50111,7 @@
         </is>
       </c>
       <c r="E1212" s="2" t="n">
-        <v>46077.32020447057</v>
+        <v>46077.32020446759</v>
       </c>
       <c r="F1212" t="n">
         <v>294</v>
@@ -50152,7 +50152,7 @@
         </is>
       </c>
       <c r="E1213" s="2" t="n">
-        <v>46073.77853781653</v>
+        <v>46073.7785378125</v>
       </c>
       <c r="F1213" t="n">
         <v>173</v>
@@ -50193,7 +50193,7 @@
         </is>
       </c>
       <c r="E1214" s="2" t="n">
-        <v>46091.32020451521</v>
+        <v>46091.32020451389</v>
       </c>
       <c r="F1214" t="n">
         <v>200</v>
@@ -50234,7 +50234,7 @@
         </is>
       </c>
       <c r="E1215" s="2" t="n">
-        <v>46070.69520451845</v>
+        <v>46070.69520451389</v>
       </c>
       <c r="F1215" t="n">
         <v>245</v>
@@ -50251,6 +50251,703 @@
       </c>
       <c r="I1215" t="n">
         <v>5.02</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>664a9943-f00e-4c4b-b316-86c6c5f46f94</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>f48019e7-999b-4317-9403-9b8e8d2711d4</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1216" s="2" t="n">
+        <v>46087.23202781272</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1216" t="n">
+        <v>16.51</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>3b05a5e7-a89b-4244-8b69-5fd6005ece95</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>80655c77-8f27-4983-8d4d-b04d89771d2c</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1217" s="2" t="n">
+        <v>46076.89869448257</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1217" t="n">
+        <v>15.09</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>7f302a69-48d8-402b-a781-c4f8a73e2dbb</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>be0e7970-0143-4ca7-8c37-a14f24520ff6</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1218" s="2" t="n">
+        <v>46092.31536115283</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>163</v>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1218" t="n">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>29d181c9-4f0a-44e2-8156-c03f3199ba6c</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>d382560e-3fcc-445f-a9c2-d22d1eb7044e</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1219" s="2" t="n">
+        <v>46081.94036115604</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>70</v>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1219" t="n">
+        <v>19.88</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>d15a2f4c-b039-4980-822d-31e9c2d856ee</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>0197dd93-9ce6-4273-b639-9784221dd6f3</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1220" s="2" t="n">
+        <v>46080.48202783246</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1220" t="n">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>3c113b79-701f-4c6d-84c7-272ad87ef949</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>92099a09-e744-442b-a1cd-9e1ecd8ca4f2</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1221" s="2" t="n">
+        <v>46081.27369450233</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>291</v>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1221" t="n">
+        <v>13.97</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>25dece42-fca7-44a1-97af-51648874fcde</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>d95794c3-deef-4947-b8ec-f013e0efb976</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1222" s="2" t="n">
+        <v>46076.98202785321</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>177</v>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1222" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>75398e6d-2de5-433b-b4d9-500a5c175be4</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>48fdcfea-c655-4cc0-8934-5abcdc8dace9</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1223" s="2" t="n">
+        <v>46086.73202786253</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>162</v>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1223" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>3160fa05-463d-441d-96f5-26d61d5a10c1</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>93f55430-9a80-45b0-9764-ddf699c98e25</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1224" s="2" t="n">
+        <v>46089.56536119951</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>209</v>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1224" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>6c1652ca-2f17-4db2-8460-33e1a5940c22</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>cbf618be-dbca-496a-a064-b965492b6c15</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1225" s="2" t="n">
+        <v>46088.89869453915</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1225" t="n">
+        <v>18.71</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>c597a945-7608-49d7-bb16-bea22079f490</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>d6fdd8e2-4730-4743-b64b-a5bec9ce6cd3</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1226" s="2" t="n">
+        <v>46067.27369454567</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>87</v>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1226" t="n">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>6f821987-577c-4c99-8a10-b124fae87200</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>f5e3eb7e-a4a5-4ded-9ff1-8d5540d6e01c</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1227" s="2" t="n">
+        <v>46070.9820278919</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1227" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>0cf5f716-b93a-481d-873c-617eb904e0bc</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>61f386ac-b7af-426f-8096-88c4cee1ff79</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1228" s="2" t="n">
+        <v>46067.77369456185</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>249</v>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1228" t="n">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>9fbef2fe-20d1-413e-99c9-d7860a66e475</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>bc204b5d-406a-4d12-9817-456cb21aea28</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1229" s="2" t="n">
+        <v>46086.64869456566</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1229" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>54758334-f7a2-41f1-879b-9625f74ef068</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>89d07e56-7818-47c0-937c-fcb343a26006</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1230" s="2" t="n">
+        <v>46069.35702793668</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1230" t="n">
+        <v>12.07</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>8366ab0b-57c8-4046-88cd-0279352d4512</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>6699f832-5e6e-4045-8472-433e8f8b44d1</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1231" s="2" t="n">
+        <v>46081.69036127628</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1231" t="n">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>7a7393f8-ae8a-49bf-9ff3-982a4c99ae13</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>095d6db6-2d7a-4b9a-a2df-f30fd93347e6</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1232" s="2" t="n">
+        <v>46072.23202794674</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>129</v>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1232" t="n">
+        <v>10.92</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1232"/>
+  <dimension ref="A1:I1254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50275,7 +50275,7 @@
         </is>
       </c>
       <c r="E1216" s="2" t="n">
-        <v>46087.23202781272</v>
+        <v>46087.2320278125</v>
       </c>
       <c r="F1216" t="n">
         <v>200</v>
@@ -50316,7 +50316,7 @@
         </is>
       </c>
       <c r="E1217" s="2" t="n">
-        <v>46076.89869448257</v>
+        <v>46076.89869447917</v>
       </c>
       <c r="F1217" t="n">
         <v>160</v>
@@ -50357,7 +50357,7 @@
         </is>
       </c>
       <c r="E1218" s="2" t="n">
-        <v>46092.31536115283</v>
+        <v>46092.31536115741</v>
       </c>
       <c r="F1218" t="n">
         <v>163</v>
@@ -50398,7 +50398,7 @@
         </is>
       </c>
       <c r="E1219" s="2" t="n">
-        <v>46081.94036115604</v>
+        <v>46081.94036115741</v>
       </c>
       <c r="F1219" t="n">
         <v>70</v>
@@ -50439,7 +50439,7 @@
         </is>
       </c>
       <c r="E1220" s="2" t="n">
-        <v>46080.48202783246</v>
+        <v>46080.48202783565</v>
       </c>
       <c r="F1220" t="n">
         <v>54</v>
@@ -50480,7 +50480,7 @@
         </is>
       </c>
       <c r="E1221" s="2" t="n">
-        <v>46081.27369450233</v>
+        <v>46081.27369450231</v>
       </c>
       <c r="F1221" t="n">
         <v>291</v>
@@ -50521,7 +50521,7 @@
         </is>
       </c>
       <c r="E1222" s="2" t="n">
-        <v>46076.98202785321</v>
+        <v>46076.98202785879</v>
       </c>
       <c r="F1222" t="n">
         <v>177</v>
@@ -50562,7 +50562,7 @@
         </is>
       </c>
       <c r="E1223" s="2" t="n">
-        <v>46086.73202786253</v>
+        <v>46086.73202785879</v>
       </c>
       <c r="F1223" t="n">
         <v>162</v>
@@ -50603,7 +50603,7 @@
         </is>
       </c>
       <c r="E1224" s="2" t="n">
-        <v>46089.56536119951</v>
+        <v>46089.56536120371</v>
       </c>
       <c r="F1224" t="n">
         <v>209</v>
@@ -50644,7 +50644,7 @@
         </is>
       </c>
       <c r="E1225" s="2" t="n">
-        <v>46088.89869453915</v>
+        <v>46088.89869453703</v>
       </c>
       <c r="F1225" t="n">
         <v>216</v>
@@ -50685,7 +50685,7 @@
         </is>
       </c>
       <c r="E1226" s="2" t="n">
-        <v>46067.27369454567</v>
+        <v>46067.27369454861</v>
       </c>
       <c r="F1226" t="n">
         <v>87</v>
@@ -50726,7 +50726,7 @@
         </is>
       </c>
       <c r="E1227" s="2" t="n">
-        <v>46070.9820278919</v>
+        <v>46070.98202789351</v>
       </c>
       <c r="F1227" t="n">
         <v>273</v>
@@ -50767,7 +50767,7 @@
         </is>
       </c>
       <c r="E1228" s="2" t="n">
-        <v>46067.77369456185</v>
+        <v>46067.77369456019</v>
       </c>
       <c r="F1228" t="n">
         <v>249</v>
@@ -50808,7 +50808,7 @@
         </is>
       </c>
       <c r="E1229" s="2" t="n">
-        <v>46086.64869456566</v>
+        <v>46086.64869456019</v>
       </c>
       <c r="F1229" t="n">
         <v>100</v>
@@ -50849,7 +50849,7 @@
         </is>
       </c>
       <c r="E1230" s="2" t="n">
-        <v>46069.35702793668</v>
+        <v>46069.35702793981</v>
       </c>
       <c r="F1230" t="n">
         <v>272</v>
@@ -50890,7 +50890,7 @@
         </is>
       </c>
       <c r="E1231" s="2" t="n">
-        <v>46081.69036127628</v>
+        <v>46081.69036127315</v>
       </c>
       <c r="F1231" t="n">
         <v>90</v>
@@ -50931,7 +50931,7 @@
         </is>
       </c>
       <c r="E1232" s="2" t="n">
-        <v>46072.23202794674</v>
+        <v>46072.23202795139</v>
       </c>
       <c r="F1232" t="n">
         <v>129</v>
@@ -50948,6 +50948,908 @@
       </c>
       <c r="I1232" t="n">
         <v>10.92</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>e2b4e181-a1c0-46e7-9bfd-f6c8539f8077</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>1f674834-e9d9-4ffe-aed3-6da70bdbeba1</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1233" s="2" t="n">
+        <v>46072.02368415768</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1233" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>6e755bba-9d8c-4633-8c70-22e3e8e1623a</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>eb6dd856-0d4e-4610-a87b-d75d9f16ac28</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1234" s="2" t="n">
+        <v>46067.35701749549</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1234" t="n">
+        <v>15.71</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>406cc946-c528-428a-be8e-fc7fbc58aab3</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>79b5363a-81d6-441a-9b8d-05b8a1ca66bf</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1235" s="2" t="n">
+        <v>46071.56535084858</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>235</v>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1235" t="n">
+        <v>18.51</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>8e417277-4557-498d-9398-c5dd6cee13ac</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>5e829dbb-8b07-41bc-9a60-5774368e4329</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1236" s="2" t="n">
+        <v>46073.52368419505</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1236" t="n">
+        <v>17.63</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>59884ced-0806-439a-9818-a0ab100cd822</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>a2a3a49f-0c62-4beb-b615-ddd0b060c1df</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1237" s="2" t="n">
+        <v>46071.9403508651</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>134</v>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1237" t="n">
+        <v>9.18</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>e0c8c640-076c-450e-aff2-a0a6100c599b</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>35b7239e-f2ea-44a4-b606-1d405546bdc8</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1238" s="2" t="n">
+        <v>46072.39868420803</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>163</v>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1238" t="n">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>476a4e71-da89-47b7-a3e2-85c2a00b6fd3</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>d84661f3-195f-4d4c-84c0-7f380814848c</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1239" s="2" t="n">
+        <v>46069.85701754485</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1239" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>636df9e1-2d5f-4e28-a126-b86267097045</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>b32992c9-7d78-427f-9ab8-6b3f1c78d0a4</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1240" s="2" t="n">
+        <v>46085.98201755746</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1240" t="n">
+        <v>13.89</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>c4555ec7-2972-4408-aac8-1bd7cfcea765</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>9ebfb409-b6d1-4cf6-804b-851544185e9c</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1241" s="2" t="n">
+        <v>46078.69035090365</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1241" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>0e4177d7-7ade-43d0-9581-7700a56f35e4</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>476554e1-8f89-4a26-97dc-358a34c18eb6</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1242" s="2" t="n">
+        <v>46079.85701757357</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>283</v>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1242" t="n">
+        <v>15.46</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>ca972724-43cb-4d95-96d7-5a0d93e8250b</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>73160825-60cb-4895-8eb4-ebf448b6a105</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1243" s="2" t="n">
+        <v>46090.6070175803</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1243" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>3a415c53-3ba3-46c1-a9bf-5b9f76ef015f</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>37445a43-f812-44c2-9141-e1205166ba98</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1244" s="2" t="n">
+        <v>46073.94035092311</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>207</v>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1244" t="n">
+        <v>18.14</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>44d1855f-1ced-476e-8fba-2f6a35aa3d5c</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>879748fe-de2b-4994-a430-8d5cd113e09e</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1245" s="2" t="n">
+        <v>46078.23201759325</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1245" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>b87336ae-69aa-47fc-a47d-0dd829aacf3f</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>a59634e0-ee6e-4cf3-a572-e18c495b9ef9</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1246" s="2" t="n">
+        <v>46078.73201759651</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>251</v>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1246" t="n">
+        <v>16.13</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>c4dc0b1f-f667-4d31-b2d4-7cc162ff14d4</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>6dec47b2-c7b2-4343-b655-05e97d18e572</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1247" s="2" t="n">
+        <v>46068.02368426964</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1247" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>ef131db5-c26f-4e60-9fcb-473599b7b01c</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>c052cbdb-7ea9-419c-8676-6b68fa790940</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1248" s="2" t="n">
+        <v>46073.73201760627</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>177</v>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1248" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>1d0f2264-f4f2-49eb-a6e3-859634775c3d</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>4d4ab262-416c-4d15-801c-943ed2595045</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1249" s="2" t="n">
+        <v>46088.06535094587</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>199</v>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1249" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>06032fc8-323a-401c-816c-5e4abceccb7a</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>e355010c-c1d5-4fb6-9ba5-8ef406a2309c</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1250" s="2" t="n">
+        <v>46089.48201761633</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1250" t="n">
+        <v>18.44</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>f8322ada-2eb6-4367-8bdd-c563d3b2db0f</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>93376066-57d5-47a6-8ab2-f4870e7489ba</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1251" s="2" t="n">
+        <v>46087.85701763221</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1251" t="n">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>a9c0aa1d-2f5e-4ce0-a134-eb7296a103c8</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>95047ee0-53c4-453e-8c17-378b3eb751ad</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1252" s="2" t="n">
+        <v>46095.31535096878</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>264</v>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1252" t="n">
+        <v>12.79</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>18c36798-39f8-4594-9c6d-8b9e8b3a0c93</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>3358826c-9f04-43e3-a28b-9a0b453f6a4b</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1253" s="2" t="n">
+        <v>46066.52368430559</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1253" t="n">
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>1e6979bc-eea6-4296-ba00-deb82bd3e9a9</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>620ff471-ffb9-4ece-9144-82381555726b</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1254" s="2" t="n">
+        <v>46075.69035097883</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1254" t="n">
+        <v>10.34</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1254"/>
+  <dimension ref="A1:I1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50972,7 +50972,7 @@
         </is>
       </c>
       <c r="E1233" s="2" t="n">
-        <v>46072.02368415768</v>
+        <v>46072.02368415509</v>
       </c>
       <c r="F1233" t="n">
         <v>85</v>
@@ -51013,7 +51013,7 @@
         </is>
       </c>
       <c r="E1234" s="2" t="n">
-        <v>46067.35701749549</v>
+        <v>46067.3570175</v>
       </c>
       <c r="F1234" t="n">
         <v>109</v>
@@ -51054,7 +51054,7 @@
         </is>
       </c>
       <c r="E1235" s="2" t="n">
-        <v>46071.56535084858</v>
+        <v>46071.56535084491</v>
       </c>
       <c r="F1235" t="n">
         <v>235</v>
@@ -51095,7 +51095,7 @@
         </is>
       </c>
       <c r="E1236" s="2" t="n">
-        <v>46073.52368419505</v>
+        <v>46073.52368418981</v>
       </c>
       <c r="F1236" t="n">
         <v>175</v>
@@ -51136,7 +51136,7 @@
         </is>
       </c>
       <c r="E1237" s="2" t="n">
-        <v>46071.9403508651</v>
+        <v>46071.94035086806</v>
       </c>
       <c r="F1237" t="n">
         <v>134</v>
@@ -51177,7 +51177,7 @@
         </is>
       </c>
       <c r="E1238" s="2" t="n">
-        <v>46072.39868420803</v>
+        <v>46072.39868421296</v>
       </c>
       <c r="F1238" t="n">
         <v>163</v>
@@ -51218,7 +51218,7 @@
         </is>
       </c>
       <c r="E1239" s="2" t="n">
-        <v>46069.85701754485</v>
+        <v>46069.8570175463</v>
       </c>
       <c r="F1239" t="n">
         <v>234</v>
@@ -51259,7 +51259,7 @@
         </is>
       </c>
       <c r="E1240" s="2" t="n">
-        <v>46085.98201755746</v>
+        <v>46085.98201755787</v>
       </c>
       <c r="F1240" t="n">
         <v>46</v>
@@ -51300,7 +51300,7 @@
         </is>
       </c>
       <c r="E1241" s="2" t="n">
-        <v>46078.69035090365</v>
+        <v>46078.69035090278</v>
       </c>
       <c r="F1241" t="n">
         <v>169</v>
@@ -51341,7 +51341,7 @@
         </is>
       </c>
       <c r="E1242" s="2" t="n">
-        <v>46079.85701757357</v>
+        <v>46079.85701756945</v>
       </c>
       <c r="F1242" t="n">
         <v>283</v>
@@ -51382,7 +51382,7 @@
         </is>
       </c>
       <c r="E1243" s="2" t="n">
-        <v>46090.6070175803</v>
+        <v>46090.60701758102</v>
       </c>
       <c r="F1243" t="n">
         <v>225</v>
@@ -51423,7 +51423,7 @@
         </is>
       </c>
       <c r="E1244" s="2" t="n">
-        <v>46073.94035092311</v>
+        <v>46073.94035092593</v>
       </c>
       <c r="F1244" t="n">
         <v>207</v>
@@ -51464,7 +51464,7 @@
         </is>
       </c>
       <c r="E1245" s="2" t="n">
-        <v>46078.23201759325</v>
+        <v>46078.23201759259</v>
       </c>
       <c r="F1245" t="n">
         <v>250</v>
@@ -51505,7 +51505,7 @@
         </is>
       </c>
       <c r="E1246" s="2" t="n">
-        <v>46078.73201759651</v>
+        <v>46078.73201759259</v>
       </c>
       <c r="F1246" t="n">
         <v>251</v>
@@ -51546,7 +51546,7 @@
         </is>
       </c>
       <c r="E1247" s="2" t="n">
-        <v>46068.02368426964</v>
+        <v>46068.02368427083</v>
       </c>
       <c r="F1247" t="n">
         <v>80</v>
@@ -51587,7 +51587,7 @@
         </is>
       </c>
       <c r="E1248" s="2" t="n">
-        <v>46073.73201760627</v>
+        <v>46073.73201760417</v>
       </c>
       <c r="F1248" t="n">
         <v>177</v>
@@ -51628,7 +51628,7 @@
         </is>
       </c>
       <c r="E1249" s="2" t="n">
-        <v>46088.06535094587</v>
+        <v>46088.06535094907</v>
       </c>
       <c r="F1249" t="n">
         <v>199</v>
@@ -51669,7 +51669,7 @@
         </is>
       </c>
       <c r="E1250" s="2" t="n">
-        <v>46089.48201761633</v>
+        <v>46089.48201761574</v>
       </c>
       <c r="F1250" t="n">
         <v>224</v>
@@ -51710,7 +51710,7 @@
         </is>
       </c>
       <c r="E1251" s="2" t="n">
-        <v>46087.85701763221</v>
+        <v>46087.85701762731</v>
       </c>
       <c r="F1251" t="n">
         <v>90</v>
@@ -51751,7 +51751,7 @@
         </is>
       </c>
       <c r="E1252" s="2" t="n">
-        <v>46095.31535096878</v>
+        <v>46095.31535097223</v>
       </c>
       <c r="F1252" t="n">
         <v>264</v>
@@ -51792,7 +51792,7 @@
         </is>
       </c>
       <c r="E1253" s="2" t="n">
-        <v>46066.52368430559</v>
+        <v>46066.52368430555</v>
       </c>
       <c r="F1253" t="n">
         <v>42</v>
@@ -51833,7 +51833,7 @@
         </is>
       </c>
       <c r="E1254" s="2" t="n">
-        <v>46075.69035097883</v>
+        <v>46075.69035098379</v>
       </c>
       <c r="F1254" t="n">
         <v>36</v>
@@ -51850,6 +51850,744 @@
       </c>
       <c r="I1254" t="n">
         <v>10.34</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>3a6f9b22-6182-4648-8071-50d91efbe343</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>83224b2c-5ec7-4466-b698-bbafdf81c442</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1255" s="2" t="n">
+        <v>46066.1557481889</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>144</v>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1255" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>a5437a04-d57d-4503-b0d1-6e470c93169a</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>320d0c87-cae9-4861-9cf8-d20aba4be967</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1256" s="2" t="n">
+        <v>46089.73908152674</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1256" t="n">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>df097dda-b106-4f93-9ea1-b33b07101991</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>bf6dd4ca-a3c9-43c7-ade1-86e48f5e7869</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1257" s="2" t="n">
+        <v>46084.11408153009</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>246</v>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1257" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>96fbaabc-6355-421d-a722-973d40e85f9e</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>c843b932-7faa-4b48-9a8e-931d53be25e1</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1258" s="2" t="n">
+        <v>46070.94741486687</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1258" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>c0b891d6-ccaa-49a0-b4cf-68352a4d0aac</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>7ae4c4eb-909c-4b4b-8481-a9d6f5122c0a</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1259" s="2" t="n">
+        <v>46066.98908157492</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>201</v>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1259" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>176109e0-62ad-4ca2-be40-c72dbf7b5b15</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>872c59fd-1cec-4303-b338-0572e9f5324f</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1260" s="2" t="n">
+        <v>46093.36408157808</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>269</v>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1260" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>70685306-bbcd-4579-a5c9-7a9854771e3f</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>ed3b5dfc-e0d3-4ece-aff7-179f4d814088</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1261" s="2" t="n">
+        <v>46064.73908158763</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1261" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>e5c3828d-c35a-4c34-87f5-dc115f4768c1</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>2bfb1917-dffd-4baf-8aec-38564c81f617</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1262" s="2" t="n">
+        <v>46094.36408159731</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>193</v>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1262" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>70c52daa-326d-4ada-b1dc-344307d7cdc4</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>7a474783-92a1-4edd-93a1-d8d7694b2067</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1263" s="2" t="n">
+        <v>46094.53074826714</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1263" t="n">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2d28dd7d-0727-4999-9cc7-5fa1e6eff6cb</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>2285bf33-70e3-465a-8027-0faff0015f8e</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1264" s="2" t="n">
+        <v>46074.53074827041</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>193</v>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1264" t="n">
+        <v>18.31</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>ba5f9c20-dd2f-486f-8d2b-93c56546b9e4</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>9533e7dc-62b8-4260-8807-e57b5e1be5c9</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1265" s="2" t="n">
+        <v>46091.69741494059</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>264</v>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1265" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>57e3c386-62ba-4820-b807-7cf13342ba05</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>b777372a-3087-4298-a559-84dd56993e1e</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1266" s="2" t="n">
+        <v>46082.57241494687</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>251</v>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1266" t="n">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>3b40eb03-8235-4b37-9c9e-81648e148a6f</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>58ef9f73-c42f-43b1-a082-0a4a4f59c947</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1267" s="2" t="n">
+        <v>46083.19741495662</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1267" t="n">
+        <v>10.88</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>164ab487-4780-450d-aab2-4b6b1bebd781</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>02e28b1a-865b-490b-a569-96ff2b1be336</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1268" s="2" t="n">
+        <v>46082.57241496615</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>174</v>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1268" t="n">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>0992aa88-0398-4e2b-a900-71fddfba1173</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>05a77a81-2614-4534-8815-b2e132a018df</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1269" s="2" t="n">
+        <v>46085.6140816517</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1269" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>c01c04ec-f071-4cca-b4ae-d70f187c817a</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>88a4902c-1ab7-44f4-a432-12f2c726583f</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1270" s="2" t="n">
+        <v>46067.36408165807</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1270" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>09a69770-cacf-4c15-99ef-d1d83ce52f69</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>a58d9e10-5e67-4749-948f-970e5b4cfb04</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1271" s="2" t="n">
+        <v>46084.32241499481</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1271" t="n">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>e3a20d0f-a93b-42c9-8811-50acde26a5d7</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>9b10d58c-94b2-4ccf-9fb2-169e486f04f1</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1272" s="2" t="n">
+        <v>46091.57241500749</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>258</v>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1272" t="n">
+        <v>5.32</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1272"/>
+  <dimension ref="A1:I1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51874,7 +51874,7 @@
         </is>
       </c>
       <c r="E1255" s="2" t="n">
-        <v>46066.1557481889</v>
+        <v>46066.15574819445</v>
       </c>
       <c r="F1255" t="n">
         <v>144</v>
@@ -51915,7 +51915,7 @@
         </is>
       </c>
       <c r="E1256" s="2" t="n">
-        <v>46089.73908152674</v>
+        <v>46089.73908152778</v>
       </c>
       <c r="F1256" t="n">
         <v>239</v>
@@ -51956,7 +51956,7 @@
         </is>
       </c>
       <c r="E1257" s="2" t="n">
-        <v>46084.11408153009</v>
+        <v>46084.11408152778</v>
       </c>
       <c r="F1257" t="n">
         <v>246</v>
@@ -51997,7 +51997,7 @@
         </is>
       </c>
       <c r="E1258" s="2" t="n">
-        <v>46070.94741486687</v>
+        <v>46070.94741486111</v>
       </c>
       <c r="F1258" t="n">
         <v>118</v>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="E1259" s="2" t="n">
-        <v>46066.98908157492</v>
+        <v>46066.98908157407</v>
       </c>
       <c r="F1259" t="n">
         <v>201</v>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="E1260" s="2" t="n">
-        <v>46093.36408157808</v>
+        <v>46093.36408157407</v>
       </c>
       <c r="F1260" t="n">
         <v>269</v>
@@ -52120,7 +52120,7 @@
         </is>
       </c>
       <c r="E1261" s="2" t="n">
-        <v>46064.73908158763</v>
+        <v>46064.73908158565</v>
       </c>
       <c r="F1261" t="n">
         <v>170</v>
@@ -52161,7 +52161,7 @@
         </is>
       </c>
       <c r="E1262" s="2" t="n">
-        <v>46094.36408159731</v>
+        <v>46094.36408159722</v>
       </c>
       <c r="F1262" t="n">
         <v>193</v>
@@ -52202,7 +52202,7 @@
         </is>
       </c>
       <c r="E1263" s="2" t="n">
-        <v>46094.53074826714</v>
+        <v>46094.53074826389</v>
       </c>
       <c r="F1263" t="n">
         <v>85</v>
@@ -52243,7 +52243,7 @@
         </is>
       </c>
       <c r="E1264" s="2" t="n">
-        <v>46074.53074827041</v>
+        <v>46074.53074827547</v>
       </c>
       <c r="F1264" t="n">
         <v>193</v>
@@ -52284,7 +52284,7 @@
         </is>
       </c>
       <c r="E1265" s="2" t="n">
-        <v>46091.69741494059</v>
+        <v>46091.69741494213</v>
       </c>
       <c r="F1265" t="n">
         <v>264</v>
@@ -52325,7 +52325,7 @@
         </is>
       </c>
       <c r="E1266" s="2" t="n">
-        <v>46082.57241494687</v>
+        <v>46082.57241494213</v>
       </c>
       <c r="F1266" t="n">
         <v>251</v>
@@ -52366,7 +52366,7 @@
         </is>
       </c>
       <c r="E1267" s="2" t="n">
-        <v>46083.19741495662</v>
+        <v>46083.19741495371</v>
       </c>
       <c r="F1267" t="n">
         <v>37</v>
@@ -52407,7 +52407,7 @@
         </is>
       </c>
       <c r="E1268" s="2" t="n">
-        <v>46082.57241496615</v>
+        <v>46082.57241496527</v>
       </c>
       <c r="F1268" t="n">
         <v>174</v>
@@ -52448,7 +52448,7 @@
         </is>
       </c>
       <c r="E1269" s="2" t="n">
-        <v>46085.6140816517</v>
+        <v>46085.61408165509</v>
       </c>
       <c r="F1269" t="n">
         <v>58</v>
@@ -52489,7 +52489,7 @@
         </is>
       </c>
       <c r="E1270" s="2" t="n">
-        <v>46067.36408165807</v>
+        <v>46067.36408165509</v>
       </c>
       <c r="F1270" t="n">
         <v>123</v>
@@ -52530,7 +52530,7 @@
         </is>
       </c>
       <c r="E1271" s="2" t="n">
-        <v>46084.32241499481</v>
+        <v>46084.322415</v>
       </c>
       <c r="F1271" t="n">
         <v>216</v>
@@ -52571,7 +52571,7 @@
         </is>
       </c>
       <c r="E1272" s="2" t="n">
-        <v>46091.57241500749</v>
+        <v>46091.57241501157</v>
       </c>
       <c r="F1272" t="n">
         <v>258</v>
@@ -52588,6 +52588,580 @@
       </c>
       <c r="I1272" t="n">
         <v>5.32</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>e99a4147-9f47-4443-8844-f87a9f3a76de</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>57f41738-7b7e-4803-bc68-a429341cc133</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1273" s="2" t="n">
+        <v>46064.91220201082</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>286</v>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1273" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>814d530e-1c2b-499b-956d-fc39f31560d8</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>d3aac4ef-08cc-4411-ae7b-6e0d7be892de</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1274" s="2" t="n">
+        <v>46076.0788686819</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1274" t="n">
+        <v>13.51</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>f56c9f20-1f12-4e9a-b495-9d72b40fde84</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>4b4f5f66-693a-4519-b3f7-eeb4ea00d29d</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1275" s="2" t="n">
+        <v>46065.4122020184</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>92</v>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1275" t="n">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>387eb075-a87a-4b1c-a9e4-ae813c73f134</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>cdf69ed7-ea81-4af3-af50-ebcfddd9cfb0</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1276" s="2" t="n">
+        <v>46065.28720202745</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1276" t="n">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>9078f8ab-9948-4dd7-af8e-0b590a8de717</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>13d6d1df-3f38-4e58-9b4a-c1045326fc84</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1277" s="2" t="n">
+        <v>46069.7872020389</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>101</v>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1277" t="n">
+        <v>17.11</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>71c258ae-c4c1-40cf-a285-a349e95d6af4</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>d6920277-e86c-422a-96f7-83ceaaafd044</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1278" s="2" t="n">
+        <v>46087.70386870849</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1278" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>b03d9ee9-92be-435e-b482-fc91f3e27e69</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>c0ac25ac-5cc1-4053-b571-58564b1c20f0</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1279" s="2" t="n">
+        <v>46067.66220204782</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>245</v>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1279" t="n">
+        <v>11.79</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>ac86038a-dbbb-405a-b3a2-f57e91fafeb7</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>17dd2faa-9ba2-4ad8-ace6-319b5209b872</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1280" s="2" t="n">
+        <v>46082.12053542016</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>266</v>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1280" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>a11e86cb-80c9-4f01-aa2e-cac9f3d8aa86</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>9ac62bc9-635e-4efd-a09b-6209dbcb57b8</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1281" s="2" t="n">
+        <v>46079.82886875913</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1281" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>db4df0ba-b7f7-4b3d-8217-d23400dc281d</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>5995116c-941a-4db0-9851-37a3b33f9313</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1282" s="2" t="n">
+        <v>46092.37053543726</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1282" t="n">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>37affedd-8c1f-481a-84dc-a64e439b7544</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>65dbe4b1-dc08-417b-845f-05c43909dea7</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1283" s="2" t="n">
+        <v>46078.66220212373</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>117</v>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1283" t="n">
+        <v>18.32</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>1eca990a-8001-4e96-bb99-0fd670cb1139</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>7f9c4361-cde2-4e5c-9685-933d5fcfbf81</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1284" s="2" t="n">
+        <v>46091.82886879896</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1284" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>02e4a416-c96c-4d18-8545-e5e0453cf5d2</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>59dcc20d-a88f-431a-8f12-670dfef62203</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1285" s="2" t="n">
+        <v>46094.74553546849</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1285" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>fbef27f6-6c99-4b1a-ae09-e7047842ade5</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>ef3be33e-0035-41b4-8e27-c3b6cf1ca5af</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1286" s="2" t="n">
+        <v>46069.87053547987</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>196</v>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1286" t="n">
+        <v>12.78</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1286"/>
+  <dimension ref="A1:I1303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52612,7 +52612,7 @@
         </is>
       </c>
       <c r="E1273" s="2" t="n">
-        <v>46064.91220201082</v>
+        <v>46064.91220201389</v>
       </c>
       <c r="F1273" t="n">
         <v>286</v>
@@ -52653,7 +52653,7 @@
         </is>
       </c>
       <c r="E1274" s="2" t="n">
-        <v>46076.0788686819</v>
+        <v>46076.07886868055</v>
       </c>
       <c r="F1274" t="n">
         <v>57</v>
@@ -52694,7 +52694,7 @@
         </is>
       </c>
       <c r="E1275" s="2" t="n">
-        <v>46065.4122020184</v>
+        <v>46065.41220201389</v>
       </c>
       <c r="F1275" t="n">
         <v>92</v>
@@ -52735,7 +52735,7 @@
         </is>
       </c>
       <c r="E1276" s="2" t="n">
-        <v>46065.28720202745</v>
+        <v>46065.28720202547</v>
       </c>
       <c r="F1276" t="n">
         <v>120</v>
@@ -52776,7 +52776,7 @@
         </is>
       </c>
       <c r="E1277" s="2" t="n">
-        <v>46069.7872020389</v>
+        <v>46069.78720203703</v>
       </c>
       <c r="F1277" t="n">
         <v>101</v>
@@ -52817,7 +52817,7 @@
         </is>
       </c>
       <c r="E1278" s="2" t="n">
-        <v>46087.70386870849</v>
+        <v>46087.70386870371</v>
       </c>
       <c r="F1278" t="n">
         <v>168</v>
@@ -52858,7 +52858,7 @@
         </is>
       </c>
       <c r="E1279" s="2" t="n">
-        <v>46067.66220204782</v>
+        <v>46067.66220204861</v>
       </c>
       <c r="F1279" t="n">
         <v>245</v>
@@ -52899,7 +52899,7 @@
         </is>
       </c>
       <c r="E1280" s="2" t="n">
-        <v>46082.12053542016</v>
+        <v>46082.12053541667</v>
       </c>
       <c r="F1280" t="n">
         <v>266</v>
@@ -52940,7 +52940,7 @@
         </is>
       </c>
       <c r="E1281" s="2" t="n">
-        <v>46079.82886875913</v>
+        <v>46079.82886876157</v>
       </c>
       <c r="F1281" t="n">
         <v>239</v>
@@ -52981,7 +52981,7 @@
         </is>
       </c>
       <c r="E1282" s="2" t="n">
-        <v>46092.37053543726</v>
+        <v>46092.37053543981</v>
       </c>
       <c r="F1282" t="n">
         <v>107</v>
@@ -53022,7 +53022,7 @@
         </is>
       </c>
       <c r="E1283" s="2" t="n">
-        <v>46078.66220212373</v>
+        <v>46078.66220211805</v>
       </c>
       <c r="F1283" t="n">
         <v>117</v>
@@ -53063,7 +53063,7 @@
         </is>
       </c>
       <c r="E1284" s="2" t="n">
-        <v>46091.82886879896</v>
+        <v>46091.8288687963</v>
       </c>
       <c r="F1284" t="n">
         <v>48</v>
@@ -53104,7 +53104,7 @@
         </is>
       </c>
       <c r="E1285" s="2" t="n">
-        <v>46094.74553546849</v>
+        <v>46094.74553546296</v>
       </c>
       <c r="F1285" t="n">
         <v>91</v>
@@ -53145,7 +53145,7 @@
         </is>
       </c>
       <c r="E1286" s="2" t="n">
-        <v>46069.87053547987</v>
+        <v>46069.87053547454</v>
       </c>
       <c r="F1286" t="n">
         <v>196</v>
@@ -53162,6 +53162,703 @@
       </c>
       <c r="I1286" t="n">
         <v>12.78</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>673d4390-c355-4d57-a78b-989c65ce850f</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>85e864d1-93a0-4c65-9502-5529becaa801</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1287" s="2" t="n">
+        <v>46093.04016804005</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1287" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>41a6b3f6-833c-47e7-b6cf-10af3430ae67</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>5647bbb1-78f1-4d7e-81a8-02a5d935b1ea</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1288" s="2" t="n">
+        <v>46077.54016804439</v>
+      </c>
+      <c r="F1288" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1288" t="n">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>ed90abf6-fade-419f-8e85-c2040b084338</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>55e59e17-30b2-46ff-85c0-142ba503b27c</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1289" s="2" t="n">
+        <v>46067.37350138757</v>
+      </c>
+      <c r="F1289" t="n">
+        <v>122</v>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1289" t="n">
+        <v>19.55</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>c8d715aa-9ed6-4a9f-9632-88a47fa1606f</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>62cc64f6-0e53-41dd-9341-fa2415ec0318</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1290" s="2" t="n">
+        <v>46084.24850139086</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1290" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>c489b40e-f564-4a66-b0f7-80fb393b3188</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>87efe4f4-f4bb-424a-83ed-4c98e177e4db</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1291" s="2" t="n">
+        <v>46073.91516807349</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>183</v>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1291" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>480052f8-5216-4040-979b-b25320056641</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>b1cdf600-aee3-4c24-ac39-589610771f82</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1292" s="2" t="n">
+        <v>46068.45683475673</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1292" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>d48de705-b576-43b0-8076-94b01858e0ac</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>85e684c5-b1fe-4da6-86f1-fa40a543d96e</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1293" s="2" t="n">
+        <v>46082.04016810909</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1293" t="n">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>0873e5ff-1dbd-4a75-9b75-1e30aa06aeb3</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>22eeb9eb-f42d-46fb-8490-cc7ce076e5f9</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1294" s="2" t="n">
+        <v>46090.12350144878</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>116</v>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1294" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>352b17c5-05fb-427a-9283-e9ba66e1cfa6</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>88e16a58-7131-4f4f-9003-e81c195d9b32</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1295" s="2" t="n">
+        <v>46083.79016811865</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>113</v>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1295" t="n">
+        <v>18.77</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>483a8fe2-849c-4f86-b918-d14caed40c9f</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>07389750-106f-42f8-94c4-955df45f1154</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1296" s="2" t="n">
+        <v>46091.54016813801</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>94</v>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1296" t="n">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>d43cdb8c-c8c8-4544-96ae-b47f652ffdd8</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>91ea965a-17d5-4057-87e4-477e7ba504ae</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1297" s="2" t="n">
+        <v>46064.41516815065</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>289</v>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1297" t="n">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>ac418a93-f7d8-4b9d-92de-5cccf9a20e47</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>1e15a108-f6c5-4b6b-b27a-2e34bdc296a6</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1298" s="2" t="n">
+        <v>46092.99850148722</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>179</v>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1298" t="n">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>379c4228-62f9-4a9e-ac4b-cb955ae27d4e</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>e61f64c3-23fa-43ef-ae55-d632f8bb4335</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1299" s="2" t="n">
+        <v>46065.62350149057</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1299" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>dc99ac43-2418-49f7-8cc5-6678d2a18326</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>17a6172d-e199-406b-9598-6b36c75d6906</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1300" s="2" t="n">
+        <v>46068.20683483014</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>217</v>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1300" t="n">
+        <v>19.77</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>214d5859-ac02-4805-b085-b9d8e9bbf09e</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>5858956a-d3c3-4a21-bfc0-577636ddfdb6</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1301" s="2" t="n">
+        <v>46080.12350150661</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>253</v>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1301" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>0d3e3b6f-3bc3-45df-8826-ffe000530053</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>a450f4e0-d3ff-4686-9c55-3cbfd7fb028e</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1302" s="2" t="n">
+        <v>46071.70683484317</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1302" t="n">
+        <v>17.71</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>7df12249-4580-49ac-a43d-7cc70da0ef26</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>57c6d59d-69ca-44f8-80c1-1100f8918336</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1303" s="2" t="n">
+        <v>46070.08183485285</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>128</v>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1303" t="n">
+        <v>18.39</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1303"/>
+  <dimension ref="A1:I1326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53186,7 +53186,7 @@
         </is>
       </c>
       <c r="E1287" s="2" t="n">
-        <v>46093.04016804005</v>
+        <v>46093.04016804398</v>
       </c>
       <c r="F1287" t="n">
         <v>43</v>
@@ -53227,7 +53227,7 @@
         </is>
       </c>
       <c r="E1288" s="2" t="n">
-        <v>46077.54016804439</v>
+        <v>46077.54016804398</v>
       </c>
       <c r="F1288" t="n">
         <v>69</v>
@@ -53268,7 +53268,7 @@
         </is>
       </c>
       <c r="E1289" s="2" t="n">
-        <v>46067.37350138757</v>
+        <v>46067.37350138889</v>
       </c>
       <c r="F1289" t="n">
         <v>122</v>
@@ -53309,7 +53309,7 @@
         </is>
       </c>
       <c r="E1290" s="2" t="n">
-        <v>46084.24850139086</v>
+        <v>46084.24850138889</v>
       </c>
       <c r="F1290" t="n">
         <v>104</v>
@@ -53350,7 +53350,7 @@
         </is>
       </c>
       <c r="E1291" s="2" t="n">
-        <v>46073.91516807349</v>
+        <v>46073.9151680787</v>
       </c>
       <c r="F1291" t="n">
         <v>183</v>
@@ -53391,7 +53391,7 @@
         </is>
       </c>
       <c r="E1292" s="2" t="n">
-        <v>46068.45683475673</v>
+        <v>46068.45683475694</v>
       </c>
       <c r="F1292" t="n">
         <v>298</v>
@@ -53432,7 +53432,7 @@
         </is>
       </c>
       <c r="E1293" s="2" t="n">
-        <v>46082.04016810909</v>
+        <v>46082.04016811342</v>
       </c>
       <c r="F1293" t="n">
         <v>125</v>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="E1294" s="2" t="n">
-        <v>46090.12350144878</v>
+        <v>46090.12350144676</v>
       </c>
       <c r="F1294" t="n">
         <v>116</v>
@@ -53514,7 +53514,7 @@
         </is>
       </c>
       <c r="E1295" s="2" t="n">
-        <v>46083.79016811865</v>
+        <v>46083.79016811342</v>
       </c>
       <c r="F1295" t="n">
         <v>113</v>
@@ -53555,7 +53555,7 @@
         </is>
       </c>
       <c r="E1296" s="2" t="n">
-        <v>46091.54016813801</v>
+        <v>46091.54016813658</v>
       </c>
       <c r="F1296" t="n">
         <v>94</v>
@@ -53596,7 +53596,7 @@
         </is>
       </c>
       <c r="E1297" s="2" t="n">
-        <v>46064.41516815065</v>
+        <v>46064.41516814815</v>
       </c>
       <c r="F1297" t="n">
         <v>289</v>
@@ -53637,7 +53637,7 @@
         </is>
       </c>
       <c r="E1298" s="2" t="n">
-        <v>46092.99850148722</v>
+        <v>46092.99850148148</v>
       </c>
       <c r="F1298" t="n">
         <v>179</v>
@@ -53678,7 +53678,7 @@
         </is>
       </c>
       <c r="E1299" s="2" t="n">
-        <v>46065.62350149057</v>
+        <v>46065.62350149306</v>
       </c>
       <c r="F1299" t="n">
         <v>62</v>
@@ -53719,7 +53719,7 @@
         </is>
       </c>
       <c r="E1300" s="2" t="n">
-        <v>46068.20683483014</v>
+        <v>46068.20683482639</v>
       </c>
       <c r="F1300" t="n">
         <v>217</v>
@@ -53760,7 +53760,7 @@
         </is>
       </c>
       <c r="E1301" s="2" t="n">
-        <v>46080.12350150661</v>
+        <v>46080.12350150463</v>
       </c>
       <c r="F1301" t="n">
         <v>253</v>
@@ -53801,7 +53801,7 @@
         </is>
       </c>
       <c r="E1302" s="2" t="n">
-        <v>46071.70683484317</v>
+        <v>46071.70683483796</v>
       </c>
       <c r="F1302" t="n">
         <v>47</v>
@@ -53842,7 +53842,7 @@
         </is>
       </c>
       <c r="E1303" s="2" t="n">
-        <v>46070.08183485285</v>
+        <v>46070.08183484954</v>
       </c>
       <c r="F1303" t="n">
         <v>128</v>
@@ -53859,6 +53859,949 @@
       </c>
       <c r="I1303" t="n">
         <v>18.39</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>269aeb36-c4fc-424b-a676-c7c82cb798ff</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>c072fd0e-4eb3-44ce-91d2-1bbc18b963ce</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1304" s="2" t="n">
+        <v>46080.13121300923</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>193</v>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1304" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>e30acc8e-a7c6-4b4c-9886-bf2359195b9d</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>d17ad55a-c8d9-400d-a0d5-ad32729713f0</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1305" s="2" t="n">
+        <v>46092.0062130128</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>164</v>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1305" t="n">
+        <v>7.67</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>cbde8c35-e179-4808-abb1-2feb49dd037f</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>d6b529f6-f055-4f04-bc39-a628f4685db6</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1306" s="2" t="n">
+        <v>46084.67287968269</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1306" t="n">
+        <v>11.47</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>16a8e804-b4f8-43d2-830f-3e89c21b96c3</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>8c10ee77-73a0-4311-8ced-6c6b9be5d963</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1307" s="2" t="n">
+        <v>46084.71454636859</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>131</v>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1307" t="n">
+        <v>18.17</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>47340b2f-7c64-4b79-a16d-8399d4080a8b</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>8e55cca2-7da3-4c5b-bb26-3b8b343e4c88</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1308" s="2" t="n">
+        <v>46079.46454637178</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>283</v>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1308" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>1a566c34-655f-4f18-879a-45c3cb3858bb</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>be51c0fe-91ab-493c-95b5-b6ce25248f7d</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1309" s="2" t="n">
+        <v>46092.17287970828</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>95</v>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1309" t="n">
+        <v>18.05</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>31d86126-9423-488d-b07a-374083d17999</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>c9c1cbe4-7222-461b-bd7e-2612acb340c0</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1310" s="2" t="n">
+        <v>46080.04787971474</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1310" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>f943941d-f4b9-42b4-ad14-725943841894</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>fd9100de-4183-4513-be7b-761945c6890f</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1311" s="2" t="n">
+        <v>46066.79787972096</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>242</v>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1311" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>33b83376-09b6-488a-824f-c0e0fde9dc6a</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>dafcd799-1246-47c9-92e7-32d888246eb1</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1312" s="2" t="n">
+        <v>46068.0478797273</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1312" t="n">
+        <v>17.74</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>3ea2b302-9fd0-4933-aa78-64d25649ce7c</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>af8942af-f2af-4160-8255-bc1e7254cb1f</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1313" s="2" t="n">
+        <v>46083.04787973349</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1313" t="n">
+        <v>11.16</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>22687366-9524-4172-8286-c9f2dd3ae455</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>cc855c68-f503-4bbd-b85f-9b6a1ab64128</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1314" s="2" t="n">
+        <v>46090.50621307611</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>196</v>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1314" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>22af3205-3460-495e-a71d-c9751cdd2e1f</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>84064b46-b489-4748-9416-ba39eb3b354c</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1315" s="2" t="n">
+        <v>46090.67287974623</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1315" t="n">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>cd620344-51ed-4962-b5bc-542cf0665186</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>620d67a3-df41-4ef8-b115-5fd742c1d291</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1316" s="2" t="n">
+        <v>46080.63121308573</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1316" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>eaba9d1b-998b-4b7e-942d-a76fbd97e412</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>8fbc4756-4146-42c3-aee5-cd28e1beadde</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1317" s="2" t="n">
+        <v>46084.63121308887</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1317" t="n">
+        <v>17.31</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>6e62004c-d684-4d06-87d5-1bcd284e422c</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>c4e20a2d-6adb-4b7a-989e-23edc9f4635e</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1318" s="2" t="n">
+        <v>46068.54787976513</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>92</v>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1318" t="n">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>f2c00ee9-3810-4a7d-b14f-2005a1ffc5ac</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>ec37ebbe-e143-4e49-bbde-1ada0a928388</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1319" s="2" t="n">
+        <v>46075.25621311411</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>283</v>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1319" t="n">
+        <v>14.85</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>6dede443-e9c7-48a5-b1a2-fd4f2fd9eee5</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>b8fa15c1-4abd-4d7c-85a4-a53fc7d414c7</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1320" s="2" t="n">
+        <v>46065.08954645672</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>182</v>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1320" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>e1035503-5575-4105-b421-12ed319828b5</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>43e83733-3eb4-4149-8e3d-bdbb5a69daf4</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1321" s="2" t="n">
+        <v>46081.71454646312</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>126</v>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1321" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>b8f20b18-5e04-40ba-8c3e-3acb498b61ee</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>30fe41bd-1433-4901-8b47-efa2fb725be3</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1322" s="2" t="n">
+        <v>46071.79787979958</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1322" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>67292839-b8f0-4a4c-8d14-fddd38cad9ca</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>2ebce75a-8e1a-48a4-9c16-609cee7d5cec</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1323" s="2" t="n">
+        <v>46067.50621313612</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1323" t="n">
+        <v>18.85</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>43f61e9a-83f5-4889-bc23-f0fd506ba816</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>5bd98706-e6bd-45d8-bf41-2190ff636651</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1324" s="2" t="n">
+        <v>46069.5062131394</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1324" t="n">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>e772b7bd-025e-447e-a2b7-d4677c6f7ed3</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>3a364fd8-5345-4b9b-8cab-16a275182e44</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1325" s="2" t="n">
+        <v>46074.67287981855</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>247</v>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1325" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>952d52d2-4e4b-42cf-b3d0-d9995df743b7</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>6e58cf05-b686-44c4-9ea1-41714df152a2</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1326" s="2" t="n">
+        <v>46076.17287982172</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1326" t="n">
+        <v>14.53</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1326"/>
+  <dimension ref="A1:I1345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53883,7 +53883,7 @@
         </is>
       </c>
       <c r="E1304" s="2" t="n">
-        <v>46080.13121300923</v>
+        <v>46080.13121300926</v>
       </c>
       <c r="F1304" t="n">
         <v>193</v>
@@ -53924,7 +53924,7 @@
         </is>
       </c>
       <c r="E1305" s="2" t="n">
-        <v>46092.0062130128</v>
+        <v>46092.00621300926</v>
       </c>
       <c r="F1305" t="n">
         <v>164</v>
@@ -53965,7 +53965,7 @@
         </is>
       </c>
       <c r="E1306" s="2" t="n">
-        <v>46084.67287968269</v>
+        <v>46084.6728796875</v>
       </c>
       <c r="F1306" t="n">
         <v>206</v>
@@ -54006,7 +54006,7 @@
         </is>
       </c>
       <c r="E1307" s="2" t="n">
-        <v>46084.71454636859</v>
+        <v>46084.71454636574</v>
       </c>
       <c r="F1307" t="n">
         <v>131</v>
@@ -54047,7 +54047,7 @@
         </is>
       </c>
       <c r="E1308" s="2" t="n">
-        <v>46079.46454637178</v>
+        <v>46079.46454637731</v>
       </c>
       <c r="F1308" t="n">
         <v>283</v>
@@ -54088,7 +54088,7 @@
         </is>
       </c>
       <c r="E1309" s="2" t="n">
-        <v>46092.17287970828</v>
+        <v>46092.17287971065</v>
       </c>
       <c r="F1309" t="n">
         <v>95</v>
@@ -54129,7 +54129,7 @@
         </is>
       </c>
       <c r="E1310" s="2" t="n">
-        <v>46080.04787971474</v>
+        <v>46080.04787971065</v>
       </c>
       <c r="F1310" t="n">
         <v>78</v>
@@ -54170,7 +54170,7 @@
         </is>
       </c>
       <c r="E1311" s="2" t="n">
-        <v>46066.79787972096</v>
+        <v>46066.79787972222</v>
       </c>
       <c r="F1311" t="n">
         <v>242</v>
@@ -54211,7 +54211,7 @@
         </is>
       </c>
       <c r="E1312" s="2" t="n">
-        <v>46068.0478797273</v>
+        <v>46068.04787972222</v>
       </c>
       <c r="F1312" t="n">
         <v>79</v>
@@ -54252,7 +54252,7 @@
         </is>
       </c>
       <c r="E1313" s="2" t="n">
-        <v>46083.04787973349</v>
+        <v>46083.04787973379</v>
       </c>
       <c r="F1313" t="n">
         <v>75</v>
@@ -54293,7 +54293,7 @@
         </is>
       </c>
       <c r="E1314" s="2" t="n">
-        <v>46090.50621307611</v>
+        <v>46090.5062130787</v>
       </c>
       <c r="F1314" t="n">
         <v>196</v>
@@ -54334,7 +54334,7 @@
         </is>
       </c>
       <c r="E1315" s="2" t="n">
-        <v>46090.67287974623</v>
+        <v>46090.67287974537</v>
       </c>
       <c r="F1315" t="n">
         <v>140</v>
@@ -54375,7 +54375,7 @@
         </is>
       </c>
       <c r="E1316" s="2" t="n">
-        <v>46080.63121308573</v>
+        <v>46080.63121309028</v>
       </c>
       <c r="F1316" t="n">
         <v>234</v>
@@ -54416,7 +54416,7 @@
         </is>
       </c>
       <c r="E1317" s="2" t="n">
-        <v>46084.63121308887</v>
+        <v>46084.63121309028</v>
       </c>
       <c r="F1317" t="n">
         <v>41</v>
@@ -54457,7 +54457,7 @@
         </is>
       </c>
       <c r="E1318" s="2" t="n">
-        <v>46068.54787976513</v>
+        <v>46068.54787976852</v>
       </c>
       <c r="F1318" t="n">
         <v>92</v>
@@ -54498,7 +54498,7 @@
         </is>
       </c>
       <c r="E1319" s="2" t="n">
-        <v>46075.25621311411</v>
+        <v>46075.25621311343</v>
       </c>
       <c r="F1319" t="n">
         <v>283</v>
@@ -54539,7 +54539,7 @@
         </is>
       </c>
       <c r="E1320" s="2" t="n">
-        <v>46065.08954645672</v>
+        <v>46065.08954645833</v>
       </c>
       <c r="F1320" t="n">
         <v>182</v>
@@ -54580,7 +54580,7 @@
         </is>
       </c>
       <c r="E1321" s="2" t="n">
-        <v>46081.71454646312</v>
+        <v>46081.71454645833</v>
       </c>
       <c r="F1321" t="n">
         <v>126</v>
@@ -54621,7 +54621,7 @@
         </is>
       </c>
       <c r="E1322" s="2" t="n">
-        <v>46071.79787979958</v>
+        <v>46071.79787980324</v>
       </c>
       <c r="F1322" t="n">
         <v>140</v>
@@ -54662,7 +54662,7 @@
         </is>
       </c>
       <c r="E1323" s="2" t="n">
-        <v>46067.50621313612</v>
+        <v>46067.50621313658</v>
       </c>
       <c r="F1323" t="n">
         <v>215</v>
@@ -54703,7 +54703,7 @@
         </is>
       </c>
       <c r="E1324" s="2" t="n">
-        <v>46069.5062131394</v>
+        <v>46069.50621313658</v>
       </c>
       <c r="F1324" t="n">
         <v>78</v>
@@ -54744,7 +54744,7 @@
         </is>
       </c>
       <c r="E1325" s="2" t="n">
-        <v>46074.67287981855</v>
+        <v>46074.67287981482</v>
       </c>
       <c r="F1325" t="n">
         <v>247</v>
@@ -54785,7 +54785,7 @@
         </is>
       </c>
       <c r="E1326" s="2" t="n">
-        <v>46076.17287982172</v>
+        <v>46076.17287982639</v>
       </c>
       <c r="F1326" t="n">
         <v>78</v>
@@ -54802,6 +54802,785 @@
       </c>
       <c r="I1326" t="n">
         <v>14.53</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>5f34ea9f-3dcb-4e23-9dc5-1e43d4008ec4</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>5adc800b-416d-440a-9cf7-b9cfab9cdd33</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1327" s="2" t="n">
+        <v>46078.87130427993</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1327" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>058b32f9-1ec1-4e02-835f-2fc4d933c83f</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>bb4ab9e5-1bf1-4c64-9561-2c7fa7c8956b</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1328" s="2" t="n">
+        <v>46090.53797099173</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>284</v>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1328" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>f40d4bdd-5a4a-4022-947b-31af0d6d3320</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>20130502-ee29-465f-8137-997888c1c8d1</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1329" s="2" t="n">
+        <v>46091.03797099819</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>67</v>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1329" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>9a98fe2c-4299-4380-bbd0-b48087fd744f</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>dd83d4b1-402e-4edf-ade2-c62c4b01a476</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1330" s="2" t="n">
+        <v>46069.49630433822</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1330" t="n">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>20a2c938-4884-432a-8952-a9d2ae0c67bb</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>281d9d42-f7b8-4b14-82a6-87674d458080</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1331" s="2" t="n">
+        <v>46065.53797101144</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1331" t="n">
+        <v>9.210000000000001</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>481c51ac-59a1-4fec-895a-11ae371866df</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>ae2e09db-d2f6-4733-ac1e-effcd4782ef9</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1332" s="2" t="n">
+        <v>46078.07963768456</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1332" t="n">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>297ce680-a7f6-4f8f-8639-24e13bdd0005</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>81cd89ec-d268-4d3d-ac1c-35fe2ec6b892</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1333" s="2" t="n">
+        <v>46077.91297102117</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>136</v>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1333" t="n">
+        <v>12.48</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>74c3e516-380c-46ee-84ec-ee04a47bd5ea</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>c4769407-80ef-499c-a8dd-9374f75406d6</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1334" s="2" t="n">
+        <v>46075.99630437021</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1334" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>bbe6e3d3-66eb-4fec-82ad-6e68fcf90eb0</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>3426f460-6573-46ac-905e-cae7ece471c9</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1335" s="2" t="n">
+        <v>46084.45463770686</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1335" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>804998b9-eb9d-494d-9482-ca5995fc47d1</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>312be8d8-16f5-4b36-aabc-ccee0473beaa</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1336" s="2" t="n">
+        <v>46074.03797104963</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1336" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>56cf3e65-4193-4fa6-825b-90f8068b6fe6</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>602ea725-ce60-4753-ad36-e3ffefb22502</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1337" s="2" t="n">
+        <v>46065.49630438674</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1337" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>e13eda08-4612-4899-a69b-784b6c23d478</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>84da8fa5-210d-4896-800c-a39ae68c0503</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1338" s="2" t="n">
+        <v>46068.99630439629</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1338" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>e6ec883f-88e2-4d85-bcb0-c46397542bd9</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>8954d2ce-ccce-406a-9037-ccf8457c9b58</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1339" s="2" t="n">
+        <v>46074.66297106618</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>228</v>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1339" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>b0dc7377-640b-416f-b119-2add3fae6a92</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>ddb53b85-fce1-4ab6-9207-7198dfde0387</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1340" s="2" t="n">
+        <v>46092.57963773607</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1340" t="n">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>c670c639-6f5b-4ecc-982d-207259e26314</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>ce7895f7-0ffe-4c70-87e7-05ce87ea11fb</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1341" s="2" t="n">
+        <v>46087.49630440911</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>113</v>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1341" t="n">
+        <v>13.24</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>39e95617-c9c8-4860-a797-406ba1472d51</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>9ec11615-ab55-41b2-84de-fef7ba9a1914</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1342" s="2" t="n">
+        <v>46067.74630441231</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>183</v>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1342" t="n">
+        <v>11.56</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>1559f970-e0c6-4100-95ed-4c3ed10dbda1</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>f7094cf3-4387-495f-ac3f-4e5060e39e3f</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1343" s="2" t="n">
+        <v>46075.16297108587</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>296</v>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1343" t="n">
+        <v>12.27</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>46ba954f-3b2e-40f8-b49f-17c7be8053db</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>1ad063a4-184d-4e14-9a8a-6419e70617f0</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1344" s="2" t="n">
+        <v>46080.1629710921</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1344" t="n">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>e76b7a5e-99bc-46b4-b9ab-1874c774119c</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>007c3e29-954f-4ed1-ab7b-6c36a3b33301</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1345" s="2" t="n">
+        <v>46086.57963776856</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>238</v>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1345" t="n">
+        <v>6.61</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1345"/>
+  <dimension ref="A1:I1365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54826,7 +54826,7 @@
         </is>
       </c>
       <c r="E1327" s="2" t="n">
-        <v>46078.87130427993</v>
+        <v>46078.87130428241</v>
       </c>
       <c r="F1327" t="n">
         <v>48</v>
@@ -54867,7 +54867,7 @@
         </is>
       </c>
       <c r="E1328" s="2" t="n">
-        <v>46090.53797099173</v>
+        <v>46090.53797099537</v>
       </c>
       <c r="F1328" t="n">
         <v>284</v>
@@ -54908,7 +54908,7 @@
         </is>
       </c>
       <c r="E1329" s="2" t="n">
-        <v>46091.03797099819</v>
+        <v>46091.03797099537</v>
       </c>
       <c r="F1329" t="n">
         <v>67</v>
@@ -54949,7 +54949,7 @@
         </is>
       </c>
       <c r="E1330" s="2" t="n">
-        <v>46069.49630433822</v>
+        <v>46069.49630434027</v>
       </c>
       <c r="F1330" t="n">
         <v>168</v>
@@ -54990,7 +54990,7 @@
         </is>
       </c>
       <c r="E1331" s="2" t="n">
-        <v>46065.53797101144</v>
+        <v>46065.53797100695</v>
       </c>
       <c r="F1331" t="n">
         <v>273</v>
@@ -55031,7 +55031,7 @@
         </is>
       </c>
       <c r="E1332" s="2" t="n">
-        <v>46078.07963768456</v>
+        <v>46078.07963768519</v>
       </c>
       <c r="F1332" t="n">
         <v>133</v>
@@ -55072,7 +55072,7 @@
         </is>
       </c>
       <c r="E1333" s="2" t="n">
-        <v>46077.91297102117</v>
+        <v>46077.91297101852</v>
       </c>
       <c r="F1333" t="n">
         <v>136</v>
@@ -55113,7 +55113,7 @@
         </is>
       </c>
       <c r="E1334" s="2" t="n">
-        <v>46075.99630437021</v>
+        <v>46075.996304375</v>
       </c>
       <c r="F1334" t="n">
         <v>81</v>
@@ -55154,7 +55154,7 @@
         </is>
       </c>
       <c r="E1335" s="2" t="n">
-        <v>46084.45463770686</v>
+        <v>46084.45463770833</v>
       </c>
       <c r="F1335" t="n">
         <v>220</v>
@@ -55195,7 +55195,7 @@
         </is>
       </c>
       <c r="E1336" s="2" t="n">
-        <v>46074.03797104963</v>
+        <v>46074.03797105324</v>
       </c>
       <c r="F1336" t="n">
         <v>178</v>
@@ -55236,7 +55236,7 @@
         </is>
       </c>
       <c r="E1337" s="2" t="n">
-        <v>46065.49630438674</v>
+        <v>46065.49630438657</v>
       </c>
       <c r="F1337" t="n">
         <v>38</v>
@@ -55277,7 +55277,7 @@
         </is>
       </c>
       <c r="E1338" s="2" t="n">
-        <v>46068.99630439629</v>
+        <v>46068.99630439815</v>
       </c>
       <c r="F1338" t="n">
         <v>82</v>
@@ -55318,7 +55318,7 @@
         </is>
       </c>
       <c r="E1339" s="2" t="n">
-        <v>46074.66297106618</v>
+        <v>46074.66297106481</v>
       </c>
       <c r="F1339" t="n">
         <v>228</v>
@@ -55359,7 +55359,7 @@
         </is>
       </c>
       <c r="E1340" s="2" t="n">
-        <v>46092.57963773607</v>
+        <v>46092.57963773148</v>
       </c>
       <c r="F1340" t="n">
         <v>188</v>
@@ -55400,7 +55400,7 @@
         </is>
       </c>
       <c r="E1341" s="2" t="n">
-        <v>46087.49630440911</v>
+        <v>46087.49630440972</v>
       </c>
       <c r="F1341" t="n">
         <v>113</v>
@@ -55441,7 +55441,7 @@
         </is>
       </c>
       <c r="E1342" s="2" t="n">
-        <v>46067.74630441231</v>
+        <v>46067.74630440972</v>
       </c>
       <c r="F1342" t="n">
         <v>183</v>
@@ -55482,7 +55482,7 @@
         </is>
       </c>
       <c r="E1343" s="2" t="n">
-        <v>46075.16297108587</v>
+        <v>46075.16297108796</v>
       </c>
       <c r="F1343" t="n">
         <v>296</v>
@@ -55523,7 +55523,7 @@
         </is>
       </c>
       <c r="E1344" s="2" t="n">
-        <v>46080.1629710921</v>
+        <v>46080.16297108796</v>
       </c>
       <c r="F1344" t="n">
         <v>78</v>
@@ -55564,7 +55564,7 @@
         </is>
       </c>
       <c r="E1345" s="2" t="n">
-        <v>46086.57963776856</v>
+        <v>46086.5796377662</v>
       </c>
       <c r="F1345" t="n">
         <v>238</v>
@@ -55581,6 +55581,826 @@
       </c>
       <c r="I1345" t="n">
         <v>6.61</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>0def87dc-d33f-42b5-b288-2a5b3d7581ca</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>5282ac41-92ce-4bdc-956e-2f9d2a74f8aa</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1346" s="2" t="n">
+        <v>46077.38104054666</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>146</v>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1346" t="n">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>696ed0b0-5349-4075-85dd-5bba4b0436c6</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>aafce256-6222-4e32-a40b-edb02fd78968</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1347" s="2" t="n">
+        <v>46079.25604055127</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1347" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>46ddb7d5-49e6-46c5-81b1-8b720fc0ebfb</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>b3b4be0b-760b-42b7-8d93-25042a23e463</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1348" s="2" t="n">
+        <v>46087.08937389448</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>237</v>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1348" t="n">
+        <v>9.73</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>1d77e6cc-9ad8-40c0-861b-31424b7f41e9</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>4be25e09-b3ff-43ac-bf87-119da95d741b</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1349" s="2" t="n">
+        <v>46090.63104056441</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1349" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>70e2d2b6-7e63-426d-ad00-75019f3a6bcd</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>4a395266-4035-4f33-9736-7a1df2109451</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1350" s="2" t="n">
+        <v>46086.38104057415</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>247</v>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1350" t="n">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>f25c29cc-90ce-4941-8023-656ee00cdeff</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>2ed87277-75c9-414f-b2a8-9444efc12755</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1351" s="2" t="n">
+        <v>46093.8810405774</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1351" t="n">
+        <v>13.82</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>0e274a8e-bbbe-43ac-8493-23db560b16b6</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>50d2a716-0101-469c-ac24-0805ef43f114</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1352" s="2" t="n">
+        <v>46092.33937392043</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>116</v>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1352" t="n">
+        <v>16.72</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>581565e6-2ac5-46bf-bd40-c2f6defcc8bd</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>5abf6457-8424-4b98-a6ea-040eb92b28f1</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1353" s="2" t="n">
+        <v>46092.63104059355</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1353" t="n">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>82959fce-6f7e-44a1-80bd-2ee3b2b7f339</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>9bdbfb78-cf81-47a2-88bb-e4045dcb5237</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1354" s="2" t="n">
+        <v>46067.79770728209</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1354" t="n">
+        <v>15.87</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>7fb84888-f61d-431e-a08b-9ae1e2be62b3</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>2dc5c890-ac25-40b8-b8ec-c14ed2788088</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1355" s="2" t="n">
+        <v>46090.17270729769</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1355" t="n">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>65d60cf1-1037-4931-b7e9-73f70f45727a</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>420ff1fc-8512-4a00-9eac-79e998c08510</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1356" s="2" t="n">
+        <v>46072.04770730092</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>291</v>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1356" t="n">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>ac3b1f75-149b-43e6-b651-f8b7fb062af5</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>907fc3b8-3fa3-4089-812d-d00d985001f6</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1357" s="2" t="n">
+        <v>46073.29770730729</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1357" t="n">
+        <v>10.37</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>be8887eb-2290-47a4-8b60-e8aeebe40de6</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>a59a9b78-8bc6-4029-bbe1-a35006800f4e</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1358" s="2" t="n">
+        <v>46076.38104065323</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>268</v>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1358" t="n">
+        <v>11.39</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>8a7938fd-96df-43fb-a283-b3e89d205532</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>32404818-3f75-474b-8e01-ced54d019605</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1359" s="2" t="n">
+        <v>46067.29770733565</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>164</v>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1359" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>5e2526ef-60b8-4516-bac2-6e79b4b93f3a</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>aec00298-c54f-4965-bed5-730d8ed1745f</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1360" s="2" t="n">
+        <v>46088.29770733897</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1360" t="n">
+        <v>18.62</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>42211d30-cfa4-4328-9d13-f710220d96fe</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>0d94a837-1153-4d77-9bba-00cc0d96d73d</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1361" s="2" t="n">
+        <v>46085.50604067558</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>221</v>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1361" t="n">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>c64a1434-3dcb-486d-b5d8-0f84780ffd2c</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>6ed971cb-09e6-4525-823c-fa0a740cda52</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1362" s="2" t="n">
+        <v>46083.13104068177</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1362" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>8205a136-80bd-4a1e-b4b7-0a43dd424321</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>9c44a389-4c98-4762-8534-603802b9ff09</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1363" s="2" t="n">
+        <v>46091.67270735798</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1363" t="n">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>3b618ddd-e02e-42d9-9bd0-989de4b31a69</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>68bddb6c-09cc-4ffb-9f59-7340edc982ed</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1364" s="2" t="n">
+        <v>46078.67270736746</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>157</v>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1364" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>585b0f22-fc4d-4867-9019-60679d4e7678</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>f37ff74b-7c3b-40b2-b57d-b80d732d2072</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1365" s="2" t="n">
+        <v>46083.71437403731</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>154</v>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1365" t="n">
+        <v>15.97</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1365"/>
+  <dimension ref="A1:I1381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55605,7 +55605,7 @@
         </is>
       </c>
       <c r="E1346" s="2" t="n">
-        <v>46077.38104054666</v>
+        <v>46077.38104054398</v>
       </c>
       <c r="F1346" t="n">
         <v>146</v>
@@ -55646,7 +55646,7 @@
         </is>
       </c>
       <c r="E1347" s="2" t="n">
-        <v>46079.25604055127</v>
+        <v>46079.25604055556</v>
       </c>
       <c r="F1347" t="n">
         <v>120</v>
@@ -55687,7 +55687,7 @@
         </is>
       </c>
       <c r="E1348" s="2" t="n">
-        <v>46087.08937389448</v>
+        <v>46087.08937388889</v>
       </c>
       <c r="F1348" t="n">
         <v>237</v>
@@ -55728,7 +55728,7 @@
         </is>
       </c>
       <c r="E1349" s="2" t="n">
-        <v>46090.63104056441</v>
+        <v>46090.63104056713</v>
       </c>
       <c r="F1349" t="n">
         <v>214</v>
@@ -55769,7 +55769,7 @@
         </is>
       </c>
       <c r="E1350" s="2" t="n">
-        <v>46086.38104057415</v>
+        <v>46086.3810405787</v>
       </c>
       <c r="F1350" t="n">
         <v>247</v>
@@ -55810,7 +55810,7 @@
         </is>
       </c>
       <c r="E1351" s="2" t="n">
-        <v>46093.8810405774</v>
+        <v>46093.8810405787</v>
       </c>
       <c r="F1351" t="n">
         <v>139</v>
@@ -55851,7 +55851,7 @@
         </is>
       </c>
       <c r="E1352" s="2" t="n">
-        <v>46092.33937392043</v>
+        <v>46092.33937392361</v>
       </c>
       <c r="F1352" t="n">
         <v>116</v>
@@ -55892,7 +55892,7 @@
         </is>
       </c>
       <c r="E1353" s="2" t="n">
-        <v>46092.63104059355</v>
+        <v>46092.63104059028</v>
       </c>
       <c r="F1353" t="n">
         <v>78</v>
@@ -55933,7 +55933,7 @@
         </is>
       </c>
       <c r="E1354" s="2" t="n">
-        <v>46067.79770728209</v>
+        <v>46067.79770728009</v>
       </c>
       <c r="F1354" t="n">
         <v>214</v>
@@ -55974,7 +55974,7 @@
         </is>
       </c>
       <c r="E1355" s="2" t="n">
-        <v>46090.17270729769</v>
+        <v>46090.17270730324</v>
       </c>
       <c r="F1355" t="n">
         <v>137</v>
@@ -56015,7 +56015,7 @@
         </is>
       </c>
       <c r="E1356" s="2" t="n">
-        <v>46072.04770730092</v>
+        <v>46072.04770730324</v>
       </c>
       <c r="F1356" t="n">
         <v>291</v>
@@ -56056,7 +56056,7 @@
         </is>
       </c>
       <c r="E1357" s="2" t="n">
-        <v>46073.29770730729</v>
+        <v>46073.29770730324</v>
       </c>
       <c r="F1357" t="n">
         <v>186</v>
@@ -56097,7 +56097,7 @@
         </is>
       </c>
       <c r="E1358" s="2" t="n">
-        <v>46076.38104065323</v>
+        <v>46076.38104064815</v>
       </c>
       <c r="F1358" t="n">
         <v>268</v>
@@ -56138,7 +56138,7 @@
         </is>
       </c>
       <c r="E1359" s="2" t="n">
-        <v>46067.29770733565</v>
+        <v>46067.29770733797</v>
       </c>
       <c r="F1359" t="n">
         <v>164</v>
@@ -56179,7 +56179,7 @@
         </is>
       </c>
       <c r="E1360" s="2" t="n">
-        <v>46088.29770733897</v>
+        <v>46088.29770733797</v>
       </c>
       <c r="F1360" t="n">
         <v>37</v>
@@ -56220,7 +56220,7 @@
         </is>
       </c>
       <c r="E1361" s="2" t="n">
-        <v>46085.50604067558</v>
+        <v>46085.50604067129</v>
       </c>
       <c r="F1361" t="n">
         <v>221</v>
@@ -56261,7 +56261,7 @@
         </is>
       </c>
       <c r="E1362" s="2" t="n">
-        <v>46083.13104068177</v>
+        <v>46083.13104068287</v>
       </c>
       <c r="F1362" t="n">
         <v>166</v>
@@ -56302,7 +56302,7 @@
         </is>
       </c>
       <c r="E1363" s="2" t="n">
-        <v>46091.67270735798</v>
+        <v>46091.67270736111</v>
       </c>
       <c r="F1363" t="n">
         <v>250</v>
@@ -56343,7 +56343,7 @@
         </is>
       </c>
       <c r="E1364" s="2" t="n">
-        <v>46078.67270736746</v>
+        <v>46078.67270737269</v>
       </c>
       <c r="F1364" t="n">
         <v>157</v>
@@ -56384,7 +56384,7 @@
         </is>
       </c>
       <c r="E1365" s="2" t="n">
-        <v>46083.71437403731</v>
+        <v>46083.71437403935</v>
       </c>
       <c r="F1365" t="n">
         <v>154</v>
@@ -56401,6 +56401,662 @@
       </c>
       <c r="I1365" t="n">
         <v>15.97</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>efd52dc8-db6e-45fe-b731-c29956941a33</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>aca6b24b-5514-4530-a42a-b7aa2fab6499</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1366" s="2" t="n">
+        <v>46084.41726441612</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1366" t="n">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>80e3836f-920a-4087-ad7b-d10ced418ef7</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>1554212b-44c2-469a-9e24-6c7ade110808</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1367" s="2" t="n">
+        <v>46086.04226442067</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>241</v>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1367" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>c1fe32f3-3418-41df-8482-e09ad4e57e59</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>60464ddc-6e71-4e1a-a46d-c9f2c8e7938b</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1368" s="2" t="n">
+        <v>46079.20893110046</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1368" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>bd25f6fd-2ea4-4e5d-89ec-df8f23e474cc</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>f19ae37c-fd65-4cf6-b0ab-a3f627eb93ef</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1369" s="2" t="n">
+        <v>46074.37559779626</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1369" t="n">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>b0a5df5d-e5bb-40ef-97fe-d280fb74b445</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>0f119790-a233-4cc1-b210-ff63caa7aa02</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1370" s="2" t="n">
+        <v>46076.70893113933</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1370" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>d7d39ee7-cca2-4887-8336-4b24330266a8</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>6083aebf-67c7-46cc-b0f6-08e42147d545</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1371" s="2" t="n">
+        <v>46081.16726449159</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>256</v>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1371" t="n">
+        <v>13.11</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>a1966495-1bbf-4ece-981a-66acbfbdeeb4</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>95434fc4-dcdf-450e-9645-eb1ee87abace</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1372" s="2" t="n">
+        <v>46089.41726449504</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1372" t="n">
+        <v>9.960000000000001</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>3a084a13-51ed-4222-a5e4-abdc719ab743</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>c5d2f921-07e7-4b32-85e1-16277216694d</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1373" s="2" t="n">
+        <v>46080.16726449829</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1373" t="n">
+        <v>12.18</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>0c218519-002f-4e22-8b9f-04ba1b1c54c8</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>4c824f20-d9fe-425d-a0b7-0487648f4eba</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1374" s="2" t="n">
+        <v>46087.66726450151</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>152</v>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1374" t="n">
+        <v>13.88</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>5e072380-9e6d-4af6-aa4f-812b3bbc43f3</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>deec2ed8-9149-4389-bbf4-9666cfc36a06</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1375" s="2" t="n">
+        <v>46096.20893118437</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1375" t="n">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>b2c70f9e-4a51-4edb-8b12-9092b0b28393</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>eae4661e-b1b6-4e92-a28d-233fe16d5d29</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1376" s="2" t="n">
+        <v>46093.58393120343</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1376" t="n">
+        <v>17.31</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>de884166-78f8-4cf5-92f4-06b0c99310b1</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>69546235-e199-4ddb-a75d-0f4eaf3219bb</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1377" s="2" t="n">
+        <v>46069.62559787346</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>194</v>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1377" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>23e3c7df-1a46-414c-9d4a-a725da9b79d2</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>10b9c2e7-2d56-4aac-af88-432974a787a4</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1378" s="2" t="n">
+        <v>46067.62559788015</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1378" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>19bb72ea-7a6c-485b-a34b-409579e94e25</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>00a8faed-7d25-42c8-b006-aa32478cb614</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1379" s="2" t="n">
+        <v>46067.66726455028</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1379" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>5502fe76-0505-4767-8ca8-b17f6ceb3059</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>467f80d5-3043-4f93-b300-0ec3df78bedd</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1380" s="2" t="n">
+        <v>46090.95893122016</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1380" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>4e046d8d-f04a-4f5b-b54f-ba4d0a716339</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>201e78a9-64bb-424e-8d17-01b871dac61a</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1381" s="2" t="n">
+        <v>46085.70893123292</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>130</v>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1381" t="n">
+        <v>3.14</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1381"/>
+  <dimension ref="A1:I1402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56425,7 +56425,7 @@
         </is>
       </c>
       <c r="E1366" s="2" t="n">
-        <v>46084.41726441612</v>
+        <v>46084.4172644213</v>
       </c>
       <c r="F1366" t="n">
         <v>99</v>
@@ -56466,7 +56466,7 @@
         </is>
       </c>
       <c r="E1367" s="2" t="n">
-        <v>46086.04226442067</v>
+        <v>46086.0422644213</v>
       </c>
       <c r="F1367" t="n">
         <v>241</v>
@@ -56507,7 +56507,7 @@
         </is>
       </c>
       <c r="E1368" s="2" t="n">
-        <v>46079.20893110046</v>
+        <v>46079.20893109954</v>
       </c>
       <c r="F1368" t="n">
         <v>32</v>
@@ -56548,7 +56548,7 @@
         </is>
       </c>
       <c r="E1369" s="2" t="n">
-        <v>46074.37559779626</v>
+        <v>46074.37559780093</v>
       </c>
       <c r="F1369" t="n">
         <v>78</v>
@@ -56589,7 +56589,7 @@
         </is>
       </c>
       <c r="E1370" s="2" t="n">
-        <v>46076.70893113933</v>
+        <v>46076.70893113426</v>
       </c>
       <c r="F1370" t="n">
         <v>49</v>
@@ -56630,7 +56630,7 @@
         </is>
       </c>
       <c r="E1371" s="2" t="n">
-        <v>46081.16726449159</v>
+        <v>46081.16726449074</v>
       </c>
       <c r="F1371" t="n">
         <v>256</v>
@@ -56671,7 +56671,7 @@
         </is>
       </c>
       <c r="E1372" s="2" t="n">
-        <v>46089.41726449504</v>
+        <v>46089.41726449074</v>
       </c>
       <c r="F1372" t="n">
         <v>71</v>
@@ -56712,7 +56712,7 @@
         </is>
       </c>
       <c r="E1373" s="2" t="n">
-        <v>46080.16726449829</v>
+        <v>46080.16726450231</v>
       </c>
       <c r="F1373" t="n">
         <v>219</v>
@@ -56753,7 +56753,7 @@
         </is>
       </c>
       <c r="E1374" s="2" t="n">
-        <v>46087.66726450151</v>
+        <v>46087.66726450231</v>
       </c>
       <c r="F1374" t="n">
         <v>152</v>
@@ -56794,7 +56794,7 @@
         </is>
       </c>
       <c r="E1375" s="2" t="n">
-        <v>46096.20893118437</v>
+        <v>46096.20893118055</v>
       </c>
       <c r="F1375" t="n">
         <v>111</v>
@@ -56835,7 +56835,7 @@
         </is>
       </c>
       <c r="E1376" s="2" t="n">
-        <v>46093.58393120343</v>
+        <v>46093.58393120371</v>
       </c>
       <c r="F1376" t="n">
         <v>161</v>
@@ -56876,7 +56876,7 @@
         </is>
       </c>
       <c r="E1377" s="2" t="n">
-        <v>46069.62559787346</v>
+        <v>46069.62559787037</v>
       </c>
       <c r="F1377" t="n">
         <v>194</v>
@@ -56917,7 +56917,7 @@
         </is>
       </c>
       <c r="E1378" s="2" t="n">
-        <v>46067.62559788015</v>
+        <v>46067.62559788195</v>
       </c>
       <c r="F1378" t="n">
         <v>120</v>
@@ -56958,7 +56958,7 @@
         </is>
       </c>
       <c r="E1379" s="2" t="n">
-        <v>46067.66726455028</v>
+        <v>46067.66726454861</v>
       </c>
       <c r="F1379" t="n">
         <v>135</v>
@@ -56999,7 +56999,7 @@
         </is>
       </c>
       <c r="E1380" s="2" t="n">
-        <v>46090.95893122016</v>
+        <v>46090.95893121527</v>
       </c>
       <c r="F1380" t="n">
         <v>43</v>
@@ -57040,7 +57040,7 @@
         </is>
       </c>
       <c r="E1381" s="2" t="n">
-        <v>46085.70893123292</v>
+        <v>46085.70893123843</v>
       </c>
       <c r="F1381" t="n">
         <v>130</v>
@@ -57057,6 +57057,867 @@
       </c>
       <c r="I1381" t="n">
         <v>3.14</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>041e7f9e-e663-482d-8d5e-113e9aa96857</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>720d29e7-78ca-41f8-9e48-d7e2349f341c</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1382" s="2" t="n">
+        <v>46091.49147911149</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1382" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>7724b5d3-c2b7-47d7-8514-04b065aaa3cb</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>d5943736-d4fe-4616-ba92-50c2cc0543fc</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1383" s="2" t="n">
+        <v>46083.32481245133</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>238</v>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1383" t="n">
+        <v>13.77</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>0a2ec7fe-1ae3-4bcc-a062-fd2ecb3ea783</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>878e2dcc-3688-49c3-8bf6-8f6363749023</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1384" s="2" t="n">
+        <v>46085.44981246075</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>149</v>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1384" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>574587ed-85a4-43e6-ad0a-af4541870a38</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>bdeea709-9b0b-4185-a96a-1acb1d0d0d16</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1385" s="2" t="n">
+        <v>46092.36647914351</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>294</v>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1385" t="n">
+        <v>17.18</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>d5a25012-30b4-4992-bd20-5e3308f7204e</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>993bbaf1-9b79-433e-be10-4f916c6ad636</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1386" s="2" t="n">
+        <v>46084.3248124801</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1386" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2d5a7cfb-5f71-412c-8ecc-b4039c1cbcda</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>bdcec807-da13-476d-b8c7-b62e5455e146</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1387" s="2" t="n">
+        <v>46075.86647915636</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1387" t="n">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>66619c99-5073-4c2f-889a-4cbdb98b341a</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>18c108b7-7c60-4e82-b8c0-8baf365baa8b</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1388" s="2" t="n">
+        <v>46090.65814582927</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>128</v>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1388" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>8561bd77-b6f1-4b8f-a4fb-c90b36bbc54b</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>c49b6e67-abb0-4d37-8821-56a7e58ea359</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1389" s="2" t="n">
+        <v>46094.36647916908</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>290</v>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1389" t="n">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>40c04fb4-9baa-4e10-8800-4cc1f8433eaa</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>57480402-6498-4db3-87df-9a67cad1c0ad</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1390" s="2" t="n">
+        <v>46088.82481251006</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>56</v>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1390" t="n">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>392b0d15-880f-469c-9c34-16c422115af3</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>3e243556-2999-430a-a5c5-1a8b09c8a26c</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1391" s="2" t="n">
+        <v>46083.65814584662</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1391" t="n">
+        <v>16.86</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>235c7463-d67d-4d3a-9c41-2ca2e606cca2</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>a4ec492e-e745-4c2a-9536-074a878fadab</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1392" s="2" t="n">
+        <v>46082.57481252978</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>116</v>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1392" t="n">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>76ca7fb2-0b22-477c-8d8f-a8080956731e</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>aef3a830-35ae-4259-834e-b70fd4a2c8da</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1393" s="2" t="n">
+        <v>46079.86647920236</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1393" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>6a635546-c2c6-40e5-a264-85c2303d975d</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>b36d487d-f4a4-496f-ac59-3b99c0c79ea4</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1394" s="2" t="n">
+        <v>46086.94981254907</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1394" t="n">
+        <v>19.59</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>c8e0ef5c-9fcc-4b95-8874-d3f8ad520799</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>d4077156-b06e-4f8f-be34-d7e2336ce439</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1395" s="2" t="n">
+        <v>46068.19981255545</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>146</v>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1395" t="n">
+        <v>15.87</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2ca74192-cdef-49ce-a878-d87529c93093</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>9ffe2a4c-a63e-4322-b697-706e71234018</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1396" s="2" t="n">
+        <v>46086.07481255876</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>235</v>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1396" t="n">
+        <v>17.84</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>e070a123-4694-443f-a032-8e1cf90bfd4e</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>e6dc6948-9b17-4cac-b71c-75912339b85f</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1397" s="2" t="n">
+        <v>46084.99147923485</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>299</v>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1397" t="n">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>4d6f8420-4ea3-4ee1-a939-e5aa266d04b1</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>5a7d5080-5973-4fad-946f-5fd3ca8018b6</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1398" s="2" t="n">
+        <v>46075.69981257441</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>251</v>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1398" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>f0675e95-bf33-4fa6-a4c5-378f689630d5</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>788e0eac-30e3-4262-b345-2322accf9b60</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1399" s="2" t="n">
+        <v>46080.65814592048</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>231</v>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1399" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>88fc8c56-655b-42b9-a5db-954bf9ebf90a</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>3801c712-6326-4a2f-9606-61192611f821</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1400" s="2" t="n">
+        <v>46074.86647925732</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1400" t="n">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>8fc7ce16-a531-4971-b283-be01f2087126</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>0fec882f-d353-40c4-81d2-88a5aab43f5a</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1401" s="2" t="n">
+        <v>46090.8664792605</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1401" t="n">
+        <v>16.66</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>dba56109-c8c1-408d-9b2a-503dce600065</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>33f306a8-a368-4b73-b7db-f1b57b60e109</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1402" s="2" t="n">
+        <v>46089.11647926374</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1402" t="n">
+        <v>5.67</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1402"/>
+  <dimension ref="A1:I1420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57081,7 +57081,7 @@
         </is>
       </c>
       <c r="E1382" s="2" t="n">
-        <v>46091.49147911149</v>
+        <v>46091.49147910879</v>
       </c>
       <c r="F1382" t="n">
         <v>156</v>
@@ -57122,7 +57122,7 @@
         </is>
       </c>
       <c r="E1383" s="2" t="n">
-        <v>46083.32481245133</v>
+        <v>46083.32481245371</v>
       </c>
       <c r="F1383" t="n">
         <v>238</v>
@@ -57163,7 +57163,7 @@
         </is>
       </c>
       <c r="E1384" s="2" t="n">
-        <v>46085.44981246075</v>
+        <v>46085.44981246527</v>
       </c>
       <c r="F1384" t="n">
         <v>149</v>
@@ -57204,7 +57204,7 @@
         </is>
       </c>
       <c r="E1385" s="2" t="n">
-        <v>46092.36647914351</v>
+        <v>46092.36647914352</v>
       </c>
       <c r="F1385" t="n">
         <v>294</v>
@@ -57245,7 +57245,7 @@
         </is>
       </c>
       <c r="E1386" s="2" t="n">
-        <v>46084.3248124801</v>
+        <v>46084.32481247685</v>
       </c>
       <c r="F1386" t="n">
         <v>145</v>
@@ -57286,7 +57286,7 @@
         </is>
       </c>
       <c r="E1387" s="2" t="n">
-        <v>46075.86647915636</v>
+        <v>46075.86647915509</v>
       </c>
       <c r="F1387" t="n">
         <v>54</v>
@@ -57327,7 +57327,7 @@
         </is>
       </c>
       <c r="E1388" s="2" t="n">
-        <v>46090.65814582927</v>
+        <v>46090.65814583333</v>
       </c>
       <c r="F1388" t="n">
         <v>128</v>
@@ -57368,7 +57368,7 @@
         </is>
       </c>
       <c r="E1389" s="2" t="n">
-        <v>46094.36647916908</v>
+        <v>46094.36647916667</v>
       </c>
       <c r="F1389" t="n">
         <v>290</v>
@@ -57409,7 +57409,7 @@
         </is>
       </c>
       <c r="E1390" s="2" t="n">
-        <v>46088.82481251006</v>
+        <v>46088.82481251157</v>
       </c>
       <c r="F1390" t="n">
         <v>56</v>
@@ -57450,7 +57450,7 @@
         </is>
       </c>
       <c r="E1391" s="2" t="n">
-        <v>46083.65814584662</v>
+        <v>46083.65814584491</v>
       </c>
       <c r="F1391" t="n">
         <v>272</v>
@@ -57491,7 +57491,7 @@
         </is>
       </c>
       <c r="E1392" s="2" t="n">
-        <v>46082.57481252978</v>
+        <v>46082.57481253472</v>
       </c>
       <c r="F1392" t="n">
         <v>116</v>
@@ -57532,7 +57532,7 @@
         </is>
       </c>
       <c r="E1393" s="2" t="n">
-        <v>46079.86647920236</v>
+        <v>46079.86647920139</v>
       </c>
       <c r="F1393" t="n">
         <v>40</v>
@@ -57573,7 +57573,7 @@
         </is>
       </c>
       <c r="E1394" s="2" t="n">
-        <v>46086.94981254907</v>
+        <v>46086.9498125463</v>
       </c>
       <c r="F1394" t="n">
         <v>233</v>
@@ -57614,7 +57614,7 @@
         </is>
       </c>
       <c r="E1395" s="2" t="n">
-        <v>46068.19981255545</v>
+        <v>46068.19981255787</v>
       </c>
       <c r="F1395" t="n">
         <v>146</v>
@@ -57655,7 +57655,7 @@
         </is>
       </c>
       <c r="E1396" s="2" t="n">
-        <v>46086.07481255876</v>
+        <v>46086.07481255787</v>
       </c>
       <c r="F1396" t="n">
         <v>235</v>
@@ -57696,7 +57696,7 @@
         </is>
       </c>
       <c r="E1397" s="2" t="n">
-        <v>46084.99147923485</v>
+        <v>46084.99147923611</v>
       </c>
       <c r="F1397" t="n">
         <v>299</v>
@@ -57737,7 +57737,7 @@
         </is>
       </c>
       <c r="E1398" s="2" t="n">
-        <v>46075.69981257441</v>
+        <v>46075.69981256944</v>
       </c>
       <c r="F1398" t="n">
         <v>251</v>
@@ -57778,7 +57778,7 @@
         </is>
       </c>
       <c r="E1399" s="2" t="n">
-        <v>46080.65814592048</v>
+        <v>46080.65814592593</v>
       </c>
       <c r="F1399" t="n">
         <v>231</v>
@@ -57819,7 +57819,7 @@
         </is>
       </c>
       <c r="E1400" s="2" t="n">
-        <v>46074.86647925732</v>
+        <v>46074.86647925926</v>
       </c>
       <c r="F1400" t="n">
         <v>265</v>
@@ -57860,7 +57860,7 @@
         </is>
       </c>
       <c r="E1401" s="2" t="n">
-        <v>46090.8664792605</v>
+        <v>46090.86647925926</v>
       </c>
       <c r="F1401" t="n">
         <v>93</v>
@@ -57901,7 +57901,7 @@
         </is>
       </c>
       <c r="E1402" s="2" t="n">
-        <v>46089.11647926374</v>
+        <v>46089.11647925926</v>
       </c>
       <c r="F1402" t="n">
         <v>229</v>
@@ -57918,6 +57918,744 @@
       </c>
       <c r="I1402" t="n">
         <v>5.67</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>87f3e16a-b87c-4e80-aebd-92ccc68beb87</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>f93b5a6c-25f1-48e1-be61-82629d0caf45</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1403" s="2" t="n">
+        <v>46092.01632209864</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>258</v>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1403" t="n">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>7c7654a0-fb66-44d9-8000-47a232342120</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>2848be88-6c4a-4276-b456-d5b2ab270d85</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1404" s="2" t="n">
+        <v>46083.55798876832</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1404" t="n">
+        <v>16.51</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>9b1261c5-bfbe-4388-b15e-8c5f91b185b6</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>7398ee89-6428-4963-b242-71426724fe43</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1405" s="2" t="n">
+        <v>46085.30798877138</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1405" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>ffc42f49-62c9-41b0-b78e-8218036033cb</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>4c3546ea-407f-4e61-b88b-cf0c5dfcdcd5</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1406" s="2" t="n">
+        <v>46090.22465544155</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1406" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>b6640bfe-00b1-4e07-80d7-4b29c1f2526a</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>ecb94131-d4f0-418c-abb1-521893a05497</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1407" s="2" t="n">
+        <v>46089.68298878097</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>243</v>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1407" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>1fba9ee7-bf4c-44a3-a32c-e8cd3adce9c6</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>be0cdedb-06e7-4163-8330-645689141783</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1408" s="2" t="n">
+        <v>46084.72465545389</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1408" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>23e888e2-12c0-4c0b-bf9b-dbbb04101330</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>b39192ac-406a-4f29-b690-43e0bedd9c9a</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1409" s="2" t="n">
+        <v>46097.09965550083</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>127</v>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1409" t="n">
+        <v>10.69</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>ca285a62-e667-45b0-9e20-bde437315a4a</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>34585048-c3d0-4784-8070-b5a534d2301c</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1410" s="2" t="n">
+        <v>46071.39132217051</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>87</v>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1410" t="n">
+        <v>19.28</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>7e2a954e-7a24-4d9a-b29d-de6269ccdaa5</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>2f5ed040-84de-4543-9c1c-003707f602bc</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1411" s="2" t="n">
+        <v>46068.47465550675</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1411" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>30c0cdf5-fa82-491d-9683-4882cdd148c8</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>302496be-ba7e-4a5d-aef3-ae769a8760fc</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1412" s="2" t="n">
+        <v>46073.72465551856</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1412" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>5790e464-23be-40b4-ad4a-a81ca8a9360b</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>f9141d65-6cd2-4b88-a0bb-668595e694a9</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1413" s="2" t="n">
+        <v>46066.68298886067</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1413" t="n">
+        <v>19.15</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>b7e5d8d7-fbf3-4a0d-a336-8a74f35ebf8d</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>7460801b-4fad-405f-a8ff-1c99a68546ba</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1414" s="2" t="n">
+        <v>46085.47465553024</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>187</v>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1414" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>abecfd46-1b93-440f-8311-2fcbc4f385ff</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>d153f903-45af-4888-b3d9-10ac296525ce</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1415" s="2" t="n">
+        <v>46089.84965553668</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>179</v>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1415" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>e5850744-257d-46ee-8398-5a7c85e91fa7</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>db395035-424e-4272-9417-f559f2532359</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1416" s="2" t="n">
+        <v>46070.93298887878</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1416" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>d684fd7c-f773-4270-883a-430812c4f03b</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>464796d2-a561-4793-87c2-05d3ac49031a</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1417" s="2" t="n">
+        <v>46080.89132221512</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1417" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>ae0ccd90-45e1-4ee3-b0fe-12d03eb2352a</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>9fdb5198-c062-4c9c-ac89-63b4651474b0</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1418" s="2" t="n">
+        <v>46082.34965555136</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>235</v>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1418" t="n">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>cfff5b9b-df51-4b25-a74b-36b7a51d78c7</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>1158d580-8d8a-43d0-be5d-6559794dfd4a</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1419" s="2" t="n">
+        <v>46087.09965556298</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>209</v>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1419" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>abc10318-e6e3-49d8-b065-44f6784e19f0</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>a786838b-e381-4bd1-b805-c2524c2de491</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1420" s="2" t="n">
+        <v>46082.89132223569</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1420" t="n">
+        <v>18.18</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1420"/>
+  <dimension ref="A1:I1440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57942,7 +57942,7 @@
         </is>
       </c>
       <c r="E1403" s="2" t="n">
-        <v>46092.01632209864</v>
+        <v>46092.01632209491</v>
       </c>
       <c r="F1403" t="n">
         <v>258</v>
@@ -57983,7 +57983,7 @@
         </is>
       </c>
       <c r="E1404" s="2" t="n">
-        <v>46083.55798876832</v>
+        <v>46083.55798877315</v>
       </c>
       <c r="F1404" t="n">
         <v>54</v>
@@ -58024,7 +58024,7 @@
         </is>
       </c>
       <c r="E1405" s="2" t="n">
-        <v>46085.30798877138</v>
+        <v>46085.30798877315</v>
       </c>
       <c r="F1405" t="n">
         <v>272</v>
@@ -58065,7 +58065,7 @@
         </is>
       </c>
       <c r="E1406" s="2" t="n">
-        <v>46090.22465544155</v>
+        <v>46090.22465543982</v>
       </c>
       <c r="F1406" t="n">
         <v>168</v>
@@ -58106,7 +58106,7 @@
         </is>
       </c>
       <c r="E1407" s="2" t="n">
-        <v>46089.68298878097</v>
+        <v>46089.68298878472</v>
       </c>
       <c r="F1407" t="n">
         <v>243</v>
@@ -58147,7 +58147,7 @@
         </is>
       </c>
       <c r="E1408" s="2" t="n">
-        <v>46084.72465545389</v>
+        <v>46084.72465545139</v>
       </c>
       <c r="F1408" t="n">
         <v>216</v>
@@ -58188,7 +58188,7 @@
         </is>
       </c>
       <c r="E1409" s="2" t="n">
-        <v>46097.09965550083</v>
+        <v>46097.09965549769</v>
       </c>
       <c r="F1409" t="n">
         <v>127</v>
@@ -58229,7 +58229,7 @@
         </is>
       </c>
       <c r="E1410" s="2" t="n">
-        <v>46071.39132217051</v>
+        <v>46071.39132217593</v>
       </c>
       <c r="F1410" t="n">
         <v>87</v>
@@ -58270,7 +58270,7 @@
         </is>
       </c>
       <c r="E1411" s="2" t="n">
-        <v>46068.47465550675</v>
+        <v>46068.47465550926</v>
       </c>
       <c r="F1411" t="n">
         <v>74</v>
@@ -58311,7 +58311,7 @@
         </is>
       </c>
       <c r="E1412" s="2" t="n">
-        <v>46073.72465551856</v>
+        <v>46073.72465552083</v>
       </c>
       <c r="F1412" t="n">
         <v>30</v>
@@ -58352,7 +58352,7 @@
         </is>
       </c>
       <c r="E1413" s="2" t="n">
-        <v>46066.68298886067</v>
+        <v>46066.68298886574</v>
       </c>
       <c r="F1413" t="n">
         <v>42</v>
@@ -58393,7 +58393,7 @@
         </is>
       </c>
       <c r="E1414" s="2" t="n">
-        <v>46085.47465553024</v>
+        <v>46085.47465553241</v>
       </c>
       <c r="F1414" t="n">
         <v>187</v>
@@ -58434,7 +58434,7 @@
         </is>
       </c>
       <c r="E1415" s="2" t="n">
-        <v>46089.84965553668</v>
+        <v>46089.84965553241</v>
       </c>
       <c r="F1415" t="n">
         <v>179</v>
@@ -58475,7 +58475,7 @@
         </is>
       </c>
       <c r="E1416" s="2" t="n">
-        <v>46070.93298887878</v>
+        <v>46070.93298887731</v>
       </c>
       <c r="F1416" t="n">
         <v>137</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="E1417" s="2" t="n">
-        <v>46080.89132221512</v>
+        <v>46080.89132221065</v>
       </c>
       <c r="F1417" t="n">
         <v>63</v>
@@ -58557,7 +58557,7 @@
         </is>
       </c>
       <c r="E1418" s="2" t="n">
-        <v>46082.34965555136</v>
+        <v>46082.34965555555</v>
       </c>
       <c r="F1418" t="n">
         <v>235</v>
@@ -58598,7 +58598,7 @@
         </is>
       </c>
       <c r="E1419" s="2" t="n">
-        <v>46087.09965556298</v>
+        <v>46087.09965556713</v>
       </c>
       <c r="F1419" t="n">
         <v>209</v>
@@ -58639,7 +58639,7 @@
         </is>
       </c>
       <c r="E1420" s="2" t="n">
-        <v>46082.89132223569</v>
+        <v>46082.89132223379</v>
       </c>
       <c r="F1420" t="n">
         <v>89</v>
@@ -58656,6 +58656,826 @@
       </c>
       <c r="I1420" t="n">
         <v>18.18</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>4c62adfc-d1c6-43d2-aa96-a6fdef018b00</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>83c018e3-4271-4e9c-a378-91614f6cc058</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1421" s="2" t="n">
+        <v>46076.41045561214</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>251</v>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1421" t="n">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>8f4f47e0-a37b-43d7-b211-e54ae35a11d5</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>88b2adce-79e4-403b-8a10-68f1df7e60a8</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1422" s="2" t="n">
+        <v>46076.2854556294</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1422" t="n">
+        <v>13.22</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>1c0ad8e4-ac1d-41be-889b-344313b77b77</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>6d2b5d0f-3c8a-4896-931c-5c8371194ff9</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1423" s="2" t="n">
+        <v>46088.5771223112</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>157</v>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1423" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>bf00fd79-c0bf-4322-b378-35a98d6a8fe5</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>3c43aa41-afa6-41ec-a80a-d929b5abf07c</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1424" s="2" t="n">
+        <v>46092.6604556475</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1424" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>f4fafe77-5d0c-4623-b827-585b91571046</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>fd46c116-9e75-4f3b-b5d1-4c3cbf61537e</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1425" s="2" t="n">
+        <v>46074.57712232605</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1425" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>5db9a229-1bc6-408d-b268-0685e664e511</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>8987bb73-1dae-41f5-9cc1-9fda0c4e43e6</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1426" s="2" t="n">
+        <v>46070.28545566827</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1426" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>91f5cc82-45f2-4789-804d-31a9d77a1a7f</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>434897eb-ac91-4116-9962-2dbcec826976</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1427" s="2" t="n">
+        <v>46091.82712233791</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1427" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>0ab2e589-b1b4-4752-818a-5c6ef297aaaf</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>16b39dce-130f-479a-8621-d5a3e7933f3b</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1428" s="2" t="n">
+        <v>46080.45212234096</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>182</v>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1428" t="n">
+        <v>16.11</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>c3af5225-0635-4921-900e-94fb0f4297ec</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>babfc56f-bf2e-4396-ab2b-6cdd3978a6a4</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1429" s="2" t="n">
+        <v>46092.82712234456</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1429" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>8231ab84-c997-4483-96ae-c0746d827bb9</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>8ce0b448-3ccb-4c28-ba1c-25bf348970eb</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1430" s="2" t="n">
+        <v>46078.99378902007</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>131</v>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1430" t="n">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>8b0b1b34-f57f-46eb-b8d7-efc99290c090</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>9000766e-7dca-45fb-a495-6ed944453192</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1431" s="2" t="n">
+        <v>46093.49378902835</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1431" t="n">
+        <v>19.28</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>8c5e88f9-6c2c-4d75-bc60-7c15f05cf593</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>70104fd8-1988-46cf-b0c2-6365c19599cf</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1432" s="2" t="n">
+        <v>46075.53545570149</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1432" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>ca6cd6ac-5373-4fe3-8296-d33a76ce280e</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>a8841efd-b56f-4faf-ba21-5a5cf77a60ed</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1433" s="2" t="n">
+        <v>46072.99378904019</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>276</v>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1433" t="n">
+        <v>12.59</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>90fdb7a0-2f39-493f-9617-8d34f5641430</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>28424044-8ce8-493a-a844-903e34096210</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1434" s="2" t="n">
+        <v>46086.91045572448</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>221</v>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1434" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>d8efc622-c33b-41e7-bb72-fff2e538d0ba</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>72b4f35c-19ed-4a5a-ae30-373b31cfaecc</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1435" s="2" t="n">
+        <v>46075.86878907105</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1435" t="n">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>7ad16d97-c95e-4ad4-816d-ce60020fca4b</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>86730ff0-2f83-46fb-bde9-3e110c6b3f6d</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1436" s="2" t="n">
+        <v>46097.36878908508</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1436" t="n">
+        <v>15.03</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>910cd38d-6e95-4a57-bb49-8c9630d1f0aa</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>b5b8a20b-a345-41c4-8c1d-a7c0983a07f5</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1437" s="2" t="n">
+        <v>46081.28545575486</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1437" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>dde340ec-ff0c-4b06-a479-3aacf6cf2023</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>64d4b17b-ba77-40b8-a563-8cbdaaa533aa</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1438" s="2" t="n">
+        <v>46088.36878909738</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1438" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>6a7e7c3d-dcc4-4d56-bb96-1fbd38204c4d</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>33e7882c-f411-43ca-9352-63a53cd06e3d</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1439" s="2" t="n">
+        <v>46086.74378910643</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1439" t="n">
+        <v>14.31</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>9f028c8c-7bfa-4d06-97e9-b058d7aa3c9d</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>65931096-a377-474a-9a27-30bdf5fff4cb</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1440" s="2" t="n">
+        <v>46078.74378910949</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1440" t="n">
+        <v>15.33</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1440"/>
+  <dimension ref="A1:I1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58680,7 +58680,7 @@
         </is>
       </c>
       <c r="E1421" s="2" t="n">
-        <v>46076.41045561214</v>
+        <v>46076.41045561343</v>
       </c>
       <c r="F1421" t="n">
         <v>251</v>
@@ -58721,7 +58721,7 @@
         </is>
       </c>
       <c r="E1422" s="2" t="n">
-        <v>46076.2854556294</v>
+        <v>46076.285455625</v>
       </c>
       <c r="F1422" t="n">
         <v>102</v>
@@ -58762,7 +58762,7 @@
         </is>
       </c>
       <c r="E1423" s="2" t="n">
-        <v>46088.5771223112</v>
+        <v>46088.57712231481</v>
       </c>
       <c r="F1423" t="n">
         <v>157</v>
@@ -58803,7 +58803,7 @@
         </is>
       </c>
       <c r="E1424" s="2" t="n">
-        <v>46092.6604556475</v>
+        <v>46092.66045564815</v>
       </c>
       <c r="F1424" t="n">
         <v>84</v>
@@ -58844,7 +58844,7 @@
         </is>
       </c>
       <c r="E1425" s="2" t="n">
-        <v>46074.57712232605</v>
+        <v>46074.57712232639</v>
       </c>
       <c r="F1425" t="n">
         <v>63</v>
@@ -58885,7 +58885,7 @@
         </is>
       </c>
       <c r="E1426" s="2" t="n">
-        <v>46070.28545566827</v>
+        <v>46070.2854556713</v>
       </c>
       <c r="F1426" t="n">
         <v>188</v>
@@ -58926,7 +58926,7 @@
         </is>
       </c>
       <c r="E1427" s="2" t="n">
-        <v>46091.82712233791</v>
+        <v>46091.82712233796</v>
       </c>
       <c r="F1427" t="n">
         <v>229</v>
@@ -58967,7 +58967,7 @@
         </is>
       </c>
       <c r="E1428" s="2" t="n">
-        <v>46080.45212234096</v>
+        <v>46080.45212233796</v>
       </c>
       <c r="F1428" t="n">
         <v>182</v>
@@ -59008,7 +59008,7 @@
         </is>
       </c>
       <c r="E1429" s="2" t="n">
-        <v>46092.82712234456</v>
+        <v>46092.82712234954</v>
       </c>
       <c r="F1429" t="n">
         <v>50</v>
@@ -59049,7 +59049,7 @@
         </is>
       </c>
       <c r="E1430" s="2" t="n">
-        <v>46078.99378902007</v>
+        <v>46078.9937890162</v>
       </c>
       <c r="F1430" t="n">
         <v>131</v>
@@ -59090,7 +59090,7 @@
         </is>
       </c>
       <c r="E1431" s="2" t="n">
-        <v>46093.49378902835</v>
+        <v>46093.49378902778</v>
       </c>
       <c r="F1431" t="n">
         <v>259</v>
@@ -59131,7 +59131,7 @@
         </is>
       </c>
       <c r="E1432" s="2" t="n">
-        <v>46075.53545570149</v>
+        <v>46075.53545570602</v>
       </c>
       <c r="F1432" t="n">
         <v>123</v>
@@ -59172,7 +59172,7 @@
         </is>
       </c>
       <c r="E1433" s="2" t="n">
-        <v>46072.99378904019</v>
+        <v>46072.99378903935</v>
       </c>
       <c r="F1433" t="n">
         <v>276</v>
@@ -59213,7 +59213,7 @@
         </is>
       </c>
       <c r="E1434" s="2" t="n">
-        <v>46086.91045572448</v>
+        <v>46086.91045572916</v>
       </c>
       <c r="F1434" t="n">
         <v>221</v>
@@ -59254,7 +59254,7 @@
         </is>
       </c>
       <c r="E1435" s="2" t="n">
-        <v>46075.86878907105</v>
+        <v>46075.86878907408</v>
       </c>
       <c r="F1435" t="n">
         <v>99</v>
@@ -59295,7 +59295,7 @@
         </is>
       </c>
       <c r="E1436" s="2" t="n">
-        <v>46097.36878908508</v>
+        <v>46097.36878908565</v>
       </c>
       <c r="F1436" t="n">
         <v>216</v>
@@ -59336,7 +59336,7 @@
         </is>
       </c>
       <c r="E1437" s="2" t="n">
-        <v>46081.28545575486</v>
+        <v>46081.28545575232</v>
       </c>
       <c r="F1437" t="n">
         <v>216</v>
@@ -59377,7 +59377,7 @@
         </is>
       </c>
       <c r="E1438" s="2" t="n">
-        <v>46088.36878909738</v>
+        <v>46088.36878909722</v>
       </c>
       <c r="F1438" t="n">
         <v>53</v>
@@ -59418,7 +59418,7 @@
         </is>
       </c>
       <c r="E1439" s="2" t="n">
-        <v>46086.74378910643</v>
+        <v>46086.7437891088</v>
       </c>
       <c r="F1439" t="n">
         <v>133</v>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="E1440" s="2" t="n">
-        <v>46078.74378910949</v>
+        <v>46078.7437891088</v>
       </c>
       <c r="F1440" t="n">
         <v>77</v>
@@ -59476,6 +59476,867 @@
       </c>
       <c r="I1440" t="n">
         <v>15.33</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>d6020e31-b449-4c4e-905f-0eb3f441a614</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>e99d6ed5-0261-46c9-8185-cc13f6fe26dd</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1441" s="2" t="n">
+        <v>46077.83586142759</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>248</v>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1441" t="n">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>fb55bd71-df40-4101-86dc-b550c6f62782</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>eb7f4cea-b347-4cb9-9164-26dd7c9084d4</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1442" s="2" t="n">
+        <v>46082.71086143692</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1442" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>00976adb-0822-4ec4-a6f6-946ba4528fed</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>ac9589df-ec2f-448d-bd16-ab15d72154fe</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1443" s="2" t="n">
+        <v>46090.62752810663</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1443" t="n">
+        <v>17.78</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>af3c11e5-98ec-439f-ae11-38e328d1916b</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>e6d9778e-f06d-4faa-8b52-691c228c1827</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1444" s="2" t="n">
+        <v>46078.79419478856</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1444" t="n">
+        <v>17.38</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>c4dd4ee3-849a-47ac-8883-8f8fd6978cf6</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>1a4934ff-3dc6-4918-85de-51671c90a039</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1445" s="2" t="n">
+        <v>46088.79419479187</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1445" t="n">
+        <v>19.13</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>9e3d4067-5619-40c7-9cef-b11be6740376</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>2b93fd29-9d71-4f33-97f5-c75d62fdc9dd</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1446" s="2" t="n">
+        <v>46077.58586146727</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1446" t="n">
+        <v>11.72</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>858bb886-7801-47a9-b9a5-63cd2755b6a6</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>9adeb431-3285-42bc-857d-4c68b746bfc8</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1447" s="2" t="n">
+        <v>46090.21086147346</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1447" t="n">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>c8d5ea2b-9ea8-47f9-b30b-84f1dbbda8f4</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>61899502-2c85-467b-9d50-23ee028e8d38</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1448" s="2" t="n">
+        <v>46086.54419481568</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>261</v>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1448" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>9436cbfa-1e62-4cfd-8fee-12265fc499fd</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>1653c2ac-ada1-4826-a340-d2dbedf42b9c</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1449" s="2" t="n">
+        <v>46088.96086148532</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1449" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>8bce983a-3b2e-48d6-8a80-eb46a539d69d</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>53f7b809-6144-41ce-bdef-49ac28197b6c</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1450" s="2" t="n">
+        <v>46075.54419482461</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1450" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>8dd23657-fa93-454d-b6dc-3b483a5f6a6d</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>45ca3ac6-2ff7-41fb-8f97-05b07f80a0f1</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1451" s="2" t="n">
+        <v>46080.00252816107</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1451" t="n">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>e0c69db3-9fe1-485a-b51a-c59925a1f867</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>761f4523-3f7e-40e5-87ea-6beb743100f7</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1452" s="2" t="n">
+        <v>46090.71086150609</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>155</v>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1452" t="n">
+        <v>18.53</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>118b4370-2b6a-4dde-900d-1713c15c1a21</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>a92c4481-c740-4095-a2f9-c17d3069cb6f</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1453" s="2" t="n">
+        <v>46092.00252817572</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1453" t="n">
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>ba8ba40d-b480-46fe-b7ef-e34d9970fdc9</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>234e1c7c-abcb-484d-b2e8-5549e8144e21</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1454" s="2" t="n">
+        <v>46093.08586151212</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>192</v>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1454" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>1fc6365d-5c9e-48ef-a71a-f1e245b093d7</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>80c4ce1b-1723-4eef-b671-efcdcc48aaca</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1455" s="2" t="n">
+        <v>46083.96086151808</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>189</v>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1455" t="n">
+        <v>18.96</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>417c390e-304a-42b5-9789-f0de27c7091a</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>455be0bc-561c-4ee5-85bd-5397f7e0521c</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1456" s="2" t="n">
+        <v>46093.75252819046</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1456" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>919b60f4-15dd-4ce2-9539-1c4e39d13c56</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>381c5f1f-606d-4616-b3c9-1d6f172182aa</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1457" s="2" t="n">
+        <v>46095.2525281936</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>226</v>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1457" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>8dfd16bd-4e30-4813-ba69-69632e307213</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>e8711708-01b0-4c30-8e3f-bc022e095b84</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1458" s="2" t="n">
+        <v>46079.37752819661</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1458" t="n">
+        <v>19.59</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>5dcd1b15-22d1-4b29-b360-1e38864016fc</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>fc4d879e-3d45-4f7b-8483-4e51135ba6c3</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1459" s="2" t="n">
+        <v>46079.37752820536</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>193</v>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1459" t="n">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>e97ce05e-d865-48c2-b886-9cc6b8d7dcbc</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>44ab6d79-c225-4d1b-9c6b-bdedd7ef5a45</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1460" s="2" t="n">
+        <v>46099.00252821985</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>87</v>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1460" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2ea0691a-6508-4d2f-ac9f-bff577df3d56</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>20351498-2ad5-4ac4-84aa-3476a23c9736</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1461" s="2" t="n">
+        <v>46096.79419488984</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>113</v>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1461" t="n">
+        <v>10.85</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1461"/>
+  <dimension ref="A1:I1482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59500,7 +59500,7 @@
         </is>
       </c>
       <c r="E1441" s="2" t="n">
-        <v>46077.83586142759</v>
+        <v>46077.83586142361</v>
       </c>
       <c r="F1441" t="n">
         <v>248</v>
@@ -59541,7 +59541,7 @@
         </is>
       </c>
       <c r="E1442" s="2" t="n">
-        <v>46082.71086143692</v>
+        <v>46082.71086143518</v>
       </c>
       <c r="F1442" t="n">
         <v>168</v>
@@ -59582,7 +59582,7 @@
         </is>
       </c>
       <c r="E1443" s="2" t="n">
-        <v>46090.62752810663</v>
+        <v>46090.62752810185</v>
       </c>
       <c r="F1443" t="n">
         <v>272</v>
@@ -59623,7 +59623,7 @@
         </is>
       </c>
       <c r="E1444" s="2" t="n">
-        <v>46078.79419478856</v>
+        <v>46078.79419479167</v>
       </c>
       <c r="F1444" t="n">
         <v>133</v>
@@ -59664,7 +59664,7 @@
         </is>
       </c>
       <c r="E1445" s="2" t="n">
-        <v>46088.79419479187</v>
+        <v>46088.79419479167</v>
       </c>
       <c r="F1445" t="n">
         <v>165</v>
@@ -59705,7 +59705,7 @@
         </is>
       </c>
       <c r="E1446" s="2" t="n">
-        <v>46077.58586146727</v>
+        <v>46077.58586146991</v>
       </c>
       <c r="F1446" t="n">
         <v>102</v>
@@ -59746,7 +59746,7 @@
         </is>
       </c>
       <c r="E1447" s="2" t="n">
-        <v>46090.21086147346</v>
+        <v>46090.21086146991</v>
       </c>
       <c r="F1447" t="n">
         <v>137</v>
@@ -59787,7 +59787,7 @@
         </is>
       </c>
       <c r="E1448" s="2" t="n">
-        <v>46086.54419481568</v>
+        <v>46086.54419481481</v>
       </c>
       <c r="F1448" t="n">
         <v>261</v>
@@ -59828,7 +59828,7 @@
         </is>
       </c>
       <c r="E1449" s="2" t="n">
-        <v>46088.96086148532</v>
+        <v>46088.96086148148</v>
       </c>
       <c r="F1449" t="n">
         <v>89</v>
@@ -59869,7 +59869,7 @@
         </is>
       </c>
       <c r="E1450" s="2" t="n">
-        <v>46075.54419482461</v>
+        <v>46075.54419482639</v>
       </c>
       <c r="F1450" t="n">
         <v>273</v>
@@ -59910,7 +59910,7 @@
         </is>
       </c>
       <c r="E1451" s="2" t="n">
-        <v>46080.00252816107</v>
+        <v>46080.00252815972</v>
       </c>
       <c r="F1451" t="n">
         <v>49</v>
@@ -59951,7 +59951,7 @@
         </is>
       </c>
       <c r="E1452" s="2" t="n">
-        <v>46090.71086150609</v>
+        <v>46090.71086150463</v>
       </c>
       <c r="F1452" t="n">
         <v>155</v>
@@ -59992,7 +59992,7 @@
         </is>
       </c>
       <c r="E1453" s="2" t="n">
-        <v>46092.00252817572</v>
+        <v>46092.0025281713</v>
       </c>
       <c r="F1453" t="n">
         <v>37</v>
@@ -60033,7 +60033,7 @@
         </is>
       </c>
       <c r="E1454" s="2" t="n">
-        <v>46093.08586151212</v>
+        <v>46093.08586151621</v>
       </c>
       <c r="F1454" t="n">
         <v>192</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="E1455" s="2" t="n">
-        <v>46083.96086151808</v>
+        <v>46083.96086151621</v>
       </c>
       <c r="F1455" t="n">
         <v>189</v>
@@ -60115,7 +60115,7 @@
         </is>
       </c>
       <c r="E1456" s="2" t="n">
-        <v>46093.75252819046</v>
+        <v>46093.75252819445</v>
       </c>
       <c r="F1456" t="n">
         <v>100</v>
@@ -60156,7 +60156,7 @@
         </is>
       </c>
       <c r="E1457" s="2" t="n">
-        <v>46095.2525281936</v>
+        <v>46095.25252819445</v>
       </c>
       <c r="F1457" t="n">
         <v>226</v>
@@ -60197,7 +60197,7 @@
         </is>
       </c>
       <c r="E1458" s="2" t="n">
-        <v>46079.37752819661</v>
+        <v>46079.37752819445</v>
       </c>
       <c r="F1458" t="n">
         <v>107</v>
@@ -60238,7 +60238,7 @@
         </is>
       </c>
       <c r="E1459" s="2" t="n">
-        <v>46079.37752820536</v>
+        <v>46079.37752820602</v>
       </c>
       <c r="F1459" t="n">
         <v>193</v>
@@ -60279,7 +60279,7 @@
         </is>
       </c>
       <c r="E1460" s="2" t="n">
-        <v>46099.00252821985</v>
+        <v>46099.00252821759</v>
       </c>
       <c r="F1460" t="n">
         <v>87</v>
@@ -60320,7 +60320,7 @@
         </is>
       </c>
       <c r="E1461" s="2" t="n">
-        <v>46096.79419488984</v>
+        <v>46096.79419488426</v>
       </c>
       <c r="F1461" t="n">
         <v>113</v>
@@ -60337,6 +60337,867 @@
       </c>
       <c r="I1461" t="n">
         <v>10.85</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2bf43579-0783-410b-bc5f-8a2a45923344</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>6c58a490-8abc-4b38-a0cd-dbfa6104f8b6</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1462" s="2" t="n">
+        <v>46087.25745870076</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>153</v>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1462" t="n">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>514e00ab-cf87-4301-9e6d-9977fddbcac4</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>d3538d6b-648f-4002-8aa8-26267bcf8c6f</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1463" s="2" t="n">
+        <v>46083.00745870479</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1463" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2e05fca9-2210-480d-969e-585589bdf99e</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>04017b9f-c248-4612-b871-6fb8a9dfadc0</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1464" s="2" t="n">
+        <v>46093.50745870786</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>152</v>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1464" t="n">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>517019e6-87e4-4b51-9bda-5a9a3d063f69</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>a32c4100-69e6-4197-ae92-09af3250a787</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1465" s="2" t="n">
+        <v>46108.54912539222</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>88</v>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1465" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>34f165b0-d85e-4d46-a7e3-6fdeff853faa</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>7c5d6048-6868-4b44-a528-01497e13f278</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1466" s="2" t="n">
+        <v>46097.17412540089</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1466" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>b57943ec-c224-4dcb-ac5d-4bf55e635524</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>f9d8c398-2960-4457-be4e-411f5283583c</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1467" s="2" t="n">
+        <v>46099.0491254042</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1467" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>02bc224d-7db1-414e-b0af-dbe600758447</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>5a49ee9a-39de-4868-b83a-63fe7da8ac96</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1468" s="2" t="n">
+        <v>46106.13245874338</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>271</v>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1468" t="n">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>a9f4c37e-f4f4-499b-a4d0-f5279e37b80f</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>abd94144-a131-4d5e-b3cf-df8578b57d54</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1469" s="2" t="n">
+        <v>46108.2991254133</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1469" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>a8e07276-5b65-43fd-8da1-e2e1fc4c014a</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>0f015210-c584-4032-bc92-5ad227fefcfe</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1470" s="2" t="n">
+        <v>46097.9657920886</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1470" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>8c26df12-e947-40e4-ab7a-ee4de972a373</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>1858e4a4-139e-4280-919e-e996df5995c2</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1471" s="2" t="n">
+        <v>46085.96579211223</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1471" t="n">
+        <v>14.28</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>3502077a-f9e9-4d17-a215-0aa861de3914</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>ccb16702-f320-4a5c-9695-c15e62e988c1</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1472" s="2" t="n">
+        <v>46085.34079211824</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1472" t="n">
+        <v>13.01</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>ffd30368-517b-478c-95f3-b5697878df33</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>69378a71-3117-428d-aed7-15649449ef9e</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1473" s="2" t="n">
+        <v>46090.6324587878</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1473" t="n">
+        <v>19.08</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>1588b480-c3ac-49a6-829b-34fa5c631c87</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>e2034f08-3128-49f0-925c-53c23e5e8db7</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1474" s="2" t="n">
+        <v>46090.9657921387</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1474" t="n">
+        <v>18.69</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>d6f1bf40-e7ac-4766-87d6-1e746b367424</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>2cdb3fc7-ef16-4ec6-9e5b-149e073cf90d</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1475" s="2" t="n">
+        <v>46107.42412547784</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1475" t="n">
+        <v>17.55</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>d2db22c9-695d-4d18-aa0d-b6a41963e645</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>56d3384e-7668-4ed4-b7cd-fdf5063fc7cc</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1476" s="2" t="n">
+        <v>46084.54912548076</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1476" t="n">
+        <v>18.21</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>76dbc018-60c9-46e9-b426-9513764cbc31</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>bb74f87c-fa2e-4efb-a091-b62c08f6a8f1</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1477" s="2" t="n">
+        <v>46091.38245882024</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>256</v>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1477" t="n">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>bd22c7d5-2a6b-4619-a732-21847febb8dd</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>b1458259-f676-43c3-b532-9bc205d93922</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1478" s="2" t="n">
+        <v>46109.46579215928</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1478" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>5c32fee7-ac6d-493a-bcf4-e08400f76602</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>eabeb247-bdb5-45e9-8b9b-af71cf87ce6f</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1479" s="2" t="n">
+        <v>46110.09079216243</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>76</v>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1479" t="n">
+        <v>11.47</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>e4488c5a-820f-4e0a-8bfe-073f4da7de17</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>67377218-68ee-4745-a837-dec3696db118</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1480" s="2" t="n">
+        <v>46101.34079216804</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>290</v>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1480" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1480" t="n">
+        <v>18.93</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>be661d7b-72d7-478c-95f4-e057b04cc74a</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>7588ce30-f20f-426b-8b4b-ed54887a0d85</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1481" s="2" t="n">
+        <v>46093.67412550432</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>274</v>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1481" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>796cf8dd-edc0-4bc6-aaea-b32f852c93e1</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>fc5dfbe4-4f6f-4cfd-9192-64544555a29e</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1482" s="2" t="n">
+        <v>46088.00745884361</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>92</v>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1482" t="n">
+        <v>13.63</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1482"/>
+  <dimension ref="A1:I1501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60361,7 +60361,7 @@
         </is>
       </c>
       <c r="E1462" s="2" t="n">
-        <v>46087.25745870076</v>
+        <v>46087.2574587037</v>
       </c>
       <c r="F1462" t="n">
         <v>153</v>
@@ -60402,7 +60402,7 @@
         </is>
       </c>
       <c r="E1463" s="2" t="n">
-        <v>46083.00745870479</v>
+        <v>46083.0074587037</v>
       </c>
       <c r="F1463" t="n">
         <v>125</v>
@@ -60443,7 +60443,7 @@
         </is>
       </c>
       <c r="E1464" s="2" t="n">
-        <v>46093.50745870786</v>
+        <v>46093.5074587037</v>
       </c>
       <c r="F1464" t="n">
         <v>152</v>
@@ -60484,7 +60484,7 @@
         </is>
       </c>
       <c r="E1465" s="2" t="n">
-        <v>46108.54912539222</v>
+        <v>46108.54912539352</v>
       </c>
       <c r="F1465" t="n">
         <v>88</v>
@@ -60525,7 +60525,7 @@
         </is>
       </c>
       <c r="E1466" s="2" t="n">
-        <v>46097.17412540089</v>
+        <v>46097.17412540509</v>
       </c>
       <c r="F1466" t="n">
         <v>78</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="E1467" s="2" t="n">
-        <v>46099.0491254042</v>
+        <v>46099.04912540509</v>
       </c>
       <c r="F1467" t="n">
         <v>225</v>
@@ -60607,7 +60607,7 @@
         </is>
       </c>
       <c r="E1468" s="2" t="n">
-        <v>46106.13245874338</v>
+        <v>46106.13245873842</v>
       </c>
       <c r="F1468" t="n">
         <v>271</v>
@@ -60648,7 +60648,7 @@
         </is>
       </c>
       <c r="E1469" s="2" t="n">
-        <v>46108.2991254133</v>
+        <v>46108.29912541667</v>
       </c>
       <c r="F1469" t="n">
         <v>49</v>
@@ -60689,7 +60689,7 @@
         </is>
       </c>
       <c r="E1470" s="2" t="n">
-        <v>46097.9657920886</v>
+        <v>46097.96579208333</v>
       </c>
       <c r="F1470" t="n">
         <v>51</v>
@@ -60730,7 +60730,7 @@
         </is>
       </c>
       <c r="E1471" s="2" t="n">
-        <v>46085.96579211223</v>
+        <v>46085.96579210648</v>
       </c>
       <c r="F1471" t="n">
         <v>135</v>
@@ -60771,7 +60771,7 @@
         </is>
       </c>
       <c r="E1472" s="2" t="n">
-        <v>46085.34079211824</v>
+        <v>46085.34079211806</v>
       </c>
       <c r="F1472" t="n">
         <v>125</v>
@@ -60812,7 +60812,7 @@
         </is>
       </c>
       <c r="E1473" s="2" t="n">
-        <v>46090.6324587878</v>
+        <v>46090.63245878472</v>
       </c>
       <c r="F1473" t="n">
         <v>169</v>
@@ -60853,7 +60853,7 @@
         </is>
       </c>
       <c r="E1474" s="2" t="n">
-        <v>46090.9657921387</v>
+        <v>46090.96579214121</v>
       </c>
       <c r="F1474" t="n">
         <v>109</v>
@@ -60894,7 +60894,7 @@
         </is>
       </c>
       <c r="E1475" s="2" t="n">
-        <v>46107.42412547784</v>
+        <v>46107.42412547454</v>
       </c>
       <c r="F1475" t="n">
         <v>57</v>
@@ -60935,7 +60935,7 @@
         </is>
       </c>
       <c r="E1476" s="2" t="n">
-        <v>46084.54912548076</v>
+        <v>46084.54912548611</v>
       </c>
       <c r="F1476" t="n">
         <v>41</v>
@@ -60976,7 +60976,7 @@
         </is>
       </c>
       <c r="E1477" s="2" t="n">
-        <v>46091.38245882024</v>
+        <v>46091.38245881945</v>
       </c>
       <c r="F1477" t="n">
         <v>256</v>
@@ -61017,7 +61017,7 @@
         </is>
       </c>
       <c r="E1478" s="2" t="n">
-        <v>46109.46579215928</v>
+        <v>46109.46579216435</v>
       </c>
       <c r="F1478" t="n">
         <v>64</v>
@@ -61058,7 +61058,7 @@
         </is>
       </c>
       <c r="E1479" s="2" t="n">
-        <v>46110.09079216243</v>
+        <v>46110.09079216435</v>
       </c>
       <c r="F1479" t="n">
         <v>76</v>
@@ -61099,7 +61099,7 @@
         </is>
       </c>
       <c r="E1480" s="2" t="n">
-        <v>46101.34079216804</v>
+        <v>46101.34079216435</v>
       </c>
       <c r="F1480" t="n">
         <v>290</v>
@@ -61140,7 +61140,7 @@
         </is>
       </c>
       <c r="E1481" s="2" t="n">
-        <v>46093.67412550432</v>
+        <v>46093.67412550926</v>
       </c>
       <c r="F1481" t="n">
         <v>274</v>
@@ -61181,7 +61181,7 @@
         </is>
       </c>
       <c r="E1482" s="2" t="n">
-        <v>46088.00745884361</v>
+        <v>46088.00745884259</v>
       </c>
       <c r="F1482" t="n">
         <v>92</v>
@@ -61198,6 +61198,785 @@
       </c>
       <c r="I1482" t="n">
         <v>13.63</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>768442ed-338b-4f0e-b2e9-c76c8897789b</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>86f79c8a-3ce4-4499-b183-70ca4c96ad60</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1483" s="2" t="n">
+        <v>46090.09128829498</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1483" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>68d9c8f2-7931-422a-b3e0-68b34fd05431</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>aa99a0fe-8224-4fa3-8f1e-2c5952ef68cd</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1484" s="2" t="n">
+        <v>46101.34128830113</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1484" t="n">
+        <v>19.02</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>a15d9968-7c4c-4af4-a287-7002160a41b8</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>8848e721-32d3-44a5-8bc3-bda1ce2e7a4e</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1485" s="2" t="n">
+        <v>46109.04962164926</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1485" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>40029ead-1cd5-4327-a4ae-2fa579984f32</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>76186695-684a-45ff-864e-119f2252de1c</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1486" s="2" t="n">
+        <v>46087.96628831908</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>66</v>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1486" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>a05697e2-5ad0-4b11-a35b-4fbcb5f27fed</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>33eaa31d-6355-4913-b329-f500845266b5</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1487" s="2" t="n">
+        <v>46112.46628833076</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>237</v>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1487" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>d8a8b8a2-d46d-4417-9cb7-c67f4ec9aa48</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>0d158a09-b267-403e-8fb6-3a03fbde5ac9</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1488" s="2" t="n">
+        <v>46103.29962169062</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>151</v>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1488" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>7bddaf97-81ab-4cbc-b411-74cd97d46b5b</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>d97d6e59-1c92-4820-b514-74b03fdf4c75</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1489" s="2" t="n">
+        <v>46115.25795502978</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>98</v>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1489" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>b9f98911-48d5-44f6-bba7-dc4ba9b46a09</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>c720a512-6ae2-4101-912b-b723c41f5eb0</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1490" s="2" t="n">
+        <v>46104.34128836904</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1490" t="n">
+        <v>12.59</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>62bb63c1-6cf3-422b-a258-6120df436de8</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>a9426f4e-019d-47e9-859c-b32ad86cfab9</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1491" s="2" t="n">
+        <v>46105.42462171696</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1491" t="n">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>f1332f93-7406-4898-bbab-dd25fd864ef4</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>cbe82f8a-e338-4e26-b032-19267c3af621</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1492" s="2" t="n">
+        <v>46098.5912883866</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1492" t="n">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>5db861e5-6f57-4daa-98ed-3486d94a305d</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>5cbd427b-a7b3-4b44-81f2-12ac4eafe661</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1493" s="2" t="n">
+        <v>46089.92462172313</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1493" t="n">
+        <v>13.43</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>d20b8b74-bbc7-4c55-965a-d0061e24c3fa</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>15dacd4e-4462-47d9-bd19-a37ff1cefd16</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1494" s="2" t="n">
+        <v>46098.29962172612</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1494" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1494" t="n">
+        <v>19.63</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>4d764c6e-6478-4314-87bb-3ecb6c3150ca</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>2fe9ca10-d794-41a2-a962-1f24b85e443e</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1495" s="2" t="n">
+        <v>46100.34128839573</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>141</v>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1495" t="n">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>55d30730-c1a8-4049-9774-2c211e364722</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>2e174f39-34b8-41be-a6df-672e9fe4c418</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1496" s="2" t="n">
+        <v>46116.13295506837</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>149</v>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1496" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>232a6a46-099b-4c03-b3d6-57f3c21c81d1</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>49f2de2a-d88c-4e2e-ba00-232ea947b781</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1497" s="2" t="n">
+        <v>46107.6746217436</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1497" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>6ad7e97f-719f-42bb-bbdb-41827f1694e3</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>7cb7e1f4-3cd1-4dbc-8571-1d59fdcc1323</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1498" s="2" t="n">
+        <v>46109.42462174674</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1498" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>de7131c7-5e2c-44f0-8d76-148e333e7395</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>ae756b9d-42ed-48a7-980e-5afede965182</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1499" s="2" t="n">
+        <v>46105.71628842496</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1499" t="n">
+        <v>13.49</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>9eddfeda-7c17-4858-9ee6-8281ac0bc108</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>1883acbf-dd37-4328-8a96-3a001895e32f</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1500" s="2" t="n">
+        <v>46107.2579550946</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1500" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>71698b23-37e6-4d36-bafa-8528d0f7e92e</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>8b00edf6-8213-4536-983f-ae5e9427d756</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1501" s="2" t="n">
+        <v>46109.84128843373</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1501" t="n">
+        <v>18.56</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1501"/>
+  <dimension ref="A1:I1522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61222,7 +61222,7 @@
         </is>
       </c>
       <c r="E1483" s="2" t="n">
-        <v>46090.09128829498</v>
+        <v>46090.09128829861</v>
       </c>
       <c r="F1483" t="n">
         <v>75</v>
@@ -61263,7 +61263,7 @@
         </is>
       </c>
       <c r="E1484" s="2" t="n">
-        <v>46101.34128830113</v>
+        <v>46101.34128829861</v>
       </c>
       <c r="F1484" t="n">
         <v>140</v>
@@ -61304,7 +61304,7 @@
         </is>
       </c>
       <c r="E1485" s="2" t="n">
-        <v>46109.04962164926</v>
+        <v>46109.04962164352</v>
       </c>
       <c r="F1485" t="n">
         <v>64</v>
@@ -61345,7 +61345,7 @@
         </is>
       </c>
       <c r="E1486" s="2" t="n">
-        <v>46087.96628831908</v>
+        <v>46087.96628832176</v>
       </c>
       <c r="F1486" t="n">
         <v>66</v>
@@ -61386,7 +61386,7 @@
         </is>
       </c>
       <c r="E1487" s="2" t="n">
-        <v>46112.46628833076</v>
+        <v>46112.46628833334</v>
       </c>
       <c r="F1487" t="n">
         <v>237</v>
@@ -61427,7 +61427,7 @@
         </is>
       </c>
       <c r="E1488" s="2" t="n">
-        <v>46103.29962169062</v>
+        <v>46103.29962168982</v>
       </c>
       <c r="F1488" t="n">
         <v>151</v>
@@ -61468,7 +61468,7 @@
         </is>
       </c>
       <c r="E1489" s="2" t="n">
-        <v>46115.25795502978</v>
+        <v>46115.25795503472</v>
       </c>
       <c r="F1489" t="n">
         <v>98</v>
@@ -61509,7 +61509,7 @@
         </is>
       </c>
       <c r="E1490" s="2" t="n">
-        <v>46104.34128836904</v>
+        <v>46104.34128836806</v>
       </c>
       <c r="F1490" t="n">
         <v>212</v>
@@ -61550,7 +61550,7 @@
         </is>
       </c>
       <c r="E1491" s="2" t="n">
-        <v>46105.42462171696</v>
+        <v>46105.42462171296</v>
       </c>
       <c r="F1491" t="n">
         <v>139</v>
@@ -61591,7 +61591,7 @@
         </is>
       </c>
       <c r="E1492" s="2" t="n">
-        <v>46098.5912883866</v>
+        <v>46098.5912883912</v>
       </c>
       <c r="F1492" t="n">
         <v>121</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="E1493" s="2" t="n">
-        <v>46089.92462172313</v>
+        <v>46089.92462172454</v>
       </c>
       <c r="F1493" t="n">
         <v>73</v>
@@ -61673,7 +61673,7 @@
         </is>
       </c>
       <c r="E1494" s="2" t="n">
-        <v>46098.29962172612</v>
+        <v>46098.29962172454</v>
       </c>
       <c r="F1494" t="n">
         <v>60</v>
@@ -61714,7 +61714,7 @@
         </is>
       </c>
       <c r="E1495" s="2" t="n">
-        <v>46100.34128839573</v>
+        <v>46100.3412883912</v>
       </c>
       <c r="F1495" t="n">
         <v>141</v>
@@ -61755,7 +61755,7 @@
         </is>
       </c>
       <c r="E1496" s="2" t="n">
-        <v>46116.13295506837</v>
+        <v>46116.13295506944</v>
       </c>
       <c r="F1496" t="n">
         <v>149</v>
@@ -61796,7 +61796,7 @@
         </is>
       </c>
       <c r="E1497" s="2" t="n">
-        <v>46107.6746217436</v>
+        <v>46107.67462174768</v>
       </c>
       <c r="F1497" t="n">
         <v>35</v>
@@ -61837,7 +61837,7 @@
         </is>
       </c>
       <c r="E1498" s="2" t="n">
-        <v>46109.42462174674</v>
+        <v>46109.42462174768</v>
       </c>
       <c r="F1498" t="n">
         <v>81</v>
@@ -61878,7 +61878,7 @@
         </is>
       </c>
       <c r="E1499" s="2" t="n">
-        <v>46105.71628842496</v>
+        <v>46105.71628842592</v>
       </c>
       <c r="F1499" t="n">
         <v>132</v>
@@ -61919,7 +61919,7 @@
         </is>
       </c>
       <c r="E1500" s="2" t="n">
-        <v>46107.2579550946</v>
+        <v>46107.25795509259</v>
       </c>
       <c r="F1500" t="n">
         <v>229</v>
@@ -61960,7 +61960,7 @@
         </is>
       </c>
       <c r="E1501" s="2" t="n">
-        <v>46109.84128843373</v>
+        <v>46109.8412884375</v>
       </c>
       <c r="F1501" t="n">
         <v>137</v>
@@ -61977,6 +61977,867 @@
       </c>
       <c r="I1501" t="n">
         <v>18.56</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>f5912c23-3112-4123-949b-4735a4c829ee</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>b386f207-5508-4359-bf5b-14b31f636cd9</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1502" s="2" t="n">
+        <v>46115.67742696558</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>261</v>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1502" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>9aec047a-7302-4b6e-bbf2-40a7ed70f358</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>248aedc4-561e-480f-8fc8-07ba1f264d81</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1503" s="2" t="n">
+        <v>46107.63576030317</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1503" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>3b546eee-f6b7-4808-afef-87979b4ad9d7</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>4b9d7886-f113-4cb9-842f-eb2f58a3d630</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1504" s="2" t="n">
+        <v>46108.09409364856</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>179</v>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1504" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1504" t="n">
+        <v>19.17</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>e8884345-eb6a-4da0-81cc-ecd2531b6a2c</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>21ae2f48-fd1b-49d3-8db0-90e4e9cd71fa</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1505" s="2" t="n">
+        <v>46109.30242699087</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>153</v>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1505" t="n">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>b05c0210-23b8-4c68-aa7b-3e40f2ba44d3</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>6bb37da3-3031-4c71-8157-f6ad7607abc5</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1506" s="2" t="n">
+        <v>46110.13576034535</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>251</v>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1506" t="n">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>0fbda4a4-6367-48d0-b670-898c68194667</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>756337bd-fde1-4725-91b6-7f586d635be3</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1507" s="2" t="n">
+        <v>46119.84409368454</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1507" t="n">
+        <v>16.76</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>02664f0f-6dc0-4c25-a50d-be19de3432e5</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>5d4cac3b-14a5-4f7c-b871-73793c302cda</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1508" s="2" t="n">
+        <v>46122.67742702668</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>296</v>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1508" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>6c033076-433b-46a2-8800-101ba538d9e1</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>d01e9815-e093-4fd7-8f84-c264d1200b2c</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1509" s="2" t="n">
+        <v>46111.88576036297</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1509" t="n">
+        <v>13.81</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>69e8ef1a-2e1a-4711-9c73-32783558feae</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>95bf7903-fc6f-4324-bb0e-e8e66d1d95ee</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1510" s="2" t="n">
+        <v>46123.71909370497</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1510" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>f1da0836-541b-4288-a61a-aba21fcbc458</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>9a8a57fb-40ec-4a1b-95ba-ce117e7d2b97</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1511" s="2" t="n">
+        <v>46106.01076037461</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>222</v>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1511" t="n">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>913fe0a7-fe84-4526-a81d-bb1d697d15b3</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>7b15ace7-3fb3-433a-b6ff-49c52bb4e082</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1512" s="2" t="n">
+        <v>46104.05242704432</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1512" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>6c496c4d-1e3d-4c04-b9c5-38843067de19</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>ed725711-da6f-4aa7-8b0e-4bed69602a85</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1513" s="2" t="n">
+        <v>46116.96909372833</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>103</v>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1513" t="n">
+        <v>14.07</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2a552b7e-71cf-4cbc-a0ba-35fbf8866deb</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>30cee7c2-c36f-4a47-9946-f0b4099f4950</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1514" s="2" t="n">
+        <v>46101.51076039793</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>275</v>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1514" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>efd563a2-7067-4b1e-b21c-e9d20e878d72</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>9042a557-981e-47e9-bef6-b15f144cc2a0</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1515" s="2" t="n">
+        <v>46116.59409373716</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1515" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>c34bc0b3-a9c9-4d17-a176-aa0940b09029</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>f17767db-1b31-44d8-b486-ca29cded9387</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1516" s="2" t="n">
+        <v>46114.63576040674</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1516" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>eb8b8a85-9ff3-4a85-91f3-2c135c168d70</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>e2072760-7fcc-4f33-8159-634e4f632c5f</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1517" s="2" t="n">
+        <v>46101.0107604097</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1517" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>ec1c3ed8-749d-4853-9c8b-529b7c279a5c</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>0de03ae9-bbd2-4328-aefe-07a6666887bc</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1518" s="2" t="n">
+        <v>46096.71909374886</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>263</v>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1518" t="n">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>58b4ac84-5577-41a5-841d-3703d51d3a0d</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>b525d396-180f-4783-9e1e-c800f21e4e75</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1519" s="2" t="n">
+        <v>46122.26076042719</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>155</v>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1519" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>8a8176e3-da03-4cd6-a622-537db9c56437</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>531fc318-154a-49d9-93e4-e16c9d9a3667</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1520" s="2" t="n">
+        <v>46097.2607604301</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>130</v>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1520" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>e23313eb-e037-4f22-9c8c-f9a74d88e41b</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>a0f0e116-7218-44a2-83b6-4091895cf9b2</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1521" s="2" t="n">
+        <v>46097.84409376937</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1521" t="n">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>38f9244a-069c-47ca-bc70-f105692043dd</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>4b944881-e7bd-4fe1-adbd-34c402d21411</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1522" s="2" t="n">
+        <v>46116.55242710566</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>87</v>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1522" t="n">
+        <v>11.82</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1522"/>
+  <dimension ref="A1:I1539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62001,7 +62001,7 @@
         </is>
       </c>
       <c r="E1502" s="2" t="n">
-        <v>46115.67742696558</v>
+        <v>46115.6774269676</v>
       </c>
       <c r="F1502" t="n">
         <v>261</v>
@@ -62042,7 +62042,7 @@
         </is>
       </c>
       <c r="E1503" s="2" t="n">
-        <v>46107.63576030317</v>
+        <v>46107.63576030092</v>
       </c>
       <c r="F1503" t="n">
         <v>106</v>
@@ -62083,7 +62083,7 @@
         </is>
       </c>
       <c r="E1504" s="2" t="n">
-        <v>46108.09409364856</v>
+        <v>46108.09409364584</v>
       </c>
       <c r="F1504" t="n">
         <v>179</v>
@@ -62124,7 +62124,7 @@
         </is>
       </c>
       <c r="E1505" s="2" t="n">
-        <v>46109.30242699087</v>
+        <v>46109.30242699074</v>
       </c>
       <c r="F1505" t="n">
         <v>153</v>
@@ -62165,7 +62165,7 @@
         </is>
       </c>
       <c r="E1506" s="2" t="n">
-        <v>46110.13576034535</v>
+        <v>46110.13576034722</v>
       </c>
       <c r="F1506" t="n">
         <v>251</v>
@@ -62206,7 +62206,7 @@
         </is>
       </c>
       <c r="E1507" s="2" t="n">
-        <v>46119.84409368454</v>
+        <v>46119.84409368056</v>
       </c>
       <c r="F1507" t="n">
         <v>132</v>
@@ -62247,7 +62247,7 @@
         </is>
       </c>
       <c r="E1508" s="2" t="n">
-        <v>46122.67742702668</v>
+        <v>46122.67742702546</v>
       </c>
       <c r="F1508" t="n">
         <v>296</v>
@@ -62288,7 +62288,7 @@
         </is>
       </c>
       <c r="E1509" s="2" t="n">
-        <v>46111.88576036297</v>
+        <v>46111.8857603588</v>
       </c>
       <c r="F1509" t="n">
         <v>185</v>
@@ -62329,7 +62329,7 @@
         </is>
       </c>
       <c r="E1510" s="2" t="n">
-        <v>46123.71909370497</v>
+        <v>46123.7190937037</v>
       </c>
       <c r="F1510" t="n">
         <v>225</v>
@@ -62370,7 +62370,7 @@
         </is>
       </c>
       <c r="E1511" s="2" t="n">
-        <v>46106.01076037461</v>
+        <v>46106.01076037037</v>
       </c>
       <c r="F1511" t="n">
         <v>222</v>
@@ -62411,7 +62411,7 @@
         </is>
       </c>
       <c r="E1512" s="2" t="n">
-        <v>46104.05242704432</v>
+        <v>46104.05242704861</v>
       </c>
       <c r="F1512" t="n">
         <v>200</v>
@@ -62452,7 +62452,7 @@
         </is>
       </c>
       <c r="E1513" s="2" t="n">
-        <v>46116.96909372833</v>
+        <v>46116.96909372685</v>
       </c>
       <c r="F1513" t="n">
         <v>103</v>
@@ -62493,7 +62493,7 @@
         </is>
       </c>
       <c r="E1514" s="2" t="n">
-        <v>46101.51076039793</v>
+        <v>46101.51076039352</v>
       </c>
       <c r="F1514" t="n">
         <v>275</v>
@@ -62534,7 +62534,7 @@
         </is>
       </c>
       <c r="E1515" s="2" t="n">
-        <v>46116.59409373716</v>
+        <v>46116.59409373843</v>
       </c>
       <c r="F1515" t="n">
         <v>203</v>
@@ -62575,7 +62575,7 @@
         </is>
       </c>
       <c r="E1516" s="2" t="n">
-        <v>46114.63576040674</v>
+        <v>46114.63576040509</v>
       </c>
       <c r="F1516" t="n">
         <v>195</v>
@@ -62616,7 +62616,7 @@
         </is>
       </c>
       <c r="E1517" s="2" t="n">
-        <v>46101.0107604097</v>
+        <v>46101.01076040509</v>
       </c>
       <c r="F1517" t="n">
         <v>272</v>
@@ -62657,7 +62657,7 @@
         </is>
       </c>
       <c r="E1518" s="2" t="n">
-        <v>46096.71909374886</v>
+        <v>46096.71909375</v>
       </c>
       <c r="F1518" t="n">
         <v>263</v>
@@ -62698,7 +62698,7 @@
         </is>
       </c>
       <c r="E1519" s="2" t="n">
-        <v>46122.26076042719</v>
+        <v>46122.26076042824</v>
       </c>
       <c r="F1519" t="n">
         <v>155</v>
@@ -62739,7 +62739,7 @@
         </is>
       </c>
       <c r="E1520" s="2" t="n">
-        <v>46097.2607604301</v>
+        <v>46097.26076042824</v>
       </c>
       <c r="F1520" t="n">
         <v>130</v>
@@ -62780,7 +62780,7 @@
         </is>
       </c>
       <c r="E1521" s="2" t="n">
-        <v>46097.84409376937</v>
+        <v>46097.84409377315</v>
       </c>
       <c r="F1521" t="n">
         <v>47</v>
@@ -62821,7 +62821,7 @@
         </is>
       </c>
       <c r="E1522" s="2" t="n">
-        <v>46116.55242710566</v>
+        <v>46116.55242710648</v>
       </c>
       <c r="F1522" t="n">
         <v>87</v>
@@ -62838,6 +62838,703 @@
       </c>
       <c r="I1522" t="n">
         <v>11.82</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>b9778933-5571-4a7a-9750-98b550539a3f</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>e1314cfb-5a26-4be0-899b-4f13621c1df8</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1523" s="2" t="n">
+        <v>46114.17911048192</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>197</v>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1523" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>45b6488e-45d3-4560-9cb7-2fb2e7c25d9b</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>87b64205-3569-4916-bd4e-ba6f35906f53</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1524" s="2" t="n">
+        <v>46105.3874438213</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>196</v>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1524" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>853c6c7f-719b-4a49-a611-23c9a11c1ce7</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>1dd0d3eb-210a-4c33-8f98-33be97dcbb47</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1525" s="2" t="n">
+        <v>46105.17911049107</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1525" t="n">
+        <v>19.44</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>728470b0-a2a6-4ccc-9c61-8c9da35e8bbc</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>1bd5a642-ff93-4c36-a7bf-12d4cc30e6a2</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1526" s="2" t="n">
+        <v>46104.22077718138</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>134</v>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1526" t="n">
+        <v>19.76</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>b7b07daa-2eb5-4a7d-b486-781c5f105999</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>c11750c4-cb86-4dfe-9a4a-ee27fdce4bfc</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1527" s="2" t="n">
+        <v>46118.97077718459</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1527" t="n">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>8db81376-fac5-4ff0-9ac7-9280f3681a29</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>77408f6a-be1a-4d7f-a4f4-f732b6582dae</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1528" s="2" t="n">
+        <v>46131.84577718755</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1528" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>10f7c431-a1f6-4bf1-b536-60779622142a</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>6f088949-be78-4175-8b2c-1d1a0b96cf31</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1529" s="2" t="n">
+        <v>46103.42911052667</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>95</v>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1529" t="n">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>e1c8ca3d-0cd0-433e-af30-6e879b57994e</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>aff7880b-356f-47f9-969a-9650d91fc192</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1530" s="2" t="n">
+        <v>46116.51244387744</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1530" t="n">
+        <v>16.92</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>ab360537-325a-426e-bb98-c9544503c10d</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>fa3e684d-c79e-4f32-ac6f-83f490c85045</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1531" s="2" t="n">
+        <v>46130.59577721969</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>235</v>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1531" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>c59571e5-d5b2-4af6-b4e0-97a2e44cf882</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>8fcf85b0-8d6f-435f-bea6-8e8338fecf40</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1532" s="2" t="n">
+        <v>46112.22077722543</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1532" t="n">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>cded5a61-c18f-4f7c-9c49-81309fe7ff1f</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>f47f8daf-5ab2-4c93-8d29-c0604cd3ef99</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1533" s="2" t="n">
+        <v>46107.63744389804</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1533" t="n">
+        <v>16.24</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>17befcb9-340e-4b2e-9d1b-923746df61c1</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>86d10244-1b03-4e5b-9907-8b7de5732ebc</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1534" s="2" t="n">
+        <v>46115.26244390664</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>67</v>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1534" t="n">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>f0ea7fec-d83b-4d32-a92e-ceb43fa8e4dc</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>a401df63-1661-40e7-b25b-a864aabc4a63</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1535" s="2" t="n">
+        <v>46120.63744390976</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1535" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>fb86f8d3-9e8b-41f9-bf5b-fc0bc29fcd0f</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>9b581de4-7234-4b27-ab88-cd0a7941ea8d</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1536" s="2" t="n">
+        <v>46115.34577724613</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1536" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>87e6efe5-894c-42c2-a321-35b59637e951</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>6afcabcb-29e8-464c-9a4a-10496bc4e0a1</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1537" s="2" t="n">
+        <v>46123.05411058825</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1537" t="n">
+        <v>14.47</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>468e7927-8ce2-4431-82c8-a548e8325caf</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>951ac4e4-366e-471d-9e6b-59269b145be8</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1538" s="2" t="n">
+        <v>46103.55411059126</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1538" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>9e9c646a-635c-48b5-a9c3-9e2b971072c9</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>2447225a-c3c2-4606-86eb-7d8384bcd17f</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1539" s="2" t="n">
+        <v>46116.2624439425</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>289</v>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1539" t="n">
+        <v>11.84</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1539"/>
+  <dimension ref="A1:I1555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62862,7 +62862,7 @@
         </is>
       </c>
       <c r="E1523" s="2" t="n">
-        <v>46114.17911048192</v>
+        <v>46114.17911048611</v>
       </c>
       <c r="F1523" t="n">
         <v>197</v>
@@ -62903,7 +62903,7 @@
         </is>
       </c>
       <c r="E1524" s="2" t="n">
-        <v>46105.3874438213</v>
+        <v>46105.38744381945</v>
       </c>
       <c r="F1524" t="n">
         <v>196</v>
@@ -62944,7 +62944,7 @@
         </is>
       </c>
       <c r="E1525" s="2" t="n">
-        <v>46105.17911049107</v>
+        <v>46105.17911048611</v>
       </c>
       <c r="F1525" t="n">
         <v>186</v>
@@ -62985,7 +62985,7 @@
         </is>
       </c>
       <c r="E1526" s="2" t="n">
-        <v>46104.22077718138</v>
+        <v>46104.22077717593</v>
       </c>
       <c r="F1526" t="n">
         <v>134</v>
@@ -63026,7 +63026,7 @@
         </is>
       </c>
       <c r="E1527" s="2" t="n">
-        <v>46118.97077718459</v>
+        <v>46118.9707771875</v>
       </c>
       <c r="F1527" t="n">
         <v>47</v>
@@ -63067,7 +63067,7 @@
         </is>
       </c>
       <c r="E1528" s="2" t="n">
-        <v>46131.84577718755</v>
+        <v>46131.8457771875</v>
       </c>
       <c r="F1528" t="n">
         <v>265</v>
@@ -63108,7 +63108,7 @@
         </is>
       </c>
       <c r="E1529" s="2" t="n">
-        <v>46103.42911052667</v>
+        <v>46103.42911053241</v>
       </c>
       <c r="F1529" t="n">
         <v>95</v>
@@ -63149,7 +63149,7 @@
         </is>
       </c>
       <c r="E1530" s="2" t="n">
-        <v>46116.51244387744</v>
+        <v>46116.51244387731</v>
       </c>
       <c r="F1530" t="n">
         <v>75</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="E1531" s="2" t="n">
-        <v>46130.59577721969</v>
+        <v>46130.59577722222</v>
       </c>
       <c r="F1531" t="n">
         <v>235</v>
@@ -63231,7 +63231,7 @@
         </is>
       </c>
       <c r="E1532" s="2" t="n">
-        <v>46112.22077722543</v>
+        <v>46112.22077722222</v>
       </c>
       <c r="F1532" t="n">
         <v>63</v>
@@ -63272,7 +63272,7 @@
         </is>
       </c>
       <c r="E1533" s="2" t="n">
-        <v>46107.63744389804</v>
+        <v>46107.63744390046</v>
       </c>
       <c r="F1533" t="n">
         <v>145</v>
@@ -63313,7 +63313,7 @@
         </is>
       </c>
       <c r="E1534" s="2" t="n">
-        <v>46115.26244390664</v>
+        <v>46115.26244391203</v>
       </c>
       <c r="F1534" t="n">
         <v>67</v>
@@ -63354,7 +63354,7 @@
         </is>
       </c>
       <c r="E1535" s="2" t="n">
-        <v>46120.63744390976</v>
+        <v>46120.63744391203</v>
       </c>
       <c r="F1535" t="n">
         <v>145</v>
@@ -63395,7 +63395,7 @@
         </is>
       </c>
       <c r="E1536" s="2" t="n">
-        <v>46115.34577724613</v>
+        <v>46115.34577724537</v>
       </c>
       <c r="F1536" t="n">
         <v>140</v>
@@ -63436,7 +63436,7 @@
         </is>
       </c>
       <c r="E1537" s="2" t="n">
-        <v>46123.05411058825</v>
+        <v>46123.05411059028</v>
       </c>
       <c r="F1537" t="n">
         <v>150</v>
@@ -63477,7 +63477,7 @@
         </is>
       </c>
       <c r="E1538" s="2" t="n">
-        <v>46103.55411059126</v>
+        <v>46103.55411059028</v>
       </c>
       <c r="F1538" t="n">
         <v>38</v>
@@ -63518,7 +63518,7 @@
         </is>
       </c>
       <c r="E1539" s="2" t="n">
-        <v>46116.2624439425</v>
+        <v>46116.26244394676</v>
       </c>
       <c r="F1539" t="n">
         <v>289</v>
@@ -63535,6 +63535,662 @@
       </c>
       <c r="I1539" t="n">
         <v>11.84</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>83285a3e-9983-46e3-a9b9-25e576176a43</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>3de22007-ed74-456b-8e7d-0d0306c04b31</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1540" s="2" t="n">
+        <v>46120.26458358517</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>254</v>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1540" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>d4aed202-b407-4e6c-9292-f94006e69e95</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>4480065b-eda3-4e2a-a05e-57309218d511</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1541" s="2" t="n">
+        <v>46112.6812502752</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1541" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1541" t="n">
+        <v>12.19</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>9a6ff263-a825-4808-bf61-e4d2ede32952</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>06053289-4183-4c39-863c-bbee73c84f8b</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1542" s="2" t="n">
+        <v>46128.51458361174</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>134</v>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1542" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1542" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>a7921e75-0b22-4646-b1a6-6e1d208ad862</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>61b03f0e-b350-42c6-9f5c-55e266945fd9</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1543" s="2" t="n">
+        <v>46122.6395836234</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>243</v>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1543" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1543" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>ad7bbf06-6219-4ce6-b869-28d4fb63a24c</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>320e9378-4481-4bdc-bc3b-c46cc2bdc02a</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1544" s="2" t="n">
+        <v>46130.43125029296</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1544" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1544" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>596a3031-5510-43dd-b869-3af86ee59205</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>0e4801cb-3922-4a15-8a0e-2212e4fbe461</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1545" s="2" t="n">
+        <v>46110.51458363214</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1545" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1545" t="n">
+        <v>10.88</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>78c3c8bc-58a0-45ee-b858-52f158cda6b8</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>1342814a-db64-46b6-b619-2c3b99771868</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1546" s="2" t="n">
+        <v>46126.55625030755</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>279</v>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1546" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>fa322fcc-a2a8-43e8-b7a0-0edc35aa26fe</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>71ef4759-7fa4-4ee8-98c0-cd5efdb3150b</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1547" s="2" t="n">
+        <v>46120.09791698573</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1547" t="n">
+        <v>15.39</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>e25577c7-a4c8-462d-8798-fc17fae26f0d</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>3390b109-a1d6-4ef0-8b56-1a19e3cbfcb4</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1548" s="2" t="n">
+        <v>46127.38958365531</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1548" t="n">
+        <v>18.67</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>67dbbb56-be8b-455a-91d5-db67f67b8de3</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>443af151-9ad3-4abb-84f0-b5205e6dad00</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1549" s="2" t="n">
+        <v>46125.26458366412</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>288</v>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1549" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1549" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>3b653396-de3e-46cf-9f57-90a4c772f263</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>bb04ef21-2ff7-415d-ac18-cf2aa790550b</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1550" s="2" t="n">
+        <v>46127.7229170212</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>235</v>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1550" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1550" t="n">
+        <v>18.91</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>83fa8314-4a64-474c-b0e9-2db2762e5be8</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>709569ab-6e31-4a99-953b-56741f56dc94</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1551" s="2" t="n">
+        <v>46131.30625036057</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1551" t="n">
+        <v>17.17</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>a2d1e124-b40f-4769-900b-b2af0d07680b</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>481f4624-94ca-4d3d-9a63-a212271d29c1</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1552" s="2" t="n">
+        <v>46135.13958370265</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1552" t="n">
+        <v>18.04</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>e216c857-e605-4b8d-8bec-8191fa267ac6</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>16665fd3-43af-4003-906e-c212c6ea2afc</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1553" s="2" t="n">
+        <v>46119.84791704176</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>222</v>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1553" t="n">
+        <v>15.52</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>3cf8c227-b44f-40d8-88e8-65d25c427d72</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>59df0552-5e89-4521-938d-e9741eb6d2a7</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1554" s="2" t="n">
+        <v>46138.51458371129</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>134</v>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1554" t="n">
+        <v>15.11</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>a861dcee-33d4-4273-ad01-46a8dd32ccc7</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>39ea93a7-86b8-42d4-95e8-3925145cc196</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1555" s="2" t="n">
+        <v>46132.68125038396</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>221</v>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1555" t="n">
+        <v>17.01</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1555"/>
+  <dimension ref="A1:I1573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63559,7 +63559,7 @@
         </is>
       </c>
       <c r="E1540" s="2" t="n">
-        <v>46120.26458358517</v>
+        <v>46120.26458358796</v>
       </c>
       <c r="F1540" t="n">
         <v>254</v>
@@ -63600,7 +63600,7 @@
         </is>
       </c>
       <c r="E1541" s="2" t="n">
-        <v>46112.6812502752</v>
+        <v>46112.68125027778</v>
       </c>
       <c r="F1541" t="n">
         <v>191</v>
@@ -63641,7 +63641,7 @@
         </is>
       </c>
       <c r="E1542" s="2" t="n">
-        <v>46128.51458361174</v>
+        <v>46128.51458361111</v>
       </c>
       <c r="F1542" t="n">
         <v>134</v>
@@ -63682,7 +63682,7 @@
         </is>
       </c>
       <c r="E1543" s="2" t="n">
-        <v>46122.6395836234</v>
+        <v>46122.63958362269</v>
       </c>
       <c r="F1543" t="n">
         <v>243</v>
@@ -63723,7 +63723,7 @@
         </is>
       </c>
       <c r="E1544" s="2" t="n">
-        <v>46130.43125029296</v>
+        <v>46130.43125028935</v>
       </c>
       <c r="F1544" t="n">
         <v>135</v>
@@ -63764,7 +63764,7 @@
         </is>
       </c>
       <c r="E1545" s="2" t="n">
-        <v>46110.51458363214</v>
+        <v>46110.51458363426</v>
       </c>
       <c r="F1545" t="n">
         <v>72</v>
@@ -63805,7 +63805,7 @@
         </is>
       </c>
       <c r="E1546" s="2" t="n">
-        <v>46126.55625030755</v>
+        <v>46126.5562503125</v>
       </c>
       <c r="F1546" t="n">
         <v>279</v>
@@ -63846,7 +63846,7 @@
         </is>
       </c>
       <c r="E1547" s="2" t="n">
-        <v>46120.09791698573</v>
+        <v>46120.09791699074</v>
       </c>
       <c r="F1547" t="n">
         <v>214</v>
@@ -63887,7 +63887,7 @@
         </is>
       </c>
       <c r="E1548" s="2" t="n">
-        <v>46127.38958365531</v>
+        <v>46127.38958365741</v>
       </c>
       <c r="F1548" t="n">
         <v>111</v>
@@ -63928,7 +63928,7 @@
         </is>
       </c>
       <c r="E1549" s="2" t="n">
-        <v>46125.26458366412</v>
+        <v>46125.26458366898</v>
       </c>
       <c r="F1549" t="n">
         <v>288</v>
@@ -63969,7 +63969,7 @@
         </is>
       </c>
       <c r="E1550" s="2" t="n">
-        <v>46127.7229170212</v>
+        <v>46127.72291702546</v>
       </c>
       <c r="F1550" t="n">
         <v>235</v>
@@ -64010,7 +64010,7 @@
         </is>
       </c>
       <c r="E1551" s="2" t="n">
-        <v>46131.30625036057</v>
+        <v>46131.30625035879</v>
       </c>
       <c r="F1551" t="n">
         <v>99</v>
@@ -64051,7 +64051,7 @@
         </is>
       </c>
       <c r="E1552" s="2" t="n">
-        <v>46135.13958370265</v>
+        <v>46135.13958370371</v>
       </c>
       <c r="F1552" t="n">
         <v>273</v>
@@ -64092,7 +64092,7 @@
         </is>
       </c>
       <c r="E1553" s="2" t="n">
-        <v>46119.84791704176</v>
+        <v>46119.84791703703</v>
       </c>
       <c r="F1553" t="n">
         <v>222</v>
@@ -64133,7 +64133,7 @@
         </is>
       </c>
       <c r="E1554" s="2" t="n">
-        <v>46138.51458371129</v>
+        <v>46138.51458371528</v>
       </c>
       <c r="F1554" t="n">
         <v>134</v>
@@ -64174,7 +64174,7 @@
         </is>
       </c>
       <c r="E1555" s="2" t="n">
-        <v>46132.68125038396</v>
+        <v>46132.68125038195</v>
       </c>
       <c r="F1555" t="n">
         <v>221</v>
@@ -64191,6 +64191,744 @@
       </c>
       <c r="I1555" t="n">
         <v>17.01</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>ff7dfd3d-70bb-49ea-84b2-9243576dfb48</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>3afeb1fc-90cc-4a17-bcc9-378e78b6775b</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1556" s="2" t="n">
+        <v>46145.72721828825</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>86</v>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1556" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>d1286ea2-64af-4e0d-96a2-e78128e0e8ca</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>625a1aca-4d45-4bbe-aa2d-604d4adad15d</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1557" s="2" t="n">
+        <v>46130.56055163478</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1557" t="n">
+        <v>17.96</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>4f048e00-8d70-49e2-8b91-eb94b44f2d0f</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>f3ade415-5bbf-40bf-80ec-dc9fd4cd72eb</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1558" s="2" t="n">
+        <v>46145.39388497397</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>245</v>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1558" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1558" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>d6f455b8-17d1-486d-a1d7-7a8000dda6f4</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>35488e43-abdc-4771-884a-2aa8e3909e15</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1559" s="2" t="n">
+        <v>46121.51888498023</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>277</v>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1559" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>d26701c5-f029-42da-8dd7-e49fa10a3373</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>6d02df80-168e-405d-a0bb-a863a0f92cd3</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1560" s="2" t="n">
+        <v>46128.18555165896</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1560" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>54ad8f16-6b61-455e-9a0d-eb4ff594eb33</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>c961b20a-90aa-4ac4-b8d3-e22a69402bb3</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1561" s="2" t="n">
+        <v>46130.81055167071</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1561" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1561" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>61697a51-1504-4240-9ac1-ba7fd8476994</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>87ee6cc0-49a5-4eca-8200-d853ffacce58</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1562" s="2" t="n">
+        <v>46130.81055169668</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1562" t="n">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>95ba0ce4-d4ee-4d9b-9004-2b7211028311</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>231bb382-edc0-4c5d-b0fb-e271e1b041c2</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1563" s="2" t="n">
+        <v>46123.14388505062</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1563" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>4b1678f1-91a7-45e3-991f-547ea4f64043</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>19ed22c0-eb8f-4cfa-869f-a3a1d1a8a9d2</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1564" s="2" t="n">
+        <v>46117.22721838688</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>264</v>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1564" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>1fbec85d-7eac-4719-983b-249b8e09e800</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>79c45949-39c9-4e73-bf3c-3ed6bc55f545</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1565" s="2" t="n">
+        <v>46132.22721838984</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1565" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1565" t="n">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>3dfc7836-fe05-444c-930e-5af36a95ae36</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>775c267b-89a0-4608-9ff9-1d027fc14ebb</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1566" s="2" t="n">
+        <v>46133.85221839862</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1566" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>b2d1b3d4-2e46-4899-86ee-a3b8cf92ebe7</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>1e10405b-a7e7-49ce-b188-185746d38482</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1567" s="2" t="n">
+        <v>46120.31055173784</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1567" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>e87140d8-7206-470e-8c25-c44a8a111174</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>d6229689-e974-4d87-90f7-2dbe7e29b781</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1568" s="2" t="n">
+        <v>46138.93555174076</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1568" t="n">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>36fd5997-df51-4779-b616-9fbd41af4643</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>f66f6688-7411-4082-86e8-7d4b3f09b669</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1569" s="2" t="n">
+        <v>46139.47721841037</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>246</v>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1569" t="n">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>eb9cbaf7-020d-4b93-aa5f-afe1d676f506</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>e1fa1a5b-c018-464f-82ae-8018fdcab9a6</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1570" s="2" t="n">
+        <v>46140.43555174967</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>240</v>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1570" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>cf0d4196-f46a-4fb0-b235-bd99e14754a3</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>d27fe18e-38f9-48f6-b828-0dd208b09266</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1571" s="2" t="n">
+        <v>46142.72721842486</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1571" t="n">
+        <v>15.89</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>bfb4d215-4ef6-4508-9124-b8cdfafc9c9c</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>ec8e5e4a-6a07-4d84-a1a7-b9a86e83f8d9</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1572" s="2" t="n">
+        <v>46117.76888509744</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>66</v>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1572" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1572" t="n">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>6d779ada-5f84-4430-96e9-ef24b5b1fd21</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>61a507ee-68f4-4270-a1af-3ab5f51b6c1d</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1573" s="2" t="n">
+        <v>46137.39388510039</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>236</v>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1573" t="n">
+        <v>18.75</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1573"/>
+  <dimension ref="A1:I1593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64215,7 +64215,7 @@
         </is>
       </c>
       <c r="E1556" s="2" t="n">
-        <v>46145.72721828825</v>
+        <v>46145.72721828704</v>
       </c>
       <c r="F1556" t="n">
         <v>86</v>
@@ -64256,7 +64256,7 @@
         </is>
       </c>
       <c r="E1557" s="2" t="n">
-        <v>46130.56055163478</v>
+        <v>46130.56055163194</v>
       </c>
       <c r="F1557" t="n">
         <v>82</v>
@@ -64297,7 +64297,7 @@
         </is>
       </c>
       <c r="E1558" s="2" t="n">
-        <v>46145.39388497397</v>
+        <v>46145.39388497685</v>
       </c>
       <c r="F1558" t="n">
         <v>245</v>
@@ -64338,7 +64338,7 @@
         </is>
       </c>
       <c r="E1559" s="2" t="n">
-        <v>46121.51888498023</v>
+        <v>46121.51888497685</v>
       </c>
       <c r="F1559" t="n">
         <v>277</v>
@@ -64379,7 +64379,7 @@
         </is>
       </c>
       <c r="E1560" s="2" t="n">
-        <v>46128.18555165896</v>
+        <v>46128.18555165509</v>
       </c>
       <c r="F1560" t="n">
         <v>38</v>
@@ -64420,7 +64420,7 @@
         </is>
       </c>
       <c r="E1561" s="2" t="n">
-        <v>46130.81055167071</v>
+        <v>46130.81055166667</v>
       </c>
       <c r="F1561" t="n">
         <v>168</v>
@@ -64461,7 +64461,7 @@
         </is>
       </c>
       <c r="E1562" s="2" t="n">
-        <v>46130.81055169668</v>
+        <v>46130.81055170139</v>
       </c>
       <c r="F1562" t="n">
         <v>69</v>
@@ -64502,7 +64502,7 @@
         </is>
       </c>
       <c r="E1563" s="2" t="n">
-        <v>46123.14388505062</v>
+        <v>46123.14388504629</v>
       </c>
       <c r="F1563" t="n">
         <v>161</v>
@@ -64543,7 +64543,7 @@
         </is>
       </c>
       <c r="E1564" s="2" t="n">
-        <v>46117.22721838688</v>
+        <v>46117.22721839121</v>
       </c>
       <c r="F1564" t="n">
         <v>264</v>
@@ -64584,7 +64584,7 @@
         </is>
       </c>
       <c r="E1565" s="2" t="n">
-        <v>46132.22721838984</v>
+        <v>46132.22721839121</v>
       </c>
       <c r="F1565" t="n">
         <v>137</v>
@@ -64625,7 +64625,7 @@
         </is>
       </c>
       <c r="E1566" s="2" t="n">
-        <v>46133.85221839862</v>
+        <v>46133.85221840278</v>
       </c>
       <c r="F1566" t="n">
         <v>43</v>
@@ -64666,7 +64666,7 @@
         </is>
       </c>
       <c r="E1567" s="2" t="n">
-        <v>46120.31055173784</v>
+        <v>46120.31055173611</v>
       </c>
       <c r="F1567" t="n">
         <v>215</v>
@@ -64707,7 +64707,7 @@
         </is>
       </c>
       <c r="E1568" s="2" t="n">
-        <v>46138.93555174076</v>
+        <v>46138.93555173611</v>
       </c>
       <c r="F1568" t="n">
         <v>44</v>
@@ -64748,7 +64748,7 @@
         </is>
       </c>
       <c r="E1569" s="2" t="n">
-        <v>46139.47721841037</v>
+        <v>46139.47721841435</v>
       </c>
       <c r="F1569" t="n">
         <v>246</v>
@@ -64789,7 +64789,7 @@
         </is>
       </c>
       <c r="E1570" s="2" t="n">
-        <v>46140.43555174967</v>
+        <v>46140.43555174769</v>
       </c>
       <c r="F1570" t="n">
         <v>240</v>
@@ -64830,7 +64830,7 @@
         </is>
       </c>
       <c r="E1571" s="2" t="n">
-        <v>46142.72721842486</v>
+        <v>46142.72721842593</v>
       </c>
       <c r="F1571" t="n">
         <v>100</v>
@@ -64871,7 +64871,7 @@
         </is>
       </c>
       <c r="E1572" s="2" t="n">
-        <v>46117.76888509744</v>
+        <v>46117.76888509259</v>
       </c>
       <c r="F1572" t="n">
         <v>66</v>
@@ -64912,7 +64912,7 @@
         </is>
       </c>
       <c r="E1573" s="2" t="n">
-        <v>46137.39388510039</v>
+        <v>46137.39388510417</v>
       </c>
       <c r="F1573" t="n">
         <v>236</v>
@@ -64929,6 +64929,826 @@
       </c>
       <c r="I1573" t="n">
         <v>18.75</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>0544f20e-2d3f-4e8c-8b48-7a98cdba977f</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>ae13dd5e-3206-4c9a-a063-2eaf0d11b489</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1574" s="2" t="n">
+        <v>46145.02139675363</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1574" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1574" t="n">
+        <v>8.539999999999999</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>3d21195a-3f5d-4ef2-88e0-90de5bfa049c</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>93cc4c49-b3c6-4de6-aeab-8f495f2a8340</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1575" s="2" t="n">
+        <v>46131.72973009871</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1575" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>091af81e-b74b-4bd2-a3bb-c02b91816104</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>28a63ed7-d794-4756-a175-982de8c40e74</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1576" s="2" t="n">
+        <v>46126.64639677089</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1576" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1576" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>b75b87fa-4f3e-4409-b354-7ca4941f559b</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>e7b855bd-16a5-46f2-a6d2-78422da690e4</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1577" s="2" t="n">
+        <v>46150.729730107</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>154</v>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1577" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>abc5efc4-60f5-4c81-b6e8-a42e987bcdc8</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>413cb8a3-9966-4821-892a-657b1a25e8b3</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1578" s="2" t="n">
+        <v>46134.3963967767</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1578" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1578" t="n">
+        <v>14.35</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>e73f43a8-5bfe-49a4-866f-12f14ce01e15</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>7aaeb1cb-006d-474d-b78a-8fe70a8127db</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1579" s="2" t="n">
+        <v>46143.68806344878</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>245</v>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1579" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>843ab3cb-5d7f-4267-8914-726e514b1262</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>d054b5d3-ea98-4b25-bb54-a63590b22ac4</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1580" s="2" t="n">
+        <v>46141.77139678766</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>231</v>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1580" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1580" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>cf1a64c8-4428-4b98-9792-16c1d6934078</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>dbef9414-76b2-408b-9e30-4f8c5e8636e2</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1581" s="2" t="n">
+        <v>46144.35473012378</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>229</v>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1581" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1581" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>deb3c181-e489-4dbf-9d5c-28affaf7f4f2</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>9a05b6ad-95d9-4a06-8fb8-8e721be58f48</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1582" s="2" t="n">
+        <v>46139.43806346255</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1582" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>8d605a0b-35a1-4ba8-96de-2e3affbef2ec</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>da700596-5897-4da3-9d77-9f66e9c6f8a8</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1583" s="2" t="n">
+        <v>46137.56306347618</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1583" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1583" t="n">
+        <v>16.38</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>1670f8a5-3f49-435b-8a09-1dc5f7141a53</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>58323067-ae7e-4de5-b1e6-e85d3b45bc68</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1584" s="2" t="n">
+        <v>46137.47973014829</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1584" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>a6e23e17-64cb-44a3-a725-713bf6926191</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>583f2da5-7411-4fe6-a375-115d1959bb7d</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1585" s="2" t="n">
+        <v>46122.52139682025</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1585" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>f7a1a17e-530d-45a3-8869-9097807f1261</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>a1e8fa18-b03b-43c8-b627-30633f79d68c</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1586" s="2" t="n">
+        <v>46144.77139684148</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1586" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>07f92e50-37c7-414e-a71d-81eb8466a125</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>1b1923c9-df3b-4acd-a617-93b831debad7</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1587" s="2" t="n">
+        <v>46139.35473018052</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>197</v>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1587" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>f8c4f17c-e7c3-46a0-b48d-b71591e9ed45</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>1dd6589e-3b3b-4b7d-bbf7-7c3c27d644ef</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1588" s="2" t="n">
+        <v>46127.31306351659</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1588" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>84ef603f-5f2c-440a-9ef8-6b077349257f</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>e8497abe-f0b5-405a-846e-efa5e581c5bf</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1589" s="2" t="n">
+        <v>46151.35473019156</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1589" t="n">
+        <v>8.369999999999999</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>e56d5919-3ea2-4f88-9620-bec93f542a94</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>e0346bd0-6b2d-45fe-8d14-a20d6abc0ac3</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1590" s="2" t="n">
+        <v>46150.5630635277</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1590" t="n">
+        <v>18.65</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>92c8b6f0-e729-42ff-bf07-2d775c1f738d</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>310143f4-46ee-4a21-92bf-a9930af56c9d</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1591" s="2" t="n">
+        <v>46124.27139686378</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1591" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1591" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>c87c9792-22e0-42a7-a85a-382d8968fc19</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>ab87d038-e0af-4078-8708-436d7da263ad</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1592" s="2" t="n">
+        <v>46125.18806353591</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1592" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1592" t="n">
+        <v>17.54</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>c4d1d361-0553-444d-8711-e621cc39079d</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>2d5061aa-cf5c-4687-afad-970aec89f70f</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1593" s="2" t="n">
+        <v>46128.14639687195</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>173</v>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1593" t="n">
+        <v>9.109999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1593"/>
+  <dimension ref="A1:I1612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64953,7 +64953,7 @@
         </is>
       </c>
       <c r="E1574" s="2" t="n">
-        <v>46145.02139675363</v>
+        <v>46145.02139675926</v>
       </c>
       <c r="F1574" t="n">
         <v>39</v>
@@ -64994,7 +64994,7 @@
         </is>
       </c>
       <c r="E1575" s="2" t="n">
-        <v>46131.72973009871</v>
+        <v>46131.72973010417</v>
       </c>
       <c r="F1575" t="n">
         <v>41</v>
@@ -65035,7 +65035,7 @@
         </is>
       </c>
       <c r="E1576" s="2" t="n">
-        <v>46126.64639677089</v>
+        <v>46126.64639677083</v>
       </c>
       <c r="F1576" t="n">
         <v>176</v>
@@ -65076,7 +65076,7 @@
         </is>
       </c>
       <c r="E1577" s="2" t="n">
-        <v>46150.729730107</v>
+        <v>46150.72973010417</v>
       </c>
       <c r="F1577" t="n">
         <v>154</v>
@@ -65117,7 +65117,7 @@
         </is>
       </c>
       <c r="E1578" s="2" t="n">
-        <v>46134.3963967767</v>
+        <v>46134.39639678241</v>
       </c>
       <c r="F1578" t="n">
         <v>195</v>
@@ -65158,7 +65158,7 @@
         </is>
       </c>
       <c r="E1579" s="2" t="n">
-        <v>46143.68806344878</v>
+        <v>46143.68806344907</v>
       </c>
       <c r="F1579" t="n">
         <v>245</v>
@@ -65199,7 +65199,7 @@
         </is>
       </c>
       <c r="E1580" s="2" t="n">
-        <v>46141.77139678766</v>
+        <v>46141.77139678241</v>
       </c>
       <c r="F1580" t="n">
         <v>231</v>
@@ -65240,7 +65240,7 @@
         </is>
       </c>
       <c r="E1581" s="2" t="n">
-        <v>46144.35473012378</v>
+        <v>46144.35473012731</v>
       </c>
       <c r="F1581" t="n">
         <v>229</v>
@@ -65281,7 +65281,7 @@
         </is>
       </c>
       <c r="E1582" s="2" t="n">
-        <v>46139.43806346255</v>
+        <v>46139.43806346065</v>
       </c>
       <c r="F1582" t="n">
         <v>81</v>
@@ -65322,7 +65322,7 @@
         </is>
       </c>
       <c r="E1583" s="2" t="n">
-        <v>46137.56306347618</v>
+        <v>46137.56306347223</v>
       </c>
       <c r="F1583" t="n">
         <v>172</v>
@@ -65363,7 +65363,7 @@
         </is>
       </c>
       <c r="E1584" s="2" t="n">
-        <v>46137.47973014829</v>
+        <v>46137.47973015047</v>
       </c>
       <c r="F1584" t="n">
         <v>214</v>
@@ -65404,7 +65404,7 @@
         </is>
       </c>
       <c r="E1585" s="2" t="n">
-        <v>46122.52139682025</v>
+        <v>46122.52139681713</v>
       </c>
       <c r="F1585" t="n">
         <v>109</v>
@@ -65445,7 +65445,7 @@
         </is>
       </c>
       <c r="E1586" s="2" t="n">
-        <v>46144.77139684148</v>
+        <v>46144.77139684027</v>
       </c>
       <c r="F1586" t="n">
         <v>93</v>
@@ -65486,7 +65486,7 @@
         </is>
       </c>
       <c r="E1587" s="2" t="n">
-        <v>46139.35473018052</v>
+        <v>46139.35473018519</v>
       </c>
       <c r="F1587" t="n">
         <v>197</v>
@@ -65527,7 +65527,7 @@
         </is>
       </c>
       <c r="E1588" s="2" t="n">
-        <v>46127.31306351659</v>
+        <v>46127.31306351852</v>
       </c>
       <c r="F1588" t="n">
         <v>161</v>
@@ -65568,7 +65568,7 @@
         </is>
       </c>
       <c r="E1589" s="2" t="n">
-        <v>46151.35473019156</v>
+        <v>46151.35473019676</v>
       </c>
       <c r="F1589" t="n">
         <v>71</v>
@@ -65609,7 +65609,7 @@
         </is>
       </c>
       <c r="E1590" s="2" t="n">
-        <v>46150.5630635277</v>
+        <v>46150.56306353009</v>
       </c>
       <c r="F1590" t="n">
         <v>259</v>
@@ -65650,7 +65650,7 @@
         </is>
       </c>
       <c r="E1591" s="2" t="n">
-        <v>46124.27139686378</v>
+        <v>46124.27139686343</v>
       </c>
       <c r="F1591" t="n">
         <v>233</v>
@@ -65691,7 +65691,7 @@
         </is>
       </c>
       <c r="E1592" s="2" t="n">
-        <v>46125.18806353591</v>
+        <v>46125.18806354167</v>
       </c>
       <c r="F1592" t="n">
         <v>75</v>
@@ -65732,7 +65732,7 @@
         </is>
       </c>
       <c r="E1593" s="2" t="n">
-        <v>46128.14639687195</v>
+        <v>46128.146396875</v>
       </c>
       <c r="F1593" t="n">
         <v>173</v>
@@ -65749,6 +65749,785 @@
       </c>
       <c r="I1593" t="n">
         <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>12164bee-6d59-499a-978f-7d9f3eaf79eb</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>6e9e2926-a679-48ba-914d-a395d80659ac</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1594" s="2" t="n">
+        <v>46158.94979604334</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1594" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1594" t="n">
+        <v>19.15</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>a58ebcda-df73-4446-aaf5-0ce008569188</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>22808ac4-6561-4660-b648-af87f2313034</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1595" s="2" t="n">
+        <v>46144.9914627142</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1595" t="n">
+        <v>18.16</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>cd1d9319-f97b-4f13-9a90-996a4950e35e</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>54e4ca2e-ccbc-424a-b10c-44f7840f1626</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1596" s="2" t="n">
+        <v>46158.32479605381</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1596" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1596" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>161341e5-ced3-4a9b-9e30-0c3f64762a90</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>75351440-54d8-450f-8e61-266b5e61189c</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1597" s="2" t="n">
+        <v>46145.49146275329</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1597" t="n">
+        <v>13.55</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>c44386e3-3aae-486c-8147-8426f96a3063</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>5b21d15c-eadd-4d07-ac68-cc8eb393f933</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1598" s="2" t="n">
+        <v>46150.94979609546</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>277</v>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1598" t="n">
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>37e59cc2-a361-4f64-81ed-2957ddc0a60c</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>41b1a502-8d57-4372-8b58-b76d71c5d76d</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1599" s="2" t="n">
+        <v>46138.32479610725</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1599" t="n">
+        <v>19.14</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>4707b26e-9af9-40a8-a2cc-67a46420a4ce</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>8ccc76f2-ccc1-4f70-b810-b319ac8ee790</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1600" s="2" t="n">
+        <v>46152.24146278008</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>283</v>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1600" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1600" t="n">
+        <v>15.78</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>37374031-a276-4a8c-a4c5-1d5d921f12c4</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>6a87a05c-6bb2-4900-a8fc-b1959593b5ed</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1601" s="2" t="n">
+        <v>46141.8664627859</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>162</v>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1601" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>6e91824b-06b4-487b-a65a-bc6a8c7697d8</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>4d1ded5f-aa83-4255-876f-8c5d7d7d25a4</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1602" s="2" t="n">
+        <v>46144.99146279768</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1602" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>95b3318a-025a-4c51-9c7a-77642e0ee164</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>e6d23e2c-5d52-4072-952b-83409463d26a</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1603" s="2" t="n">
+        <v>46147.74146280663</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>192</v>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1603" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>01ca4351-2a9c-48bc-b2b2-5c481c6820f8</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>192a85cb-b7ee-45c8-be86-ae58511d327f</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1604" s="2" t="n">
+        <v>46140.15812947633</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>231</v>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1604" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1604" t="n">
+        <v>17.11</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>ad3014db-1f4a-47f4-a999-3235aad964b4</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>651edf98-4375-457f-9658-3a0617c44138</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1605" s="2" t="n">
+        <v>46134.32479615181</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1605" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1605" t="n">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>167f2047-fd32-4100-b994-faa834e89b78</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>a7ed57ae-32d6-4008-83c4-24e8060f149f</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1606" s="2" t="n">
+        <v>46142.65812949111</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1606" t="n">
+        <v>19.56</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>f0182bb4-9fb6-445e-be94-844a474aa7f0</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>a08a4166-14d1-4229-8bd9-48853fb2e8c4</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1607" s="2" t="n">
+        <v>46131.90812949694</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1607" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1607" t="n">
+        <v>14.92</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>d72d6f50-8ddd-44cc-9954-3e3c6cb8de1c</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>e80b994c-3071-4dfa-8d12-2517afa6d5b3</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1608" s="2" t="n">
+        <v>46134.28312949992</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1608" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>e3f81f18-892c-4794-bf6d-05ad64934ef1</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>09872592-d100-4248-b222-46e7f2e9ac5b</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1609" s="2" t="n">
+        <v>46138.86646283931</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>262</v>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1609" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1609" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>13109beb-28f7-4818-8a8e-aff439874e5b</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>73c5a27f-c498-4fd8-8b8d-2c68d5c7e314</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1610" s="2" t="n">
+        <v>46141.28312951241</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1610" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1610" t="n">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>054805d1-ed43-49f8-a142-0fd13ce45a3a</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>96ece705-98c7-4463-aa46-bbf74b8eb0a7</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1611" s="2" t="n">
+        <v>46148.78312951537</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1611" t="n">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>ed33738b-5c1b-4111-96a6-623158d4389c</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>bf640594-d057-4bc4-9454-f7a27c10ab1d</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1612" s="2" t="n">
+        <v>46132.11646285751</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>228</v>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1612" t="n">
+        <v>11.33</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1612"/>
+  <dimension ref="A1:I1627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65773,7 +65773,7 @@
         </is>
       </c>
       <c r="E1594" s="2" t="n">
-        <v>46158.94979604334</v>
+        <v>46158.94979604167</v>
       </c>
       <c r="F1594" t="n">
         <v>82</v>
@@ -65814,7 +65814,7 @@
         </is>
       </c>
       <c r="E1595" s="2" t="n">
-        <v>46144.9914627142</v>
+        <v>46144.99146271991</v>
       </c>
       <c r="F1595" t="n">
         <v>99</v>
@@ -65855,7 +65855,7 @@
         </is>
       </c>
       <c r="E1596" s="2" t="n">
-        <v>46158.32479605381</v>
+        <v>46158.32479605324</v>
       </c>
       <c r="F1596" t="n">
         <v>78</v>
@@ -65896,7 +65896,7 @@
         </is>
       </c>
       <c r="E1597" s="2" t="n">
-        <v>46145.49146275329</v>
+        <v>46145.49146275463</v>
       </c>
       <c r="F1597" t="n">
         <v>190</v>
@@ -65937,7 +65937,7 @@
         </is>
       </c>
       <c r="E1598" s="2" t="n">
-        <v>46150.94979609546</v>
+        <v>46150.94979609954</v>
       </c>
       <c r="F1598" t="n">
         <v>277</v>
@@ -65978,7 +65978,7 @@
         </is>
       </c>
       <c r="E1599" s="2" t="n">
-        <v>46138.32479610725</v>
+        <v>46138.32479611111</v>
       </c>
       <c r="F1599" t="n">
         <v>91</v>
@@ -66019,7 +66019,7 @@
         </is>
       </c>
       <c r="E1600" s="2" t="n">
-        <v>46152.24146278008</v>
+        <v>46152.24146277778</v>
       </c>
       <c r="F1600" t="n">
         <v>283</v>
@@ -66060,7 +66060,7 @@
         </is>
       </c>
       <c r="E1601" s="2" t="n">
-        <v>46141.8664627859</v>
+        <v>46141.86646278935</v>
       </c>
       <c r="F1601" t="n">
         <v>162</v>
@@ -66101,7 +66101,7 @@
         </is>
       </c>
       <c r="E1602" s="2" t="n">
-        <v>46144.99146279768</v>
+        <v>46144.99146280093</v>
       </c>
       <c r="F1602" t="n">
         <v>280</v>
@@ -66142,7 +66142,7 @@
         </is>
       </c>
       <c r="E1603" s="2" t="n">
-        <v>46147.74146280663</v>
+        <v>46147.74146280093</v>
       </c>
       <c r="F1603" t="n">
         <v>192</v>
@@ -66183,7 +66183,7 @@
         </is>
       </c>
       <c r="E1604" s="2" t="n">
-        <v>46140.15812947633</v>
+        <v>46140.15812947917</v>
       </c>
       <c r="F1604" t="n">
         <v>231</v>
@@ -66224,7 +66224,7 @@
         </is>
       </c>
       <c r="E1605" s="2" t="n">
-        <v>46134.32479615181</v>
+        <v>46134.32479615741</v>
       </c>
       <c r="F1605" t="n">
         <v>37</v>
@@ -66265,7 +66265,7 @@
         </is>
       </c>
       <c r="E1606" s="2" t="n">
-        <v>46142.65812949111</v>
+        <v>46142.65812949074</v>
       </c>
       <c r="F1606" t="n">
         <v>172</v>
@@ -66306,7 +66306,7 @@
         </is>
       </c>
       <c r="E1607" s="2" t="n">
-        <v>46131.90812949694</v>
+        <v>46131.90812950231</v>
       </c>
       <c r="F1607" t="n">
         <v>250</v>
@@ -66347,7 +66347,7 @@
         </is>
       </c>
       <c r="E1608" s="2" t="n">
-        <v>46134.28312949992</v>
+        <v>46134.28312950231</v>
       </c>
       <c r="F1608" t="n">
         <v>62</v>
@@ -66388,7 +66388,7 @@
         </is>
       </c>
       <c r="E1609" s="2" t="n">
-        <v>46138.86646283931</v>
+        <v>46138.86646283565</v>
       </c>
       <c r="F1609" t="n">
         <v>262</v>
@@ -66429,7 +66429,7 @@
         </is>
       </c>
       <c r="E1610" s="2" t="n">
-        <v>46141.28312951241</v>
+        <v>46141.28312951389</v>
       </c>
       <c r="F1610" t="n">
         <v>111</v>
@@ -66470,7 +66470,7 @@
         </is>
       </c>
       <c r="E1611" s="2" t="n">
-        <v>46148.78312951537</v>
+        <v>46148.78312951389</v>
       </c>
       <c r="F1611" t="n">
         <v>265</v>
@@ -66511,7 +66511,7 @@
         </is>
       </c>
       <c r="E1612" s="2" t="n">
-        <v>46132.11646285751</v>
+        <v>46132.11646285879</v>
       </c>
       <c r="F1612" t="n">
         <v>228</v>
@@ -66528,6 +66528,621 @@
       </c>
       <c r="I1612" t="n">
         <v>11.33</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>4dea983d-830b-4017-a259-93b37740ced9</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>80ce0cf1-7a74-4342-a23a-ddb8a2e6e1a6</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>port_hold</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1613" s="2" t="n">
+        <v>46191.94668152197</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>189</v>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>Synthetic event: port_hold</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1613" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>4f1346ed-b3d8-4151-a1dc-91962abe6e8f</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>e4a04421-2838-42e0-b29a-b08f508b1061</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1614" s="2" t="n">
+        <v>46180.90501486124</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1614" t="n">
+        <v>11.04</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>4d1363e0-1e08-48a4-a859-70dfaec321f9</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>4927b454-b161-4631-81f2-5e1145a6569e</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1615" s="2" t="n">
+        <v>46188.6133482057</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="I1615" t="n">
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>edde8330-23a5-4ee5-889d-3023798f120d</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>d8da36e2-b6ce-4cd8-b97c-e05a83e97973</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1616" s="2" t="n">
+        <v>46183.44668154173</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1616" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1616" t="n">
+        <v>18.89</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>f923eec1-3071-4f29-8761-b101ad28d48b</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>6943557f-d811-4145-af01-a6320c60698d</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1617" s="2" t="n">
+        <v>46190.61334821927</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1617" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1617" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>c7dfe7f9-9beb-4b90-9f67-70cdd178dd86</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>0a76bee1-ef22-451e-b79e-1df82223dc5c</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1618" s="2" t="n">
+        <v>46192.6133482275</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1618" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>9a4e65f6-d94f-4c38-9a97-d8ee282ec464</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>98ad7093-d602-45b2-97b5-74ef26439912</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1619" s="2" t="n">
+        <v>46189.40501489691</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>Synthetic event: delay</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1619" t="n">
+        <v>14.58</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>dad7caac-2631-4cd4-aa0b-1aadfe399bfc</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>39152d84-4517-47b0-a257-742e11b6667e</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1620" s="2" t="n">
+        <v>46192.15501490771</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>244</v>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1620" t="n">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>7fb9df7f-a3c9-4695-96d0-e16c1efe16e5</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>4b8dfd46-3573-4ede-85fe-64f657ec61e6</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1621" s="2" t="n">
+        <v>46190.90501493464</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1621" t="n">
+        <v>18.77</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>717cca31-c56b-4244-85da-264abc0f99c3</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>106cb744-ca4d-42c2-a9ae-279a7d674e46</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>temperature_spike</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1622" s="2" t="n">
+        <v>46175.73834827341</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>241</v>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>Synthetic event: temperature_spike</t>
+        </is>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1622" t="n">
+        <v>9.01</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>31a2e407-2d46-4c16-8799-a25118ecc61e</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>b7dd7004-3877-412e-a938-a5db7dbf853f</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1623" s="2" t="n">
+        <v>46205.11334828413</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>258</v>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1623" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>ef592a07-ef82-40f7-8aa3-c9489a8aaf4c</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>aca4f778-5566-4eb8-8307-d329bbb65958</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E1624" s="2" t="n">
+        <v>46197.48834829487</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>187</v>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>Synthetic event: handling</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>US Distribution</t>
+        </is>
+      </c>
+      <c r="I1624" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>946f707a-122e-4692-996a-0946eb948dab</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>47b1762e-9ee4-48eb-941f-91ee9e2a8f83</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1625" s="2" t="n">
+        <v>46197.57168163097</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1625" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>0f0ddc3a-ee05-43d5-a729-796c7cd62770</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>bf1bcee2-5433-4823-a821-c65ba0775ab6</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1626" s="2" t="n">
+        <v>46184.9050149698</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>70</v>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1626" t="inlineStr">
+        <is>
+          <t>Dubai Port</t>
+        </is>
+      </c>
+      <c r="I1626" t="n">
+        <v>19.38</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>83975305-47a4-4a01-bb2c-d5c618af9716</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>f98796d3-c78d-4b83-b848-0424a2d0840c</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>humidity_drop</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1627" s="2" t="n">
+        <v>46186.1966816471</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>238</v>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>Synthetic event: humidity_drop</t>
+        </is>
+      </c>
+      <c r="H1627" t="inlineStr">
+        <is>
+          <t>Rotterdam Port</t>
+        </is>
+      </c>
+      <c r="I1627" t="n">
+        <v>13.14</v>
       </c>
     </row>
   </sheetData>
